--- a/document/成果物ドキュメント_タスク編集機能.xlsx
+++ b/document/成果物ドキュメント_タスク編集機能.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\TaskManager62\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{091C0E2A-F33A-4BA5-8B34-CE59694C7ED2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1EF54EA-3327-422B-9610-7801784718EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="3" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="126">
   <si>
     <t>プロジェクト型演習　成果ドキュメント</t>
   </si>
@@ -1573,6 +1573,72 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1585,9 +1651,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1678,24 +1741,24 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1720,93 +1783,33 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1823,9 +1826,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1907,6 +1907,138 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="図 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{638F80EF-0657-B0D1-BCB0-1CD2286DFA7E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="381000" y="1762125"/>
+          <a:ext cx="7543800" cy="2571750"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>295275</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>139584</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>762000</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="図 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F0EB3575-6DC8-9368-570E-167DFEBA2D6D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="295275" y="1053984"/>
+          <a:ext cx="8181975" cy="4499091"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -1955,7 +2087,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -2021,7 +2153,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -2294,85 +2426,85 @@
   <sheetData>
     <row r="1" spans="3:16" ht="30" customHeight="1"/>
     <row r="2" spans="3:16" ht="30" customHeight="1">
-      <c r="C2" s="46" t="s">
+      <c r="C2" s="67" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
-      <c r="I2" s="47"/>
-      <c r="J2" s="47"/>
-      <c r="K2" s="47"/>
-      <c r="L2" s="47"/>
-      <c r="M2" s="47"/>
-      <c r="N2" s="47"/>
-      <c r="O2" s="47"/>
+      <c r="D2" s="68"/>
+      <c r="E2" s="68"/>
+      <c r="F2" s="68"/>
+      <c r="G2" s="68"/>
+      <c r="H2" s="68"/>
+      <c r="I2" s="68"/>
+      <c r="J2" s="68"/>
+      <c r="K2" s="68"/>
+      <c r="L2" s="68"/>
+      <c r="M2" s="68"/>
+      <c r="N2" s="68"/>
+      <c r="O2" s="68"/>
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="45"/>
-      <c r="D3" s="45"/>
-      <c r="E3" s="45"/>
-      <c r="F3" s="45"/>
-      <c r="G3" s="45"/>
-      <c r="H3" s="45"/>
-      <c r="I3" s="45"/>
-      <c r="J3" s="45"/>
-      <c r="K3" s="45"/>
-      <c r="L3" s="45"/>
-      <c r="M3" s="45"/>
-      <c r="N3" s="45"/>
-      <c r="O3" s="45"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="52"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="52"/>
+      <c r="G3" s="52"/>
+      <c r="H3" s="52"/>
+      <c r="I3" s="52"/>
+      <c r="J3" s="52"/>
+      <c r="K3" s="52"/>
+      <c r="L3" s="52"/>
+      <c r="M3" s="52"/>
+      <c r="N3" s="52"/>
+      <c r="O3" s="52"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="45"/>
-      <c r="D4" s="45"/>
-      <c r="E4" s="45"/>
-      <c r="F4" s="45"/>
-      <c r="G4" s="45"/>
-      <c r="H4" s="45"/>
-      <c r="I4" s="45"/>
-      <c r="J4" s="45"/>
-      <c r="K4" s="45"/>
-      <c r="L4" s="45"/>
-      <c r="M4" s="45"/>
-      <c r="N4" s="45"/>
-      <c r="O4" s="45"/>
+      <c r="C4" s="52"/>
+      <c r="D4" s="52"/>
+      <c r="E4" s="52"/>
+      <c r="F4" s="52"/>
+      <c r="G4" s="52"/>
+      <c r="H4" s="52"/>
+      <c r="I4" s="52"/>
+      <c r="J4" s="52"/>
+      <c r="K4" s="52"/>
+      <c r="L4" s="52"/>
+      <c r="M4" s="52"/>
+      <c r="N4" s="52"/>
+      <c r="O4" s="52"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="45"/>
-      <c r="D5" s="45"/>
-      <c r="E5" s="45"/>
-      <c r="F5" s="45"/>
-      <c r="G5" s="45"/>
-      <c r="H5" s="45"/>
-      <c r="I5" s="45"/>
-      <c r="J5" s="45"/>
-      <c r="K5" s="45"/>
-      <c r="L5" s="45"/>
-      <c r="M5" s="45"/>
-      <c r="N5" s="45"/>
-      <c r="O5" s="45"/>
+      <c r="C5" s="52"/>
+      <c r="D5" s="52"/>
+      <c r="E5" s="52"/>
+      <c r="F5" s="52"/>
+      <c r="G5" s="52"/>
+      <c r="H5" s="52"/>
+      <c r="I5" s="52"/>
+      <c r="J5" s="52"/>
+      <c r="K5" s="52"/>
+      <c r="L5" s="52"/>
+      <c r="M5" s="52"/>
+      <c r="N5" s="52"/>
+      <c r="O5" s="52"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="45"/>
-      <c r="D6" s="45"/>
-      <c r="E6" s="45"/>
-      <c r="F6" s="45"/>
-      <c r="G6" s="45"/>
-      <c r="H6" s="45"/>
-      <c r="I6" s="45"/>
-      <c r="J6" s="45"/>
-      <c r="K6" s="45"/>
-      <c r="L6" s="45"/>
-      <c r="M6" s="45"/>
-      <c r="N6" s="45"/>
-      <c r="O6" s="45"/>
+      <c r="C6" s="52"/>
+      <c r="D6" s="52"/>
+      <c r="E6" s="52"/>
+      <c r="F6" s="52"/>
+      <c r="G6" s="52"/>
+      <c r="H6" s="52"/>
+      <c r="I6" s="52"/>
+      <c r="J6" s="52"/>
+      <c r="K6" s="52"/>
+      <c r="L6" s="52"/>
+      <c r="M6" s="52"/>
+      <c r="N6" s="52"/>
+      <c r="O6" s="52"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -2392,46 +2524,46 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="48" t="s">
+      <c r="E8" s="69" t="s">
         <v>124</v>
       </c>
-      <c r="F8" s="45"/>
-      <c r="G8" s="45"/>
-      <c r="H8" s="45"/>
-      <c r="I8" s="45"/>
-      <c r="J8" s="45"/>
-      <c r="K8" s="45"/>
-      <c r="L8" s="45"/>
-      <c r="M8" s="45"/>
+      <c r="F8" s="52"/>
+      <c r="G8" s="52"/>
+      <c r="H8" s="52"/>
+      <c r="I8" s="52"/>
+      <c r="J8" s="52"/>
+      <c r="K8" s="52"/>
+      <c r="L8" s="52"/>
+      <c r="M8" s="52"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="41" t="s">
+      <c r="G13" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="H13" s="43"/>
-      <c r="I13" s="41" t="s">
+      <c r="H13" s="65"/>
+      <c r="I13" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="J13" s="42"/>
-      <c r="K13" s="43"/>
+      <c r="J13" s="64"/>
+      <c r="K13" s="65"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="41"/>
-      <c r="H14" s="43"/>
-      <c r="I14" s="41"/>
-      <c r="J14" s="42"/>
-      <c r="K14" s="43"/>
+      <c r="G14" s="63"/>
+      <c r="H14" s="65"/>
+      <c r="I14" s="63"/>
+      <c r="J14" s="64"/>
+      <c r="K14" s="65"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="41"/>
-      <c r="H15" s="43"/>
-      <c r="I15" s="41"/>
-      <c r="J15" s="42"/>
-      <c r="K15" s="43"/>
+      <c r="G15" s="63"/>
+      <c r="H15" s="65"/>
+      <c r="I15" s="63"/>
+      <c r="J15" s="64"/>
+      <c r="K15" s="65"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -2440,13 +2572,13 @@
       <c r="J16" s="3"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="44" t="s">
+      <c r="G17" s="66" t="s">
         <v>125</v>
       </c>
-      <c r="H17" s="45"/>
-      <c r="I17" s="45"/>
-      <c r="J17" s="45"/>
-      <c r="K17" s="45"/>
+      <c r="H17" s="52"/>
+      <c r="I17" s="52"/>
+      <c r="J17" s="52"/>
+      <c r="K17" s="52"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -3461,19 +3593,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="64" t="s">
+      <c r="A1" s="85" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="49" t="s">
+      <c r="B1" s="86"/>
+      <c r="C1" s="87"/>
+      <c r="D1" s="70" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="50"/>
-      <c r="F1" s="49" t="s">
+      <c r="E1" s="71"/>
+      <c r="F1" s="70" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="50"/>
+      <c r="G1" s="71"/>
       <c r="H1" s="39" t="s">
         <v>6</v>
       </c>
@@ -3485,190 +3617,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="67"/>
-      <c r="B2" s="68"/>
-      <c r="C2" s="54"/>
-      <c r="D2" s="51" t="s">
+      <c r="A2" s="88"/>
+      <c r="B2" s="89"/>
+      <c r="C2" s="75"/>
+      <c r="D2" s="72" t="s">
         <v>73</v>
       </c>
-      <c r="E2" s="52"/>
-      <c r="F2" s="51" t="s">
+      <c r="E2" s="73"/>
+      <c r="F2" s="72" t="s">
         <v>72</v>
       </c>
-      <c r="G2" s="52"/>
-      <c r="H2" s="57">
+      <c r="G2" s="73"/>
+      <c r="H2" s="78">
         <v>46121</v>
       </c>
-      <c r="I2" s="60" t="s">
+      <c r="I2" s="81" t="s">
         <v>71</v>
       </c>
-      <c r="J2" s="78"/>
+      <c r="J2" s="97"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="67"/>
-      <c r="B3" s="68"/>
-      <c r="C3" s="54"/>
-      <c r="D3" s="53"/>
-      <c r="E3" s="54"/>
-      <c r="F3" s="53"/>
-      <c r="G3" s="54"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="79"/>
+      <c r="A3" s="88"/>
+      <c r="B3" s="89"/>
+      <c r="C3" s="75"/>
+      <c r="D3" s="74"/>
+      <c r="E3" s="75"/>
+      <c r="F3" s="74"/>
+      <c r="G3" s="75"/>
+      <c r="H3" s="79"/>
+      <c r="I3" s="79"/>
+      <c r="J3" s="98"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="69"/>
-      <c r="B4" s="70"/>
-      <c r="C4" s="56"/>
-      <c r="D4" s="55"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="55"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="59"/>
-      <c r="I4" s="59"/>
-      <c r="J4" s="80"/>
+      <c r="A4" s="90"/>
+      <c r="B4" s="91"/>
+      <c r="C4" s="77"/>
+      <c r="D4" s="76"/>
+      <c r="E4" s="77"/>
+      <c r="F4" s="76"/>
+      <c r="G4" s="77"/>
+      <c r="H4" s="80"/>
+      <c r="I4" s="80"/>
+      <c r="J4" s="99"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="71" t="s">
+      <c r="A5" s="92" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="72"/>
-      <c r="C5" s="50"/>
-      <c r="D5" s="88" t="s">
+      <c r="B5" s="93"/>
+      <c r="C5" s="71"/>
+      <c r="D5" s="109" t="s">
         <v>70</v>
       </c>
-      <c r="E5" s="72"/>
-      <c r="F5" s="72"/>
-      <c r="G5" s="72"/>
-      <c r="H5" s="72"/>
-      <c r="I5" s="72"/>
-      <c r="J5" s="89"/>
+      <c r="E5" s="93"/>
+      <c r="F5" s="93"/>
+      <c r="G5" s="93"/>
+      <c r="H5" s="93"/>
+      <c r="I5" s="93"/>
+      <c r="J5" s="110"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="73" t="s">
+      <c r="A6" s="94" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="74"/>
-      <c r="C6" s="75"/>
-      <c r="D6" s="76" t="s">
+      <c r="B6" s="95"/>
+      <c r="C6" s="96"/>
+      <c r="D6" s="101" t="s">
         <v>69</v>
       </c>
-      <c r="E6" s="74"/>
-      <c r="F6" s="74"/>
-      <c r="G6" s="74"/>
-      <c r="H6" s="74"/>
-      <c r="I6" s="74"/>
-      <c r="J6" s="77"/>
+      <c r="E6" s="95"/>
+      <c r="F6" s="95"/>
+      <c r="G6" s="95"/>
+      <c r="H6" s="95"/>
+      <c r="I6" s="95"/>
+      <c r="J6" s="102"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="73" t="s">
+      <c r="A7" s="94" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="74"/>
-      <c r="C7" s="75"/>
-      <c r="D7" s="76" t="s">
+      <c r="B7" s="95"/>
+      <c r="C7" s="96"/>
+      <c r="D7" s="101" t="s">
         <v>68</v>
       </c>
-      <c r="E7" s="74"/>
-      <c r="F7" s="74"/>
-      <c r="G7" s="74"/>
-      <c r="H7" s="74"/>
-      <c r="I7" s="74"/>
-      <c r="J7" s="77"/>
+      <c r="E7" s="95"/>
+      <c r="F7" s="95"/>
+      <c r="G7" s="95"/>
+      <c r="H7" s="95"/>
+      <c r="I7" s="95"/>
+      <c r="J7" s="102"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="73" t="s">
+      <c r="A8" s="94" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="74"/>
-      <c r="C8" s="75"/>
-      <c r="D8" s="76" t="s">
+      <c r="B8" s="95"/>
+      <c r="C8" s="96"/>
+      <c r="D8" s="101" t="s">
         <v>67</v>
       </c>
-      <c r="E8" s="74"/>
-      <c r="F8" s="74"/>
-      <c r="G8" s="74"/>
-      <c r="H8" s="74"/>
-      <c r="I8" s="74"/>
-      <c r="J8" s="77"/>
+      <c r="E8" s="95"/>
+      <c r="F8" s="95"/>
+      <c r="G8" s="95"/>
+      <c r="H8" s="95"/>
+      <c r="I8" s="95"/>
+      <c r="J8" s="102"/>
     </row>
     <row r="9" spans="1:10" ht="78" customHeight="1">
-      <c r="A9" s="83" t="s">
+      <c r="A9" s="104" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="81" t="s">
+      <c r="B9" s="100" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="75"/>
-      <c r="D9" s="82" t="s">
+      <c r="C9" s="96"/>
+      <c r="D9" s="103" t="s">
         <v>120</v>
       </c>
-      <c r="E9" s="74"/>
-      <c r="F9" s="74"/>
-      <c r="G9" s="74"/>
-      <c r="H9" s="74"/>
-      <c r="I9" s="74"/>
-      <c r="J9" s="77"/>
+      <c r="E9" s="95"/>
+      <c r="F9" s="95"/>
+      <c r="G9" s="95"/>
+      <c r="H9" s="95"/>
+      <c r="I9" s="95"/>
+      <c r="J9" s="102"/>
     </row>
     <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="84"/>
-      <c r="B10" s="81" t="s">
+      <c r="A10" s="105"/>
+      <c r="B10" s="100" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="75"/>
-      <c r="D10" s="76"/>
-      <c r="E10" s="74"/>
-      <c r="F10" s="74"/>
-      <c r="G10" s="74"/>
-      <c r="H10" s="74"/>
-      <c r="I10" s="74"/>
-      <c r="J10" s="77"/>
+      <c r="C10" s="96"/>
+      <c r="D10" s="101"/>
+      <c r="E10" s="95"/>
+      <c r="F10" s="95"/>
+      <c r="G10" s="95"/>
+      <c r="H10" s="95"/>
+      <c r="I10" s="95"/>
+      <c r="J10" s="102"/>
     </row>
     <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="85"/>
-      <c r="B11" s="81" t="s">
+      <c r="A11" s="106"/>
+      <c r="B11" s="100" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="75"/>
-      <c r="D11" s="82" t="s">
+      <c r="C11" s="96"/>
+      <c r="D11" s="103" t="s">
         <v>66</v>
       </c>
-      <c r="E11" s="74"/>
-      <c r="F11" s="74"/>
-      <c r="G11" s="74"/>
-      <c r="H11" s="74"/>
-      <c r="I11" s="74"/>
-      <c r="J11" s="77"/>
+      <c r="E11" s="95"/>
+      <c r="F11" s="95"/>
+      <c r="G11" s="95"/>
+      <c r="H11" s="95"/>
+      <c r="I11" s="95"/>
+      <c r="J11" s="102"/>
     </row>
     <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="73" t="s">
+      <c r="A12" s="94" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="74"/>
-      <c r="C12" s="75"/>
-      <c r="D12" s="76" t="s">
+      <c r="B12" s="95"/>
+      <c r="C12" s="96"/>
+      <c r="D12" s="101" t="s">
         <v>65</v>
       </c>
-      <c r="E12" s="74"/>
-      <c r="F12" s="74"/>
-      <c r="G12" s="74"/>
-      <c r="H12" s="74"/>
-      <c r="I12" s="74"/>
-      <c r="J12" s="77"/>
+      <c r="E12" s="95"/>
+      <c r="F12" s="95"/>
+      <c r="G12" s="95"/>
+      <c r="H12" s="95"/>
+      <c r="I12" s="95"/>
+      <c r="J12" s="102"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A13" s="61" t="s">
+      <c r="A13" s="82" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="62"/>
-      <c r="C13" s="63"/>
-      <c r="D13" s="86"/>
-      <c r="E13" s="62"/>
-      <c r="F13" s="62"/>
-      <c r="G13" s="62"/>
-      <c r="H13" s="62"/>
-      <c r="I13" s="62"/>
-      <c r="J13" s="87"/>
+      <c r="B13" s="83"/>
+      <c r="C13" s="84"/>
+      <c r="D13" s="107"/>
+      <c r="E13" s="83"/>
+      <c r="F13" s="83"/>
+      <c r="G13" s="83"/>
+      <c r="H13" s="83"/>
+      <c r="I13" s="83"/>
+      <c r="J13" s="108"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -4704,19 +4836,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="96" t="s">
+      <c r="A1" s="48" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="97"/>
-      <c r="C1" s="98"/>
-      <c r="D1" s="104" t="s">
+      <c r="B1" s="49"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="57" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="105"/>
-      <c r="F1" s="104" t="s">
+      <c r="E1" s="58"/>
+      <c r="F1" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="105"/>
+      <c r="G1" s="58"/>
       <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
@@ -4728,40 +4860,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="99"/>
-      <c r="B2" s="45"/>
-      <c r="C2" s="100"/>
-      <c r="D2" s="106"/>
-      <c r="E2" s="107"/>
-      <c r="F2" s="106"/>
-      <c r="G2" s="107"/>
-      <c r="H2" s="90"/>
-      <c r="I2" s="90"/>
-      <c r="J2" s="93"/>
+      <c r="A2" s="51"/>
+      <c r="B2" s="52"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="59" t="s">
+        <v>97</v>
+      </c>
+      <c r="E2" s="60"/>
+      <c r="F2" s="59" t="s">
+        <v>98</v>
+      </c>
+      <c r="G2" s="60"/>
+      <c r="H2" s="41">
+        <v>46125</v>
+      </c>
+      <c r="I2" s="44" t="s">
+        <v>99</v>
+      </c>
+      <c r="J2" s="45"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="99"/>
-      <c r="B3" s="45"/>
-      <c r="C3" s="100"/>
-      <c r="D3" s="108"/>
-      <c r="E3" s="100"/>
-      <c r="F3" s="108"/>
-      <c r="G3" s="100"/>
-      <c r="H3" s="91"/>
-      <c r="I3" s="91"/>
-      <c r="J3" s="94"/>
+      <c r="A3" s="51"/>
+      <c r="B3" s="52"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="61"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="61"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="42"/>
+      <c r="I3" s="42"/>
+      <c r="J3" s="46"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="101"/>
-      <c r="B4" s="102"/>
-      <c r="C4" s="103"/>
-      <c r="D4" s="109"/>
-      <c r="E4" s="103"/>
-      <c r="F4" s="109"/>
-      <c r="G4" s="103"/>
-      <c r="H4" s="92"/>
-      <c r="I4" s="92"/>
-      <c r="J4" s="95"/>
+      <c r="A4" s="54"/>
+      <c r="B4" s="55"/>
+      <c r="C4" s="56"/>
+      <c r="D4" s="62"/>
+      <c r="E4" s="56"/>
+      <c r="F4" s="62"/>
+      <c r="G4" s="56"/>
+      <c r="H4" s="43"/>
+      <c r="I4" s="43"/>
+      <c r="J4" s="47"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="7"/>
@@ -4901,7 +5041,6 @@
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
       <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
       <c r="G16" s="8"/>
       <c r="H16" s="8"/>
       <c r="I16" s="8"/>
@@ -6103,6 +6242,7 @@
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="landscape"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -6117,19 +6257,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="96" t="s">
+      <c r="A1" s="48" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="97"/>
-      <c r="C1" s="98"/>
-      <c r="D1" s="104" t="s">
+      <c r="B1" s="49"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="57" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="105"/>
-      <c r="F1" s="104" t="s">
+      <c r="E1" s="58"/>
+      <c r="F1" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="105"/>
+      <c r="G1" s="58"/>
       <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
@@ -6141,48 +6281,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="99"/>
-      <c r="B2" s="45"/>
-      <c r="C2" s="100"/>
-      <c r="D2" s="106" t="s">
+      <c r="A2" s="51"/>
+      <c r="B2" s="52"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="59" t="s">
         <v>97</v>
       </c>
-      <c r="E2" s="107"/>
-      <c r="F2" s="106" t="s">
+      <c r="E2" s="60"/>
+      <c r="F2" s="59" t="s">
         <v>98</v>
       </c>
-      <c r="G2" s="107"/>
-      <c r="H2" s="110">
+      <c r="G2" s="60"/>
+      <c r="H2" s="41">
         <v>46122</v>
       </c>
-      <c r="I2" s="90" t="s">
+      <c r="I2" s="44" t="s">
         <v>123</v>
       </c>
-      <c r="J2" s="93"/>
+      <c r="J2" s="45"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="99"/>
-      <c r="B3" s="45"/>
-      <c r="C3" s="100"/>
-      <c r="D3" s="108"/>
-      <c r="E3" s="100"/>
-      <c r="F3" s="108"/>
-      <c r="G3" s="100"/>
-      <c r="H3" s="91"/>
-      <c r="I3" s="91"/>
-      <c r="J3" s="94"/>
+      <c r="A3" s="51"/>
+      <c r="B3" s="52"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="61"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="61"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="42"/>
+      <c r="I3" s="42"/>
+      <c r="J3" s="46"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="101"/>
-      <c r="B4" s="102"/>
-      <c r="C4" s="103"/>
-      <c r="D4" s="109"/>
-      <c r="E4" s="103"/>
-      <c r="F4" s="109"/>
-      <c r="G4" s="103"/>
-      <c r="H4" s="92"/>
-      <c r="I4" s="92"/>
-      <c r="J4" s="95"/>
+      <c r="A4" s="54"/>
+      <c r="B4" s="55"/>
+      <c r="C4" s="56"/>
+      <c r="D4" s="62"/>
+      <c r="E4" s="56"/>
+      <c r="F4" s="62"/>
+      <c r="G4" s="56"/>
+      <c r="H4" s="43"/>
+      <c r="I4" s="43"/>
+      <c r="J4" s="47"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="7"/>
@@ -7514,6 +7654,7 @@
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="landscape"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -7531,19 +7672,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="96" t="s">
+      <c r="A1" s="48" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="97"/>
-      <c r="C1" s="98"/>
-      <c r="D1" s="104" t="s">
+      <c r="B1" s="49"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="57" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="105"/>
-      <c r="F1" s="104" t="s">
+      <c r="E1" s="58"/>
+      <c r="F1" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="105"/>
+      <c r="G1" s="58"/>
       <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
@@ -7555,190 +7696,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="99"/>
-      <c r="B2" s="45"/>
-      <c r="C2" s="100"/>
-      <c r="D2" s="106" t="s">
+      <c r="A2" s="51"/>
+      <c r="B2" s="52"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="59" t="s">
         <v>97</v>
       </c>
-      <c r="E2" s="107"/>
-      <c r="F2" s="106" t="s">
+      <c r="E2" s="60"/>
+      <c r="F2" s="59" t="s">
         <v>98</v>
       </c>
-      <c r="G2" s="107"/>
-      <c r="H2" s="110">
+      <c r="G2" s="60"/>
+      <c r="H2" s="41">
         <v>46121</v>
       </c>
-      <c r="I2" s="90" t="s">
+      <c r="I2" s="44" t="s">
         <v>99</v>
       </c>
-      <c r="J2" s="93"/>
+      <c r="J2" s="45"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="99"/>
-      <c r="B3" s="45"/>
-      <c r="C3" s="100"/>
-      <c r="D3" s="108"/>
-      <c r="E3" s="100"/>
-      <c r="F3" s="108"/>
-      <c r="G3" s="100"/>
-      <c r="H3" s="91"/>
-      <c r="I3" s="91"/>
-      <c r="J3" s="94"/>
+      <c r="A3" s="51"/>
+      <c r="B3" s="52"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="61"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="61"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="42"/>
+      <c r="I3" s="42"/>
+      <c r="J3" s="46"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="99"/>
-      <c r="B4" s="45"/>
-      <c r="C4" s="100"/>
-      <c r="D4" s="108"/>
-      <c r="E4" s="100"/>
-      <c r="F4" s="108"/>
-      <c r="G4" s="100"/>
-      <c r="H4" s="91"/>
-      <c r="I4" s="91"/>
-      <c r="J4" s="94"/>
+      <c r="A4" s="51"/>
+      <c r="B4" s="52"/>
+      <c r="C4" s="53"/>
+      <c r="D4" s="61"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="61"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="42"/>
+      <c r="I4" s="42"/>
+      <c r="J4" s="46"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="125" t="s">
+      <c r="A5" s="116" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="118"/>
-      <c r="C5" s="105"/>
-      <c r="D5" s="117" t="s">
+      <c r="B5" s="117"/>
+      <c r="C5" s="58"/>
+      <c r="D5" s="119" t="s">
         <v>112</v>
       </c>
-      <c r="E5" s="118"/>
-      <c r="F5" s="118"/>
-      <c r="G5" s="118"/>
-      <c r="H5" s="118"/>
-      <c r="I5" s="118"/>
-      <c r="J5" s="119"/>
+      <c r="E5" s="117"/>
+      <c r="F5" s="117"/>
+      <c r="G5" s="117"/>
+      <c r="H5" s="117"/>
+      <c r="I5" s="117"/>
+      <c r="J5" s="120"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="116" t="s">
+      <c r="A6" s="118" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="42"/>
-      <c r="C6" s="42"/>
-      <c r="D6" s="42"/>
-      <c r="E6" s="42"/>
-      <c r="F6" s="42"/>
-      <c r="G6" s="42"/>
-      <c r="H6" s="42"/>
-      <c r="I6" s="42"/>
-      <c r="J6" s="113"/>
+      <c r="B6" s="64"/>
+      <c r="C6" s="64"/>
+      <c r="D6" s="64"/>
+      <c r="E6" s="64"/>
+      <c r="F6" s="64"/>
+      <c r="G6" s="64"/>
+      <c r="H6" s="64"/>
+      <c r="I6" s="64"/>
+      <c r="J6" s="112"/>
     </row>
     <row r="7" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A7" s="120"/>
-      <c r="B7" s="121"/>
-      <c r="C7" s="121"/>
-      <c r="D7" s="121"/>
-      <c r="E7" s="121"/>
-      <c r="F7" s="121"/>
-      <c r="G7" s="121"/>
-      <c r="H7" s="121"/>
-      <c r="I7" s="121"/>
-      <c r="J7" s="122"/>
+      <c r="A7" s="121"/>
+      <c r="B7" s="122"/>
+      <c r="C7" s="122"/>
+      <c r="D7" s="122"/>
+      <c r="E7" s="122"/>
+      <c r="F7" s="122"/>
+      <c r="G7" s="122"/>
+      <c r="H7" s="122"/>
+      <c r="I7" s="122"/>
+      <c r="J7" s="123"/>
     </row>
     <row r="8" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A8" s="99"/>
-      <c r="B8" s="45"/>
-      <c r="C8" s="45"/>
-      <c r="D8" s="45"/>
-      <c r="E8" s="45"/>
-      <c r="F8" s="45"/>
-      <c r="G8" s="45"/>
-      <c r="H8" s="45"/>
-      <c r="I8" s="45"/>
-      <c r="J8" s="123"/>
+      <c r="A8" s="51"/>
+      <c r="B8" s="52"/>
+      <c r="C8" s="52"/>
+      <c r="D8" s="52"/>
+      <c r="E8" s="52"/>
+      <c r="F8" s="52"/>
+      <c r="G8" s="52"/>
+      <c r="H8" s="52"/>
+      <c r="I8" s="52"/>
+      <c r="J8" s="124"/>
     </row>
     <row r="9" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A9" s="99"/>
-      <c r="B9" s="45"/>
-      <c r="C9" s="45"/>
-      <c r="D9" s="45"/>
-      <c r="E9" s="45"/>
-      <c r="F9" s="45"/>
-      <c r="G9" s="45"/>
-      <c r="H9" s="45"/>
-      <c r="I9" s="45"/>
-      <c r="J9" s="123"/>
+      <c r="A9" s="51"/>
+      <c r="B9" s="52"/>
+      <c r="C9" s="52"/>
+      <c r="D9" s="52"/>
+      <c r="E9" s="52"/>
+      <c r="F9" s="52"/>
+      <c r="G9" s="52"/>
+      <c r="H9" s="52"/>
+      <c r="I9" s="52"/>
+      <c r="J9" s="124"/>
     </row>
     <row r="10" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A10" s="99"/>
-      <c r="B10" s="45"/>
-      <c r="C10" s="45"/>
-      <c r="D10" s="45"/>
-      <c r="E10" s="45"/>
-      <c r="F10" s="45"/>
-      <c r="G10" s="45"/>
-      <c r="H10" s="45"/>
-      <c r="I10" s="45"/>
-      <c r="J10" s="123"/>
+      <c r="A10" s="51"/>
+      <c r="B10" s="52"/>
+      <c r="C10" s="52"/>
+      <c r="D10" s="52"/>
+      <c r="E10" s="52"/>
+      <c r="F10" s="52"/>
+      <c r="G10" s="52"/>
+      <c r="H10" s="52"/>
+      <c r="I10" s="52"/>
+      <c r="J10" s="124"/>
     </row>
     <row r="11" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A11" s="99"/>
-      <c r="B11" s="45"/>
-      <c r="C11" s="45"/>
-      <c r="D11" s="45"/>
-      <c r="E11" s="45"/>
-      <c r="F11" s="45"/>
-      <c r="G11" s="45"/>
-      <c r="H11" s="45"/>
-      <c r="I11" s="45"/>
-      <c r="J11" s="123"/>
+      <c r="A11" s="51"/>
+      <c r="B11" s="52"/>
+      <c r="C11" s="52"/>
+      <c r="D11" s="52"/>
+      <c r="E11" s="52"/>
+      <c r="F11" s="52"/>
+      <c r="G11" s="52"/>
+      <c r="H11" s="52"/>
+      <c r="I11" s="52"/>
+      <c r="J11" s="124"/>
     </row>
     <row r="12" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A12" s="99"/>
-      <c r="B12" s="45"/>
-      <c r="C12" s="45"/>
-      <c r="D12" s="45"/>
-      <c r="E12" s="45"/>
-      <c r="F12" s="45"/>
-      <c r="G12" s="45"/>
-      <c r="H12" s="45"/>
-      <c r="I12" s="45"/>
-      <c r="J12" s="123"/>
+      <c r="A12" s="51"/>
+      <c r="B12" s="52"/>
+      <c r="C12" s="52"/>
+      <c r="D12" s="52"/>
+      <c r="E12" s="52"/>
+      <c r="F12" s="52"/>
+      <c r="G12" s="52"/>
+      <c r="H12" s="52"/>
+      <c r="I12" s="52"/>
+      <c r="J12" s="124"/>
     </row>
     <row r="13" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A13" s="99"/>
-      <c r="B13" s="45"/>
-      <c r="C13" s="45"/>
-      <c r="D13" s="45"/>
-      <c r="E13" s="45"/>
-      <c r="F13" s="45"/>
-      <c r="G13" s="45"/>
-      <c r="H13" s="45"/>
-      <c r="I13" s="45"/>
-      <c r="J13" s="123"/>
+      <c r="A13" s="51"/>
+      <c r="B13" s="52"/>
+      <c r="C13" s="52"/>
+      <c r="D13" s="52"/>
+      <c r="E13" s="52"/>
+      <c r="F13" s="52"/>
+      <c r="G13" s="52"/>
+      <c r="H13" s="52"/>
+      <c r="I13" s="52"/>
+      <c r="J13" s="124"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="116" t="s">
+      <c r="A14" s="118" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="42"/>
-      <c r="C14" s="42"/>
-      <c r="D14" s="42"/>
-      <c r="E14" s="42"/>
-      <c r="F14" s="42"/>
-      <c r="G14" s="42"/>
-      <c r="H14" s="42"/>
-      <c r="I14" s="42"/>
-      <c r="J14" s="113"/>
+      <c r="B14" s="64"/>
+      <c r="C14" s="64"/>
+      <c r="D14" s="64"/>
+      <c r="E14" s="64"/>
+      <c r="F14" s="64"/>
+      <c r="G14" s="64"/>
+      <c r="H14" s="64"/>
+      <c r="I14" s="64"/>
+      <c r="J14" s="112"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="116" t="s">
+      <c r="A15" s="118" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="42"/>
-      <c r="C15" s="43"/>
-      <c r="D15" s="112" t="s">
+      <c r="B15" s="64"/>
+      <c r="C15" s="65"/>
+      <c r="D15" s="111" t="s">
         <v>74</v>
       </c>
-      <c r="E15" s="42"/>
-      <c r="F15" s="42"/>
-      <c r="G15" s="42"/>
-      <c r="H15" s="43"/>
+      <c r="E15" s="64"/>
+      <c r="F15" s="64"/>
+      <c r="G15" s="64"/>
+      <c r="H15" s="65"/>
       <c r="I15" s="14" t="s">
         <v>26</v>
       </c>
@@ -7747,11 +7888,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="116" t="s">
+      <c r="A16" s="118" t="s">
         <v>27</v>
       </c>
-      <c r="B16" s="42"/>
-      <c r="C16" s="43"/>
+      <c r="B16" s="64"/>
+      <c r="C16" s="65"/>
       <c r="D16" s="14" t="s">
         <v>28</v>
       </c>
@@ -7764,18 +7905,18 @@
       <c r="G16" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="H16" s="124" t="s">
+      <c r="H16" s="125" t="s">
         <v>18</v>
       </c>
-      <c r="I16" s="42"/>
-      <c r="J16" s="113"/>
+      <c r="I16" s="64"/>
+      <c r="J16" s="112"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="111" t="s">
+      <c r="A17" s="113" t="s">
         <v>76</v>
       </c>
-      <c r="B17" s="42"/>
-      <c r="C17" s="43"/>
+      <c r="B17" s="64"/>
+      <c r="C17" s="65"/>
       <c r="D17" s="16" t="s">
         <v>100</v>
       </c>
@@ -7786,18 +7927,18 @@
         <v>88</v>
       </c>
       <c r="G17" s="17"/>
-      <c r="H17" s="112" t="s">
+      <c r="H17" s="111" t="s">
         <v>91</v>
       </c>
-      <c r="I17" s="42"/>
-      <c r="J17" s="113"/>
+      <c r="I17" s="64"/>
+      <c r="J17" s="112"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="111" t="s">
+      <c r="A18" s="113" t="s">
         <v>77</v>
       </c>
-      <c r="B18" s="42"/>
-      <c r="C18" s="43"/>
+      <c r="B18" s="64"/>
+      <c r="C18" s="65"/>
       <c r="D18" s="16" t="s">
         <v>101</v>
       </c>
@@ -7808,18 +7949,18 @@
         <v>107</v>
       </c>
       <c r="G18" s="17"/>
-      <c r="H18" s="112" t="s">
+      <c r="H18" s="111" t="s">
         <v>109</v>
       </c>
-      <c r="I18" s="42"/>
-      <c r="J18" s="113"/>
+      <c r="I18" s="64"/>
+      <c r="J18" s="112"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="111" t="s">
+      <c r="A19" s="113" t="s">
         <v>78</v>
       </c>
-      <c r="B19" s="42"/>
-      <c r="C19" s="43"/>
+      <c r="B19" s="64"/>
+      <c r="C19" s="65"/>
       <c r="D19" s="16" t="s">
         <v>102</v>
       </c>
@@ -7830,18 +7971,18 @@
         <v>89</v>
       </c>
       <c r="G19" s="17"/>
-      <c r="H19" s="112" t="s">
+      <c r="H19" s="111" t="s">
         <v>92</v>
       </c>
-      <c r="I19" s="42"/>
-      <c r="J19" s="113"/>
+      <c r="I19" s="64"/>
+      <c r="J19" s="112"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="111" t="s">
+      <c r="A20" s="113" t="s">
         <v>79</v>
       </c>
-      <c r="B20" s="42"/>
-      <c r="C20" s="43"/>
+      <c r="B20" s="64"/>
+      <c r="C20" s="65"/>
       <c r="D20" s="16" t="s">
         <v>103</v>
       </c>
@@ -7852,18 +7993,18 @@
         <v>122</v>
       </c>
       <c r="G20" s="17"/>
-      <c r="H20" s="112" t="s">
+      <c r="H20" s="111" t="s">
         <v>110</v>
       </c>
-      <c r="I20" s="42"/>
-      <c r="J20" s="113"/>
+      <c r="I20" s="64"/>
+      <c r="J20" s="112"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="111" t="s">
+      <c r="A21" s="113" t="s">
         <v>80</v>
       </c>
-      <c r="B21" s="42"/>
-      <c r="C21" s="43"/>
+      <c r="B21" s="64"/>
+      <c r="C21" s="65"/>
       <c r="D21" s="16" t="s">
         <v>104</v>
       </c>
@@ -7874,14 +8015,14 @@
         <v>106</v>
       </c>
       <c r="G21" s="17"/>
-      <c r="H21" s="112" t="s">
+      <c r="H21" s="111" t="s">
         <v>111</v>
       </c>
-      <c r="I21" s="42"/>
-      <c r="J21" s="113"/>
+      <c r="I21" s="64"/>
+      <c r="J21" s="112"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="111" t="s">
+      <c r="A22" s="113" t="s">
         <v>81</v>
       </c>
       <c r="B22" s="114"/>
@@ -7896,14 +8037,14 @@
         <v>90</v>
       </c>
       <c r="G22" s="17"/>
-      <c r="H22" s="112" t="s">
+      <c r="H22" s="111" t="s">
         <v>93</v>
       </c>
-      <c r="I22" s="42"/>
-      <c r="J22" s="113"/>
+      <c r="I22" s="64"/>
+      <c r="J22" s="112"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="111" t="s">
+      <c r="A23" s="113" t="s">
         <v>82</v>
       </c>
       <c r="B23" s="114"/>
@@ -7918,11 +8059,11 @@
       <c r="G23" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="H23" s="112" t="s">
+      <c r="H23" s="111" t="s">
         <v>96</v>
       </c>
-      <c r="I23" s="42"/>
-      <c r="J23" s="113"/>
+      <c r="I23" s="64"/>
+      <c r="J23" s="112"/>
     </row>
     <row r="24" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
       <c r="A24" s="126" t="s">
@@ -8925,6 +9066,8 @@
     <row r="1001" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="33">
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="H16:J16"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="A24:C24"/>
@@ -8940,7 +9083,14 @@
     <mergeCell ref="H23:J23"/>
     <mergeCell ref="H2:H4"/>
     <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="A21:C21"/>
     <mergeCell ref="A16:C16"/>
     <mergeCell ref="A17:C17"/>
     <mergeCell ref="D5:J5"/>
@@ -8949,15 +9099,6 @@
     <mergeCell ref="A14:J14"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="D15:H15"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -8971,7 +9112,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J1001"/>
+  <dimension ref="A1:J995"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="5.140625" customWidth="1"/>
@@ -8980,19 +9121,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="96" t="s">
+      <c r="A1" s="48" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="97"/>
-      <c r="C1" s="98"/>
-      <c r="D1" s="104" t="s">
+      <c r="B1" s="49"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="57" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="105"/>
-      <c r="F1" s="104" t="s">
+      <c r="E1" s="58"/>
+      <c r="F1" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="105"/>
+      <c r="G1" s="58"/>
       <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
@@ -9004,190 +9145,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="99"/>
-      <c r="B2" s="45"/>
-      <c r="C2" s="100"/>
-      <c r="D2" s="106" t="s">
+      <c r="A2" s="51"/>
+      <c r="B2" s="52"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="59" t="s">
         <v>97</v>
       </c>
-      <c r="E2" s="107"/>
-      <c r="F2" s="106" t="s">
+      <c r="E2" s="60"/>
+      <c r="F2" s="59" t="s">
         <v>98</v>
       </c>
-      <c r="G2" s="107"/>
-      <c r="H2" s="110">
+      <c r="G2" s="60"/>
+      <c r="H2" s="41">
         <v>46121</v>
       </c>
-      <c r="I2" s="90" t="s">
+      <c r="I2" s="44" t="s">
         <v>99</v>
       </c>
-      <c r="J2" s="93"/>
+      <c r="J2" s="45"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="99"/>
-      <c r="B3" s="45"/>
-      <c r="C3" s="100"/>
-      <c r="D3" s="108"/>
-      <c r="E3" s="100"/>
-      <c r="F3" s="108"/>
-      <c r="G3" s="100"/>
-      <c r="H3" s="91"/>
-      <c r="I3" s="91"/>
-      <c r="J3" s="94"/>
+      <c r="A3" s="51"/>
+      <c r="B3" s="52"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="61"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="61"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="42"/>
+      <c r="I3" s="42"/>
+      <c r="J3" s="46"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="99"/>
-      <c r="B4" s="45"/>
-      <c r="C4" s="100"/>
-      <c r="D4" s="108"/>
-      <c r="E4" s="100"/>
-      <c r="F4" s="108"/>
-      <c r="G4" s="100"/>
-      <c r="H4" s="91"/>
-      <c r="I4" s="91"/>
-      <c r="J4" s="94"/>
+      <c r="A4" s="51"/>
+      <c r="B4" s="52"/>
+      <c r="C4" s="53"/>
+      <c r="D4" s="61"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="61"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="42"/>
+      <c r="I4" s="42"/>
+      <c r="J4" s="46"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="125" t="s">
+      <c r="A5" s="116" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="118"/>
-      <c r="C5" s="105"/>
-      <c r="D5" s="117" t="s">
+      <c r="B5" s="117"/>
+      <c r="C5" s="58"/>
+      <c r="D5" s="119" t="s">
         <v>113</v>
       </c>
-      <c r="E5" s="118"/>
-      <c r="F5" s="118"/>
-      <c r="G5" s="118"/>
-      <c r="H5" s="118"/>
-      <c r="I5" s="118"/>
-      <c r="J5" s="119"/>
+      <c r="E5" s="117"/>
+      <c r="F5" s="117"/>
+      <c r="G5" s="117"/>
+      <c r="H5" s="117"/>
+      <c r="I5" s="117"/>
+      <c r="J5" s="120"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="116" t="s">
+      <c r="A6" s="118" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="42"/>
-      <c r="C6" s="42"/>
-      <c r="D6" s="42"/>
-      <c r="E6" s="42"/>
-      <c r="F6" s="42"/>
-      <c r="G6" s="42"/>
-      <c r="H6" s="42"/>
-      <c r="I6" s="42"/>
-      <c r="J6" s="113"/>
+      <c r="B6" s="64"/>
+      <c r="C6" s="64"/>
+      <c r="D6" s="64"/>
+      <c r="E6" s="64"/>
+      <c r="F6" s="64"/>
+      <c r="G6" s="64"/>
+      <c r="H6" s="64"/>
+      <c r="I6" s="64"/>
+      <c r="J6" s="112"/>
     </row>
     <row r="7" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A7" s="120"/>
-      <c r="B7" s="121"/>
-      <c r="C7" s="121"/>
-      <c r="D7" s="121"/>
-      <c r="E7" s="121"/>
-      <c r="F7" s="121"/>
-      <c r="G7" s="121"/>
-      <c r="H7" s="121"/>
-      <c r="I7" s="121"/>
-      <c r="J7" s="122"/>
+      <c r="A7" s="121"/>
+      <c r="B7" s="122"/>
+      <c r="C7" s="122"/>
+      <c r="D7" s="122"/>
+      <c r="E7" s="122"/>
+      <c r="F7" s="122"/>
+      <c r="G7" s="122"/>
+      <c r="H7" s="122"/>
+      <c r="I7" s="122"/>
+      <c r="J7" s="123"/>
     </row>
     <row r="8" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A8" s="99"/>
-      <c r="B8" s="45"/>
-      <c r="C8" s="45"/>
-      <c r="D8" s="45"/>
-      <c r="E8" s="45"/>
-      <c r="F8" s="45"/>
-      <c r="G8" s="45"/>
-      <c r="H8" s="45"/>
-      <c r="I8" s="45"/>
-      <c r="J8" s="123"/>
+      <c r="A8" s="51"/>
+      <c r="B8" s="52"/>
+      <c r="C8" s="52"/>
+      <c r="D8" s="52"/>
+      <c r="E8" s="52"/>
+      <c r="F8" s="52"/>
+      <c r="G8" s="52"/>
+      <c r="H8" s="52"/>
+      <c r="I8" s="52"/>
+      <c r="J8" s="124"/>
     </row>
     <row r="9" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A9" s="99"/>
-      <c r="B9" s="45"/>
-      <c r="C9" s="45"/>
-      <c r="D9" s="45"/>
-      <c r="E9" s="45"/>
-      <c r="F9" s="45"/>
-      <c r="G9" s="45"/>
-      <c r="H9" s="45"/>
-      <c r="I9" s="45"/>
-      <c r="J9" s="123"/>
+      <c r="A9" s="51"/>
+      <c r="B9" s="52"/>
+      <c r="C9" s="52"/>
+      <c r="D9" s="52"/>
+      <c r="E9" s="52"/>
+      <c r="F9" s="52"/>
+      <c r="G9" s="52"/>
+      <c r="H9" s="52"/>
+      <c r="I9" s="52"/>
+      <c r="J9" s="124"/>
     </row>
     <row r="10" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A10" s="99"/>
-      <c r="B10" s="45"/>
-      <c r="C10" s="45"/>
-      <c r="D10" s="45"/>
-      <c r="E10" s="45"/>
-      <c r="F10" s="45"/>
-      <c r="G10" s="45"/>
-      <c r="H10" s="45"/>
-      <c r="I10" s="45"/>
-      <c r="J10" s="123"/>
+      <c r="A10" s="51"/>
+      <c r="B10" s="52"/>
+      <c r="C10" s="52"/>
+      <c r="D10" s="52"/>
+      <c r="E10" s="52"/>
+      <c r="F10" s="52"/>
+      <c r="G10" s="52"/>
+      <c r="H10" s="52"/>
+      <c r="I10" s="52"/>
+      <c r="J10" s="124"/>
     </row>
     <row r="11" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A11" s="99"/>
-      <c r="B11" s="45"/>
-      <c r="C11" s="45"/>
-      <c r="D11" s="45"/>
-      <c r="E11" s="45"/>
-      <c r="F11" s="45"/>
-      <c r="G11" s="45"/>
-      <c r="H11" s="45"/>
-      <c r="I11" s="45"/>
-      <c r="J11" s="123"/>
+      <c r="A11" s="51"/>
+      <c r="B11" s="52"/>
+      <c r="C11" s="52"/>
+      <c r="D11" s="52"/>
+      <c r="E11" s="52"/>
+      <c r="F11" s="52"/>
+      <c r="G11" s="52"/>
+      <c r="H11" s="52"/>
+      <c r="I11" s="52"/>
+      <c r="J11" s="124"/>
     </row>
     <row r="12" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A12" s="99"/>
-      <c r="B12" s="45"/>
-      <c r="C12" s="45"/>
-      <c r="D12" s="45"/>
-      <c r="E12" s="45"/>
-      <c r="F12" s="45"/>
-      <c r="G12" s="45"/>
-      <c r="H12" s="45"/>
-      <c r="I12" s="45"/>
-      <c r="J12" s="123"/>
+      <c r="A12" s="51"/>
+      <c r="B12" s="52"/>
+      <c r="C12" s="52"/>
+      <c r="D12" s="52"/>
+      <c r="E12" s="52"/>
+      <c r="F12" s="52"/>
+      <c r="G12" s="52"/>
+      <c r="H12" s="52"/>
+      <c r="I12" s="52"/>
+      <c r="J12" s="124"/>
     </row>
     <row r="13" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A13" s="99"/>
-      <c r="B13" s="45"/>
-      <c r="C13" s="45"/>
-      <c r="D13" s="45"/>
-      <c r="E13" s="45"/>
-      <c r="F13" s="45"/>
-      <c r="G13" s="45"/>
-      <c r="H13" s="45"/>
-      <c r="I13" s="45"/>
-      <c r="J13" s="123"/>
+      <c r="A13" s="51"/>
+      <c r="B13" s="52"/>
+      <c r="C13" s="52"/>
+      <c r="D13" s="52"/>
+      <c r="E13" s="52"/>
+      <c r="F13" s="52"/>
+      <c r="G13" s="52"/>
+      <c r="H13" s="52"/>
+      <c r="I13" s="52"/>
+      <c r="J13" s="124"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="116" t="s">
+      <c r="A14" s="118" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="42"/>
-      <c r="C14" s="42"/>
-      <c r="D14" s="42"/>
-      <c r="E14" s="42"/>
-      <c r="F14" s="42"/>
-      <c r="G14" s="42"/>
-      <c r="H14" s="42"/>
-      <c r="I14" s="42"/>
-      <c r="J14" s="113"/>
+      <c r="B14" s="64"/>
+      <c r="C14" s="64"/>
+      <c r="D14" s="64"/>
+      <c r="E14" s="64"/>
+      <c r="F14" s="64"/>
+      <c r="G14" s="64"/>
+      <c r="H14" s="64"/>
+      <c r="I14" s="64"/>
+      <c r="J14" s="112"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="116" t="s">
+      <c r="A15" s="118" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="42"/>
-      <c r="C15" s="43"/>
-      <c r="D15" s="112" t="s">
+      <c r="B15" s="64"/>
+      <c r="C15" s="65"/>
+      <c r="D15" s="111" t="s">
         <v>116</v>
       </c>
-      <c r="E15" s="42"/>
-      <c r="F15" s="42"/>
-      <c r="G15" s="42"/>
-      <c r="H15" s="43"/>
+      <c r="E15" s="64"/>
+      <c r="F15" s="64"/>
+      <c r="G15" s="64"/>
+      <c r="H15" s="65"/>
       <c r="I15" s="14" t="s">
         <v>26</v>
       </c>
@@ -9196,11 +9337,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="116" t="s">
+      <c r="A16" s="118" t="s">
         <v>27</v>
       </c>
-      <c r="B16" s="42"/>
-      <c r="C16" s="43"/>
+      <c r="B16" s="64"/>
+      <c r="C16" s="65"/>
       <c r="D16" s="14" t="s">
         <v>28</v>
       </c>
@@ -9213,18 +9354,18 @@
       <c r="G16" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="H16" s="124" t="s">
+      <c r="H16" s="125" t="s">
         <v>18</v>
       </c>
-      <c r="I16" s="42"/>
-      <c r="J16" s="113"/>
+      <c r="I16" s="64"/>
+      <c r="J16" s="112"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="111" t="s">
+      <c r="A17" s="113" t="s">
         <v>76</v>
       </c>
-      <c r="B17" s="42"/>
-      <c r="C17" s="43"/>
+      <c r="B17" s="64"/>
+      <c r="C17" s="65"/>
       <c r="D17" s="40" t="s">
         <v>114</v>
       </c>
@@ -9235,96 +9376,30 @@
       <c r="G17" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="H17" s="112" t="s">
+      <c r="H17" s="111" t="s">
         <v>121</v>
       </c>
-      <c r="I17" s="42"/>
-      <c r="J17" s="113"/>
-    </row>
-    <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="111"/>
-      <c r="B18" s="42"/>
-      <c r="C18" s="43"/>
-      <c r="D18" s="16"/>
-      <c r="E18" s="16"/>
-      <c r="F18" s="17"/>
-      <c r="G18" s="17"/>
-      <c r="H18" s="112"/>
-      <c r="I18" s="42"/>
-      <c r="J18" s="113"/>
-    </row>
-    <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="111"/>
-      <c r="B19" s="42"/>
-      <c r="C19" s="43"/>
-      <c r="D19" s="16"/>
-      <c r="E19" s="16"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="17"/>
-      <c r="H19" s="112"/>
-      <c r="I19" s="42"/>
-      <c r="J19" s="113"/>
-    </row>
-    <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="111"/>
-      <c r="B20" s="42"/>
-      <c r="C20" s="43"/>
-      <c r="D20" s="16"/>
-      <c r="E20" s="16"/>
-      <c r="F20" s="17"/>
-      <c r="G20" s="17"/>
-      <c r="H20" s="112"/>
-      <c r="I20" s="42"/>
-      <c r="J20" s="113"/>
-    </row>
-    <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="111"/>
-      <c r="B21" s="42"/>
-      <c r="C21" s="43"/>
-      <c r="D21" s="16"/>
-      <c r="E21" s="16"/>
-      <c r="F21" s="17"/>
-      <c r="G21" s="17"/>
-      <c r="H21" s="112"/>
-      <c r="I21" s="42"/>
-      <c r="J21" s="113"/>
-    </row>
-    <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="111"/>
-      <c r="B22" s="114"/>
-      <c r="C22" s="115"/>
-      <c r="D22" s="16"/>
-      <c r="E22" s="16"/>
-      <c r="F22" s="17"/>
-      <c r="G22" s="17"/>
-      <c r="H22" s="112"/>
-      <c r="I22" s="42"/>
-      <c r="J22" s="113"/>
-    </row>
-    <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="111"/>
-      <c r="B23" s="114"/>
-      <c r="C23" s="115"/>
-      <c r="D23" s="16"/>
-      <c r="E23" s="16"/>
-      <c r="F23" s="17"/>
-      <c r="G23" s="17"/>
-      <c r="H23" s="112"/>
-      <c r="I23" s="42"/>
-      <c r="J23" s="113"/>
-    </row>
-    <row r="24" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A24" s="126"/>
-      <c r="B24" s="127"/>
-      <c r="C24" s="128"/>
-      <c r="D24" s="18"/>
-      <c r="E24" s="18"/>
-      <c r="F24" s="19"/>
-      <c r="G24" s="19"/>
-      <c r="H24" s="129"/>
-      <c r="I24" s="130"/>
-      <c r="J24" s="131"/>
-    </row>
+      <c r="I17" s="64"/>
+      <c r="J17" s="112"/>
+    </row>
+    <row r="18" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
+      <c r="A18" s="126"/>
+      <c r="B18" s="127"/>
+      <c r="C18" s="128"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="18"/>
+      <c r="F18" s="19"/>
+      <c r="G18" s="19"/>
+      <c r="H18" s="129"/>
+      <c r="I18" s="130"/>
+      <c r="J18" s="131"/>
+    </row>
+    <row r="19" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="20" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="21" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="22" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="23" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="26" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="27" spans="1:10" ht="12.75" customHeight="1"/>
@@ -10296,21 +10371,10 @@
     <row r="993" ht="12.75" customHeight="1"/>
     <row r="994" ht="12.75" customHeight="1"/>
     <row r="995" ht="12.75" customHeight="1"/>
-    <row r="996" ht="12.75" customHeight="1"/>
-    <row r="997" ht="12.75" customHeight="1"/>
-    <row r="998" ht="12.75" customHeight="1"/>
-    <row r="999" ht="12.75" customHeight="1"/>
-    <row r="1000" ht="12.75" customHeight="1"/>
-    <row r="1001" ht="12.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="33">
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="A6:J6"/>
+  <mergeCells count="21">
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A15:C15"/>
     <mergeCell ref="A7:J13"/>
     <mergeCell ref="A1:C4"/>
     <mergeCell ref="D1:E1"/>
@@ -10318,25 +10382,18 @@
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="F2:G4"/>
     <mergeCell ref="H2:H4"/>
-    <mergeCell ref="A14:J14"/>
-    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:J6"/>
     <mergeCell ref="D15:H15"/>
     <mergeCell ref="A16:C16"/>
     <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
     <mergeCell ref="A18:C18"/>
     <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="H24:J24"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -10350,7 +10407,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J1001"/>
+  <dimension ref="A1:J995"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="5.140625" customWidth="1"/>
@@ -10359,19 +10416,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="96" t="s">
+      <c r="A1" s="48" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="97"/>
-      <c r="C1" s="98"/>
-      <c r="D1" s="104" t="s">
+      <c r="B1" s="49"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="57" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="105"/>
-      <c r="F1" s="104" t="s">
+      <c r="E1" s="58"/>
+      <c r="F1" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="105"/>
+      <c r="G1" s="58"/>
       <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
@@ -10383,190 +10440,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="99"/>
-      <c r="B2" s="45"/>
-      <c r="C2" s="100"/>
-      <c r="D2" s="106" t="s">
+      <c r="A2" s="51"/>
+      <c r="B2" s="52"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="59" t="s">
         <v>97</v>
       </c>
-      <c r="E2" s="107"/>
-      <c r="F2" s="106" t="s">
+      <c r="E2" s="60"/>
+      <c r="F2" s="59" t="s">
         <v>98</v>
       </c>
-      <c r="G2" s="107"/>
-      <c r="H2" s="110">
+      <c r="G2" s="60"/>
+      <c r="H2" s="41">
         <v>46121</v>
       </c>
-      <c r="I2" s="90" t="s">
+      <c r="I2" s="44" t="s">
         <v>99</v>
       </c>
-      <c r="J2" s="93"/>
+      <c r="J2" s="45"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="99"/>
-      <c r="B3" s="45"/>
-      <c r="C3" s="100"/>
-      <c r="D3" s="108"/>
-      <c r="E3" s="100"/>
-      <c r="F3" s="108"/>
-      <c r="G3" s="100"/>
-      <c r="H3" s="91"/>
-      <c r="I3" s="91"/>
-      <c r="J3" s="94"/>
+      <c r="A3" s="51"/>
+      <c r="B3" s="52"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="61"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="61"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="42"/>
+      <c r="I3" s="42"/>
+      <c r="J3" s="46"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="99"/>
-      <c r="B4" s="45"/>
-      <c r="C4" s="100"/>
-      <c r="D4" s="108"/>
-      <c r="E4" s="100"/>
-      <c r="F4" s="108"/>
-      <c r="G4" s="100"/>
-      <c r="H4" s="91"/>
-      <c r="I4" s="91"/>
-      <c r="J4" s="94"/>
+      <c r="A4" s="51"/>
+      <c r="B4" s="52"/>
+      <c r="C4" s="53"/>
+      <c r="D4" s="61"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="61"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="42"/>
+      <c r="I4" s="42"/>
+      <c r="J4" s="46"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="125" t="s">
+      <c r="A5" s="116" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="118"/>
-      <c r="C5" s="105"/>
-      <c r="D5" s="117" t="s">
+      <c r="B5" s="117"/>
+      <c r="C5" s="58"/>
+      <c r="D5" s="119" t="s">
         <v>113</v>
       </c>
-      <c r="E5" s="118"/>
-      <c r="F5" s="118"/>
-      <c r="G5" s="118"/>
-      <c r="H5" s="118"/>
-      <c r="I5" s="118"/>
-      <c r="J5" s="119"/>
+      <c r="E5" s="117"/>
+      <c r="F5" s="117"/>
+      <c r="G5" s="117"/>
+      <c r="H5" s="117"/>
+      <c r="I5" s="117"/>
+      <c r="J5" s="120"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="116" t="s">
+      <c r="A6" s="118" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="42"/>
-      <c r="C6" s="42"/>
-      <c r="D6" s="42"/>
-      <c r="E6" s="42"/>
-      <c r="F6" s="42"/>
-      <c r="G6" s="42"/>
-      <c r="H6" s="42"/>
-      <c r="I6" s="42"/>
-      <c r="J6" s="113"/>
+      <c r="B6" s="64"/>
+      <c r="C6" s="64"/>
+      <c r="D6" s="64"/>
+      <c r="E6" s="64"/>
+      <c r="F6" s="64"/>
+      <c r="G6" s="64"/>
+      <c r="H6" s="64"/>
+      <c r="I6" s="64"/>
+      <c r="J6" s="112"/>
     </row>
     <row r="7" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A7" s="120"/>
-      <c r="B7" s="121"/>
-      <c r="C7" s="121"/>
-      <c r="D7" s="121"/>
-      <c r="E7" s="121"/>
-      <c r="F7" s="121"/>
-      <c r="G7" s="121"/>
-      <c r="H7" s="121"/>
-      <c r="I7" s="121"/>
-      <c r="J7" s="122"/>
+      <c r="A7" s="121"/>
+      <c r="B7" s="122"/>
+      <c r="C7" s="122"/>
+      <c r="D7" s="122"/>
+      <c r="E7" s="122"/>
+      <c r="F7" s="122"/>
+      <c r="G7" s="122"/>
+      <c r="H7" s="122"/>
+      <c r="I7" s="122"/>
+      <c r="J7" s="123"/>
     </row>
     <row r="8" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A8" s="99"/>
-      <c r="B8" s="45"/>
-      <c r="C8" s="45"/>
-      <c r="D8" s="45"/>
-      <c r="E8" s="45"/>
-      <c r="F8" s="45"/>
-      <c r="G8" s="45"/>
-      <c r="H8" s="45"/>
-      <c r="I8" s="45"/>
-      <c r="J8" s="123"/>
+      <c r="A8" s="51"/>
+      <c r="B8" s="52"/>
+      <c r="C8" s="52"/>
+      <c r="D8" s="52"/>
+      <c r="E8" s="52"/>
+      <c r="F8" s="52"/>
+      <c r="G8" s="52"/>
+      <c r="H8" s="52"/>
+      <c r="I8" s="52"/>
+      <c r="J8" s="124"/>
     </row>
     <row r="9" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A9" s="99"/>
-      <c r="B9" s="45"/>
-      <c r="C9" s="45"/>
-      <c r="D9" s="45"/>
-      <c r="E9" s="45"/>
-      <c r="F9" s="45"/>
-      <c r="G9" s="45"/>
-      <c r="H9" s="45"/>
-      <c r="I9" s="45"/>
-      <c r="J9" s="123"/>
+      <c r="A9" s="51"/>
+      <c r="B9" s="52"/>
+      <c r="C9" s="52"/>
+      <c r="D9" s="52"/>
+      <c r="E9" s="52"/>
+      <c r="F9" s="52"/>
+      <c r="G9" s="52"/>
+      <c r="H9" s="52"/>
+      <c r="I9" s="52"/>
+      <c r="J9" s="124"/>
     </row>
     <row r="10" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A10" s="99"/>
-      <c r="B10" s="45"/>
-      <c r="C10" s="45"/>
-      <c r="D10" s="45"/>
-      <c r="E10" s="45"/>
-      <c r="F10" s="45"/>
-      <c r="G10" s="45"/>
-      <c r="H10" s="45"/>
-      <c r="I10" s="45"/>
-      <c r="J10" s="123"/>
+      <c r="A10" s="51"/>
+      <c r="B10" s="52"/>
+      <c r="C10" s="52"/>
+      <c r="D10" s="52"/>
+      <c r="E10" s="52"/>
+      <c r="F10" s="52"/>
+      <c r="G10" s="52"/>
+      <c r="H10" s="52"/>
+      <c r="I10" s="52"/>
+      <c r="J10" s="124"/>
     </row>
     <row r="11" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A11" s="99"/>
-      <c r="B11" s="45"/>
-      <c r="C11" s="45"/>
-      <c r="D11" s="45"/>
-      <c r="E11" s="45"/>
-      <c r="F11" s="45"/>
-      <c r="G11" s="45"/>
-      <c r="H11" s="45"/>
-      <c r="I11" s="45"/>
-      <c r="J11" s="123"/>
+      <c r="A11" s="51"/>
+      <c r="B11" s="52"/>
+      <c r="C11" s="52"/>
+      <c r="D11" s="52"/>
+      <c r="E11" s="52"/>
+      <c r="F11" s="52"/>
+      <c r="G11" s="52"/>
+      <c r="H11" s="52"/>
+      <c r="I11" s="52"/>
+      <c r="J11" s="124"/>
     </row>
     <row r="12" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A12" s="99"/>
-      <c r="B12" s="45"/>
-      <c r="C12" s="45"/>
-      <c r="D12" s="45"/>
-      <c r="E12" s="45"/>
-      <c r="F12" s="45"/>
-      <c r="G12" s="45"/>
-      <c r="H12" s="45"/>
-      <c r="I12" s="45"/>
-      <c r="J12" s="123"/>
+      <c r="A12" s="51"/>
+      <c r="B12" s="52"/>
+      <c r="C12" s="52"/>
+      <c r="D12" s="52"/>
+      <c r="E12" s="52"/>
+      <c r="F12" s="52"/>
+      <c r="G12" s="52"/>
+      <c r="H12" s="52"/>
+      <c r="I12" s="52"/>
+      <c r="J12" s="124"/>
     </row>
     <row r="13" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A13" s="99"/>
-      <c r="B13" s="45"/>
-      <c r="C13" s="45"/>
-      <c r="D13" s="45"/>
-      <c r="E13" s="45"/>
-      <c r="F13" s="45"/>
-      <c r="G13" s="45"/>
-      <c r="H13" s="45"/>
-      <c r="I13" s="45"/>
-      <c r="J13" s="123"/>
+      <c r="A13" s="51"/>
+      <c r="B13" s="52"/>
+      <c r="C13" s="52"/>
+      <c r="D13" s="52"/>
+      <c r="E13" s="52"/>
+      <c r="F13" s="52"/>
+      <c r="G13" s="52"/>
+      <c r="H13" s="52"/>
+      <c r="I13" s="52"/>
+      <c r="J13" s="124"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="116" t="s">
+      <c r="A14" s="118" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="42"/>
-      <c r="C14" s="42"/>
-      <c r="D14" s="42"/>
-      <c r="E14" s="42"/>
-      <c r="F14" s="42"/>
-      <c r="G14" s="42"/>
-      <c r="H14" s="42"/>
-      <c r="I14" s="42"/>
-      <c r="J14" s="113"/>
+      <c r="B14" s="64"/>
+      <c r="C14" s="64"/>
+      <c r="D14" s="64"/>
+      <c r="E14" s="64"/>
+      <c r="F14" s="64"/>
+      <c r="G14" s="64"/>
+      <c r="H14" s="64"/>
+      <c r="I14" s="64"/>
+      <c r="J14" s="112"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="116" t="s">
+      <c r="A15" s="118" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="42"/>
-      <c r="C15" s="43"/>
-      <c r="D15" s="112" t="s">
+      <c r="B15" s="64"/>
+      <c r="C15" s="65"/>
+      <c r="D15" s="111" t="s">
         <v>119</v>
       </c>
-      <c r="E15" s="42"/>
-      <c r="F15" s="42"/>
-      <c r="G15" s="42"/>
-      <c r="H15" s="43"/>
+      <c r="E15" s="64"/>
+      <c r="F15" s="64"/>
+      <c r="G15" s="64"/>
+      <c r="H15" s="65"/>
       <c r="I15" s="14" t="s">
         <v>26</v>
       </c>
@@ -10575,11 +10632,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="116" t="s">
+      <c r="A16" s="118" t="s">
         <v>27</v>
       </c>
-      <c r="B16" s="42"/>
-      <c r="C16" s="43"/>
+      <c r="B16" s="64"/>
+      <c r="C16" s="65"/>
       <c r="D16" s="14" t="s">
         <v>28</v>
       </c>
@@ -10592,18 +10649,18 @@
       <c r="G16" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="H16" s="124" t="s">
+      <c r="H16" s="125" t="s">
         <v>18</v>
       </c>
-      <c r="I16" s="42"/>
-      <c r="J16" s="113"/>
+      <c r="I16" s="64"/>
+      <c r="J16" s="112"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="111" t="s">
+      <c r="A17" s="113" t="s">
         <v>76</v>
       </c>
-      <c r="B17" s="42"/>
-      <c r="C17" s="43"/>
+      <c r="B17" s="64"/>
+      <c r="C17" s="65"/>
       <c r="D17" s="40" t="s">
         <v>117</v>
       </c>
@@ -10614,96 +10671,30 @@
       <c r="G17" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="H17" s="112" t="s">
+      <c r="H17" s="111" t="s">
         <v>118</v>
       </c>
-      <c r="I17" s="42"/>
-      <c r="J17" s="113"/>
-    </row>
-    <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="111"/>
-      <c r="B18" s="42"/>
-      <c r="C18" s="43"/>
-      <c r="D18" s="16"/>
-      <c r="E18" s="16"/>
-      <c r="F18" s="17"/>
-      <c r="G18" s="17"/>
-      <c r="H18" s="112"/>
-      <c r="I18" s="42"/>
-      <c r="J18" s="113"/>
-    </row>
-    <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="111"/>
-      <c r="B19" s="42"/>
-      <c r="C19" s="43"/>
-      <c r="D19" s="16"/>
-      <c r="E19" s="16"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="17"/>
-      <c r="H19" s="112"/>
-      <c r="I19" s="42"/>
-      <c r="J19" s="113"/>
-    </row>
-    <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="111"/>
-      <c r="B20" s="42"/>
-      <c r="C20" s="43"/>
-      <c r="D20" s="16"/>
-      <c r="E20" s="16"/>
-      <c r="F20" s="17"/>
-      <c r="G20" s="17"/>
-      <c r="H20" s="112"/>
-      <c r="I20" s="42"/>
-      <c r="J20" s="113"/>
-    </row>
-    <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="111"/>
-      <c r="B21" s="42"/>
-      <c r="C21" s="43"/>
-      <c r="D21" s="16"/>
-      <c r="E21" s="16"/>
-      <c r="F21" s="17"/>
-      <c r="G21" s="17"/>
-      <c r="H21" s="112"/>
-      <c r="I21" s="42"/>
-      <c r="J21" s="113"/>
-    </row>
-    <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="111"/>
-      <c r="B22" s="114"/>
-      <c r="C22" s="115"/>
-      <c r="D22" s="16"/>
-      <c r="E22" s="16"/>
-      <c r="F22" s="17"/>
-      <c r="G22" s="17"/>
-      <c r="H22" s="112"/>
-      <c r="I22" s="42"/>
-      <c r="J22" s="113"/>
-    </row>
-    <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="111"/>
-      <c r="B23" s="114"/>
-      <c r="C23" s="115"/>
-      <c r="D23" s="16"/>
-      <c r="E23" s="16"/>
-      <c r="F23" s="17"/>
-      <c r="G23" s="17"/>
-      <c r="H23" s="112"/>
-      <c r="I23" s="42"/>
-      <c r="J23" s="113"/>
-    </row>
-    <row r="24" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A24" s="126"/>
-      <c r="B24" s="127"/>
-      <c r="C24" s="128"/>
-      <c r="D24" s="18"/>
-      <c r="E24" s="18"/>
-      <c r="F24" s="19"/>
-      <c r="G24" s="19"/>
-      <c r="H24" s="129"/>
-      <c r="I24" s="130"/>
-      <c r="J24" s="131"/>
-    </row>
+      <c r="I17" s="64"/>
+      <c r="J17" s="112"/>
+    </row>
+    <row r="18" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
+      <c r="A18" s="126"/>
+      <c r="B18" s="127"/>
+      <c r="C18" s="128"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="18"/>
+      <c r="F18" s="19"/>
+      <c r="G18" s="19"/>
+      <c r="H18" s="129"/>
+      <c r="I18" s="130"/>
+      <c r="J18" s="131"/>
+    </row>
+    <row r="19" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="20" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="21" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="22" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="23" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="26" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="27" spans="1:10" ht="12.75" customHeight="1"/>
@@ -11675,21 +11666,10 @@
     <row r="993" ht="12.75" customHeight="1"/>
     <row r="994" ht="12.75" customHeight="1"/>
     <row r="995" ht="12.75" customHeight="1"/>
-    <row r="996" ht="12.75" customHeight="1"/>
-    <row r="997" ht="12.75" customHeight="1"/>
-    <row r="998" ht="12.75" customHeight="1"/>
-    <row r="999" ht="12.75" customHeight="1"/>
-    <row r="1000" ht="12.75" customHeight="1"/>
-    <row r="1001" ht="12.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="33">
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="A6:J6"/>
+  <mergeCells count="21">
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A15:C15"/>
     <mergeCell ref="A7:J13"/>
     <mergeCell ref="A1:C4"/>
     <mergeCell ref="D1:E1"/>
@@ -11697,25 +11677,18 @@
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="F2:G4"/>
     <mergeCell ref="H2:H4"/>
-    <mergeCell ref="A14:J14"/>
-    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:J6"/>
     <mergeCell ref="D15:H15"/>
     <mergeCell ref="A16:C16"/>
     <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
     <mergeCell ref="A18:C18"/>
     <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="H24:J24"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -11738,179 +11711,179 @@
       <c r="A1" s="139" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="97"/>
-      <c r="C1" s="97"/>
-      <c r="D1" s="97"/>
-      <c r="E1" s="97"/>
-      <c r="F1" s="98"/>
-      <c r="G1" s="104" t="s">
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="57" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="118"/>
-      <c r="I1" s="118"/>
-      <c r="J1" s="105"/>
-      <c r="K1" s="104" t="s">
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
+      <c r="J1" s="58"/>
+      <c r="K1" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="L1" s="118"/>
-      <c r="M1" s="118"/>
-      <c r="N1" s="105"/>
-      <c r="O1" s="104" t="s">
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="58"/>
+      <c r="O1" s="57" t="s">
         <v>6</v>
       </c>
-      <c r="P1" s="105"/>
-      <c r="Q1" s="104" t="s">
+      <c r="P1" s="58"/>
+      <c r="Q1" s="57" t="s">
         <v>7</v>
       </c>
-      <c r="R1" s="105"/>
-      <c r="S1" s="104" t="s">
+      <c r="R1" s="58"/>
+      <c r="S1" s="57" t="s">
         <v>8</v>
       </c>
-      <c r="T1" s="119"/>
+      <c r="T1" s="120"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="99"/>
-      <c r="B2" s="45"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="100"/>
-      <c r="G2" s="106"/>
-      <c r="H2" s="121"/>
-      <c r="I2" s="121"/>
-      <c r="J2" s="107"/>
-      <c r="K2" s="106"/>
-      <c r="L2" s="121"/>
-      <c r="M2" s="121"/>
-      <c r="N2" s="107"/>
-      <c r="O2" s="106"/>
-      <c r="P2" s="107"/>
-      <c r="Q2" s="106"/>
-      <c r="R2" s="107"/>
-      <c r="S2" s="106"/>
-      <c r="T2" s="122"/>
+      <c r="A2" s="51"/>
+      <c r="B2" s="52"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="122"/>
+      <c r="I2" s="122"/>
+      <c r="J2" s="60"/>
+      <c r="K2" s="59"/>
+      <c r="L2" s="122"/>
+      <c r="M2" s="122"/>
+      <c r="N2" s="60"/>
+      <c r="O2" s="59"/>
+      <c r="P2" s="60"/>
+      <c r="Q2" s="59"/>
+      <c r="R2" s="60"/>
+      <c r="S2" s="59"/>
+      <c r="T2" s="123"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="99"/>
-      <c r="B3" s="45"/>
-      <c r="C3" s="45"/>
-      <c r="D3" s="45"/>
-      <c r="E3" s="45"/>
-      <c r="F3" s="100"/>
-      <c r="G3" s="108"/>
-      <c r="H3" s="45"/>
-      <c r="I3" s="45"/>
-      <c r="J3" s="100"/>
-      <c r="K3" s="108"/>
-      <c r="L3" s="45"/>
-      <c r="M3" s="45"/>
-      <c r="N3" s="100"/>
-      <c r="O3" s="108"/>
-      <c r="P3" s="100"/>
-      <c r="Q3" s="108"/>
-      <c r="R3" s="100"/>
-      <c r="S3" s="108"/>
-      <c r="T3" s="123"/>
+      <c r="A3" s="51"/>
+      <c r="B3" s="52"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="52"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="61"/>
+      <c r="H3" s="52"/>
+      <c r="I3" s="52"/>
+      <c r="J3" s="53"/>
+      <c r="K3" s="61"/>
+      <c r="L3" s="52"/>
+      <c r="M3" s="52"/>
+      <c r="N3" s="53"/>
+      <c r="O3" s="61"/>
+      <c r="P3" s="53"/>
+      <c r="Q3" s="61"/>
+      <c r="R3" s="53"/>
+      <c r="S3" s="61"/>
+      <c r="T3" s="124"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="101"/>
-      <c r="B4" s="102"/>
-      <c r="C4" s="102"/>
-      <c r="D4" s="102"/>
-      <c r="E4" s="102"/>
-      <c r="F4" s="103"/>
-      <c r="G4" s="109"/>
-      <c r="H4" s="102"/>
-      <c r="I4" s="102"/>
-      <c r="J4" s="103"/>
-      <c r="K4" s="109"/>
-      <c r="L4" s="102"/>
-      <c r="M4" s="102"/>
-      <c r="N4" s="103"/>
-      <c r="O4" s="109"/>
-      <c r="P4" s="103"/>
-      <c r="Q4" s="109"/>
-      <c r="R4" s="103"/>
-      <c r="S4" s="109"/>
+      <c r="A4" s="54"/>
+      <c r="B4" s="55"/>
+      <c r="C4" s="55"/>
+      <c r="D4" s="55"/>
+      <c r="E4" s="55"/>
+      <c r="F4" s="56"/>
+      <c r="G4" s="62"/>
+      <c r="H4" s="55"/>
+      <c r="I4" s="55"/>
+      <c r="J4" s="56"/>
+      <c r="K4" s="62"/>
+      <c r="L4" s="55"/>
+      <c r="M4" s="55"/>
+      <c r="N4" s="56"/>
+      <c r="O4" s="62"/>
+      <c r="P4" s="56"/>
+      <c r="Q4" s="62"/>
+      <c r="R4" s="56"/>
+      <c r="S4" s="62"/>
       <c r="T4" s="138"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="125" t="s">
+      <c r="A5" s="116" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="118"/>
-      <c r="C5" s="118"/>
-      <c r="D5" s="118"/>
-      <c r="E5" s="118"/>
-      <c r="F5" s="105"/>
+      <c r="B5" s="117"/>
+      <c r="C5" s="117"/>
+      <c r="D5" s="117"/>
+      <c r="E5" s="117"/>
+      <c r="F5" s="58"/>
       <c r="G5" s="140" t="s">
         <v>34</v>
       </c>
-      <c r="H5" s="118"/>
-      <c r="I5" s="118"/>
-      <c r="J5" s="118"/>
-      <c r="K5" s="118"/>
-      <c r="L5" s="118"/>
-      <c r="M5" s="118"/>
-      <c r="N5" s="118"/>
-      <c r="O5" s="118"/>
-      <c r="P5" s="118"/>
-      <c r="Q5" s="118"/>
-      <c r="R5" s="118"/>
-      <c r="S5" s="118"/>
-      <c r="T5" s="119"/>
+      <c r="H5" s="117"/>
+      <c r="I5" s="117"/>
+      <c r="J5" s="117"/>
+      <c r="K5" s="117"/>
+      <c r="L5" s="117"/>
+      <c r="M5" s="117"/>
+      <c r="N5" s="117"/>
+      <c r="O5" s="117"/>
+      <c r="P5" s="117"/>
+      <c r="Q5" s="117"/>
+      <c r="R5" s="117"/>
+      <c r="S5" s="117"/>
+      <c r="T5" s="120"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="116" t="s">
+      <c r="A6" s="118" t="s">
         <v>35</v>
       </c>
-      <c r="B6" s="42"/>
-      <c r="C6" s="42"/>
-      <c r="D6" s="42"/>
-      <c r="E6" s="42"/>
-      <c r="F6" s="43"/>
-      <c r="G6" s="112" t="s">
+      <c r="B6" s="64"/>
+      <c r="C6" s="64"/>
+      <c r="D6" s="64"/>
+      <c r="E6" s="64"/>
+      <c r="F6" s="65"/>
+      <c r="G6" s="111" t="s">
         <v>19</v>
       </c>
-      <c r="H6" s="42"/>
-      <c r="I6" s="42"/>
-      <c r="J6" s="42"/>
-      <c r="K6" s="42"/>
-      <c r="L6" s="42"/>
-      <c r="M6" s="42"/>
-      <c r="N6" s="42"/>
-      <c r="O6" s="42"/>
-      <c r="P6" s="42"/>
-      <c r="Q6" s="42"/>
-      <c r="R6" s="42"/>
-      <c r="S6" s="42"/>
-      <c r="T6" s="113"/>
+      <c r="H6" s="64"/>
+      <c r="I6" s="64"/>
+      <c r="J6" s="64"/>
+      <c r="K6" s="64"/>
+      <c r="L6" s="64"/>
+      <c r="M6" s="64"/>
+      <c r="N6" s="64"/>
+      <c r="O6" s="64"/>
+      <c r="P6" s="64"/>
+      <c r="Q6" s="64"/>
+      <c r="R6" s="64"/>
+      <c r="S6" s="64"/>
+      <c r="T6" s="112"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="116" t="s">
+      <c r="A7" s="118" t="s">
         <v>36</v>
       </c>
-      <c r="B7" s="42"/>
-      <c r="C7" s="42"/>
-      <c r="D7" s="42"/>
-      <c r="E7" s="42"/>
-      <c r="F7" s="43"/>
-      <c r="G7" s="112" t="s">
+      <c r="B7" s="64"/>
+      <c r="C7" s="64"/>
+      <c r="D7" s="64"/>
+      <c r="E7" s="64"/>
+      <c r="F7" s="65"/>
+      <c r="G7" s="111" t="s">
         <v>37</v>
       </c>
-      <c r="H7" s="42"/>
-      <c r="I7" s="42"/>
-      <c r="J7" s="42"/>
-      <c r="K7" s="42"/>
-      <c r="L7" s="42"/>
-      <c r="M7" s="42"/>
-      <c r="N7" s="42"/>
-      <c r="O7" s="42"/>
-      <c r="P7" s="42"/>
-      <c r="Q7" s="42"/>
-      <c r="R7" s="42"/>
-      <c r="S7" s="42"/>
-      <c r="T7" s="113"/>
+      <c r="H7" s="64"/>
+      <c r="I7" s="64"/>
+      <c r="J7" s="64"/>
+      <c r="K7" s="64"/>
+      <c r="L7" s="64"/>
+      <c r="M7" s="64"/>
+      <c r="N7" s="64"/>
+      <c r="O7" s="64"/>
+      <c r="P7" s="64"/>
+      <c r="Q7" s="64"/>
+      <c r="R7" s="64"/>
+      <c r="S7" s="64"/>
+      <c r="T7" s="112"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="7"/>
@@ -12109,37 +12082,37 @@
       <c r="T14" s="9"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="116" t="s">
+      <c r="A15" s="118" t="s">
         <v>44</v>
       </c>
-      <c r="B15" s="43"/>
+      <c r="B15" s="65"/>
       <c r="C15" s="143" t="s">
         <v>38</v>
       </c>
-      <c r="D15" s="43"/>
-      <c r="E15" s="124" t="s">
+      <c r="D15" s="65"/>
+      <c r="E15" s="125" t="s">
         <v>45</v>
       </c>
-      <c r="F15" s="43"/>
-      <c r="G15" s="124" t="s">
+      <c r="F15" s="65"/>
+      <c r="G15" s="125" t="s">
         <v>46</v>
       </c>
-      <c r="H15" s="42"/>
-      <c r="I15" s="43"/>
-      <c r="J15" s="124" t="s">
+      <c r="H15" s="64"/>
+      <c r="I15" s="65"/>
+      <c r="J15" s="125" t="s">
         <v>47</v>
       </c>
-      <c r="K15" s="43"/>
-      <c r="L15" s="124" t="s">
+      <c r="K15" s="65"/>
+      <c r="L15" s="125" t="s">
         <v>48</v>
       </c>
-      <c r="M15" s="42"/>
-      <c r="N15" s="43"/>
-      <c r="O15" s="124" t="s">
+      <c r="M15" s="64"/>
+      <c r="N15" s="65"/>
+      <c r="O15" s="125" t="s">
         <v>49</v>
       </c>
-      <c r="P15" s="42"/>
-      <c r="Q15" s="43"/>
+      <c r="P15" s="64"/>
+      <c r="Q15" s="65"/>
       <c r="R15" s="14" t="s">
         <v>50</v>
       </c>
@@ -12154,34 +12127,34 @@
       <c r="A16" s="141">
         <v>1</v>
       </c>
-      <c r="B16" s="43"/>
+      <c r="B16" s="65"/>
       <c r="C16" s="142" t="s">
         <v>53</v>
       </c>
-      <c r="D16" s="43"/>
+      <c r="D16" s="65"/>
       <c r="E16" s="142" t="s">
         <v>54</v>
       </c>
-      <c r="F16" s="43"/>
+      <c r="F16" s="65"/>
       <c r="G16" s="132" t="s">
         <v>55</v>
       </c>
-      <c r="H16" s="42"/>
-      <c r="I16" s="43"/>
+      <c r="H16" s="64"/>
+      <c r="I16" s="65"/>
       <c r="J16" s="132" t="s">
         <v>56</v>
       </c>
-      <c r="K16" s="43"/>
+      <c r="K16" s="65"/>
       <c r="L16" s="136" t="s">
         <v>57</v>
       </c>
-      <c r="M16" s="42"/>
-      <c r="N16" s="43"/>
+      <c r="M16" s="64"/>
+      <c r="N16" s="65"/>
       <c r="O16" s="136" t="s">
         <v>58</v>
       </c>
-      <c r="P16" s="42"/>
-      <c r="Q16" s="43"/>
+      <c r="P16" s="64"/>
+      <c r="Q16" s="65"/>
       <c r="R16" s="32"/>
       <c r="S16" s="32"/>
       <c r="T16" s="33"/>
@@ -12196,34 +12169,34 @@
       <c r="A17" s="141">
         <v>2</v>
       </c>
-      <c r="B17" s="43"/>
+      <c r="B17" s="65"/>
       <c r="C17" s="142" t="s">
         <v>59</v>
       </c>
-      <c r="D17" s="43"/>
+      <c r="D17" s="65"/>
       <c r="E17" s="142" t="s">
         <v>60</v>
       </c>
-      <c r="F17" s="43"/>
+      <c r="F17" s="65"/>
       <c r="G17" s="132" t="s">
         <v>61</v>
       </c>
-      <c r="H17" s="42"/>
-      <c r="I17" s="43"/>
+      <c r="H17" s="64"/>
+      <c r="I17" s="65"/>
       <c r="J17" s="132" t="s">
         <v>62</v>
       </c>
-      <c r="K17" s="43"/>
+      <c r="K17" s="65"/>
       <c r="L17" s="136" t="s">
         <v>63</v>
       </c>
-      <c r="M17" s="42"/>
-      <c r="N17" s="43"/>
+      <c r="M17" s="64"/>
+      <c r="N17" s="65"/>
       <c r="O17" s="136" t="s">
         <v>64</v>
       </c>
-      <c r="P17" s="42"/>
-      <c r="Q17" s="43"/>
+      <c r="P17" s="64"/>
+      <c r="Q17" s="65"/>
       <c r="R17" s="32"/>
       <c r="S17" s="32"/>
       <c r="T17" s="33"/>
@@ -12236,22 +12209,22 @@
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
       <c r="A18" s="141"/>
-      <c r="B18" s="43"/>
+      <c r="B18" s="65"/>
       <c r="C18" s="142"/>
-      <c r="D18" s="43"/>
+      <c r="D18" s="65"/>
       <c r="E18" s="142"/>
-      <c r="F18" s="43"/>
+      <c r="F18" s="65"/>
       <c r="G18" s="132"/>
-      <c r="H18" s="42"/>
-      <c r="I18" s="43"/>
+      <c r="H18" s="64"/>
+      <c r="I18" s="65"/>
       <c r="J18" s="132"/>
-      <c r="K18" s="43"/>
+      <c r="K18" s="65"/>
       <c r="L18" s="136"/>
-      <c r="M18" s="42"/>
-      <c r="N18" s="43"/>
+      <c r="M18" s="64"/>
+      <c r="N18" s="65"/>
       <c r="O18" s="136"/>
-      <c r="P18" s="42"/>
-      <c r="Q18" s="43"/>
+      <c r="P18" s="64"/>
+      <c r="Q18" s="65"/>
       <c r="R18" s="32"/>
       <c r="S18" s="32"/>
       <c r="T18" s="33"/>
@@ -12264,22 +12237,22 @@
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
       <c r="A19" s="141"/>
-      <c r="B19" s="43"/>
+      <c r="B19" s="65"/>
       <c r="C19" s="142"/>
-      <c r="D19" s="43"/>
+      <c r="D19" s="65"/>
       <c r="E19" s="142"/>
-      <c r="F19" s="43"/>
+      <c r="F19" s="65"/>
       <c r="G19" s="132"/>
-      <c r="H19" s="42"/>
-      <c r="I19" s="43"/>
+      <c r="H19" s="64"/>
+      <c r="I19" s="65"/>
       <c r="J19" s="132"/>
-      <c r="K19" s="43"/>
+      <c r="K19" s="65"/>
       <c r="L19" s="136"/>
-      <c r="M19" s="42"/>
-      <c r="N19" s="43"/>
+      <c r="M19" s="64"/>
+      <c r="N19" s="65"/>
       <c r="O19" s="136"/>
-      <c r="P19" s="42"/>
-      <c r="Q19" s="43"/>
+      <c r="P19" s="64"/>
+      <c r="Q19" s="65"/>
       <c r="R19" s="32"/>
       <c r="S19" s="32"/>
       <c r="T19" s="33"/>
@@ -12292,22 +12265,22 @@
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
       <c r="A20" s="141"/>
-      <c r="B20" s="43"/>
+      <c r="B20" s="65"/>
       <c r="C20" s="142"/>
-      <c r="D20" s="43"/>
+      <c r="D20" s="65"/>
       <c r="E20" s="142"/>
-      <c r="F20" s="43"/>
+      <c r="F20" s="65"/>
       <c r="G20" s="132"/>
-      <c r="H20" s="42"/>
-      <c r="I20" s="43"/>
+      <c r="H20" s="64"/>
+      <c r="I20" s="65"/>
       <c r="J20" s="132"/>
-      <c r="K20" s="43"/>
+      <c r="K20" s="65"/>
       <c r="L20" s="136"/>
-      <c r="M20" s="42"/>
-      <c r="N20" s="43"/>
+      <c r="M20" s="64"/>
+      <c r="N20" s="65"/>
       <c r="O20" s="136"/>
-      <c r="P20" s="42"/>
-      <c r="Q20" s="43"/>
+      <c r="P20" s="64"/>
+      <c r="Q20" s="65"/>
       <c r="R20" s="32"/>
       <c r="S20" s="32"/>
       <c r="T20" s="33"/>
@@ -12320,22 +12293,22 @@
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
       <c r="A21" s="141"/>
-      <c r="B21" s="43"/>
+      <c r="B21" s="65"/>
       <c r="C21" s="142"/>
-      <c r="D21" s="43"/>
+      <c r="D21" s="65"/>
       <c r="E21" s="142"/>
-      <c r="F21" s="43"/>
+      <c r="F21" s="65"/>
       <c r="G21" s="132"/>
-      <c r="H21" s="42"/>
-      <c r="I21" s="43"/>
+      <c r="H21" s="64"/>
+      <c r="I21" s="65"/>
       <c r="J21" s="132"/>
-      <c r="K21" s="43"/>
+      <c r="K21" s="65"/>
       <c r="L21" s="136"/>
-      <c r="M21" s="42"/>
-      <c r="N21" s="43"/>
+      <c r="M21" s="64"/>
+      <c r="N21" s="65"/>
       <c r="O21" s="136"/>
-      <c r="P21" s="42"/>
-      <c r="Q21" s="43"/>
+      <c r="P21" s="64"/>
+      <c r="Q21" s="65"/>
       <c r="R21" s="32"/>
       <c r="S21" s="32"/>
       <c r="T21" s="33"/>
@@ -12348,22 +12321,22 @@
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
       <c r="A22" s="141"/>
-      <c r="B22" s="43"/>
+      <c r="B22" s="65"/>
       <c r="C22" s="142"/>
-      <c r="D22" s="43"/>
+      <c r="D22" s="65"/>
       <c r="E22" s="142"/>
-      <c r="F22" s="43"/>
+      <c r="F22" s="65"/>
       <c r="G22" s="132"/>
-      <c r="H22" s="42"/>
-      <c r="I22" s="43"/>
+      <c r="H22" s="64"/>
+      <c r="I22" s="65"/>
       <c r="J22" s="132"/>
-      <c r="K22" s="43"/>
+      <c r="K22" s="65"/>
       <c r="L22" s="136"/>
-      <c r="M22" s="42"/>
-      <c r="N22" s="43"/>
+      <c r="M22" s="64"/>
+      <c r="N22" s="65"/>
       <c r="O22" s="136"/>
-      <c r="P22" s="42"/>
-      <c r="Q22" s="43"/>
+      <c r="P22" s="64"/>
+      <c r="Q22" s="65"/>
       <c r="R22" s="32"/>
       <c r="S22" s="32"/>
       <c r="T22" s="33"/>
@@ -12376,22 +12349,22 @@
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
       <c r="A23" s="141"/>
-      <c r="B23" s="43"/>
+      <c r="B23" s="65"/>
       <c r="C23" s="142"/>
-      <c r="D23" s="43"/>
+      <c r="D23" s="65"/>
       <c r="E23" s="142"/>
-      <c r="F23" s="43"/>
+      <c r="F23" s="65"/>
       <c r="G23" s="132"/>
-      <c r="H23" s="42"/>
-      <c r="I23" s="43"/>
+      <c r="H23" s="64"/>
+      <c r="I23" s="65"/>
       <c r="J23" s="132"/>
-      <c r="K23" s="43"/>
+      <c r="K23" s="65"/>
       <c r="L23" s="136"/>
-      <c r="M23" s="42"/>
-      <c r="N23" s="43"/>
+      <c r="M23" s="64"/>
+      <c r="N23" s="65"/>
       <c r="O23" s="136"/>
-      <c r="P23" s="42"/>
-      <c r="Q23" s="43"/>
+      <c r="P23" s="64"/>
+      <c r="Q23" s="65"/>
       <c r="R23" s="32"/>
       <c r="S23" s="32"/>
       <c r="T23" s="33"/>
@@ -12404,22 +12377,22 @@
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
       <c r="A24" s="141"/>
-      <c r="B24" s="43"/>
+      <c r="B24" s="65"/>
       <c r="C24" s="142"/>
-      <c r="D24" s="43"/>
+      <c r="D24" s="65"/>
       <c r="E24" s="142"/>
-      <c r="F24" s="43"/>
+      <c r="F24" s="65"/>
       <c r="G24" s="132"/>
-      <c r="H24" s="42"/>
-      <c r="I24" s="43"/>
+      <c r="H24" s="64"/>
+      <c r="I24" s="65"/>
       <c r="J24" s="132"/>
-      <c r="K24" s="43"/>
+      <c r="K24" s="65"/>
       <c r="L24" s="136"/>
-      <c r="M24" s="42"/>
-      <c r="N24" s="43"/>
+      <c r="M24" s="64"/>
+      <c r="N24" s="65"/>
       <c r="O24" s="136"/>
-      <c r="P24" s="42"/>
-      <c r="Q24" s="43"/>
+      <c r="P24" s="64"/>
+      <c r="Q24" s="65"/>
       <c r="R24" s="32"/>
       <c r="S24" s="32"/>
       <c r="T24" s="33"/>
@@ -12432,22 +12405,22 @@
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
       <c r="A25" s="141"/>
-      <c r="B25" s="43"/>
+      <c r="B25" s="65"/>
       <c r="C25" s="142"/>
-      <c r="D25" s="43"/>
+      <c r="D25" s="65"/>
       <c r="E25" s="142"/>
-      <c r="F25" s="43"/>
+      <c r="F25" s="65"/>
       <c r="G25" s="132"/>
-      <c r="H25" s="42"/>
-      <c r="I25" s="43"/>
+      <c r="H25" s="64"/>
+      <c r="I25" s="65"/>
       <c r="J25" s="132"/>
-      <c r="K25" s="43"/>
+      <c r="K25" s="65"/>
       <c r="L25" s="136"/>
-      <c r="M25" s="42"/>
-      <c r="N25" s="43"/>
+      <c r="M25" s="64"/>
+      <c r="N25" s="65"/>
       <c r="O25" s="136"/>
-      <c r="P25" s="42"/>
-      <c r="Q25" s="43"/>
+      <c r="P25" s="64"/>
+      <c r="Q25" s="65"/>
       <c r="R25" s="32"/>
       <c r="S25" s="32"/>
       <c r="T25" s="33"/>
@@ -12460,22 +12433,22 @@
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
       <c r="A26" s="141"/>
-      <c r="B26" s="43"/>
+      <c r="B26" s="65"/>
       <c r="C26" s="142"/>
-      <c r="D26" s="43"/>
+      <c r="D26" s="65"/>
       <c r="E26" s="142"/>
-      <c r="F26" s="43"/>
+      <c r="F26" s="65"/>
       <c r="G26" s="132"/>
-      <c r="H26" s="42"/>
-      <c r="I26" s="43"/>
+      <c r="H26" s="64"/>
+      <c r="I26" s="65"/>
       <c r="J26" s="132"/>
-      <c r="K26" s="43"/>
+      <c r="K26" s="65"/>
       <c r="L26" s="136"/>
-      <c r="M26" s="42"/>
-      <c r="N26" s="43"/>
+      <c r="M26" s="64"/>
+      <c r="N26" s="65"/>
       <c r="O26" s="136"/>
-      <c r="P26" s="42"/>
-      <c r="Q26" s="43"/>
+      <c r="P26" s="64"/>
+      <c r="Q26" s="65"/>
       <c r="R26" s="32"/>
       <c r="S26" s="32"/>
       <c r="T26" s="33"/>
@@ -12488,22 +12461,22 @@
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
       <c r="A27" s="141"/>
-      <c r="B27" s="43"/>
+      <c r="B27" s="65"/>
       <c r="C27" s="142"/>
-      <c r="D27" s="43"/>
+      <c r="D27" s="65"/>
       <c r="E27" s="142"/>
-      <c r="F27" s="43"/>
+      <c r="F27" s="65"/>
       <c r="G27" s="132"/>
-      <c r="H27" s="42"/>
-      <c r="I27" s="43"/>
+      <c r="H27" s="64"/>
+      <c r="I27" s="65"/>
       <c r="J27" s="132"/>
-      <c r="K27" s="43"/>
+      <c r="K27" s="65"/>
       <c r="L27" s="136"/>
-      <c r="M27" s="42"/>
-      <c r="N27" s="43"/>
+      <c r="M27" s="64"/>
+      <c r="N27" s="65"/>
       <c r="O27" s="136"/>
-      <c r="P27" s="42"/>
-      <c r="Q27" s="43"/>
+      <c r="P27" s="64"/>
+      <c r="Q27" s="65"/>
       <c r="R27" s="32"/>
       <c r="S27" s="32"/>
       <c r="T27" s="33"/>
@@ -12516,22 +12489,22 @@
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
       <c r="A28" s="141"/>
-      <c r="B28" s="43"/>
+      <c r="B28" s="65"/>
       <c r="C28" s="142"/>
-      <c r="D28" s="43"/>
+      <c r="D28" s="65"/>
       <c r="E28" s="142"/>
-      <c r="F28" s="43"/>
+      <c r="F28" s="65"/>
       <c r="G28" s="132"/>
-      <c r="H28" s="42"/>
-      <c r="I28" s="43"/>
+      <c r="H28" s="64"/>
+      <c r="I28" s="65"/>
       <c r="J28" s="132"/>
-      <c r="K28" s="43"/>
+      <c r="K28" s="65"/>
       <c r="L28" s="136"/>
-      <c r="M28" s="42"/>
-      <c r="N28" s="43"/>
+      <c r="M28" s="64"/>
+      <c r="N28" s="65"/>
       <c r="O28" s="136"/>
-      <c r="P28" s="42"/>
-      <c r="Q28" s="43"/>
+      <c r="P28" s="64"/>
+      <c r="Q28" s="65"/>
       <c r="R28" s="32"/>
       <c r="S28" s="32"/>
       <c r="T28" s="33"/>
@@ -12544,22 +12517,22 @@
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
       <c r="A29" s="141"/>
-      <c r="B29" s="43"/>
+      <c r="B29" s="65"/>
       <c r="C29" s="142"/>
-      <c r="D29" s="43"/>
+      <c r="D29" s="65"/>
       <c r="E29" s="142"/>
-      <c r="F29" s="43"/>
+      <c r="F29" s="65"/>
       <c r="G29" s="132"/>
-      <c r="H29" s="42"/>
-      <c r="I29" s="43"/>
+      <c r="H29" s="64"/>
+      <c r="I29" s="65"/>
       <c r="J29" s="132"/>
-      <c r="K29" s="43"/>
+      <c r="K29" s="65"/>
       <c r="L29" s="136"/>
-      <c r="M29" s="42"/>
-      <c r="N29" s="43"/>
+      <c r="M29" s="64"/>
+      <c r="N29" s="65"/>
       <c r="O29" s="136"/>
-      <c r="P29" s="42"/>
-      <c r="Q29" s="43"/>
+      <c r="P29" s="64"/>
+      <c r="Q29" s="65"/>
       <c r="R29" s="32"/>
       <c r="S29" s="32"/>
       <c r="T29" s="33"/>
@@ -12572,22 +12545,22 @@
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
       <c r="A30" s="141"/>
-      <c r="B30" s="43"/>
+      <c r="B30" s="65"/>
       <c r="C30" s="142"/>
-      <c r="D30" s="43"/>
+      <c r="D30" s="65"/>
       <c r="E30" s="142"/>
-      <c r="F30" s="43"/>
+      <c r="F30" s="65"/>
       <c r="G30" s="132"/>
-      <c r="H30" s="42"/>
-      <c r="I30" s="43"/>
+      <c r="H30" s="64"/>
+      <c r="I30" s="65"/>
       <c r="J30" s="132"/>
-      <c r="K30" s="43"/>
+      <c r="K30" s="65"/>
       <c r="L30" s="136"/>
-      <c r="M30" s="42"/>
-      <c r="N30" s="43"/>
+      <c r="M30" s="64"/>
+      <c r="N30" s="65"/>
       <c r="O30" s="136"/>
-      <c r="P30" s="42"/>
-      <c r="Q30" s="43"/>
+      <c r="P30" s="64"/>
+      <c r="Q30" s="65"/>
       <c r="R30" s="32"/>
       <c r="S30" s="32"/>
       <c r="T30" s="33"/>

--- a/document/成果物ドキュメント_タスク編集機能.xlsx
+++ b/document/成果物ドキュメント_タスク編集機能.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\TaskManager62\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1EF54EA-3327-422B-9610-7801784718EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E058AF2-683E-4557-AED5-8E3E5C7A252C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="3" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="127">
   <si>
     <t>プロジェクト型演習　成果ドキュメント</t>
   </si>
@@ -241,12 +241,6 @@
     <phoneticPr fontId="10"/>
   </si>
   <si>
-    <t>4a.ユーザーが編集前と同じ内容を入力し、確定した場合
-4a1.システムがDBの更新を行わない
-4a2.システムがエラー画面を表示する</t>
-    <phoneticPr fontId="10"/>
-  </si>
-  <si>
     <t>ユーザーがシステムにログインしていること</t>
     <phoneticPr fontId="10"/>
   </si>
@@ -390,23 +384,6 @@
     <t>メモを入力する</t>
     <rPh sb="3" eb="5">
       <t>ニュウリョク</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>タスク一覧</t>
-    <rPh sb="3" eb="5">
-      <t>イチラン</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>タスク一覧画面に戻る</t>
-    <rPh sb="3" eb="7">
-      <t>イチランガメン</t>
-    </rPh>
-    <rPh sb="8" eb="9">
-      <t>モド</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
@@ -681,6 +658,41 @@
     <t>チーム名 62期</t>
     <rPh sb="7" eb="8">
       <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>4a.ユーザーが編集前と同じ内容を入力し、確定した場合
+4a1.システムがエラー画面を表示する</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>タスク詳細画面に戻る</t>
+    <rPh sb="3" eb="5">
+      <t>ショウサイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>モド</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>タスク詳細画面へ</t>
+    <rPh sb="3" eb="7">
+      <t>ショウサイガメン</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>タスク詳細画面へ</t>
+    <rPh sb="3" eb="5">
+      <t>ショウサイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ガメン</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
@@ -1977,22 +1989,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>295275</xdr:colOff>
+      <xdr:colOff>304800</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>139584</xdr:rowOff>
+      <xdr:rowOff>85285</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>762000</xdr:colOff>
+      <xdr:colOff>714375</xdr:colOff>
       <xdr:row>32</xdr:row>
-      <xdr:rowOff>104775</xdr:rowOff>
+      <xdr:rowOff>19050</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="図 3">
+        <xdr:cNvPr id="2" name="図 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F0EB3575-6DC8-9368-570E-167DFEBA2D6D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9EBAB3EE-346E-8AEA-3158-AB5A964EE157}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2015,8 +2027,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="295275" y="1053984"/>
-          <a:ext cx="8181975" cy="4499091"/>
+          <a:off x="304800" y="999685"/>
+          <a:ext cx="8124825" cy="4467665"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2042,44 +2054,61 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>1082212</xdr:colOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>2</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>42314</xdr:rowOff>
+      <xdr:rowOff>53081</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>190500</xdr:colOff>
+      <xdr:colOff>89648</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>356742</xdr:rowOff>
+      <xdr:rowOff>333815</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="11" name="図 10">
+        <xdr:cNvPr id="2" name="図 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B1E4FACA-B539-0FF4-4429-3742E1B14F1B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7D02D29E-233D-3B68-3D78-457675E302E2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
-      <xdr:spPr>
+      <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="2121303" y="1566314"/>
-          <a:ext cx="4650106" cy="3119973"/>
+          <a:off x="2151531" y="1577081"/>
+          <a:ext cx="4527176" cy="3104616"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -2525,7 +2554,7 @@
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
       <c r="E8" s="69" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F8" s="52"/>
       <c r="G8" s="52"/>
@@ -2573,7 +2602,7 @@
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
       <c r="G17" s="66" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="H17" s="52"/>
       <c r="I17" s="52"/>
@@ -3621,18 +3650,18 @@
       <c r="B2" s="89"/>
       <c r="C2" s="75"/>
       <c r="D2" s="72" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E2" s="73"/>
       <c r="F2" s="72" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G2" s="73"/>
       <c r="H2" s="78">
         <v>46121</v>
       </c>
       <c r="I2" s="81" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="J2" s="97"/>
     </row>
@@ -3667,7 +3696,7 @@
       <c r="B5" s="93"/>
       <c r="C5" s="71"/>
       <c r="D5" s="109" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E5" s="93"/>
       <c r="F5" s="93"/>
@@ -3683,7 +3712,7 @@
       <c r="B6" s="95"/>
       <c r="C6" s="96"/>
       <c r="D6" s="101" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E6" s="95"/>
       <c r="F6" s="95"/>
@@ -3699,7 +3728,7 @@
       <c r="B7" s="95"/>
       <c r="C7" s="96"/>
       <c r="D7" s="101" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E7" s="95"/>
       <c r="F7" s="95"/>
@@ -3715,7 +3744,7 @@
       <c r="B8" s="95"/>
       <c r="C8" s="96"/>
       <c r="D8" s="101" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E8" s="95"/>
       <c r="F8" s="95"/>
@@ -3733,7 +3762,7 @@
       </c>
       <c r="C9" s="96"/>
       <c r="D9" s="103" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E9" s="95"/>
       <c r="F9" s="95"/>
@@ -3763,7 +3792,7 @@
       </c>
       <c r="C11" s="96"/>
       <c r="D11" s="103" t="s">
-        <v>66</v>
+        <v>123</v>
       </c>
       <c r="E11" s="95"/>
       <c r="F11" s="95"/>
@@ -4864,18 +4893,18 @@
       <c r="B2" s="52"/>
       <c r="C2" s="53"/>
       <c r="D2" s="59" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E2" s="60"/>
       <c r="F2" s="59" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G2" s="60"/>
       <c r="H2" s="41">
         <v>46125</v>
       </c>
       <c r="I2" s="44" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="J2" s="45"/>
     </row>
@@ -6285,18 +6314,18 @@
       <c r="B2" s="52"/>
       <c r="C2" s="53"/>
       <c r="D2" s="59" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E2" s="60"/>
       <c r="F2" s="59" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G2" s="60"/>
       <c r="H2" s="41">
         <v>46122</v>
       </c>
       <c r="I2" s="44" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="J2" s="45"/>
     </row>
@@ -7700,18 +7729,18 @@
       <c r="B2" s="52"/>
       <c r="C2" s="53"/>
       <c r="D2" s="59" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E2" s="60"/>
       <c r="F2" s="59" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G2" s="60"/>
       <c r="H2" s="41">
         <v>46121</v>
       </c>
       <c r="I2" s="44" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="J2" s="45"/>
     </row>
@@ -7746,7 +7775,7 @@
       <c r="B5" s="117"/>
       <c r="C5" s="58"/>
       <c r="D5" s="119" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E5" s="117"/>
       <c r="F5" s="117"/>
@@ -7874,7 +7903,7 @@
       <c r="B15" s="64"/>
       <c r="C15" s="65"/>
       <c r="D15" s="111" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E15" s="64"/>
       <c r="F15" s="64"/>
@@ -7884,7 +7913,7 @@
         <v>26</v>
       </c>
       <c r="J15" s="15" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
@@ -7913,176 +7942,176 @@
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
       <c r="A17" s="113" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B17" s="64"/>
       <c r="C17" s="65"/>
       <c r="D17" s="16" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E17" s="16" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F17" s="17" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G17" s="17"/>
       <c r="H17" s="111" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I17" s="64"/>
       <c r="J17" s="112"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
       <c r="A18" s="113" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B18" s="64"/>
       <c r="C18" s="65"/>
       <c r="D18" s="16" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E18" s="16" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="F18" s="17" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="G18" s="17"/>
       <c r="H18" s="111" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="I18" s="64"/>
       <c r="J18" s="112"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
       <c r="A19" s="113" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B19" s="64"/>
       <c r="C19" s="65"/>
       <c r="D19" s="16" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E19" s="16" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F19" s="17" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G19" s="17"/>
       <c r="H19" s="111" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I19" s="64"/>
       <c r="J19" s="112"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
       <c r="A20" s="113" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B20" s="64"/>
       <c r="C20" s="65"/>
       <c r="D20" s="16" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E20" s="16" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="F20" s="17" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="G20" s="17"/>
       <c r="H20" s="111" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="I20" s="64"/>
       <c r="J20" s="112"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
       <c r="A21" s="113" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B21" s="64"/>
       <c r="C21" s="65"/>
       <c r="D21" s="16" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E21" s="16" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="F21" s="17" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="G21" s="17"/>
       <c r="H21" s="111" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I21" s="64"/>
       <c r="J21" s="112"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
       <c r="A22" s="113" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B22" s="114"/>
       <c r="C22" s="115"/>
       <c r="D22" s="16" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="E22" s="16" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F22" s="17" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G22" s="17"/>
       <c r="H22" s="111" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I22" s="64"/>
       <c r="J22" s="112"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
       <c r="A23" s="113" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B23" s="114"/>
       <c r="C23" s="115"/>
       <c r="D23" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="E23" s="16" t="s">
         <v>84</v>
-      </c>
-      <c r="E23" s="16" t="s">
-        <v>85</v>
       </c>
       <c r="F23" s="17"/>
       <c r="G23" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H23" s="111" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="I23" s="64"/>
       <c r="J23" s="112"/>
     </row>
     <row r="24" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
       <c r="A24" s="126" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B24" s="127"/>
       <c r="C24" s="128"/>
       <c r="D24" s="18" t="s">
-        <v>94</v>
+        <v>125</v>
       </c>
       <c r="E24" s="18" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F24" s="19"/>
       <c r="G24" s="19" t="s">
-        <v>94</v>
+        <v>126</v>
       </c>
       <c r="H24" s="129" t="s">
-        <v>95</v>
+        <v>124</v>
       </c>
       <c r="I24" s="130"/>
       <c r="J24" s="131"/>
@@ -9066,10 +9095,6 @@
     <row r="1001" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
     <mergeCell ref="A24:C24"/>
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="H18:J18"/>
@@ -9081,7 +9106,13 @@
     <mergeCell ref="A20:C20"/>
     <mergeCell ref="A23:C23"/>
     <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
     <mergeCell ref="H2:H4"/>
+    <mergeCell ref="D15:H15"/>
     <mergeCell ref="I2:I4"/>
     <mergeCell ref="H21:J21"/>
     <mergeCell ref="A22:C22"/>
@@ -9097,8 +9128,6 @@
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="A7:J13"/>
     <mergeCell ref="A14:J14"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="D15:H15"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -9149,18 +9178,18 @@
       <c r="B2" s="52"/>
       <c r="C2" s="53"/>
       <c r="D2" s="59" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E2" s="60"/>
       <c r="F2" s="59" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G2" s="60"/>
       <c r="H2" s="41">
         <v>46121</v>
       </c>
       <c r="I2" s="44" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="J2" s="45"/>
     </row>
@@ -9195,7 +9224,7 @@
       <c r="B5" s="117"/>
       <c r="C5" s="58"/>
       <c r="D5" s="119" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="E5" s="117"/>
       <c r="F5" s="117"/>
@@ -9323,7 +9352,7 @@
       <c r="B15" s="64"/>
       <c r="C15" s="65"/>
       <c r="D15" s="111" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E15" s="64"/>
       <c r="F15" s="64"/>
@@ -9333,7 +9362,7 @@
         <v>26</v>
       </c>
       <c r="J15" s="15" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
@@ -9362,22 +9391,22 @@
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
       <c r="A17" s="113" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B17" s="64"/>
       <c r="C17" s="65"/>
       <c r="D17" s="40" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E17" s="16" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F17" s="17"/>
       <c r="G17" s="17" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="H17" s="111" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="I17" s="64"/>
       <c r="J17" s="112"/>
@@ -10444,18 +10473,18 @@
       <c r="B2" s="52"/>
       <c r="C2" s="53"/>
       <c r="D2" s="59" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E2" s="60"/>
       <c r="F2" s="59" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G2" s="60"/>
       <c r="H2" s="41">
         <v>46121</v>
       </c>
       <c r="I2" s="44" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="J2" s="45"/>
     </row>
@@ -10490,7 +10519,7 @@
       <c r="B5" s="117"/>
       <c r="C5" s="58"/>
       <c r="D5" s="119" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="E5" s="117"/>
       <c r="F5" s="117"/>
@@ -10618,7 +10647,7 @@
       <c r="B15" s="64"/>
       <c r="C15" s="65"/>
       <c r="D15" s="111" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="E15" s="64"/>
       <c r="F15" s="64"/>
@@ -10628,7 +10657,7 @@
         <v>26</v>
       </c>
       <c r="J15" s="15" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
@@ -10657,22 +10686,22 @@
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
       <c r="A17" s="113" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B17" s="64"/>
       <c r="C17" s="65"/>
       <c r="D17" s="40" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E17" s="16" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F17" s="17"/>
       <c r="G17" s="17" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="H17" s="111" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="I17" s="64"/>
       <c r="J17" s="112"/>

--- a/document/成果物ドキュメント_タスク編集機能.xlsx
+++ b/document/成果物ドキュメント_タスク編集機能.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\TaskManager62\document\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PCに貼ってある番号\Documents\project\TaskManager62\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E058AF2-683E-4557-AED5-8E3E5C7A252C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3255" yWindow="1185" windowWidth="15375" windowHeight="7785" tabRatio="824" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -1585,45 +1585,267 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1633,272 +1855,50 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2455,85 +2455,85 @@
   <sheetData>
     <row r="1" spans="3:16" ht="30" customHeight="1"/>
     <row r="2" spans="3:16" ht="30" customHeight="1">
-      <c r="C2" s="67" t="s">
+      <c r="C2" s="82" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="68"/>
-      <c r="E2" s="68"/>
-      <c r="F2" s="68"/>
-      <c r="G2" s="68"/>
-      <c r="H2" s="68"/>
-      <c r="I2" s="68"/>
-      <c r="J2" s="68"/>
-      <c r="K2" s="68"/>
-      <c r="L2" s="68"/>
-      <c r="M2" s="68"/>
-      <c r="N2" s="68"/>
-      <c r="O2" s="68"/>
+      <c r="D2" s="83"/>
+      <c r="E2" s="83"/>
+      <c r="F2" s="83"/>
+      <c r="G2" s="83"/>
+      <c r="H2" s="83"/>
+      <c r="I2" s="83"/>
+      <c r="J2" s="83"/>
+      <c r="K2" s="83"/>
+      <c r="L2" s="83"/>
+      <c r="M2" s="83"/>
+      <c r="N2" s="83"/>
+      <c r="O2" s="83"/>
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="52"/>
-      <c r="D3" s="52"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="52"/>
-      <c r="G3" s="52"/>
-      <c r="H3" s="52"/>
-      <c r="I3" s="52"/>
-      <c r="J3" s="52"/>
-      <c r="K3" s="52"/>
-      <c r="L3" s="52"/>
-      <c r="M3" s="52"/>
-      <c r="N3" s="52"/>
-      <c r="O3" s="52"/>
+      <c r="C3" s="67"/>
+      <c r="D3" s="67"/>
+      <c r="E3" s="67"/>
+      <c r="F3" s="67"/>
+      <c r="G3" s="67"/>
+      <c r="H3" s="67"/>
+      <c r="I3" s="67"/>
+      <c r="J3" s="67"/>
+      <c r="K3" s="67"/>
+      <c r="L3" s="67"/>
+      <c r="M3" s="67"/>
+      <c r="N3" s="67"/>
+      <c r="O3" s="67"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="52"/>
-      <c r="D4" s="52"/>
-      <c r="E4" s="52"/>
-      <c r="F4" s="52"/>
-      <c r="G4" s="52"/>
-      <c r="H4" s="52"/>
-      <c r="I4" s="52"/>
-      <c r="J4" s="52"/>
-      <c r="K4" s="52"/>
-      <c r="L4" s="52"/>
-      <c r="M4" s="52"/>
-      <c r="N4" s="52"/>
-      <c r="O4" s="52"/>
+      <c r="C4" s="67"/>
+      <c r="D4" s="67"/>
+      <c r="E4" s="67"/>
+      <c r="F4" s="67"/>
+      <c r="G4" s="67"/>
+      <c r="H4" s="67"/>
+      <c r="I4" s="67"/>
+      <c r="J4" s="67"/>
+      <c r="K4" s="67"/>
+      <c r="L4" s="67"/>
+      <c r="M4" s="67"/>
+      <c r="N4" s="67"/>
+      <c r="O4" s="67"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="52"/>
-      <c r="D5" s="52"/>
-      <c r="E5" s="52"/>
-      <c r="F5" s="52"/>
-      <c r="G5" s="52"/>
-      <c r="H5" s="52"/>
-      <c r="I5" s="52"/>
-      <c r="J5" s="52"/>
-      <c r="K5" s="52"/>
-      <c r="L5" s="52"/>
-      <c r="M5" s="52"/>
-      <c r="N5" s="52"/>
-      <c r="O5" s="52"/>
+      <c r="C5" s="67"/>
+      <c r="D5" s="67"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="67"/>
+      <c r="H5" s="67"/>
+      <c r="I5" s="67"/>
+      <c r="J5" s="67"/>
+      <c r="K5" s="67"/>
+      <c r="L5" s="67"/>
+      <c r="M5" s="67"/>
+      <c r="N5" s="67"/>
+      <c r="O5" s="67"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="52"/>
-      <c r="D6" s="52"/>
-      <c r="E6" s="52"/>
-      <c r="F6" s="52"/>
-      <c r="G6" s="52"/>
-      <c r="H6" s="52"/>
-      <c r="I6" s="52"/>
-      <c r="J6" s="52"/>
-      <c r="K6" s="52"/>
-      <c r="L6" s="52"/>
-      <c r="M6" s="52"/>
-      <c r="N6" s="52"/>
-      <c r="O6" s="52"/>
+      <c r="C6" s="67"/>
+      <c r="D6" s="67"/>
+      <c r="E6" s="67"/>
+      <c r="F6" s="67"/>
+      <c r="G6" s="67"/>
+      <c r="H6" s="67"/>
+      <c r="I6" s="67"/>
+      <c r="J6" s="67"/>
+      <c r="K6" s="67"/>
+      <c r="L6" s="67"/>
+      <c r="M6" s="67"/>
+      <c r="N6" s="67"/>
+      <c r="O6" s="67"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -2553,46 +2553,46 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="69" t="s">
+      <c r="E8" s="84" t="s">
         <v>121</v>
       </c>
-      <c r="F8" s="52"/>
-      <c r="G8" s="52"/>
-      <c r="H8" s="52"/>
-      <c r="I8" s="52"/>
-      <c r="J8" s="52"/>
-      <c r="K8" s="52"/>
-      <c r="L8" s="52"/>
-      <c r="M8" s="52"/>
+      <c r="F8" s="67"/>
+      <c r="G8" s="67"/>
+      <c r="H8" s="67"/>
+      <c r="I8" s="67"/>
+      <c r="J8" s="67"/>
+      <c r="K8" s="67"/>
+      <c r="L8" s="67"/>
+      <c r="M8" s="67"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="63" t="s">
+      <c r="G13" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="H13" s="65"/>
-      <c r="I13" s="63" t="s">
+      <c r="H13" s="51"/>
+      <c r="I13" s="80" t="s">
         <v>2</v>
       </c>
-      <c r="J13" s="64"/>
-      <c r="K13" s="65"/>
+      <c r="J13" s="45"/>
+      <c r="K13" s="51"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="63"/>
-      <c r="H14" s="65"/>
-      <c r="I14" s="63"/>
-      <c r="J14" s="64"/>
-      <c r="K14" s="65"/>
+      <c r="G14" s="80"/>
+      <c r="H14" s="51"/>
+      <c r="I14" s="80"/>
+      <c r="J14" s="45"/>
+      <c r="K14" s="51"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="63"/>
-      <c r="H15" s="65"/>
-      <c r="I15" s="63"/>
-      <c r="J15" s="64"/>
-      <c r="K15" s="65"/>
+      <c r="G15" s="80"/>
+      <c r="H15" s="51"/>
+      <c r="I15" s="80"/>
+      <c r="J15" s="45"/>
+      <c r="K15" s="51"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -2601,13 +2601,13 @@
       <c r="J16" s="3"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="66" t="s">
+      <c r="G17" s="81" t="s">
         <v>122</v>
       </c>
-      <c r="H17" s="52"/>
-      <c r="I17" s="52"/>
-      <c r="J17" s="52"/>
-      <c r="K17" s="52"/>
+      <c r="H17" s="67"/>
+      <c r="I17" s="67"/>
+      <c r="J17" s="67"/>
+      <c r="K17" s="67"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -3622,19 +3622,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="85" t="s">
+      <c r="A1" s="106" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="86"/>
-      <c r="C1" s="87"/>
-      <c r="D1" s="70" t="s">
+      <c r="B1" s="107"/>
+      <c r="C1" s="108"/>
+      <c r="D1" s="117" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="71"/>
-      <c r="F1" s="70" t="s">
+      <c r="E1" s="116"/>
+      <c r="F1" s="117" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="71"/>
+      <c r="G1" s="116"/>
       <c r="H1" s="39" t="s">
         <v>6</v>
       </c>
@@ -3646,190 +3646,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="88"/>
-      <c r="B2" s="89"/>
-      <c r="C2" s="75"/>
-      <c r="D2" s="72" t="s">
+      <c r="A2" s="109"/>
+      <c r="B2" s="110"/>
+      <c r="C2" s="111"/>
+      <c r="D2" s="118" t="s">
         <v>72</v>
       </c>
-      <c r="E2" s="73"/>
-      <c r="F2" s="72" t="s">
+      <c r="E2" s="119"/>
+      <c r="F2" s="118" t="s">
         <v>71</v>
       </c>
-      <c r="G2" s="73"/>
-      <c r="H2" s="78">
+      <c r="G2" s="119"/>
+      <c r="H2" s="122">
         <v>46121</v>
       </c>
-      <c r="I2" s="81" t="s">
+      <c r="I2" s="125" t="s">
         <v>70</v>
       </c>
-      <c r="J2" s="97"/>
+      <c r="J2" s="95"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="88"/>
-      <c r="B3" s="89"/>
-      <c r="C3" s="75"/>
-      <c r="D3" s="74"/>
-      <c r="E3" s="75"/>
-      <c r="F3" s="74"/>
-      <c r="G3" s="75"/>
-      <c r="H3" s="79"/>
-      <c r="I3" s="79"/>
-      <c r="J3" s="98"/>
+      <c r="A3" s="109"/>
+      <c r="B3" s="110"/>
+      <c r="C3" s="111"/>
+      <c r="D3" s="120"/>
+      <c r="E3" s="111"/>
+      <c r="F3" s="120"/>
+      <c r="G3" s="111"/>
+      <c r="H3" s="123"/>
+      <c r="I3" s="123"/>
+      <c r="J3" s="96"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="90"/>
-      <c r="B4" s="91"/>
-      <c r="C4" s="77"/>
-      <c r="D4" s="76"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="76"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="80"/>
-      <c r="I4" s="80"/>
-      <c r="J4" s="99"/>
+      <c r="A4" s="112"/>
+      <c r="B4" s="113"/>
+      <c r="C4" s="114"/>
+      <c r="D4" s="121"/>
+      <c r="E4" s="114"/>
+      <c r="F4" s="121"/>
+      <c r="G4" s="114"/>
+      <c r="H4" s="124"/>
+      <c r="I4" s="124"/>
+      <c r="J4" s="97"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="92" t="s">
+      <c r="A5" s="115" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="93"/>
-      <c r="C5" s="71"/>
-      <c r="D5" s="109" t="s">
+      <c r="B5" s="89"/>
+      <c r="C5" s="116"/>
+      <c r="D5" s="88" t="s">
         <v>69</v>
       </c>
-      <c r="E5" s="93"/>
-      <c r="F5" s="93"/>
-      <c r="G5" s="93"/>
-      <c r="H5" s="93"/>
-      <c r="I5" s="93"/>
-      <c r="J5" s="110"/>
+      <c r="E5" s="89"/>
+      <c r="F5" s="89"/>
+      <c r="G5" s="89"/>
+      <c r="H5" s="89"/>
+      <c r="I5" s="89"/>
+      <c r="J5" s="90"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="94" t="s">
+      <c r="A6" s="100" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="95"/>
-      <c r="C6" s="96"/>
-      <c r="D6" s="101" t="s">
+      <c r="B6" s="92"/>
+      <c r="C6" s="99"/>
+      <c r="D6" s="91" t="s">
         <v>68</v>
       </c>
-      <c r="E6" s="95"/>
-      <c r="F6" s="95"/>
-      <c r="G6" s="95"/>
-      <c r="H6" s="95"/>
-      <c r="I6" s="95"/>
-      <c r="J6" s="102"/>
+      <c r="E6" s="92"/>
+      <c r="F6" s="92"/>
+      <c r="G6" s="92"/>
+      <c r="H6" s="92"/>
+      <c r="I6" s="92"/>
+      <c r="J6" s="93"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="94" t="s">
+      <c r="A7" s="100" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="95"/>
-      <c r="C7" s="96"/>
-      <c r="D7" s="101" t="s">
+      <c r="B7" s="92"/>
+      <c r="C7" s="99"/>
+      <c r="D7" s="91" t="s">
         <v>67</v>
       </c>
-      <c r="E7" s="95"/>
-      <c r="F7" s="95"/>
-      <c r="G7" s="95"/>
-      <c r="H7" s="95"/>
-      <c r="I7" s="95"/>
-      <c r="J7" s="102"/>
+      <c r="E7" s="92"/>
+      <c r="F7" s="92"/>
+      <c r="G7" s="92"/>
+      <c r="H7" s="92"/>
+      <c r="I7" s="92"/>
+      <c r="J7" s="93"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="94" t="s">
+      <c r="A8" s="100" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="95"/>
-      <c r="C8" s="96"/>
-      <c r="D8" s="101" t="s">
+      <c r="B8" s="92"/>
+      <c r="C8" s="99"/>
+      <c r="D8" s="91" t="s">
         <v>66</v>
       </c>
-      <c r="E8" s="95"/>
-      <c r="F8" s="95"/>
-      <c r="G8" s="95"/>
-      <c r="H8" s="95"/>
-      <c r="I8" s="95"/>
-      <c r="J8" s="102"/>
+      <c r="E8" s="92"/>
+      <c r="F8" s="92"/>
+      <c r="G8" s="92"/>
+      <c r="H8" s="92"/>
+      <c r="I8" s="92"/>
+      <c r="J8" s="93"/>
     </row>
     <row r="9" spans="1:10" ht="78" customHeight="1">
-      <c r="A9" s="104" t="s">
+      <c r="A9" s="101" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="100" t="s">
+      <c r="B9" s="98" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="96"/>
-      <c r="D9" s="103" t="s">
+      <c r="C9" s="99"/>
+      <c r="D9" s="94" t="s">
         <v>117</v>
       </c>
-      <c r="E9" s="95"/>
-      <c r="F9" s="95"/>
-      <c r="G9" s="95"/>
-      <c r="H9" s="95"/>
-      <c r="I9" s="95"/>
-      <c r="J9" s="102"/>
+      <c r="E9" s="92"/>
+      <c r="F9" s="92"/>
+      <c r="G9" s="92"/>
+      <c r="H9" s="92"/>
+      <c r="I9" s="92"/>
+      <c r="J9" s="93"/>
     </row>
     <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="105"/>
-      <c r="B10" s="100" t="s">
+      <c r="A10" s="102"/>
+      <c r="B10" s="98" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="96"/>
-      <c r="D10" s="101"/>
-      <c r="E10" s="95"/>
-      <c r="F10" s="95"/>
-      <c r="G10" s="95"/>
-      <c r="H10" s="95"/>
-      <c r="I10" s="95"/>
-      <c r="J10" s="102"/>
+      <c r="C10" s="99"/>
+      <c r="D10" s="91"/>
+      <c r="E10" s="92"/>
+      <c r="F10" s="92"/>
+      <c r="G10" s="92"/>
+      <c r="H10" s="92"/>
+      <c r="I10" s="92"/>
+      <c r="J10" s="93"/>
     </row>
     <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="106"/>
-      <c r="B11" s="100" t="s">
+      <c r="A11" s="103"/>
+      <c r="B11" s="98" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="96"/>
-      <c r="D11" s="103" t="s">
+      <c r="C11" s="99"/>
+      <c r="D11" s="94" t="s">
         <v>123</v>
       </c>
-      <c r="E11" s="95"/>
-      <c r="F11" s="95"/>
-      <c r="G11" s="95"/>
-      <c r="H11" s="95"/>
-      <c r="I11" s="95"/>
-      <c r="J11" s="102"/>
+      <c r="E11" s="92"/>
+      <c r="F11" s="92"/>
+      <c r="G11" s="92"/>
+      <c r="H11" s="92"/>
+      <c r="I11" s="92"/>
+      <c r="J11" s="93"/>
     </row>
     <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="94" t="s">
+      <c r="A12" s="100" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="95"/>
-      <c r="C12" s="96"/>
-      <c r="D12" s="101" t="s">
+      <c r="B12" s="92"/>
+      <c r="C12" s="99"/>
+      <c r="D12" s="91" t="s">
         <v>65</v>
       </c>
-      <c r="E12" s="95"/>
-      <c r="F12" s="95"/>
-      <c r="G12" s="95"/>
-      <c r="H12" s="95"/>
-      <c r="I12" s="95"/>
-      <c r="J12" s="102"/>
+      <c r="E12" s="92"/>
+      <c r="F12" s="92"/>
+      <c r="G12" s="92"/>
+      <c r="H12" s="92"/>
+      <c r="I12" s="92"/>
+      <c r="J12" s="93"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A13" s="82" t="s">
+      <c r="A13" s="104" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="83"/>
-      <c r="C13" s="84"/>
-      <c r="D13" s="107"/>
-      <c r="E13" s="83"/>
-      <c r="F13" s="83"/>
-      <c r="G13" s="83"/>
-      <c r="H13" s="83"/>
-      <c r="I13" s="83"/>
-      <c r="J13" s="108"/>
+      <c r="B13" s="86"/>
+      <c r="C13" s="105"/>
+      <c r="D13" s="85"/>
+      <c r="E13" s="86"/>
+      <c r="F13" s="86"/>
+      <c r="G13" s="86"/>
+      <c r="H13" s="86"/>
+      <c r="I13" s="86"/>
+      <c r="J13" s="87"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -4820,13 +4820,17 @@
     <row r="1000" s="37" customFormat="1" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="D13:J13"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="D7:J7"/>
-    <mergeCell ref="D8:J8"/>
-    <mergeCell ref="D9:J9"/>
-    <mergeCell ref="D10:J10"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A7:C7"/>
     <mergeCell ref="J2:J4"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B11:C11"/>
@@ -4836,17 +4840,13 @@
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A9:A11"/>
     <mergeCell ref="B9:C9"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="D13:J13"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="D7:J7"/>
+    <mergeCell ref="D8:J8"/>
+    <mergeCell ref="D9:J9"/>
+    <mergeCell ref="D10:J10"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -4865,19 +4865,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="63" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="50"/>
-      <c r="D1" s="57" t="s">
+      <c r="B1" s="64"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="58" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="58"/>
-      <c r="F1" s="57" t="s">
+      <c r="E1" s="59"/>
+      <c r="F1" s="58" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="58"/>
+      <c r="G1" s="59"/>
       <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
@@ -4889,48 +4889,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="51"/>
-      <c r="B2" s="52"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="59" t="s">
+      <c r="A2" s="66"/>
+      <c r="B2" s="67"/>
+      <c r="C2" s="68"/>
+      <c r="D2" s="71" t="s">
         <v>94</v>
       </c>
-      <c r="E2" s="60"/>
-      <c r="F2" s="59" t="s">
+      <c r="E2" s="72"/>
+      <c r="F2" s="71" t="s">
         <v>95</v>
       </c>
-      <c r="G2" s="60"/>
-      <c r="H2" s="41">
+      <c r="G2" s="72"/>
+      <c r="H2" s="60">
         <v>46125</v>
       </c>
-      <c r="I2" s="44" t="s">
+      <c r="I2" s="62" t="s">
         <v>96</v>
       </c>
-      <c r="J2" s="45"/>
+      <c r="J2" s="55"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="51"/>
-      <c r="B3" s="52"/>
-      <c r="C3" s="53"/>
-      <c r="D3" s="61"/>
-      <c r="E3" s="53"/>
-      <c r="F3" s="61"/>
-      <c r="G3" s="53"/>
-      <c r="H3" s="42"/>
-      <c r="I3" s="42"/>
-      <c r="J3" s="46"/>
+      <c r="A3" s="66"/>
+      <c r="B3" s="67"/>
+      <c r="C3" s="68"/>
+      <c r="D3" s="73"/>
+      <c r="E3" s="68"/>
+      <c r="F3" s="73"/>
+      <c r="G3" s="68"/>
+      <c r="H3" s="61"/>
+      <c r="I3" s="61"/>
+      <c r="J3" s="56"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="54"/>
-      <c r="B4" s="55"/>
-      <c r="C4" s="56"/>
-      <c r="D4" s="62"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="62"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="43"/>
-      <c r="I4" s="43"/>
-      <c r="J4" s="47"/>
+      <c r="A4" s="128"/>
+      <c r="B4" s="129"/>
+      <c r="C4" s="130"/>
+      <c r="D4" s="131"/>
+      <c r="E4" s="130"/>
+      <c r="F4" s="131"/>
+      <c r="G4" s="130"/>
+      <c r="H4" s="126"/>
+      <c r="I4" s="126"/>
+      <c r="J4" s="127"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="7"/>
@@ -6286,19 +6286,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="63" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="50"/>
-      <c r="D1" s="57" t="s">
+      <c r="B1" s="64"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="58" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="58"/>
-      <c r="F1" s="57" t="s">
+      <c r="E1" s="59"/>
+      <c r="F1" s="58" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="58"/>
+      <c r="G1" s="59"/>
       <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
@@ -6310,48 +6310,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="51"/>
-      <c r="B2" s="52"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="59" t="s">
+      <c r="A2" s="66"/>
+      <c r="B2" s="67"/>
+      <c r="C2" s="68"/>
+      <c r="D2" s="71" t="s">
         <v>94</v>
       </c>
-      <c r="E2" s="60"/>
-      <c r="F2" s="59" t="s">
+      <c r="E2" s="72"/>
+      <c r="F2" s="71" t="s">
         <v>95</v>
       </c>
-      <c r="G2" s="60"/>
-      <c r="H2" s="41">
+      <c r="G2" s="72"/>
+      <c r="H2" s="60">
         <v>46122</v>
       </c>
-      <c r="I2" s="44" t="s">
+      <c r="I2" s="62" t="s">
         <v>120</v>
       </c>
-      <c r="J2" s="45"/>
+      <c r="J2" s="55"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="51"/>
-      <c r="B3" s="52"/>
-      <c r="C3" s="53"/>
-      <c r="D3" s="61"/>
-      <c r="E3" s="53"/>
-      <c r="F3" s="61"/>
-      <c r="G3" s="53"/>
-      <c r="H3" s="42"/>
-      <c r="I3" s="42"/>
-      <c r="J3" s="46"/>
+      <c r="A3" s="66"/>
+      <c r="B3" s="67"/>
+      <c r="C3" s="68"/>
+      <c r="D3" s="73"/>
+      <c r="E3" s="68"/>
+      <c r="F3" s="73"/>
+      <c r="G3" s="68"/>
+      <c r="H3" s="61"/>
+      <c r="I3" s="61"/>
+      <c r="J3" s="56"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="54"/>
-      <c r="B4" s="55"/>
-      <c r="C4" s="56"/>
-      <c r="D4" s="62"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="62"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="43"/>
-      <c r="I4" s="43"/>
-      <c r="J4" s="47"/>
+      <c r="A4" s="128"/>
+      <c r="B4" s="129"/>
+      <c r="C4" s="130"/>
+      <c r="D4" s="131"/>
+      <c r="E4" s="130"/>
+      <c r="F4" s="131"/>
+      <c r="G4" s="130"/>
+      <c r="H4" s="126"/>
+      <c r="I4" s="126"/>
+      <c r="J4" s="127"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="7"/>
@@ -7701,19 +7701,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="63" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="50"/>
-      <c r="D1" s="57" t="s">
+      <c r="B1" s="64"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="58" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="58"/>
-      <c r="F1" s="57" t="s">
+      <c r="E1" s="59"/>
+      <c r="F1" s="58" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="58"/>
+      <c r="G1" s="59"/>
       <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
@@ -7725,190 +7725,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="51"/>
-      <c r="B2" s="52"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="59" t="s">
+      <c r="A2" s="66"/>
+      <c r="B2" s="67"/>
+      <c r="C2" s="68"/>
+      <c r="D2" s="71" t="s">
         <v>94</v>
       </c>
-      <c r="E2" s="60"/>
-      <c r="F2" s="59" t="s">
+      <c r="E2" s="72"/>
+      <c r="F2" s="71" t="s">
         <v>95</v>
       </c>
-      <c r="G2" s="60"/>
-      <c r="H2" s="41">
+      <c r="G2" s="72"/>
+      <c r="H2" s="60">
         <v>46121</v>
       </c>
-      <c r="I2" s="44" t="s">
+      <c r="I2" s="62" t="s">
         <v>96</v>
       </c>
-      <c r="J2" s="45"/>
+      <c r="J2" s="55"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="51"/>
-      <c r="B3" s="52"/>
-      <c r="C3" s="53"/>
-      <c r="D3" s="61"/>
-      <c r="E3" s="53"/>
-      <c r="F3" s="61"/>
-      <c r="G3" s="53"/>
-      <c r="H3" s="42"/>
-      <c r="I3" s="42"/>
-      <c r="J3" s="46"/>
+      <c r="A3" s="66"/>
+      <c r="B3" s="67"/>
+      <c r="C3" s="68"/>
+      <c r="D3" s="73"/>
+      <c r="E3" s="68"/>
+      <c r="F3" s="73"/>
+      <c r="G3" s="68"/>
+      <c r="H3" s="61"/>
+      <c r="I3" s="61"/>
+      <c r="J3" s="56"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="51"/>
-      <c r="B4" s="52"/>
-      <c r="C4" s="53"/>
-      <c r="D4" s="61"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="61"/>
-      <c r="G4" s="53"/>
-      <c r="H4" s="42"/>
-      <c r="I4" s="42"/>
-      <c r="J4" s="46"/>
+      <c r="A4" s="66"/>
+      <c r="B4" s="67"/>
+      <c r="C4" s="68"/>
+      <c r="D4" s="73"/>
+      <c r="E4" s="68"/>
+      <c r="F4" s="73"/>
+      <c r="G4" s="68"/>
+      <c r="H4" s="61"/>
+      <c r="I4" s="61"/>
+      <c r="J4" s="56"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="116" t="s">
+      <c r="A5" s="69" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="117"/>
-      <c r="C5" s="58"/>
-      <c r="D5" s="119" t="s">
+      <c r="B5" s="70"/>
+      <c r="C5" s="59"/>
+      <c r="D5" s="74" t="s">
         <v>109</v>
       </c>
-      <c r="E5" s="117"/>
-      <c r="F5" s="117"/>
-      <c r="G5" s="117"/>
-      <c r="H5" s="117"/>
-      <c r="I5" s="117"/>
-      <c r="J5" s="120"/>
+      <c r="E5" s="70"/>
+      <c r="F5" s="70"/>
+      <c r="G5" s="70"/>
+      <c r="H5" s="70"/>
+      <c r="I5" s="70"/>
+      <c r="J5" s="75"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="118" t="s">
+      <c r="A6" s="54" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="64"/>
-      <c r="C6" s="64"/>
-      <c r="D6" s="64"/>
-      <c r="E6" s="64"/>
-      <c r="F6" s="64"/>
-      <c r="G6" s="64"/>
-      <c r="H6" s="64"/>
-      <c r="I6" s="64"/>
-      <c r="J6" s="112"/>
+      <c r="B6" s="45"/>
+      <c r="C6" s="45"/>
+      <c r="D6" s="45"/>
+      <c r="E6" s="45"/>
+      <c r="F6" s="45"/>
+      <c r="G6" s="45"/>
+      <c r="H6" s="45"/>
+      <c r="I6" s="45"/>
+      <c r="J6" s="46"/>
     </row>
     <row r="7" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A7" s="121"/>
-      <c r="B7" s="122"/>
-      <c r="C7" s="122"/>
-      <c r="D7" s="122"/>
-      <c r="E7" s="122"/>
-      <c r="F7" s="122"/>
-      <c r="G7" s="122"/>
-      <c r="H7" s="122"/>
-      <c r="I7" s="122"/>
-      <c r="J7" s="123"/>
+      <c r="A7" s="76"/>
+      <c r="B7" s="77"/>
+      <c r="C7" s="77"/>
+      <c r="D7" s="77"/>
+      <c r="E7" s="77"/>
+      <c r="F7" s="77"/>
+      <c r="G7" s="77"/>
+      <c r="H7" s="77"/>
+      <c r="I7" s="77"/>
+      <c r="J7" s="78"/>
     </row>
     <row r="8" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A8" s="51"/>
-      <c r="B8" s="52"/>
-      <c r="C8" s="52"/>
-      <c r="D8" s="52"/>
-      <c r="E8" s="52"/>
-      <c r="F8" s="52"/>
-      <c r="G8" s="52"/>
-      <c r="H8" s="52"/>
-      <c r="I8" s="52"/>
-      <c r="J8" s="124"/>
+      <c r="A8" s="66"/>
+      <c r="B8" s="67"/>
+      <c r="C8" s="67"/>
+      <c r="D8" s="67"/>
+      <c r="E8" s="67"/>
+      <c r="F8" s="67"/>
+      <c r="G8" s="67"/>
+      <c r="H8" s="67"/>
+      <c r="I8" s="67"/>
+      <c r="J8" s="79"/>
     </row>
     <row r="9" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A9" s="51"/>
-      <c r="B9" s="52"/>
-      <c r="C9" s="52"/>
-      <c r="D9" s="52"/>
-      <c r="E9" s="52"/>
-      <c r="F9" s="52"/>
-      <c r="G9" s="52"/>
-      <c r="H9" s="52"/>
-      <c r="I9" s="52"/>
-      <c r="J9" s="124"/>
+      <c r="A9" s="66"/>
+      <c r="B9" s="67"/>
+      <c r="C9" s="67"/>
+      <c r="D9" s="67"/>
+      <c r="E9" s="67"/>
+      <c r="F9" s="67"/>
+      <c r="G9" s="67"/>
+      <c r="H9" s="67"/>
+      <c r="I9" s="67"/>
+      <c r="J9" s="79"/>
     </row>
     <row r="10" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A10" s="51"/>
-      <c r="B10" s="52"/>
-      <c r="C10" s="52"/>
-      <c r="D10" s="52"/>
-      <c r="E10" s="52"/>
-      <c r="F10" s="52"/>
-      <c r="G10" s="52"/>
-      <c r="H10" s="52"/>
-      <c r="I10" s="52"/>
-      <c r="J10" s="124"/>
+      <c r="A10" s="66"/>
+      <c r="B10" s="67"/>
+      <c r="C10" s="67"/>
+      <c r="D10" s="67"/>
+      <c r="E10" s="67"/>
+      <c r="F10" s="67"/>
+      <c r="G10" s="67"/>
+      <c r="H10" s="67"/>
+      <c r="I10" s="67"/>
+      <c r="J10" s="79"/>
     </row>
     <row r="11" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A11" s="51"/>
-      <c r="B11" s="52"/>
-      <c r="C11" s="52"/>
-      <c r="D11" s="52"/>
-      <c r="E11" s="52"/>
-      <c r="F11" s="52"/>
-      <c r="G11" s="52"/>
-      <c r="H11" s="52"/>
-      <c r="I11" s="52"/>
-      <c r="J11" s="124"/>
+      <c r="A11" s="66"/>
+      <c r="B11" s="67"/>
+      <c r="C11" s="67"/>
+      <c r="D11" s="67"/>
+      <c r="E11" s="67"/>
+      <c r="F11" s="67"/>
+      <c r="G11" s="67"/>
+      <c r="H11" s="67"/>
+      <c r="I11" s="67"/>
+      <c r="J11" s="79"/>
     </row>
     <row r="12" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A12" s="51"/>
-      <c r="B12" s="52"/>
-      <c r="C12" s="52"/>
-      <c r="D12" s="52"/>
-      <c r="E12" s="52"/>
-      <c r="F12" s="52"/>
-      <c r="G12" s="52"/>
-      <c r="H12" s="52"/>
-      <c r="I12" s="52"/>
-      <c r="J12" s="124"/>
+      <c r="A12" s="66"/>
+      <c r="B12" s="67"/>
+      <c r="C12" s="67"/>
+      <c r="D12" s="67"/>
+      <c r="E12" s="67"/>
+      <c r="F12" s="67"/>
+      <c r="G12" s="67"/>
+      <c r="H12" s="67"/>
+      <c r="I12" s="67"/>
+      <c r="J12" s="79"/>
     </row>
     <row r="13" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A13" s="51"/>
-      <c r="B13" s="52"/>
-      <c r="C13" s="52"/>
-      <c r="D13" s="52"/>
-      <c r="E13" s="52"/>
-      <c r="F13" s="52"/>
-      <c r="G13" s="52"/>
-      <c r="H13" s="52"/>
-      <c r="I13" s="52"/>
-      <c r="J13" s="124"/>
+      <c r="A13" s="66"/>
+      <c r="B13" s="67"/>
+      <c r="C13" s="67"/>
+      <c r="D13" s="67"/>
+      <c r="E13" s="67"/>
+      <c r="F13" s="67"/>
+      <c r="G13" s="67"/>
+      <c r="H13" s="67"/>
+      <c r="I13" s="67"/>
+      <c r="J13" s="79"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="118" t="s">
+      <c r="A14" s="54" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="64"/>
-      <c r="C14" s="64"/>
-      <c r="D14" s="64"/>
-      <c r="E14" s="64"/>
-      <c r="F14" s="64"/>
-      <c r="G14" s="64"/>
-      <c r="H14" s="64"/>
-      <c r="I14" s="64"/>
-      <c r="J14" s="112"/>
+      <c r="B14" s="45"/>
+      <c r="C14" s="45"/>
+      <c r="D14" s="45"/>
+      <c r="E14" s="45"/>
+      <c r="F14" s="45"/>
+      <c r="G14" s="45"/>
+      <c r="H14" s="45"/>
+      <c r="I14" s="45"/>
+      <c r="J14" s="46"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="118" t="s">
+      <c r="A15" s="54" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="64"/>
-      <c r="C15" s="65"/>
-      <c r="D15" s="111" t="s">
+      <c r="B15" s="45"/>
+      <c r="C15" s="51"/>
+      <c r="D15" s="44" t="s">
         <v>73</v>
       </c>
-      <c r="E15" s="64"/>
-      <c r="F15" s="64"/>
-      <c r="G15" s="64"/>
-      <c r="H15" s="65"/>
+      <c r="E15" s="45"/>
+      <c r="F15" s="45"/>
+      <c r="G15" s="45"/>
+      <c r="H15" s="51"/>
       <c r="I15" s="14" t="s">
         <v>26</v>
       </c>
@@ -7917,11 +7917,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="118" t="s">
+      <c r="A16" s="54" t="s">
         <v>27</v>
       </c>
-      <c r="B16" s="64"/>
-      <c r="C16" s="65"/>
+      <c r="B16" s="45"/>
+      <c r="C16" s="51"/>
       <c r="D16" s="14" t="s">
         <v>28</v>
       </c>
@@ -7934,18 +7934,18 @@
       <c r="G16" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="H16" s="125" t="s">
+      <c r="H16" s="57" t="s">
         <v>18</v>
       </c>
-      <c r="I16" s="64"/>
-      <c r="J16" s="112"/>
+      <c r="I16" s="45"/>
+      <c r="J16" s="46"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="113" t="s">
+      <c r="A17" s="50" t="s">
         <v>75</v>
       </c>
-      <c r="B17" s="64"/>
-      <c r="C17" s="65"/>
+      <c r="B17" s="45"/>
+      <c r="C17" s="51"/>
       <c r="D17" s="16" t="s">
         <v>97</v>
       </c>
@@ -7956,18 +7956,18 @@
         <v>87</v>
       </c>
       <c r="G17" s="17"/>
-      <c r="H17" s="111" t="s">
+      <c r="H17" s="44" t="s">
         <v>90</v>
       </c>
-      <c r="I17" s="64"/>
-      <c r="J17" s="112"/>
+      <c r="I17" s="45"/>
+      <c r="J17" s="46"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="113" t="s">
+      <c r="A18" s="50" t="s">
         <v>76</v>
       </c>
-      <c r="B18" s="64"/>
-      <c r="C18" s="65"/>
+      <c r="B18" s="45"/>
+      <c r="C18" s="51"/>
       <c r="D18" s="16" t="s">
         <v>98</v>
       </c>
@@ -7978,18 +7978,18 @@
         <v>104</v>
       </c>
       <c r="G18" s="17"/>
-      <c r="H18" s="111" t="s">
+      <c r="H18" s="44" t="s">
         <v>106</v>
       </c>
-      <c r="I18" s="64"/>
-      <c r="J18" s="112"/>
+      <c r="I18" s="45"/>
+      <c r="J18" s="46"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="113" t="s">
+      <c r="A19" s="50" t="s">
         <v>77</v>
       </c>
-      <c r="B19" s="64"/>
-      <c r="C19" s="65"/>
+      <c r="B19" s="45"/>
+      <c r="C19" s="51"/>
       <c r="D19" s="16" t="s">
         <v>99</v>
       </c>
@@ -8000,18 +8000,18 @@
         <v>88</v>
       </c>
       <c r="G19" s="17"/>
-      <c r="H19" s="111" t="s">
+      <c r="H19" s="44" t="s">
         <v>91</v>
       </c>
-      <c r="I19" s="64"/>
-      <c r="J19" s="112"/>
+      <c r="I19" s="45"/>
+      <c r="J19" s="46"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="113" t="s">
+      <c r="A20" s="50" t="s">
         <v>78</v>
       </c>
-      <c r="B20" s="64"/>
-      <c r="C20" s="65"/>
+      <c r="B20" s="45"/>
+      <c r="C20" s="51"/>
       <c r="D20" s="16" t="s">
         <v>100</v>
       </c>
@@ -8022,18 +8022,18 @@
         <v>119</v>
       </c>
       <c r="G20" s="17"/>
-      <c r="H20" s="111" t="s">
+      <c r="H20" s="44" t="s">
         <v>107</v>
       </c>
-      <c r="I20" s="64"/>
-      <c r="J20" s="112"/>
+      <c r="I20" s="45"/>
+      <c r="J20" s="46"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="113" t="s">
+      <c r="A21" s="50" t="s">
         <v>79</v>
       </c>
-      <c r="B21" s="64"/>
-      <c r="C21" s="65"/>
+      <c r="B21" s="45"/>
+      <c r="C21" s="51"/>
       <c r="D21" s="16" t="s">
         <v>101</v>
       </c>
@@ -8044,18 +8044,18 @@
         <v>103</v>
       </c>
       <c r="G21" s="17"/>
-      <c r="H21" s="111" t="s">
+      <c r="H21" s="44" t="s">
         <v>108</v>
       </c>
-      <c r="I21" s="64"/>
-      <c r="J21" s="112"/>
+      <c r="I21" s="45"/>
+      <c r="J21" s="46"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="113" t="s">
+      <c r="A22" s="50" t="s">
         <v>80</v>
       </c>
-      <c r="B22" s="114"/>
-      <c r="C22" s="115"/>
+      <c r="B22" s="52"/>
+      <c r="C22" s="53"/>
       <c r="D22" s="16" t="s">
         <v>102</v>
       </c>
@@ -8066,18 +8066,18 @@
         <v>89</v>
       </c>
       <c r="G22" s="17"/>
-      <c r="H22" s="111" t="s">
+      <c r="H22" s="44" t="s">
         <v>92</v>
       </c>
-      <c r="I22" s="64"/>
-      <c r="J22" s="112"/>
+      <c r="I22" s="45"/>
+      <c r="J22" s="46"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="113" t="s">
+      <c r="A23" s="50" t="s">
         <v>81</v>
       </c>
-      <c r="B23" s="114"/>
-      <c r="C23" s="115"/>
+      <c r="B23" s="52"/>
+      <c r="C23" s="53"/>
       <c r="D23" s="16" t="s">
         <v>83</v>
       </c>
@@ -8088,18 +8088,18 @@
       <c r="G23" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="H23" s="111" t="s">
+      <c r="H23" s="44" t="s">
         <v>93</v>
       </c>
-      <c r="I23" s="64"/>
-      <c r="J23" s="112"/>
+      <c r="I23" s="45"/>
+      <c r="J23" s="46"/>
     </row>
     <row r="24" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A24" s="126" t="s">
+      <c r="A24" s="41" t="s">
         <v>82</v>
       </c>
-      <c r="B24" s="127"/>
-      <c r="C24" s="128"/>
+      <c r="B24" s="42"/>
+      <c r="C24" s="43"/>
       <c r="D24" s="18" t="s">
         <v>125</v>
       </c>
@@ -8110,11 +8110,11 @@
       <c r="G24" s="19" t="s">
         <v>126</v>
       </c>
-      <c r="H24" s="129" t="s">
+      <c r="H24" s="47" t="s">
         <v>124</v>
       </c>
-      <c r="I24" s="130"/>
-      <c r="J24" s="131"/>
+      <c r="I24" s="48"/>
+      <c r="J24" s="49"/>
     </row>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="26" spans="1:10" ht="12.75" customHeight="1"/>
@@ -9095,6 +9095,23 @@
     <row r="1001" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="33">
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A7:J13"/>
     <mergeCell ref="A24:C24"/>
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="H18:J18"/>
@@ -9106,28 +9123,11 @@
     <mergeCell ref="A20:C20"/>
     <mergeCell ref="A23:C23"/>
     <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="I2:I4"/>
     <mergeCell ref="H21:J21"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
     <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A16:C16"/>
     <mergeCell ref="A17:C17"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A7:J13"/>
-    <mergeCell ref="A14:J14"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -9150,19 +9150,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="63" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="50"/>
-      <c r="D1" s="57" t="s">
+      <c r="B1" s="64"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="58" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="58"/>
-      <c r="F1" s="57" t="s">
+      <c r="E1" s="59"/>
+      <c r="F1" s="58" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="58"/>
+      <c r="G1" s="59"/>
       <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
@@ -9174,190 +9174,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="51"/>
-      <c r="B2" s="52"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="59" t="s">
+      <c r="A2" s="66"/>
+      <c r="B2" s="67"/>
+      <c r="C2" s="68"/>
+      <c r="D2" s="71" t="s">
         <v>94</v>
       </c>
-      <c r="E2" s="60"/>
-      <c r="F2" s="59" t="s">
+      <c r="E2" s="72"/>
+      <c r="F2" s="71" t="s">
         <v>95</v>
       </c>
-      <c r="G2" s="60"/>
-      <c r="H2" s="41">
+      <c r="G2" s="72"/>
+      <c r="H2" s="60">
         <v>46121</v>
       </c>
-      <c r="I2" s="44" t="s">
+      <c r="I2" s="62" t="s">
         <v>96</v>
       </c>
-      <c r="J2" s="45"/>
+      <c r="J2" s="55"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="51"/>
-      <c r="B3" s="52"/>
-      <c r="C3" s="53"/>
-      <c r="D3" s="61"/>
-      <c r="E3" s="53"/>
-      <c r="F3" s="61"/>
-      <c r="G3" s="53"/>
-      <c r="H3" s="42"/>
-      <c r="I3" s="42"/>
-      <c r="J3" s="46"/>
+      <c r="A3" s="66"/>
+      <c r="B3" s="67"/>
+      <c r="C3" s="68"/>
+      <c r="D3" s="73"/>
+      <c r="E3" s="68"/>
+      <c r="F3" s="73"/>
+      <c r="G3" s="68"/>
+      <c r="H3" s="61"/>
+      <c r="I3" s="61"/>
+      <c r="J3" s="56"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="51"/>
-      <c r="B4" s="52"/>
-      <c r="C4" s="53"/>
-      <c r="D4" s="61"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="61"/>
-      <c r="G4" s="53"/>
-      <c r="H4" s="42"/>
-      <c r="I4" s="42"/>
-      <c r="J4" s="46"/>
+      <c r="A4" s="66"/>
+      <c r="B4" s="67"/>
+      <c r="C4" s="68"/>
+      <c r="D4" s="73"/>
+      <c r="E4" s="68"/>
+      <c r="F4" s="73"/>
+      <c r="G4" s="68"/>
+      <c r="H4" s="61"/>
+      <c r="I4" s="61"/>
+      <c r="J4" s="56"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="116" t="s">
+      <c r="A5" s="69" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="117"/>
-      <c r="C5" s="58"/>
-      <c r="D5" s="119" t="s">
+      <c r="B5" s="70"/>
+      <c r="C5" s="59"/>
+      <c r="D5" s="74" t="s">
         <v>110</v>
       </c>
-      <c r="E5" s="117"/>
-      <c r="F5" s="117"/>
-      <c r="G5" s="117"/>
-      <c r="H5" s="117"/>
-      <c r="I5" s="117"/>
-      <c r="J5" s="120"/>
+      <c r="E5" s="70"/>
+      <c r="F5" s="70"/>
+      <c r="G5" s="70"/>
+      <c r="H5" s="70"/>
+      <c r="I5" s="70"/>
+      <c r="J5" s="75"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="118" t="s">
+      <c r="A6" s="54" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="64"/>
-      <c r="C6" s="64"/>
-      <c r="D6" s="64"/>
-      <c r="E6" s="64"/>
-      <c r="F6" s="64"/>
-      <c r="G6" s="64"/>
-      <c r="H6" s="64"/>
-      <c r="I6" s="64"/>
-      <c r="J6" s="112"/>
+      <c r="B6" s="45"/>
+      <c r="C6" s="45"/>
+      <c r="D6" s="45"/>
+      <c r="E6" s="45"/>
+      <c r="F6" s="45"/>
+      <c r="G6" s="45"/>
+      <c r="H6" s="45"/>
+      <c r="I6" s="45"/>
+      <c r="J6" s="46"/>
     </row>
     <row r="7" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A7" s="121"/>
-      <c r="B7" s="122"/>
-      <c r="C7" s="122"/>
-      <c r="D7" s="122"/>
-      <c r="E7" s="122"/>
-      <c r="F7" s="122"/>
-      <c r="G7" s="122"/>
-      <c r="H7" s="122"/>
-      <c r="I7" s="122"/>
-      <c r="J7" s="123"/>
+      <c r="A7" s="76"/>
+      <c r="B7" s="77"/>
+      <c r="C7" s="77"/>
+      <c r="D7" s="77"/>
+      <c r="E7" s="77"/>
+      <c r="F7" s="77"/>
+      <c r="G7" s="77"/>
+      <c r="H7" s="77"/>
+      <c r="I7" s="77"/>
+      <c r="J7" s="78"/>
     </row>
     <row r="8" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A8" s="51"/>
-      <c r="B8" s="52"/>
-      <c r="C8" s="52"/>
-      <c r="D8" s="52"/>
-      <c r="E8" s="52"/>
-      <c r="F8" s="52"/>
-      <c r="G8" s="52"/>
-      <c r="H8" s="52"/>
-      <c r="I8" s="52"/>
-      <c r="J8" s="124"/>
+      <c r="A8" s="66"/>
+      <c r="B8" s="67"/>
+      <c r="C8" s="67"/>
+      <c r="D8" s="67"/>
+      <c r="E8" s="67"/>
+      <c r="F8" s="67"/>
+      <c r="G8" s="67"/>
+      <c r="H8" s="67"/>
+      <c r="I8" s="67"/>
+      <c r="J8" s="79"/>
     </row>
     <row r="9" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A9" s="51"/>
-      <c r="B9" s="52"/>
-      <c r="C9" s="52"/>
-      <c r="D9" s="52"/>
-      <c r="E9" s="52"/>
-      <c r="F9" s="52"/>
-      <c r="G9" s="52"/>
-      <c r="H9" s="52"/>
-      <c r="I9" s="52"/>
-      <c r="J9" s="124"/>
+      <c r="A9" s="66"/>
+      <c r="B9" s="67"/>
+      <c r="C9" s="67"/>
+      <c r="D9" s="67"/>
+      <c r="E9" s="67"/>
+      <c r="F9" s="67"/>
+      <c r="G9" s="67"/>
+      <c r="H9" s="67"/>
+      <c r="I9" s="67"/>
+      <c r="J9" s="79"/>
     </row>
     <row r="10" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A10" s="51"/>
-      <c r="B10" s="52"/>
-      <c r="C10" s="52"/>
-      <c r="D10" s="52"/>
-      <c r="E10" s="52"/>
-      <c r="F10" s="52"/>
-      <c r="G10" s="52"/>
-      <c r="H10" s="52"/>
-      <c r="I10" s="52"/>
-      <c r="J10" s="124"/>
+      <c r="A10" s="66"/>
+      <c r="B10" s="67"/>
+      <c r="C10" s="67"/>
+      <c r="D10" s="67"/>
+      <c r="E10" s="67"/>
+      <c r="F10" s="67"/>
+      <c r="G10" s="67"/>
+      <c r="H10" s="67"/>
+      <c r="I10" s="67"/>
+      <c r="J10" s="79"/>
     </row>
     <row r="11" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A11" s="51"/>
-      <c r="B11" s="52"/>
-      <c r="C11" s="52"/>
-      <c r="D11" s="52"/>
-      <c r="E11" s="52"/>
-      <c r="F11" s="52"/>
-      <c r="G11" s="52"/>
-      <c r="H11" s="52"/>
-      <c r="I11" s="52"/>
-      <c r="J11" s="124"/>
+      <c r="A11" s="66"/>
+      <c r="B11" s="67"/>
+      <c r="C11" s="67"/>
+      <c r="D11" s="67"/>
+      <c r="E11" s="67"/>
+      <c r="F11" s="67"/>
+      <c r="G11" s="67"/>
+      <c r="H11" s="67"/>
+      <c r="I11" s="67"/>
+      <c r="J11" s="79"/>
     </row>
     <row r="12" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A12" s="51"/>
-      <c r="B12" s="52"/>
-      <c r="C12" s="52"/>
-      <c r="D12" s="52"/>
-      <c r="E12" s="52"/>
-      <c r="F12" s="52"/>
-      <c r="G12" s="52"/>
-      <c r="H12" s="52"/>
-      <c r="I12" s="52"/>
-      <c r="J12" s="124"/>
+      <c r="A12" s="66"/>
+      <c r="B12" s="67"/>
+      <c r="C12" s="67"/>
+      <c r="D12" s="67"/>
+      <c r="E12" s="67"/>
+      <c r="F12" s="67"/>
+      <c r="G12" s="67"/>
+      <c r="H12" s="67"/>
+      <c r="I12" s="67"/>
+      <c r="J12" s="79"/>
     </row>
     <row r="13" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A13" s="51"/>
-      <c r="B13" s="52"/>
-      <c r="C13" s="52"/>
-      <c r="D13" s="52"/>
-      <c r="E13" s="52"/>
-      <c r="F13" s="52"/>
-      <c r="G13" s="52"/>
-      <c r="H13" s="52"/>
-      <c r="I13" s="52"/>
-      <c r="J13" s="124"/>
+      <c r="A13" s="66"/>
+      <c r="B13" s="67"/>
+      <c r="C13" s="67"/>
+      <c r="D13" s="67"/>
+      <c r="E13" s="67"/>
+      <c r="F13" s="67"/>
+      <c r="G13" s="67"/>
+      <c r="H13" s="67"/>
+      <c r="I13" s="67"/>
+      <c r="J13" s="79"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="118" t="s">
+      <c r="A14" s="54" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="64"/>
-      <c r="C14" s="64"/>
-      <c r="D14" s="64"/>
-      <c r="E14" s="64"/>
-      <c r="F14" s="64"/>
-      <c r="G14" s="64"/>
-      <c r="H14" s="64"/>
-      <c r="I14" s="64"/>
-      <c r="J14" s="112"/>
+      <c r="B14" s="45"/>
+      <c r="C14" s="45"/>
+      <c r="D14" s="45"/>
+      <c r="E14" s="45"/>
+      <c r="F14" s="45"/>
+      <c r="G14" s="45"/>
+      <c r="H14" s="45"/>
+      <c r="I14" s="45"/>
+      <c r="J14" s="46"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="118" t="s">
+      <c r="A15" s="54" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="64"/>
-      <c r="C15" s="65"/>
-      <c r="D15" s="111" t="s">
+      <c r="B15" s="45"/>
+      <c r="C15" s="51"/>
+      <c r="D15" s="44" t="s">
         <v>113</v>
       </c>
-      <c r="E15" s="64"/>
-      <c r="F15" s="64"/>
-      <c r="G15" s="64"/>
-      <c r="H15" s="65"/>
+      <c r="E15" s="45"/>
+      <c r="F15" s="45"/>
+      <c r="G15" s="45"/>
+      <c r="H15" s="51"/>
       <c r="I15" s="14" t="s">
         <v>26</v>
       </c>
@@ -9366,11 +9366,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="118" t="s">
+      <c r="A16" s="54" t="s">
         <v>27</v>
       </c>
-      <c r="B16" s="64"/>
-      <c r="C16" s="65"/>
+      <c r="B16" s="45"/>
+      <c r="C16" s="51"/>
       <c r="D16" s="14" t="s">
         <v>28</v>
       </c>
@@ -9383,18 +9383,18 @@
       <c r="G16" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="H16" s="125" t="s">
+      <c r="H16" s="57" t="s">
         <v>18</v>
       </c>
-      <c r="I16" s="64"/>
-      <c r="J16" s="112"/>
+      <c r="I16" s="45"/>
+      <c r="J16" s="46"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="113" t="s">
+      <c r="A17" s="50" t="s">
         <v>75</v>
       </c>
-      <c r="B17" s="64"/>
-      <c r="C17" s="65"/>
+      <c r="B17" s="45"/>
+      <c r="C17" s="51"/>
       <c r="D17" s="40" t="s">
         <v>111</v>
       </c>
@@ -9405,23 +9405,23 @@
       <c r="G17" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="H17" s="111" t="s">
+      <c r="H17" s="44" t="s">
         <v>118</v>
       </c>
-      <c r="I17" s="64"/>
-      <c r="J17" s="112"/>
+      <c r="I17" s="45"/>
+      <c r="J17" s="46"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A18" s="126"/>
-      <c r="B18" s="127"/>
-      <c r="C18" s="128"/>
+      <c r="A18" s="41"/>
+      <c r="B18" s="42"/>
+      <c r="C18" s="43"/>
       <c r="D18" s="18"/>
       <c r="E18" s="18"/>
       <c r="F18" s="19"/>
       <c r="G18" s="19"/>
-      <c r="H18" s="129"/>
-      <c r="I18" s="130"/>
-      <c r="J18" s="131"/>
+      <c r="H18" s="47"/>
+      <c r="I18" s="48"/>
+      <c r="J18" s="49"/>
     </row>
     <row r="19" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="20" spans="1:10" ht="12.75" customHeight="1"/>
@@ -10402,6 +10402,12 @@
     <row r="995" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
     <mergeCell ref="A14:J14"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="A7:J13"/>
@@ -10417,12 +10423,6 @@
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -10445,19 +10445,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="63" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="50"/>
-      <c r="D1" s="57" t="s">
+      <c r="B1" s="64"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="58" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="58"/>
-      <c r="F1" s="57" t="s">
+      <c r="E1" s="59"/>
+      <c r="F1" s="58" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="58"/>
+      <c r="G1" s="59"/>
       <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
@@ -10469,190 +10469,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="51"/>
-      <c r="B2" s="52"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="59" t="s">
+      <c r="A2" s="66"/>
+      <c r="B2" s="67"/>
+      <c r="C2" s="68"/>
+      <c r="D2" s="71" t="s">
         <v>94</v>
       </c>
-      <c r="E2" s="60"/>
-      <c r="F2" s="59" t="s">
+      <c r="E2" s="72"/>
+      <c r="F2" s="71" t="s">
         <v>95</v>
       </c>
-      <c r="G2" s="60"/>
-      <c r="H2" s="41">
+      <c r="G2" s="72"/>
+      <c r="H2" s="60">
         <v>46121</v>
       </c>
-      <c r="I2" s="44" t="s">
+      <c r="I2" s="62" t="s">
         <v>96</v>
       </c>
-      <c r="J2" s="45"/>
+      <c r="J2" s="55"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="51"/>
-      <c r="B3" s="52"/>
-      <c r="C3" s="53"/>
-      <c r="D3" s="61"/>
-      <c r="E3" s="53"/>
-      <c r="F3" s="61"/>
-      <c r="G3" s="53"/>
-      <c r="H3" s="42"/>
-      <c r="I3" s="42"/>
-      <c r="J3" s="46"/>
+      <c r="A3" s="66"/>
+      <c r="B3" s="67"/>
+      <c r="C3" s="68"/>
+      <c r="D3" s="73"/>
+      <c r="E3" s="68"/>
+      <c r="F3" s="73"/>
+      <c r="G3" s="68"/>
+      <c r="H3" s="61"/>
+      <c r="I3" s="61"/>
+      <c r="J3" s="56"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="51"/>
-      <c r="B4" s="52"/>
-      <c r="C4" s="53"/>
-      <c r="D4" s="61"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="61"/>
-      <c r="G4" s="53"/>
-      <c r="H4" s="42"/>
-      <c r="I4" s="42"/>
-      <c r="J4" s="46"/>
+      <c r="A4" s="66"/>
+      <c r="B4" s="67"/>
+      <c r="C4" s="68"/>
+      <c r="D4" s="73"/>
+      <c r="E4" s="68"/>
+      <c r="F4" s="73"/>
+      <c r="G4" s="68"/>
+      <c r="H4" s="61"/>
+      <c r="I4" s="61"/>
+      <c r="J4" s="56"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="116" t="s">
+      <c r="A5" s="69" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="117"/>
-      <c r="C5" s="58"/>
-      <c r="D5" s="119" t="s">
+      <c r="B5" s="70"/>
+      <c r="C5" s="59"/>
+      <c r="D5" s="74" t="s">
         <v>110</v>
       </c>
-      <c r="E5" s="117"/>
-      <c r="F5" s="117"/>
-      <c r="G5" s="117"/>
-      <c r="H5" s="117"/>
-      <c r="I5" s="117"/>
-      <c r="J5" s="120"/>
+      <c r="E5" s="70"/>
+      <c r="F5" s="70"/>
+      <c r="G5" s="70"/>
+      <c r="H5" s="70"/>
+      <c r="I5" s="70"/>
+      <c r="J5" s="75"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="118" t="s">
+      <c r="A6" s="54" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="64"/>
-      <c r="C6" s="64"/>
-      <c r="D6" s="64"/>
-      <c r="E6" s="64"/>
-      <c r="F6" s="64"/>
-      <c r="G6" s="64"/>
-      <c r="H6" s="64"/>
-      <c r="I6" s="64"/>
-      <c r="J6" s="112"/>
+      <c r="B6" s="45"/>
+      <c r="C6" s="45"/>
+      <c r="D6" s="45"/>
+      <c r="E6" s="45"/>
+      <c r="F6" s="45"/>
+      <c r="G6" s="45"/>
+      <c r="H6" s="45"/>
+      <c r="I6" s="45"/>
+      <c r="J6" s="46"/>
     </row>
     <row r="7" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A7" s="121"/>
-      <c r="B7" s="122"/>
-      <c r="C7" s="122"/>
-      <c r="D7" s="122"/>
-      <c r="E7" s="122"/>
-      <c r="F7" s="122"/>
-      <c r="G7" s="122"/>
-      <c r="H7" s="122"/>
-      <c r="I7" s="122"/>
-      <c r="J7" s="123"/>
+      <c r="A7" s="76"/>
+      <c r="B7" s="77"/>
+      <c r="C7" s="77"/>
+      <c r="D7" s="77"/>
+      <c r="E7" s="77"/>
+      <c r="F7" s="77"/>
+      <c r="G7" s="77"/>
+      <c r="H7" s="77"/>
+      <c r="I7" s="77"/>
+      <c r="J7" s="78"/>
     </row>
     <row r="8" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A8" s="51"/>
-      <c r="B8" s="52"/>
-      <c r="C8" s="52"/>
-      <c r="D8" s="52"/>
-      <c r="E8" s="52"/>
-      <c r="F8" s="52"/>
-      <c r="G8" s="52"/>
-      <c r="H8" s="52"/>
-      <c r="I8" s="52"/>
-      <c r="J8" s="124"/>
+      <c r="A8" s="66"/>
+      <c r="B8" s="67"/>
+      <c r="C8" s="67"/>
+      <c r="D8" s="67"/>
+      <c r="E8" s="67"/>
+      <c r="F8" s="67"/>
+      <c r="G8" s="67"/>
+      <c r="H8" s="67"/>
+      <c r="I8" s="67"/>
+      <c r="J8" s="79"/>
     </row>
     <row r="9" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A9" s="51"/>
-      <c r="B9" s="52"/>
-      <c r="C9" s="52"/>
-      <c r="D9" s="52"/>
-      <c r="E9" s="52"/>
-      <c r="F9" s="52"/>
-      <c r="G9" s="52"/>
-      <c r="H9" s="52"/>
-      <c r="I9" s="52"/>
-      <c r="J9" s="124"/>
+      <c r="A9" s="66"/>
+      <c r="B9" s="67"/>
+      <c r="C9" s="67"/>
+      <c r="D9" s="67"/>
+      <c r="E9" s="67"/>
+      <c r="F9" s="67"/>
+      <c r="G9" s="67"/>
+      <c r="H9" s="67"/>
+      <c r="I9" s="67"/>
+      <c r="J9" s="79"/>
     </row>
     <row r="10" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A10" s="51"/>
-      <c r="B10" s="52"/>
-      <c r="C10" s="52"/>
-      <c r="D10" s="52"/>
-      <c r="E10" s="52"/>
-      <c r="F10" s="52"/>
-      <c r="G10" s="52"/>
-      <c r="H10" s="52"/>
-      <c r="I10" s="52"/>
-      <c r="J10" s="124"/>
+      <c r="A10" s="66"/>
+      <c r="B10" s="67"/>
+      <c r="C10" s="67"/>
+      <c r="D10" s="67"/>
+      <c r="E10" s="67"/>
+      <c r="F10" s="67"/>
+      <c r="G10" s="67"/>
+      <c r="H10" s="67"/>
+      <c r="I10" s="67"/>
+      <c r="J10" s="79"/>
     </row>
     <row r="11" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A11" s="51"/>
-      <c r="B11" s="52"/>
-      <c r="C11" s="52"/>
-      <c r="D11" s="52"/>
-      <c r="E11" s="52"/>
-      <c r="F11" s="52"/>
-      <c r="G11" s="52"/>
-      <c r="H11" s="52"/>
-      <c r="I11" s="52"/>
-      <c r="J11" s="124"/>
+      <c r="A11" s="66"/>
+      <c r="B11" s="67"/>
+      <c r="C11" s="67"/>
+      <c r="D11" s="67"/>
+      <c r="E11" s="67"/>
+      <c r="F11" s="67"/>
+      <c r="G11" s="67"/>
+      <c r="H11" s="67"/>
+      <c r="I11" s="67"/>
+      <c r="J11" s="79"/>
     </row>
     <row r="12" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A12" s="51"/>
-      <c r="B12" s="52"/>
-      <c r="C12" s="52"/>
-      <c r="D12" s="52"/>
-      <c r="E12" s="52"/>
-      <c r="F12" s="52"/>
-      <c r="G12" s="52"/>
-      <c r="H12" s="52"/>
-      <c r="I12" s="52"/>
-      <c r="J12" s="124"/>
+      <c r="A12" s="66"/>
+      <c r="B12" s="67"/>
+      <c r="C12" s="67"/>
+      <c r="D12" s="67"/>
+      <c r="E12" s="67"/>
+      <c r="F12" s="67"/>
+      <c r="G12" s="67"/>
+      <c r="H12" s="67"/>
+      <c r="I12" s="67"/>
+      <c r="J12" s="79"/>
     </row>
     <row r="13" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A13" s="51"/>
-      <c r="B13" s="52"/>
-      <c r="C13" s="52"/>
-      <c r="D13" s="52"/>
-      <c r="E13" s="52"/>
-      <c r="F13" s="52"/>
-      <c r="G13" s="52"/>
-      <c r="H13" s="52"/>
-      <c r="I13" s="52"/>
-      <c r="J13" s="124"/>
+      <c r="A13" s="66"/>
+      <c r="B13" s="67"/>
+      <c r="C13" s="67"/>
+      <c r="D13" s="67"/>
+      <c r="E13" s="67"/>
+      <c r="F13" s="67"/>
+      <c r="G13" s="67"/>
+      <c r="H13" s="67"/>
+      <c r="I13" s="67"/>
+      <c r="J13" s="79"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="118" t="s">
+      <c r="A14" s="54" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="64"/>
-      <c r="C14" s="64"/>
-      <c r="D14" s="64"/>
-      <c r="E14" s="64"/>
-      <c r="F14" s="64"/>
-      <c r="G14" s="64"/>
-      <c r="H14" s="64"/>
-      <c r="I14" s="64"/>
-      <c r="J14" s="112"/>
+      <c r="B14" s="45"/>
+      <c r="C14" s="45"/>
+      <c r="D14" s="45"/>
+      <c r="E14" s="45"/>
+      <c r="F14" s="45"/>
+      <c r="G14" s="45"/>
+      <c r="H14" s="45"/>
+      <c r="I14" s="45"/>
+      <c r="J14" s="46"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="118" t="s">
+      <c r="A15" s="54" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="64"/>
-      <c r="C15" s="65"/>
-      <c r="D15" s="111" t="s">
+      <c r="B15" s="45"/>
+      <c r="C15" s="51"/>
+      <c r="D15" s="44" t="s">
         <v>116</v>
       </c>
-      <c r="E15" s="64"/>
-      <c r="F15" s="64"/>
-      <c r="G15" s="64"/>
-      <c r="H15" s="65"/>
+      <c r="E15" s="45"/>
+      <c r="F15" s="45"/>
+      <c r="G15" s="45"/>
+      <c r="H15" s="51"/>
       <c r="I15" s="14" t="s">
         <v>26</v>
       </c>
@@ -10661,11 +10661,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="118" t="s">
+      <c r="A16" s="54" t="s">
         <v>27</v>
       </c>
-      <c r="B16" s="64"/>
-      <c r="C16" s="65"/>
+      <c r="B16" s="45"/>
+      <c r="C16" s="51"/>
       <c r="D16" s="14" t="s">
         <v>28</v>
       </c>
@@ -10678,18 +10678,18 @@
       <c r="G16" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="H16" s="125" t="s">
+      <c r="H16" s="57" t="s">
         <v>18</v>
       </c>
-      <c r="I16" s="64"/>
-      <c r="J16" s="112"/>
+      <c r="I16" s="45"/>
+      <c r="J16" s="46"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="113" t="s">
+      <c r="A17" s="50" t="s">
         <v>75</v>
       </c>
-      <c r="B17" s="64"/>
-      <c r="C17" s="65"/>
+      <c r="B17" s="45"/>
+      <c r="C17" s="51"/>
       <c r="D17" s="40" t="s">
         <v>114</v>
       </c>
@@ -10700,23 +10700,23 @@
       <c r="G17" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="H17" s="111" t="s">
+      <c r="H17" s="44" t="s">
         <v>115</v>
       </c>
-      <c r="I17" s="64"/>
-      <c r="J17" s="112"/>
+      <c r="I17" s="45"/>
+      <c r="J17" s="46"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A18" s="126"/>
-      <c r="B18" s="127"/>
-      <c r="C18" s="128"/>
+      <c r="A18" s="41"/>
+      <c r="B18" s="42"/>
+      <c r="C18" s="43"/>
       <c r="D18" s="18"/>
       <c r="E18" s="18"/>
       <c r="F18" s="19"/>
       <c r="G18" s="19"/>
-      <c r="H18" s="129"/>
-      <c r="I18" s="130"/>
-      <c r="J18" s="131"/>
+      <c r="H18" s="47"/>
+      <c r="I18" s="48"/>
+      <c r="J18" s="49"/>
     </row>
     <row r="19" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="20" spans="1:10" ht="12.75" customHeight="1"/>
@@ -11697,6 +11697,12 @@
     <row r="995" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
     <mergeCell ref="A14:J14"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="A7:J13"/>
@@ -11712,12 +11718,6 @@
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -11737,182 +11737,182 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="139" t="s">
+      <c r="A1" s="144" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="50"/>
-      <c r="G1" s="57" t="s">
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="58" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="117"/>
-      <c r="I1" s="117"/>
-      <c r="J1" s="58"/>
-      <c r="K1" s="57" t="s">
+      <c r="H1" s="70"/>
+      <c r="I1" s="70"/>
+      <c r="J1" s="59"/>
+      <c r="K1" s="58" t="s">
         <v>5</v>
       </c>
-      <c r="L1" s="117"/>
-      <c r="M1" s="117"/>
-      <c r="N1" s="58"/>
-      <c r="O1" s="57" t="s">
+      <c r="L1" s="70"/>
+      <c r="M1" s="70"/>
+      <c r="N1" s="59"/>
+      <c r="O1" s="58" t="s">
         <v>6</v>
       </c>
-      <c r="P1" s="58"/>
-      <c r="Q1" s="57" t="s">
+      <c r="P1" s="59"/>
+      <c r="Q1" s="58" t="s">
         <v>7</v>
       </c>
-      <c r="R1" s="58"/>
-      <c r="S1" s="57" t="s">
+      <c r="R1" s="59"/>
+      <c r="S1" s="58" t="s">
         <v>8</v>
       </c>
-      <c r="T1" s="120"/>
+      <c r="T1" s="75"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="51"/>
-      <c r="B2" s="52"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="59"/>
-      <c r="H2" s="122"/>
-      <c r="I2" s="122"/>
-      <c r="J2" s="60"/>
-      <c r="K2" s="59"/>
-      <c r="L2" s="122"/>
-      <c r="M2" s="122"/>
-      <c r="N2" s="60"/>
-      <c r="O2" s="59"/>
-      <c r="P2" s="60"/>
-      <c r="Q2" s="59"/>
-      <c r="R2" s="60"/>
-      <c r="S2" s="59"/>
-      <c r="T2" s="123"/>
+      <c r="A2" s="66"/>
+      <c r="B2" s="67"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="67"/>
+      <c r="E2" s="67"/>
+      <c r="F2" s="68"/>
+      <c r="G2" s="71"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
+      <c r="J2" s="72"/>
+      <c r="K2" s="71"/>
+      <c r="L2" s="77"/>
+      <c r="M2" s="77"/>
+      <c r="N2" s="72"/>
+      <c r="O2" s="71"/>
+      <c r="P2" s="72"/>
+      <c r="Q2" s="71"/>
+      <c r="R2" s="72"/>
+      <c r="S2" s="71"/>
+      <c r="T2" s="78"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="51"/>
-      <c r="B3" s="52"/>
-      <c r="C3" s="52"/>
-      <c r="D3" s="52"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="53"/>
-      <c r="G3" s="61"/>
-      <c r="H3" s="52"/>
-      <c r="I3" s="52"/>
-      <c r="J3" s="53"/>
-      <c r="K3" s="61"/>
-      <c r="L3" s="52"/>
-      <c r="M3" s="52"/>
-      <c r="N3" s="53"/>
-      <c r="O3" s="61"/>
-      <c r="P3" s="53"/>
-      <c r="Q3" s="61"/>
-      <c r="R3" s="53"/>
-      <c r="S3" s="61"/>
-      <c r="T3" s="124"/>
+      <c r="A3" s="66"/>
+      <c r="B3" s="67"/>
+      <c r="C3" s="67"/>
+      <c r="D3" s="67"/>
+      <c r="E3" s="67"/>
+      <c r="F3" s="68"/>
+      <c r="G3" s="73"/>
+      <c r="H3" s="67"/>
+      <c r="I3" s="67"/>
+      <c r="J3" s="68"/>
+      <c r="K3" s="73"/>
+      <c r="L3" s="67"/>
+      <c r="M3" s="67"/>
+      <c r="N3" s="68"/>
+      <c r="O3" s="73"/>
+      <c r="P3" s="68"/>
+      <c r="Q3" s="73"/>
+      <c r="R3" s="68"/>
+      <c r="S3" s="73"/>
+      <c r="T3" s="79"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="54"/>
-      <c r="B4" s="55"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="55"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="56"/>
-      <c r="G4" s="62"/>
-      <c r="H4" s="55"/>
-      <c r="I4" s="55"/>
-      <c r="J4" s="56"/>
-      <c r="K4" s="62"/>
-      <c r="L4" s="55"/>
-      <c r="M4" s="55"/>
-      <c r="N4" s="56"/>
-      <c r="O4" s="62"/>
-      <c r="P4" s="56"/>
-      <c r="Q4" s="62"/>
-      <c r="R4" s="56"/>
-      <c r="S4" s="62"/>
-      <c r="T4" s="138"/>
+      <c r="A4" s="128"/>
+      <c r="B4" s="129"/>
+      <c r="C4" s="129"/>
+      <c r="D4" s="129"/>
+      <c r="E4" s="129"/>
+      <c r="F4" s="130"/>
+      <c r="G4" s="131"/>
+      <c r="H4" s="129"/>
+      <c r="I4" s="129"/>
+      <c r="J4" s="130"/>
+      <c r="K4" s="131"/>
+      <c r="L4" s="129"/>
+      <c r="M4" s="129"/>
+      <c r="N4" s="130"/>
+      <c r="O4" s="131"/>
+      <c r="P4" s="130"/>
+      <c r="Q4" s="131"/>
+      <c r="R4" s="130"/>
+      <c r="S4" s="131"/>
+      <c r="T4" s="143"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="116" t="s">
+      <c r="A5" s="69" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="117"/>
-      <c r="C5" s="117"/>
-      <c r="D5" s="117"/>
-      <c r="E5" s="117"/>
-      <c r="F5" s="58"/>
+      <c r="B5" s="70"/>
+      <c r="C5" s="70"/>
+      <c r="D5" s="70"/>
+      <c r="E5" s="70"/>
+      <c r="F5" s="59"/>
       <c r="G5" s="140" t="s">
         <v>34</v>
       </c>
-      <c r="H5" s="117"/>
-      <c r="I5" s="117"/>
-      <c r="J5" s="117"/>
-      <c r="K5" s="117"/>
-      <c r="L5" s="117"/>
-      <c r="M5" s="117"/>
-      <c r="N5" s="117"/>
-      <c r="O5" s="117"/>
-      <c r="P5" s="117"/>
-      <c r="Q5" s="117"/>
-      <c r="R5" s="117"/>
-      <c r="S5" s="117"/>
-      <c r="T5" s="120"/>
+      <c r="H5" s="70"/>
+      <c r="I5" s="70"/>
+      <c r="J5" s="70"/>
+      <c r="K5" s="70"/>
+      <c r="L5" s="70"/>
+      <c r="M5" s="70"/>
+      <c r="N5" s="70"/>
+      <c r="O5" s="70"/>
+      <c r="P5" s="70"/>
+      <c r="Q5" s="70"/>
+      <c r="R5" s="70"/>
+      <c r="S5" s="70"/>
+      <c r="T5" s="75"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="118" t="s">
+      <c r="A6" s="54" t="s">
         <v>35</v>
       </c>
-      <c r="B6" s="64"/>
-      <c r="C6" s="64"/>
-      <c r="D6" s="64"/>
-      <c r="E6" s="64"/>
-      <c r="F6" s="65"/>
-      <c r="G6" s="111" t="s">
+      <c r="B6" s="45"/>
+      <c r="C6" s="45"/>
+      <c r="D6" s="45"/>
+      <c r="E6" s="45"/>
+      <c r="F6" s="51"/>
+      <c r="G6" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="H6" s="64"/>
-      <c r="I6" s="64"/>
-      <c r="J6" s="64"/>
-      <c r="K6" s="64"/>
-      <c r="L6" s="64"/>
-      <c r="M6" s="64"/>
-      <c r="N6" s="64"/>
-      <c r="O6" s="64"/>
-      <c r="P6" s="64"/>
-      <c r="Q6" s="64"/>
-      <c r="R6" s="64"/>
-      <c r="S6" s="64"/>
-      <c r="T6" s="112"/>
+      <c r="H6" s="45"/>
+      <c r="I6" s="45"/>
+      <c r="J6" s="45"/>
+      <c r="K6" s="45"/>
+      <c r="L6" s="45"/>
+      <c r="M6" s="45"/>
+      <c r="N6" s="45"/>
+      <c r="O6" s="45"/>
+      <c r="P6" s="45"/>
+      <c r="Q6" s="45"/>
+      <c r="R6" s="45"/>
+      <c r="S6" s="45"/>
+      <c r="T6" s="46"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="118" t="s">
+      <c r="A7" s="54" t="s">
         <v>36</v>
       </c>
-      <c r="B7" s="64"/>
-      <c r="C7" s="64"/>
-      <c r="D7" s="64"/>
-      <c r="E7" s="64"/>
-      <c r="F7" s="65"/>
-      <c r="G7" s="111" t="s">
+      <c r="B7" s="45"/>
+      <c r="C7" s="45"/>
+      <c r="D7" s="45"/>
+      <c r="E7" s="45"/>
+      <c r="F7" s="51"/>
+      <c r="G7" s="44" t="s">
         <v>37</v>
       </c>
-      <c r="H7" s="64"/>
-      <c r="I7" s="64"/>
-      <c r="J7" s="64"/>
-      <c r="K7" s="64"/>
-      <c r="L7" s="64"/>
-      <c r="M7" s="64"/>
-      <c r="N7" s="64"/>
-      <c r="O7" s="64"/>
-      <c r="P7" s="64"/>
-      <c r="Q7" s="64"/>
-      <c r="R7" s="64"/>
-      <c r="S7" s="64"/>
-      <c r="T7" s="112"/>
+      <c r="H7" s="45"/>
+      <c r="I7" s="45"/>
+      <c r="J7" s="45"/>
+      <c r="K7" s="45"/>
+      <c r="L7" s="45"/>
+      <c r="M7" s="45"/>
+      <c r="N7" s="45"/>
+      <c r="O7" s="45"/>
+      <c r="P7" s="45"/>
+      <c r="Q7" s="45"/>
+      <c r="R7" s="45"/>
+      <c r="S7" s="45"/>
+      <c r="T7" s="46"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="7"/>
@@ -12111,37 +12111,37 @@
       <c r="T14" s="9"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="118" t="s">
+      <c r="A15" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="B15" s="65"/>
-      <c r="C15" s="143" t="s">
+      <c r="B15" s="51"/>
+      <c r="C15" s="142" t="s">
         <v>38</v>
       </c>
-      <c r="D15" s="65"/>
-      <c r="E15" s="125" t="s">
+      <c r="D15" s="51"/>
+      <c r="E15" s="57" t="s">
         <v>45</v>
       </c>
-      <c r="F15" s="65"/>
-      <c r="G15" s="125" t="s">
+      <c r="F15" s="51"/>
+      <c r="G15" s="57" t="s">
         <v>46</v>
       </c>
-      <c r="H15" s="64"/>
-      <c r="I15" s="65"/>
-      <c r="J15" s="125" t="s">
+      <c r="H15" s="45"/>
+      <c r="I15" s="51"/>
+      <c r="J15" s="57" t="s">
         <v>47</v>
       </c>
-      <c r="K15" s="65"/>
-      <c r="L15" s="125" t="s">
+      <c r="K15" s="51"/>
+      <c r="L15" s="57" t="s">
         <v>48</v>
       </c>
-      <c r="M15" s="64"/>
-      <c r="N15" s="65"/>
-      <c r="O15" s="125" t="s">
+      <c r="M15" s="45"/>
+      <c r="N15" s="51"/>
+      <c r="O15" s="57" t="s">
         <v>49</v>
       </c>
-      <c r="P15" s="64"/>
-      <c r="Q15" s="65"/>
+      <c r="P15" s="45"/>
+      <c r="Q15" s="51"/>
       <c r="R15" s="14" t="s">
         <v>50</v>
       </c>
@@ -12153,37 +12153,37 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="141">
+      <c r="A16" s="132">
         <v>1</v>
       </c>
-      <c r="B16" s="65"/>
-      <c r="C16" s="142" t="s">
+      <c r="B16" s="51"/>
+      <c r="C16" s="133" t="s">
         <v>53</v>
       </c>
-      <c r="D16" s="65"/>
-      <c r="E16" s="142" t="s">
+      <c r="D16" s="51"/>
+      <c r="E16" s="133" t="s">
         <v>54</v>
       </c>
-      <c r="F16" s="65"/>
-      <c r="G16" s="132" t="s">
+      <c r="F16" s="51"/>
+      <c r="G16" s="141" t="s">
         <v>55</v>
       </c>
-      <c r="H16" s="64"/>
-      <c r="I16" s="65"/>
-      <c r="J16" s="132" t="s">
+      <c r="H16" s="45"/>
+      <c r="I16" s="51"/>
+      <c r="J16" s="141" t="s">
         <v>56</v>
       </c>
-      <c r="K16" s="65"/>
-      <c r="L16" s="136" t="s">
+      <c r="K16" s="51"/>
+      <c r="L16" s="137" t="s">
         <v>57</v>
       </c>
-      <c r="M16" s="64"/>
-      <c r="N16" s="65"/>
-      <c r="O16" s="136" t="s">
+      <c r="M16" s="45"/>
+      <c r="N16" s="51"/>
+      <c r="O16" s="137" t="s">
         <v>58</v>
       </c>
-      <c r="P16" s="64"/>
-      <c r="Q16" s="65"/>
+      <c r="P16" s="45"/>
+      <c r="Q16" s="51"/>
       <c r="R16" s="32"/>
       <c r="S16" s="32"/>
       <c r="T16" s="33"/>
@@ -12195,37 +12195,37 @@
       <c r="Z16" s="34"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="141">
+      <c r="A17" s="132">
         <v>2</v>
       </c>
-      <c r="B17" s="65"/>
-      <c r="C17" s="142" t="s">
+      <c r="B17" s="51"/>
+      <c r="C17" s="133" t="s">
         <v>59</v>
       </c>
-      <c r="D17" s="65"/>
-      <c r="E17" s="142" t="s">
+      <c r="D17" s="51"/>
+      <c r="E17" s="133" t="s">
         <v>60</v>
       </c>
-      <c r="F17" s="65"/>
-      <c r="G17" s="132" t="s">
+      <c r="F17" s="51"/>
+      <c r="G17" s="141" t="s">
         <v>61</v>
       </c>
-      <c r="H17" s="64"/>
-      <c r="I17" s="65"/>
-      <c r="J17" s="132" t="s">
+      <c r="H17" s="45"/>
+      <c r="I17" s="51"/>
+      <c r="J17" s="141" t="s">
         <v>62</v>
       </c>
-      <c r="K17" s="65"/>
-      <c r="L17" s="136" t="s">
+      <c r="K17" s="51"/>
+      <c r="L17" s="137" t="s">
         <v>63</v>
       </c>
-      <c r="M17" s="64"/>
-      <c r="N17" s="65"/>
-      <c r="O17" s="136" t="s">
+      <c r="M17" s="45"/>
+      <c r="N17" s="51"/>
+      <c r="O17" s="137" t="s">
         <v>64</v>
       </c>
-      <c r="P17" s="64"/>
-      <c r="Q17" s="65"/>
+      <c r="P17" s="45"/>
+      <c r="Q17" s="51"/>
       <c r="R17" s="32"/>
       <c r="S17" s="32"/>
       <c r="T17" s="33"/>
@@ -12237,23 +12237,23 @@
       <c r="Z17" s="34"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="141"/>
-      <c r="B18" s="65"/>
-      <c r="C18" s="142"/>
-      <c r="D18" s="65"/>
-      <c r="E18" s="142"/>
-      <c r="F18" s="65"/>
-      <c r="G18" s="132"/>
-      <c r="H18" s="64"/>
-      <c r="I18" s="65"/>
-      <c r="J18" s="132"/>
-      <c r="K18" s="65"/>
-      <c r="L18" s="136"/>
-      <c r="M18" s="64"/>
-      <c r="N18" s="65"/>
-      <c r="O18" s="136"/>
-      <c r="P18" s="64"/>
-      <c r="Q18" s="65"/>
+      <c r="A18" s="132"/>
+      <c r="B18" s="51"/>
+      <c r="C18" s="133"/>
+      <c r="D18" s="51"/>
+      <c r="E18" s="133"/>
+      <c r="F18" s="51"/>
+      <c r="G18" s="141"/>
+      <c r="H18" s="45"/>
+      <c r="I18" s="51"/>
+      <c r="J18" s="141"/>
+      <c r="K18" s="51"/>
+      <c r="L18" s="137"/>
+      <c r="M18" s="45"/>
+      <c r="N18" s="51"/>
+      <c r="O18" s="137"/>
+      <c r="P18" s="45"/>
+      <c r="Q18" s="51"/>
       <c r="R18" s="32"/>
       <c r="S18" s="32"/>
       <c r="T18" s="33"/>
@@ -12265,23 +12265,23 @@
       <c r="Z18" s="34"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="141"/>
-      <c r="B19" s="65"/>
-      <c r="C19" s="142"/>
-      <c r="D19" s="65"/>
-      <c r="E19" s="142"/>
-      <c r="F19" s="65"/>
-      <c r="G19" s="132"/>
-      <c r="H19" s="64"/>
-      <c r="I19" s="65"/>
-      <c r="J19" s="132"/>
-      <c r="K19" s="65"/>
-      <c r="L19" s="136"/>
-      <c r="M19" s="64"/>
-      <c r="N19" s="65"/>
-      <c r="O19" s="136"/>
-      <c r="P19" s="64"/>
-      <c r="Q19" s="65"/>
+      <c r="A19" s="132"/>
+      <c r="B19" s="51"/>
+      <c r="C19" s="133"/>
+      <c r="D19" s="51"/>
+      <c r="E19" s="133"/>
+      <c r="F19" s="51"/>
+      <c r="G19" s="141"/>
+      <c r="H19" s="45"/>
+      <c r="I19" s="51"/>
+      <c r="J19" s="141"/>
+      <c r="K19" s="51"/>
+      <c r="L19" s="137"/>
+      <c r="M19" s="45"/>
+      <c r="N19" s="51"/>
+      <c r="O19" s="137"/>
+      <c r="P19" s="45"/>
+      <c r="Q19" s="51"/>
       <c r="R19" s="32"/>
       <c r="S19" s="32"/>
       <c r="T19" s="33"/>
@@ -12293,23 +12293,23 @@
       <c r="Z19" s="34"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="141"/>
-      <c r="B20" s="65"/>
-      <c r="C20" s="142"/>
-      <c r="D20" s="65"/>
-      <c r="E20" s="142"/>
-      <c r="F20" s="65"/>
-      <c r="G20" s="132"/>
-      <c r="H20" s="64"/>
-      <c r="I20" s="65"/>
-      <c r="J20" s="132"/>
-      <c r="K20" s="65"/>
-      <c r="L20" s="136"/>
-      <c r="M20" s="64"/>
-      <c r="N20" s="65"/>
-      <c r="O20" s="136"/>
-      <c r="P20" s="64"/>
-      <c r="Q20" s="65"/>
+      <c r="A20" s="132"/>
+      <c r="B20" s="51"/>
+      <c r="C20" s="133"/>
+      <c r="D20" s="51"/>
+      <c r="E20" s="133"/>
+      <c r="F20" s="51"/>
+      <c r="G20" s="141"/>
+      <c r="H20" s="45"/>
+      <c r="I20" s="51"/>
+      <c r="J20" s="141"/>
+      <c r="K20" s="51"/>
+      <c r="L20" s="137"/>
+      <c r="M20" s="45"/>
+      <c r="N20" s="51"/>
+      <c r="O20" s="137"/>
+      <c r="P20" s="45"/>
+      <c r="Q20" s="51"/>
       <c r="R20" s="32"/>
       <c r="S20" s="32"/>
       <c r="T20" s="33"/>
@@ -12321,23 +12321,23 @@
       <c r="Z20" s="34"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="141"/>
-      <c r="B21" s="65"/>
-      <c r="C21" s="142"/>
-      <c r="D21" s="65"/>
-      <c r="E21" s="142"/>
-      <c r="F21" s="65"/>
-      <c r="G21" s="132"/>
-      <c r="H21" s="64"/>
-      <c r="I21" s="65"/>
-      <c r="J21" s="132"/>
-      <c r="K21" s="65"/>
-      <c r="L21" s="136"/>
-      <c r="M21" s="64"/>
-      <c r="N21" s="65"/>
-      <c r="O21" s="136"/>
-      <c r="P21" s="64"/>
-      <c r="Q21" s="65"/>
+      <c r="A21" s="132"/>
+      <c r="B21" s="51"/>
+      <c r="C21" s="133"/>
+      <c r="D21" s="51"/>
+      <c r="E21" s="133"/>
+      <c r="F21" s="51"/>
+      <c r="G21" s="141"/>
+      <c r="H21" s="45"/>
+      <c r="I21" s="51"/>
+      <c r="J21" s="141"/>
+      <c r="K21" s="51"/>
+      <c r="L21" s="137"/>
+      <c r="M21" s="45"/>
+      <c r="N21" s="51"/>
+      <c r="O21" s="137"/>
+      <c r="P21" s="45"/>
+      <c r="Q21" s="51"/>
       <c r="R21" s="32"/>
       <c r="S21" s="32"/>
       <c r="T21" s="33"/>
@@ -12349,23 +12349,23 @@
       <c r="Z21" s="34"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="141"/>
-      <c r="B22" s="65"/>
-      <c r="C22" s="142"/>
-      <c r="D22" s="65"/>
-      <c r="E22" s="142"/>
-      <c r="F22" s="65"/>
-      <c r="G22" s="132"/>
-      <c r="H22" s="64"/>
-      <c r="I22" s="65"/>
-      <c r="J22" s="132"/>
-      <c r="K22" s="65"/>
-      <c r="L22" s="136"/>
-      <c r="M22" s="64"/>
-      <c r="N22" s="65"/>
-      <c r="O22" s="136"/>
-      <c r="P22" s="64"/>
-      <c r="Q22" s="65"/>
+      <c r="A22" s="132"/>
+      <c r="B22" s="51"/>
+      <c r="C22" s="133"/>
+      <c r="D22" s="51"/>
+      <c r="E22" s="133"/>
+      <c r="F22" s="51"/>
+      <c r="G22" s="141"/>
+      <c r="H22" s="45"/>
+      <c r="I22" s="51"/>
+      <c r="J22" s="141"/>
+      <c r="K22" s="51"/>
+      <c r="L22" s="137"/>
+      <c r="M22" s="45"/>
+      <c r="N22" s="51"/>
+      <c r="O22" s="137"/>
+      <c r="P22" s="45"/>
+      <c r="Q22" s="51"/>
       <c r="R22" s="32"/>
       <c r="S22" s="32"/>
       <c r="T22" s="33"/>
@@ -12377,23 +12377,23 @@
       <c r="Z22" s="34"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="141"/>
-      <c r="B23" s="65"/>
-      <c r="C23" s="142"/>
-      <c r="D23" s="65"/>
-      <c r="E23" s="142"/>
-      <c r="F23" s="65"/>
-      <c r="G23" s="132"/>
-      <c r="H23" s="64"/>
-      <c r="I23" s="65"/>
-      <c r="J23" s="132"/>
-      <c r="K23" s="65"/>
-      <c r="L23" s="136"/>
-      <c r="M23" s="64"/>
-      <c r="N23" s="65"/>
-      <c r="O23" s="136"/>
-      <c r="P23" s="64"/>
-      <c r="Q23" s="65"/>
+      <c r="A23" s="132"/>
+      <c r="B23" s="51"/>
+      <c r="C23" s="133"/>
+      <c r="D23" s="51"/>
+      <c r="E23" s="133"/>
+      <c r="F23" s="51"/>
+      <c r="G23" s="141"/>
+      <c r="H23" s="45"/>
+      <c r="I23" s="51"/>
+      <c r="J23" s="141"/>
+      <c r="K23" s="51"/>
+      <c r="L23" s="137"/>
+      <c r="M23" s="45"/>
+      <c r="N23" s="51"/>
+      <c r="O23" s="137"/>
+      <c r="P23" s="45"/>
+      <c r="Q23" s="51"/>
       <c r="R23" s="32"/>
       <c r="S23" s="32"/>
       <c r="T23" s="33"/>
@@ -12405,23 +12405,23 @@
       <c r="Z23" s="34"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="141"/>
-      <c r="B24" s="65"/>
-      <c r="C24" s="142"/>
-      <c r="D24" s="65"/>
-      <c r="E24" s="142"/>
-      <c r="F24" s="65"/>
-      <c r="G24" s="132"/>
-      <c r="H24" s="64"/>
-      <c r="I24" s="65"/>
-      <c r="J24" s="132"/>
-      <c r="K24" s="65"/>
-      <c r="L24" s="136"/>
-      <c r="M24" s="64"/>
-      <c r="N24" s="65"/>
-      <c r="O24" s="136"/>
-      <c r="P24" s="64"/>
-      <c r="Q24" s="65"/>
+      <c r="A24" s="132"/>
+      <c r="B24" s="51"/>
+      <c r="C24" s="133"/>
+      <c r="D24" s="51"/>
+      <c r="E24" s="133"/>
+      <c r="F24" s="51"/>
+      <c r="G24" s="141"/>
+      <c r="H24" s="45"/>
+      <c r="I24" s="51"/>
+      <c r="J24" s="141"/>
+      <c r="K24" s="51"/>
+      <c r="L24" s="137"/>
+      <c r="M24" s="45"/>
+      <c r="N24" s="51"/>
+      <c r="O24" s="137"/>
+      <c r="P24" s="45"/>
+      <c r="Q24" s="51"/>
       <c r="R24" s="32"/>
       <c r="S24" s="32"/>
       <c r="T24" s="33"/>
@@ -12433,23 +12433,23 @@
       <c r="Z24" s="34"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="141"/>
-      <c r="B25" s="65"/>
-      <c r="C25" s="142"/>
-      <c r="D25" s="65"/>
-      <c r="E25" s="142"/>
-      <c r="F25" s="65"/>
-      <c r="G25" s="132"/>
-      <c r="H25" s="64"/>
-      <c r="I25" s="65"/>
-      <c r="J25" s="132"/>
-      <c r="K25" s="65"/>
-      <c r="L25" s="136"/>
-      <c r="M25" s="64"/>
-      <c r="N25" s="65"/>
-      <c r="O25" s="136"/>
-      <c r="P25" s="64"/>
-      <c r="Q25" s="65"/>
+      <c r="A25" s="132"/>
+      <c r="B25" s="51"/>
+      <c r="C25" s="133"/>
+      <c r="D25" s="51"/>
+      <c r="E25" s="133"/>
+      <c r="F25" s="51"/>
+      <c r="G25" s="141"/>
+      <c r="H25" s="45"/>
+      <c r="I25" s="51"/>
+      <c r="J25" s="141"/>
+      <c r="K25" s="51"/>
+      <c r="L25" s="137"/>
+      <c r="M25" s="45"/>
+      <c r="N25" s="51"/>
+      <c r="O25" s="137"/>
+      <c r="P25" s="45"/>
+      <c r="Q25" s="51"/>
       <c r="R25" s="32"/>
       <c r="S25" s="32"/>
       <c r="T25" s="33"/>
@@ -12461,23 +12461,23 @@
       <c r="Z25" s="34"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="141"/>
-      <c r="B26" s="65"/>
-      <c r="C26" s="142"/>
-      <c r="D26" s="65"/>
-      <c r="E26" s="142"/>
-      <c r="F26" s="65"/>
-      <c r="G26" s="132"/>
-      <c r="H26" s="64"/>
-      <c r="I26" s="65"/>
-      <c r="J26" s="132"/>
-      <c r="K26" s="65"/>
-      <c r="L26" s="136"/>
-      <c r="M26" s="64"/>
-      <c r="N26" s="65"/>
-      <c r="O26" s="136"/>
-      <c r="P26" s="64"/>
-      <c r="Q26" s="65"/>
+      <c r="A26" s="132"/>
+      <c r="B26" s="51"/>
+      <c r="C26" s="133"/>
+      <c r="D26" s="51"/>
+      <c r="E26" s="133"/>
+      <c r="F26" s="51"/>
+      <c r="G26" s="141"/>
+      <c r="H26" s="45"/>
+      <c r="I26" s="51"/>
+      <c r="J26" s="141"/>
+      <c r="K26" s="51"/>
+      <c r="L26" s="137"/>
+      <c r="M26" s="45"/>
+      <c r="N26" s="51"/>
+      <c r="O26" s="137"/>
+      <c r="P26" s="45"/>
+      <c r="Q26" s="51"/>
       <c r="R26" s="32"/>
       <c r="S26" s="32"/>
       <c r="T26" s="33"/>
@@ -12489,23 +12489,23 @@
       <c r="Z26" s="34"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="141"/>
-      <c r="B27" s="65"/>
-      <c r="C27" s="142"/>
-      <c r="D27" s="65"/>
-      <c r="E27" s="142"/>
-      <c r="F27" s="65"/>
-      <c r="G27" s="132"/>
-      <c r="H27" s="64"/>
-      <c r="I27" s="65"/>
-      <c r="J27" s="132"/>
-      <c r="K27" s="65"/>
-      <c r="L27" s="136"/>
-      <c r="M27" s="64"/>
-      <c r="N27" s="65"/>
-      <c r="O27" s="136"/>
-      <c r="P27" s="64"/>
-      <c r="Q27" s="65"/>
+      <c r="A27" s="132"/>
+      <c r="B27" s="51"/>
+      <c r="C27" s="133"/>
+      <c r="D27" s="51"/>
+      <c r="E27" s="133"/>
+      <c r="F27" s="51"/>
+      <c r="G27" s="141"/>
+      <c r="H27" s="45"/>
+      <c r="I27" s="51"/>
+      <c r="J27" s="141"/>
+      <c r="K27" s="51"/>
+      <c r="L27" s="137"/>
+      <c r="M27" s="45"/>
+      <c r="N27" s="51"/>
+      <c r="O27" s="137"/>
+      <c r="P27" s="45"/>
+      <c r="Q27" s="51"/>
       <c r="R27" s="32"/>
       <c r="S27" s="32"/>
       <c r="T27" s="33"/>
@@ -12517,23 +12517,23 @@
       <c r="Z27" s="34"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="141"/>
-      <c r="B28" s="65"/>
-      <c r="C28" s="142"/>
-      <c r="D28" s="65"/>
-      <c r="E28" s="142"/>
-      <c r="F28" s="65"/>
-      <c r="G28" s="132"/>
-      <c r="H28" s="64"/>
-      <c r="I28" s="65"/>
-      <c r="J28" s="132"/>
-      <c r="K28" s="65"/>
-      <c r="L28" s="136"/>
-      <c r="M28" s="64"/>
-      <c r="N28" s="65"/>
-      <c r="O28" s="136"/>
-      <c r="P28" s="64"/>
-      <c r="Q28" s="65"/>
+      <c r="A28" s="132"/>
+      <c r="B28" s="51"/>
+      <c r="C28" s="133"/>
+      <c r="D28" s="51"/>
+      <c r="E28" s="133"/>
+      <c r="F28" s="51"/>
+      <c r="G28" s="141"/>
+      <c r="H28" s="45"/>
+      <c r="I28" s="51"/>
+      <c r="J28" s="141"/>
+      <c r="K28" s="51"/>
+      <c r="L28" s="137"/>
+      <c r="M28" s="45"/>
+      <c r="N28" s="51"/>
+      <c r="O28" s="137"/>
+      <c r="P28" s="45"/>
+      <c r="Q28" s="51"/>
       <c r="R28" s="32"/>
       <c r="S28" s="32"/>
       <c r="T28" s="33"/>
@@ -12545,23 +12545,23 @@
       <c r="Z28" s="34"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="141"/>
-      <c r="B29" s="65"/>
-      <c r="C29" s="142"/>
-      <c r="D29" s="65"/>
-      <c r="E29" s="142"/>
-      <c r="F29" s="65"/>
-      <c r="G29" s="132"/>
-      <c r="H29" s="64"/>
-      <c r="I29" s="65"/>
-      <c r="J29" s="132"/>
-      <c r="K29" s="65"/>
-      <c r="L29" s="136"/>
-      <c r="M29" s="64"/>
-      <c r="N29" s="65"/>
-      <c r="O29" s="136"/>
-      <c r="P29" s="64"/>
-      <c r="Q29" s="65"/>
+      <c r="A29" s="132"/>
+      <c r="B29" s="51"/>
+      <c r="C29" s="133"/>
+      <c r="D29" s="51"/>
+      <c r="E29" s="133"/>
+      <c r="F29" s="51"/>
+      <c r="G29" s="141"/>
+      <c r="H29" s="45"/>
+      <c r="I29" s="51"/>
+      <c r="J29" s="141"/>
+      <c r="K29" s="51"/>
+      <c r="L29" s="137"/>
+      <c r="M29" s="45"/>
+      <c r="N29" s="51"/>
+      <c r="O29" s="137"/>
+      <c r="P29" s="45"/>
+      <c r="Q29" s="51"/>
       <c r="R29" s="32"/>
       <c r="S29" s="32"/>
       <c r="T29" s="33"/>
@@ -12573,23 +12573,23 @@
       <c r="Z29" s="34"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="141"/>
-      <c r="B30" s="65"/>
-      <c r="C30" s="142"/>
-      <c r="D30" s="65"/>
-      <c r="E30" s="142"/>
-      <c r="F30" s="65"/>
-      <c r="G30" s="132"/>
-      <c r="H30" s="64"/>
-      <c r="I30" s="65"/>
-      <c r="J30" s="132"/>
-      <c r="K30" s="65"/>
-      <c r="L30" s="136"/>
-      <c r="M30" s="64"/>
-      <c r="N30" s="65"/>
-      <c r="O30" s="136"/>
-      <c r="P30" s="64"/>
-      <c r="Q30" s="65"/>
+      <c r="A30" s="132"/>
+      <c r="B30" s="51"/>
+      <c r="C30" s="133"/>
+      <c r="D30" s="51"/>
+      <c r="E30" s="133"/>
+      <c r="F30" s="51"/>
+      <c r="G30" s="141"/>
+      <c r="H30" s="45"/>
+      <c r="I30" s="51"/>
+      <c r="J30" s="141"/>
+      <c r="K30" s="51"/>
+      <c r="L30" s="137"/>
+      <c r="M30" s="45"/>
+      <c r="N30" s="51"/>
+      <c r="O30" s="137"/>
+      <c r="P30" s="45"/>
+      <c r="Q30" s="51"/>
       <c r="R30" s="32"/>
       <c r="S30" s="32"/>
       <c r="T30" s="33"/>
@@ -12601,22 +12601,22 @@
       <c r="Z30" s="34"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="144"/>
+      <c r="A31" s="134"/>
       <c r="B31" s="135"/>
-      <c r="C31" s="145"/>
+      <c r="C31" s="136"/>
       <c r="D31" s="135"/>
-      <c r="E31" s="145"/>
+      <c r="E31" s="136"/>
       <c r="F31" s="135"/>
-      <c r="G31" s="133"/>
-      <c r="H31" s="134"/>
+      <c r="G31" s="145"/>
+      <c r="H31" s="139"/>
       <c r="I31" s="135"/>
-      <c r="J31" s="133"/>
+      <c r="J31" s="145"/>
       <c r="K31" s="135"/>
-      <c r="L31" s="137"/>
-      <c r="M31" s="134"/>
+      <c r="L31" s="138"/>
+      <c r="M31" s="139"/>
       <c r="N31" s="135"/>
-      <c r="O31" s="137"/>
-      <c r="P31" s="134"/>
+      <c r="O31" s="138"/>
+      <c r="P31" s="139"/>
       <c r="Q31" s="135"/>
       <c r="R31" s="35"/>
       <c r="S31" s="35"/>
@@ -13615,6 +13615,118 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:T5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:T6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G7:T7"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="C30:D30"/>
     <mergeCell ref="E30:F30"/>
@@ -13639,118 +13751,6 @@
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="E28:F28"/>
     <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:T5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="G6:T6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="G7:T7"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/document/成果物ドキュメント_タスク編集機能.xlsx
+++ b/document/成果物ドキュメント_タスク編集機能.xlsx
@@ -8,18 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\TaskManager62\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E058AF2-683E-4557-AED5-8E3E5C7A252C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD07DDC1-56AF-4A36-8E4A-50E592B8C28A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
     <sheet name="ユースケース記述" sheetId="7" r:id="rId2"/>
     <sheet name="画面遷移図" sheetId="3" r:id="rId3"/>
     <sheet name="詳細クラス図" sheetId="4" r:id="rId4"/>
-    <sheet name="画面設計書" sheetId="5" r:id="rId5"/>
-    <sheet name="画面設計書 (2)" sheetId="8" r:id="rId6"/>
-    <sheet name="画面設計書 (3)" sheetId="9" r:id="rId7"/>
+    <sheet name="画面設計書 (タスク編集画面)" sheetId="5" r:id="rId5"/>
+    <sheet name="画面設計書 (タスク編集完了画面)" sheetId="9" r:id="rId6"/>
+    <sheet name="画面設計書 (タスク編集エラー画面)" sheetId="8" r:id="rId7"/>
     <sheet name="テスト仕様書兼結果報告書" sheetId="6" r:id="rId8"/>
   </sheets>
   <calcPr calcId="0" iterateDelta="1E-4"/>
@@ -27,15 +27,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="123">
   <si>
     <t>プロジェクト型演習　成果ドキュメント</t>
   </si>
   <si>
     <t>初版</t>
-  </si>
-  <si>
-    <t>YYYY/MM/DD</t>
   </si>
   <si>
     <t>ユースケース記述</t>
@@ -228,23 +225,6 @@
 エラーの原因がユーザ名が未入力である旨通知する</t>
   </si>
   <si>
-    <t>DBに編集後の内容が反映されていること</t>
-    <rPh sb="3" eb="6">
-      <t>ヘンシュウゴ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ナイヨウ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ハンエイ</t>
-    </rPh>
-    <phoneticPr fontId="10"/>
-  </si>
-  <si>
-    <t>ユーザーがシステムにログインしていること</t>
-    <phoneticPr fontId="10"/>
-  </si>
-  <si>
     <t>商品企画部の従業員(ユーザー)</t>
     <rPh sb="0" eb="5">
       <t>ショウヒンキカクブ</t>
@@ -258,16 +238,6 @@
     <t>タスクを編集する</t>
     <rPh sb="4" eb="6">
       <t>ヘンシュウ</t>
-    </rPh>
-    <phoneticPr fontId="10"/>
-  </si>
-  <si>
-    <t>タスク編集機能</t>
-    <rPh sb="3" eb="5">
-      <t>ヘンシュウ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>キノウ</t>
     </rPh>
     <phoneticPr fontId="10"/>
   </si>
@@ -361,46 +331,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>タスク名を入力する</t>
-    <rPh sb="3" eb="4">
-      <t>メイ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>ニュウリョク</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>期限をカレンダーから選択する</t>
-    <rPh sb="0" eb="2">
-      <t>キゲン</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>センタク</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>メモを入力する</t>
-    <rPh sb="3" eb="5">
-      <t>ニュウリョク</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>入力した内容をサーブレットに送信する</t>
-    <rPh sb="0" eb="2">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ナイヨウ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>ソウシン</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>TaskManager62</t>
     <phoneticPr fontId="8"/>
   </si>
@@ -473,62 +403,9 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>カテゴリ情報を選択する</t>
-    <rPh sb="4" eb="6">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>センタク</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>担当者をユーザー一覧から選択する</t>
-    <rPh sb="0" eb="3">
-      <t>タントウシャ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>イチラン</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>センタク</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>ステータス情報を選択する</t>
-    <rPh sb="5" eb="7">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>センタク</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>タスク編集画面</t>
     <rPh sb="3" eb="7">
       <t>ヘンシュウガメン</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>タスク編集失敗画面</t>
-    <rPh sb="3" eb="5">
-      <t>ヘンシュウ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>シッパイ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ガメン</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>戻る</t>
-    <rPh sb="0" eb="1">
-      <t>モド</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
@@ -548,92 +425,7 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>メニュー画面に遷移する</t>
-    <rPh sb="4" eb="6">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>センイ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>menu.jsp</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>1.ユーザーがタスク詳細画面を開く
-2.ユーザーが編集するタスクを選択する
-3.システムがタスク編集画面を表示する
-4.ユーザーがタスク名・カテゴリ情報・期限・担当者情報・ステータス情報・メモのうち一つまたは複数の項目の編集内容を入力する
-5.システムはタスク編集完了画面を表示する</t>
-    <rPh sb="15" eb="16">
-      <t>ヒラ</t>
-    </rPh>
-    <rPh sb="25" eb="27">
-      <t>ヘンシュウ</t>
-    </rPh>
-    <rPh sb="33" eb="35">
-      <t>センタク</t>
-    </rPh>
-    <rPh sb="48" eb="52">
-      <t>ヘンシュウガメン</t>
-    </rPh>
-    <rPh sb="53" eb="55">
-      <t>ヒョウジ</t>
-    </rPh>
-    <rPh sb="68" eb="69">
-      <t>メイ</t>
-    </rPh>
-    <rPh sb="74" eb="76">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="77" eb="79">
-      <t>キゲン</t>
-    </rPh>
-    <rPh sb="80" eb="85">
-      <t>タントウシャジョウホウ</t>
-    </rPh>
-    <rPh sb="91" eb="93">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="99" eb="100">
-      <t>ヒト</t>
-    </rPh>
-    <rPh sb="104" eb="106">
-      <t>フクスウ</t>
-    </rPh>
-    <rPh sb="107" eb="109">
-      <t>コウモク</t>
-    </rPh>
-    <rPh sb="110" eb="112">
-      <t>ヘンシュウ</t>
-    </rPh>
-    <rPh sb="112" eb="114">
-      <t>ナイヨウ</t>
-    </rPh>
-    <rPh sb="115" eb="117">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="130" eb="132">
-      <t>ヘンシュウ</t>
-    </rPh>
-    <rPh sb="132" eb="136">
-      <t>カンリョウガメン</t>
-    </rPh>
-    <rPh sb="137" eb="139">
-      <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="10"/>
-  </si>
-  <si>
-    <t>タスク編集画面に遷移する</t>
-    <rPh sb="3" eb="7">
-      <t>ヘンシュウガメン</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>センイ</t>
-    </rPh>
     <phoneticPr fontId="8"/>
   </si>
   <si>
@@ -662,37 +454,227 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>4a.ユーザーが編集前と同じ内容を入力し、確定した場合
-4a1.システムがエラー画面を表示する</t>
-    <phoneticPr fontId="10"/>
-  </si>
-  <si>
-    <t>タスク詳細画面に戻る</t>
-    <rPh sb="3" eb="5">
-      <t>ショウサイ</t>
+    <t>入力必須、最大50文字</t>
+    <rPh sb="0" eb="4">
+      <t>ニュウリョクヒッス</t>
     </rPh>
     <rPh sb="5" eb="7">
-      <t>ガメン</t>
+      <t>サイダイ</t>
     </rPh>
-    <rPh sb="8" eb="9">
-      <t>モド</t>
+    <rPh sb="9" eb="11">
+      <t>モジ</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>タスク詳細画面へ</t>
-    <rPh sb="3" eb="7">
-      <t>ショウサイガメン</t>
+    <t>(空文字)</t>
+    <rPh sb="0" eb="3">
+      <t>カラモジ</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>タスク詳細画面へ</t>
+    <t>過去の日付を選択できないようにする</t>
+    <rPh sb="0" eb="2">
+      <t>カコ</t>
+    </rPh>
     <rPh sb="3" eb="5">
-      <t>ショウサイ</t>
+      <t>ヒヅケ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>センタク</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>最大100文字</t>
+    <rPh sb="0" eb="2">
+      <t>サイダイ</t>
     </rPh>
     <rPh sb="5" eb="7">
+      <t>モジ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>データベースの対象のタスクがユーザーの編集した内容に変更されていること</t>
+    <rPh sb="7" eb="9">
+      <t>タイショウ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>ヘンコウ</t>
+    </rPh>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>3a1．ユーザーがタスクの編集を中止し、直前の画面に戻る
+3a2．システムがタスク詳細画面を表示する</t>
+    <rPh sb="13" eb="15">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>チュウシ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>チョクゼン</t>
+    </rPh>
+    <rPh sb="23" eb="25">
       <t>ガメン</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>モド</t>
+    </rPh>
+    <rPh sb="41" eb="45">
+      <t>ショウサイガメン</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>システムに登録されたタスクの内容を編集する</t>
+    <rPh sb="5" eb="7">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>ユーザーがシステムにログインしていること
+対象のタスクがシステムに存在すること</t>
+    <rPh sb="21" eb="23">
+      <t>タイショウ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ソンザイ</t>
+    </rPh>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>1．ユーザーがタスク詳細画面で編集するタスクを選択する
+2．システムがタスク編集画面を表示する
+3．ユーザーがタスクの編集内容を入力する
+4．ユーザーがタスクの編集を確定する
+5．システムが入力された内容と現在日時をデータベースに登録する
+6．システムがタスク編集完了画面を表示する</t>
+    <rPh sb="10" eb="14">
+      <t>ショウサイガメン</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="38" eb="42">
+      <t>ヘンシュウガメン</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="59" eb="61">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="61" eb="63">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="64" eb="66">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="80" eb="82">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="83" eb="85">
+      <t>カクテイ</t>
+    </rPh>
+    <rPh sb="130" eb="132">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="132" eb="136">
+      <t>カンリョウガメン</t>
+    </rPh>
+    <rPh sb="137" eb="139">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>5a．ユーザーが確定した内容が編集前と同一だった場合
+5a1．システムがエラー画面を表示する</t>
+    <rPh sb="8" eb="10">
+      <t>カクテイ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="15" eb="18">
+      <t>ヘンシュウマエ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ドウイツ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>バアイ</t>
+    </rPh>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>タスク編集完了画面</t>
+    <rPh sb="3" eb="5">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>タスク編集エラー画面</t>
+    <rPh sb="3" eb="5">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>編集画面へ</t>
+    <rPh sb="0" eb="4">
+      <t>ヘンシュウガメン</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>編集画面へ</t>
+    <rPh sb="0" eb="5">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>task-detail.jsp</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>詳細画面へ</t>
+    <rPh sb="0" eb="4">
+      <t>ショウサイガメン</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
@@ -1461,7 +1443,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="146">
+  <cellXfs count="148">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1582,7 +1564,55 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1591,39 +1621,198 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1633,272 +1822,71 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1922,23 +1910,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:rowOff>28574</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>209550</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:colOff>714015</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1">
+        <xdr:cNvPr id="3" name="図 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{638F80EF-0657-B0D1-BCB0-1CD2286DFA7E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{887D1A6A-9305-1C05-CEEE-A80BEF9A9087}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1947,7 +1935,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -1961,8 +1949,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="381000" y="1762125"/>
-          <a:ext cx="7543800" cy="2571750"/>
+          <a:off x="0" y="1752599"/>
+          <a:ext cx="8429265" cy="2533651"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1989,22 +1977,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>85285</xdr:rowOff>
+      <xdr:colOff>314324</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>714375</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:colOff>838549</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1">
+        <xdr:cNvPr id="3" name="図 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9EBAB3EE-346E-8AEA-3158-AB5A964EE157}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F506DE54-407A-E40F-F872-6736BBF4D81E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2027,8 +2015,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="304800" y="999685"/>
-          <a:ext cx="8124825" cy="4467665"/>
+          <a:off x="314324" y="1209675"/>
+          <a:ext cx="8239475" cy="3914775"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2055,22 +2043,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>2</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>53081</xdr:rowOff>
+      <xdr:colOff>561622</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>44823</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>89648</xdr:colOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>717739</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>333815</xdr:rowOff>
+      <xdr:rowOff>11206</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1">
+        <xdr:cNvPr id="5" name="図 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7D02D29E-233D-3B68-3D78-457675E302E2}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A16BE109-DC49-C7FC-93DA-EF8C538BAADD}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2093,8 +2081,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="2151531" y="1577081"/>
-          <a:ext cx="4527176" cy="3104616"/>
+          <a:off x="2713151" y="2039470"/>
+          <a:ext cx="3484264" cy="2319618"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2120,23 +2108,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>1019736</xdr:colOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>134470</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>78442</xdr:rowOff>
+      <xdr:rowOff>403411</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>156882</xdr:colOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>738230</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>420078</xdr:rowOff>
+      <xdr:rowOff>122143</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="図 4">
+        <xdr:cNvPr id="2" name="図 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{56D6AB1A-A3C3-C0ED-57B7-4143816F98A1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FCEEF59C-ED27-2C50-F934-940FDD938CAF}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2159,8 +2147,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="2061883" y="1602442"/>
-          <a:ext cx="4684058" cy="3165518"/>
+          <a:off x="2285999" y="1927411"/>
+          <a:ext cx="3931907" cy="2542614"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2186,23 +2174,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>728382</xdr:colOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>134472</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>11207</xdr:rowOff>
+      <xdr:rowOff>364885</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>100853</xdr:colOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>784413</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>364191</xdr:rowOff>
+      <xdr:rowOff>189380</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2">
+        <xdr:cNvPr id="2" name="図 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A4554BFA-39B2-086D-73C8-3970B19913E0}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E62157B6-5D62-F4F6-6193-71650CC90586}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2225,8 +2213,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="1770529" y="1535207"/>
-          <a:ext cx="4919383" cy="3176866"/>
+          <a:off x="2286001" y="1888885"/>
+          <a:ext cx="3978088" cy="2648377"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2455,85 +2443,85 @@
   <sheetData>
     <row r="1" spans="3:16" ht="30" customHeight="1"/>
     <row r="2" spans="3:16" ht="30" customHeight="1">
-      <c r="C2" s="67" t="s">
+      <c r="C2" s="79" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="68"/>
-      <c r="E2" s="68"/>
-      <c r="F2" s="68"/>
-      <c r="G2" s="68"/>
-      <c r="H2" s="68"/>
-      <c r="I2" s="68"/>
-      <c r="J2" s="68"/>
-      <c r="K2" s="68"/>
-      <c r="L2" s="68"/>
-      <c r="M2" s="68"/>
-      <c r="N2" s="68"/>
-      <c r="O2" s="68"/>
+      <c r="D2" s="80"/>
+      <c r="E2" s="80"/>
+      <c r="F2" s="80"/>
+      <c r="G2" s="80"/>
+      <c r="H2" s="80"/>
+      <c r="I2" s="80"/>
+      <c r="J2" s="80"/>
+      <c r="K2" s="80"/>
+      <c r="L2" s="80"/>
+      <c r="M2" s="80"/>
+      <c r="N2" s="80"/>
+      <c r="O2" s="80"/>
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="52"/>
-      <c r="D3" s="52"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="52"/>
-      <c r="G3" s="52"/>
-      <c r="H3" s="52"/>
-      <c r="I3" s="52"/>
-      <c r="J3" s="52"/>
-      <c r="K3" s="52"/>
-      <c r="L3" s="52"/>
-      <c r="M3" s="52"/>
-      <c r="N3" s="52"/>
-      <c r="O3" s="52"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="64"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="64"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="64"/>
+      <c r="I3" s="64"/>
+      <c r="J3" s="64"/>
+      <c r="K3" s="64"/>
+      <c r="L3" s="64"/>
+      <c r="M3" s="64"/>
+      <c r="N3" s="64"/>
+      <c r="O3" s="64"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="52"/>
-      <c r="D4" s="52"/>
-      <c r="E4" s="52"/>
-      <c r="F4" s="52"/>
-      <c r="G4" s="52"/>
-      <c r="H4" s="52"/>
-      <c r="I4" s="52"/>
-      <c r="J4" s="52"/>
-      <c r="K4" s="52"/>
-      <c r="L4" s="52"/>
-      <c r="M4" s="52"/>
-      <c r="N4" s="52"/>
-      <c r="O4" s="52"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="64"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="64"/>
+      <c r="I4" s="64"/>
+      <c r="J4" s="64"/>
+      <c r="K4" s="64"/>
+      <c r="L4" s="64"/>
+      <c r="M4" s="64"/>
+      <c r="N4" s="64"/>
+      <c r="O4" s="64"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="52"/>
-      <c r="D5" s="52"/>
-      <c r="E5" s="52"/>
-      <c r="F5" s="52"/>
-      <c r="G5" s="52"/>
-      <c r="H5" s="52"/>
-      <c r="I5" s="52"/>
-      <c r="J5" s="52"/>
-      <c r="K5" s="52"/>
-      <c r="L5" s="52"/>
-      <c r="M5" s="52"/>
-      <c r="N5" s="52"/>
-      <c r="O5" s="52"/>
+      <c r="C5" s="64"/>
+      <c r="D5" s="64"/>
+      <c r="E5" s="64"/>
+      <c r="F5" s="64"/>
+      <c r="G5" s="64"/>
+      <c r="H5" s="64"/>
+      <c r="I5" s="64"/>
+      <c r="J5" s="64"/>
+      <c r="K5" s="64"/>
+      <c r="L5" s="64"/>
+      <c r="M5" s="64"/>
+      <c r="N5" s="64"/>
+      <c r="O5" s="64"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="52"/>
-      <c r="D6" s="52"/>
-      <c r="E6" s="52"/>
-      <c r="F6" s="52"/>
-      <c r="G6" s="52"/>
-      <c r="H6" s="52"/>
-      <c r="I6" s="52"/>
-      <c r="J6" s="52"/>
-      <c r="K6" s="52"/>
-      <c r="L6" s="52"/>
-      <c r="M6" s="52"/>
-      <c r="N6" s="52"/>
-      <c r="O6" s="52"/>
+      <c r="C6" s="64"/>
+      <c r="D6" s="64"/>
+      <c r="E6" s="64"/>
+      <c r="F6" s="64"/>
+      <c r="G6" s="64"/>
+      <c r="H6" s="64"/>
+      <c r="I6" s="64"/>
+      <c r="J6" s="64"/>
+      <c r="K6" s="64"/>
+      <c r="L6" s="64"/>
+      <c r="M6" s="64"/>
+      <c r="N6" s="64"/>
+      <c r="O6" s="64"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -2553,46 +2541,46 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="69" t="s">
-        <v>121</v>
-      </c>
-      <c r="F8" s="52"/>
-      <c r="G8" s="52"/>
-      <c r="H8" s="52"/>
-      <c r="I8" s="52"/>
-      <c r="J8" s="52"/>
-      <c r="K8" s="52"/>
-      <c r="L8" s="52"/>
-      <c r="M8" s="52"/>
+      <c r="E8" s="81" t="s">
+        <v>105</v>
+      </c>
+      <c r="F8" s="64"/>
+      <c r="G8" s="64"/>
+      <c r="H8" s="64"/>
+      <c r="I8" s="64"/>
+      <c r="J8" s="64"/>
+      <c r="K8" s="64"/>
+      <c r="L8" s="64"/>
+      <c r="M8" s="64"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="63" t="s">
+      <c r="G13" s="77" t="s">
         <v>1</v>
       </c>
-      <c r="H13" s="65"/>
-      <c r="I13" s="63" t="s">
-        <v>2</v>
-      </c>
-      <c r="J13" s="64"/>
-      <c r="K13" s="65"/>
+      <c r="H13" s="48"/>
+      <c r="I13" s="146">
+        <v>46129</v>
+      </c>
+      <c r="J13" s="44"/>
+      <c r="K13" s="48"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="63"/>
-      <c r="H14" s="65"/>
-      <c r="I14" s="63"/>
-      <c r="J14" s="64"/>
-      <c r="K14" s="65"/>
+      <c r="G14" s="77"/>
+      <c r="H14" s="48"/>
+      <c r="I14" s="77"/>
+      <c r="J14" s="44"/>
+      <c r="K14" s="48"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="63"/>
-      <c r="H15" s="65"/>
-      <c r="I15" s="63"/>
-      <c r="J15" s="64"/>
-      <c r="K15" s="65"/>
+      <c r="G15" s="77"/>
+      <c r="H15" s="48"/>
+      <c r="I15" s="77"/>
+      <c r="J15" s="44"/>
+      <c r="K15" s="48"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -2601,13 +2589,13 @@
       <c r="J16" s="3"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="66" t="s">
-        <v>122</v>
-      </c>
-      <c r="H17" s="52"/>
-      <c r="I17" s="52"/>
-      <c r="J17" s="52"/>
-      <c r="K17" s="52"/>
+      <c r="G17" s="78" t="s">
+        <v>106</v>
+      </c>
+      <c r="H17" s="64"/>
+      <c r="I17" s="64"/>
+      <c r="J17" s="64"/>
+      <c r="K17" s="64"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -3622,214 +3610,216 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="85" t="s">
+      <c r="A1" s="101" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="102"/>
+      <c r="C1" s="103"/>
+      <c r="D1" s="112" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="86"/>
-      <c r="C1" s="87"/>
-      <c r="D1" s="70" t="s">
+      <c r="E1" s="111"/>
+      <c r="F1" s="112" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="71"/>
-      <c r="F1" s="70" t="s">
+      <c r="G1" s="111"/>
+      <c r="H1" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="71"/>
-      <c r="H1" s="39" t="s">
+      <c r="I1" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="39" t="s">
+      <c r="J1" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="38" t="s">
+    </row>
+    <row r="2" spans="1:10" ht="18" customHeight="1">
+      <c r="A2" s="104"/>
+      <c r="B2" s="105"/>
+      <c r="C2" s="106"/>
+      <c r="D2" s="113" t="s">
+        <v>68</v>
+      </c>
+      <c r="E2" s="114"/>
+      <c r="F2" s="113" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2" s="114"/>
+      <c r="H2" s="117">
+        <v>46121</v>
+      </c>
+      <c r="I2" s="120" t="s">
+        <v>66</v>
+      </c>
+      <c r="J2" s="90"/>
+    </row>
+    <row r="3" spans="1:10" ht="18" customHeight="1">
+      <c r="A3" s="104"/>
+      <c r="B3" s="105"/>
+      <c r="C3" s="106"/>
+      <c r="D3" s="115"/>
+      <c r="E3" s="106"/>
+      <c r="F3" s="115"/>
+      <c r="G3" s="106"/>
+      <c r="H3" s="118"/>
+      <c r="I3" s="118"/>
+      <c r="J3" s="91"/>
+    </row>
+    <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
+      <c r="A4" s="107"/>
+      <c r="B4" s="108"/>
+      <c r="C4" s="109"/>
+      <c r="D4" s="116"/>
+      <c r="E4" s="109"/>
+      <c r="F4" s="116"/>
+      <c r="G4" s="109"/>
+      <c r="H4" s="119"/>
+      <c r="I4" s="119"/>
+      <c r="J4" s="92"/>
+    </row>
+    <row r="5" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A5" s="110" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="88"/>
-      <c r="B2" s="89"/>
-      <c r="C2" s="75"/>
-      <c r="D2" s="72" t="s">
-        <v>72</v>
-      </c>
-      <c r="E2" s="73"/>
-      <c r="F2" s="72" t="s">
-        <v>71</v>
-      </c>
-      <c r="G2" s="73"/>
-      <c r="H2" s="78">
-        <v>46121</v>
-      </c>
-      <c r="I2" s="81" t="s">
-        <v>70</v>
-      </c>
-      <c r="J2" s="97"/>
-    </row>
-    <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="88"/>
-      <c r="B3" s="89"/>
-      <c r="C3" s="75"/>
-      <c r="D3" s="74"/>
-      <c r="E3" s="75"/>
-      <c r="F3" s="74"/>
-      <c r="G3" s="75"/>
-      <c r="H3" s="79"/>
-      <c r="I3" s="79"/>
-      <c r="J3" s="98"/>
-    </row>
-    <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="90"/>
-      <c r="B4" s="91"/>
-      <c r="C4" s="77"/>
-      <c r="D4" s="76"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="76"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="80"/>
-      <c r="I4" s="80"/>
-      <c r="J4" s="99"/>
-    </row>
-    <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="92" t="s">
+      <c r="B5" s="85"/>
+      <c r="C5" s="111"/>
+      <c r="D5" s="86" t="s">
+        <v>65</v>
+      </c>
+      <c r="E5" s="87"/>
+      <c r="F5" s="87"/>
+      <c r="G5" s="87"/>
+      <c r="H5" s="87"/>
+      <c r="I5" s="87"/>
+      <c r="J5" s="88"/>
+    </row>
+    <row r="6" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A6" s="95" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="93"/>
-      <c r="C5" s="71"/>
-      <c r="D5" s="109" t="s">
-        <v>69</v>
-      </c>
-      <c r="E5" s="93"/>
-      <c r="F5" s="93"/>
-      <c r="G5" s="93"/>
-      <c r="H5" s="93"/>
-      <c r="I5" s="93"/>
-      <c r="J5" s="110"/>
-    </row>
-    <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="94" t="s">
+      <c r="B6" s="87"/>
+      <c r="C6" s="94"/>
+      <c r="D6" s="86" t="s">
+        <v>113</v>
+      </c>
+      <c r="E6" s="87"/>
+      <c r="F6" s="87"/>
+      <c r="G6" s="87"/>
+      <c r="H6" s="87"/>
+      <c r="I6" s="87"/>
+      <c r="J6" s="88"/>
+    </row>
+    <row r="7" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A7" s="95" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="95"/>
-      <c r="C6" s="96"/>
-      <c r="D6" s="101" t="s">
-        <v>68</v>
-      </c>
-      <c r="E6" s="95"/>
-      <c r="F6" s="95"/>
-      <c r="G6" s="95"/>
-      <c r="H6" s="95"/>
-      <c r="I6" s="95"/>
-      <c r="J6" s="102"/>
-    </row>
-    <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="94" t="s">
+      <c r="B7" s="87"/>
+      <c r="C7" s="94"/>
+      <c r="D7" s="86" t="s">
+        <v>64</v>
+      </c>
+      <c r="E7" s="87"/>
+      <c r="F7" s="87"/>
+      <c r="G7" s="87"/>
+      <c r="H7" s="87"/>
+      <c r="I7" s="87"/>
+      <c r="J7" s="88"/>
+    </row>
+    <row r="8" spans="1:10" ht="31.5" customHeight="1">
+      <c r="A8" s="95" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="95"/>
-      <c r="C7" s="96"/>
-      <c r="D7" s="101" t="s">
-        <v>67</v>
-      </c>
-      <c r="E7" s="95"/>
-      <c r="F7" s="95"/>
-      <c r="G7" s="95"/>
-      <c r="H7" s="95"/>
-      <c r="I7" s="95"/>
-      <c r="J7" s="102"/>
-    </row>
-    <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="94" t="s">
+      <c r="B8" s="87"/>
+      <c r="C8" s="94"/>
+      <c r="D8" s="89" t="s">
+        <v>114</v>
+      </c>
+      <c r="E8" s="87"/>
+      <c r="F8" s="87"/>
+      <c r="G8" s="87"/>
+      <c r="H8" s="87"/>
+      <c r="I8" s="87"/>
+      <c r="J8" s="88"/>
+    </row>
+    <row r="9" spans="1:10" ht="93.75" customHeight="1">
+      <c r="A9" s="96" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="95"/>
-      <c r="C8" s="96"/>
-      <c r="D8" s="101" t="s">
-        <v>66</v>
-      </c>
-      <c r="E8" s="95"/>
-      <c r="F8" s="95"/>
-      <c r="G8" s="95"/>
-      <c r="H8" s="95"/>
-      <c r="I8" s="95"/>
-      <c r="J8" s="102"/>
-    </row>
-    <row r="9" spans="1:10" ht="78" customHeight="1">
-      <c r="A9" s="104" t="s">
+      <c r="B9" s="93" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="100" t="s">
+      <c r="C9" s="94"/>
+      <c r="D9" s="89" t="s">
+        <v>115</v>
+      </c>
+      <c r="E9" s="87"/>
+      <c r="F9" s="87"/>
+      <c r="G9" s="87"/>
+      <c r="H9" s="87"/>
+      <c r="I9" s="87"/>
+      <c r="J9" s="88"/>
+    </row>
+    <row r="10" spans="1:10" ht="64.5" customHeight="1">
+      <c r="A10" s="97"/>
+      <c r="B10" s="93" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="96"/>
-      <c r="D9" s="103" t="s">
-        <v>117</v>
-      </c>
-      <c r="E9" s="95"/>
-      <c r="F9" s="95"/>
-      <c r="G9" s="95"/>
-      <c r="H9" s="95"/>
-      <c r="I9" s="95"/>
-      <c r="J9" s="102"/>
-    </row>
-    <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="105"/>
-      <c r="B10" s="100" t="s">
+      <c r="C10" s="94"/>
+      <c r="D10" s="89" t="s">
+        <v>112</v>
+      </c>
+      <c r="E10" s="87"/>
+      <c r="F10" s="87"/>
+      <c r="G10" s="87"/>
+      <c r="H10" s="87"/>
+      <c r="I10" s="87"/>
+      <c r="J10" s="88"/>
+    </row>
+    <row r="11" spans="1:10" ht="64.5" customHeight="1">
+      <c r="A11" s="98"/>
+      <c r="B11" s="93" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="96"/>
-      <c r="D10" s="101"/>
-      <c r="E10" s="95"/>
-      <c r="F10" s="95"/>
-      <c r="G10" s="95"/>
-      <c r="H10" s="95"/>
-      <c r="I10" s="95"/>
-      <c r="J10" s="102"/>
-    </row>
-    <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="106"/>
-      <c r="B11" s="100" t="s">
+      <c r="C11" s="94"/>
+      <c r="D11" s="89" t="s">
+        <v>116</v>
+      </c>
+      <c r="E11" s="87"/>
+      <c r="F11" s="87"/>
+      <c r="G11" s="87"/>
+      <c r="H11" s="87"/>
+      <c r="I11" s="87"/>
+      <c r="J11" s="88"/>
+    </row>
+    <row r="12" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A12" s="95" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="96"/>
-      <c r="D11" s="103" t="s">
-        <v>123</v>
-      </c>
-      <c r="E11" s="95"/>
-      <c r="F11" s="95"/>
-      <c r="G11" s="95"/>
-      <c r="H11" s="95"/>
-      <c r="I11" s="95"/>
-      <c r="J11" s="102"/>
-    </row>
-    <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="94" t="s">
+      <c r="B12" s="87"/>
+      <c r="C12" s="94"/>
+      <c r="D12" s="86" t="s">
+        <v>111</v>
+      </c>
+      <c r="E12" s="87"/>
+      <c r="F12" s="87"/>
+      <c r="G12" s="87"/>
+      <c r="H12" s="87"/>
+      <c r="I12" s="87"/>
+      <c r="J12" s="88"/>
+    </row>
+    <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
+      <c r="A13" s="99" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="95"/>
-      <c r="C12" s="96"/>
-      <c r="D12" s="101" t="s">
-        <v>65</v>
-      </c>
-      <c r="E12" s="95"/>
-      <c r="F12" s="95"/>
-      <c r="G12" s="95"/>
-      <c r="H12" s="95"/>
-      <c r="I12" s="95"/>
-      <c r="J12" s="102"/>
-    </row>
-    <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A13" s="82" t="s">
-        <v>18</v>
-      </c>
       <c r="B13" s="83"/>
-      <c r="C13" s="84"/>
-      <c r="D13" s="107"/>
+      <c r="C13" s="100"/>
+      <c r="D13" s="82"/>
       <c r="E13" s="83"/>
       <c r="F13" s="83"/>
       <c r="G13" s="83"/>
       <c r="H13" s="83"/>
       <c r="I13" s="83"/>
-      <c r="J13" s="108"/>
+      <c r="J13" s="84"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -4820,13 +4810,17 @@
     <row r="1000" s="37" customFormat="1" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="D13:J13"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="D7:J7"/>
-    <mergeCell ref="D8:J8"/>
-    <mergeCell ref="D9:J9"/>
-    <mergeCell ref="D10:J10"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A7:C7"/>
     <mergeCell ref="J2:J4"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B11:C11"/>
@@ -4836,17 +4830,13 @@
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A9:A11"/>
     <mergeCell ref="B9:C9"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="D13:J13"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="D7:J7"/>
+    <mergeCell ref="D8:J8"/>
+    <mergeCell ref="D9:J9"/>
+    <mergeCell ref="D10:J10"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -4865,72 +4855,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="48" t="s">
-        <v>19</v>
-      </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="50"/>
-      <c r="D1" s="57" t="s">
+      <c r="A1" s="60" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="61"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="55" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="56"/>
+      <c r="F1" s="55" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="58"/>
-      <c r="F1" s="57" t="s">
+      <c r="G1" s="56"/>
+      <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="58"/>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="J1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="6" t="s">
-        <v>8</v>
-      </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="51"/>
-      <c r="B2" s="52"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="59" t="s">
-        <v>94</v>
-      </c>
-      <c r="E2" s="60"/>
-      <c r="F2" s="59" t="s">
-        <v>95</v>
-      </c>
-      <c r="G2" s="60"/>
-      <c r="H2" s="41">
+      <c r="A2" s="63"/>
+      <c r="B2" s="64"/>
+      <c r="C2" s="65"/>
+      <c r="D2" s="68" t="s">
+        <v>86</v>
+      </c>
+      <c r="E2" s="69"/>
+      <c r="F2" s="68" t="s">
+        <v>87</v>
+      </c>
+      <c r="G2" s="69"/>
+      <c r="H2" s="57">
         <v>46125</v>
       </c>
-      <c r="I2" s="44" t="s">
-        <v>96</v>
-      </c>
-      <c r="J2" s="45"/>
+      <c r="I2" s="59" t="s">
+        <v>88</v>
+      </c>
+      <c r="J2" s="52"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="51"/>
-      <c r="B3" s="52"/>
-      <c r="C3" s="53"/>
-      <c r="D3" s="61"/>
-      <c r="E3" s="53"/>
-      <c r="F3" s="61"/>
-      <c r="G3" s="53"/>
-      <c r="H3" s="42"/>
-      <c r="I3" s="42"/>
-      <c r="J3" s="46"/>
+      <c r="A3" s="63"/>
+      <c r="B3" s="64"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="70"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="70"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="53"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="54"/>
-      <c r="B4" s="55"/>
-      <c r="C4" s="56"/>
-      <c r="D4" s="62"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="62"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="43"/>
-      <c r="I4" s="43"/>
-      <c r="J4" s="47"/>
+      <c r="A4" s="123"/>
+      <c r="B4" s="124"/>
+      <c r="C4" s="125"/>
+      <c r="D4" s="126"/>
+      <c r="E4" s="125"/>
+      <c r="F4" s="126"/>
+      <c r="G4" s="125"/>
+      <c r="H4" s="121"/>
+      <c r="I4" s="121"/>
+      <c r="J4" s="122"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="7"/>
@@ -6286,72 +6276,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="48" t="s">
-        <v>20</v>
-      </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="50"/>
-      <c r="D1" s="57" t="s">
+      <c r="A1" s="60" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="61"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="55" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="56"/>
+      <c r="F1" s="55" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="58"/>
-      <c r="F1" s="57" t="s">
+      <c r="G1" s="56"/>
+      <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="58"/>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="J1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="6" t="s">
-        <v>8</v>
-      </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="51"/>
-      <c r="B2" s="52"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="59" t="s">
-        <v>94</v>
-      </c>
-      <c r="E2" s="60"/>
-      <c r="F2" s="59" t="s">
-        <v>95</v>
-      </c>
-      <c r="G2" s="60"/>
-      <c r="H2" s="41">
+      <c r="A2" s="63"/>
+      <c r="B2" s="64"/>
+      <c r="C2" s="65"/>
+      <c r="D2" s="68" t="s">
+        <v>86</v>
+      </c>
+      <c r="E2" s="69"/>
+      <c r="F2" s="68" t="s">
+        <v>87</v>
+      </c>
+      <c r="G2" s="69"/>
+      <c r="H2" s="57">
         <v>46122</v>
       </c>
-      <c r="I2" s="44" t="s">
-        <v>120</v>
-      </c>
-      <c r="J2" s="45"/>
+      <c r="I2" s="59" t="s">
+        <v>104</v>
+      </c>
+      <c r="J2" s="52"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="51"/>
-      <c r="B3" s="52"/>
-      <c r="C3" s="53"/>
-      <c r="D3" s="61"/>
-      <c r="E3" s="53"/>
-      <c r="F3" s="61"/>
-      <c r="G3" s="53"/>
-      <c r="H3" s="42"/>
-      <c r="I3" s="42"/>
-      <c r="J3" s="46"/>
+      <c r="A3" s="63"/>
+      <c r="B3" s="64"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="70"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="70"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="53"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="54"/>
-      <c r="B4" s="55"/>
-      <c r="C4" s="56"/>
-      <c r="D4" s="62"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="62"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="43"/>
-      <c r="I4" s="43"/>
-      <c r="J4" s="47"/>
+      <c r="A4" s="123"/>
+      <c r="B4" s="124"/>
+      <c r="C4" s="125"/>
+      <c r="D4" s="126"/>
+      <c r="E4" s="125"/>
+      <c r="F4" s="126"/>
+      <c r="G4" s="125"/>
+      <c r="H4" s="121"/>
+      <c r="I4" s="121"/>
+      <c r="J4" s="122"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="7"/>
@@ -6465,7 +6455,6 @@
       <c r="A14" s="7"/>
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
       <c r="E14" s="8"/>
       <c r="F14" s="8"/>
       <c r="G14" s="8"/>
@@ -7692,7 +7681,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J1001"/>
+  <dimension ref="A1:J1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="5.140625" customWidth="1"/>
@@ -7701,424 +7690,473 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="60" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="61"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="55" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="56"/>
+      <c r="F1" s="55" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="56"/>
+      <c r="H1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="18" customHeight="1">
+      <c r="A2" s="63"/>
+      <c r="B2" s="64"/>
+      <c r="C2" s="65"/>
+      <c r="D2" s="68" t="s">
+        <v>86</v>
+      </c>
+      <c r="E2" s="69"/>
+      <c r="F2" s="68" t="s">
+        <v>87</v>
+      </c>
+      <c r="G2" s="69"/>
+      <c r="H2" s="57">
+        <v>46121</v>
+      </c>
+      <c r="I2" s="59" t="s">
+        <v>88</v>
+      </c>
+      <c r="J2" s="52"/>
+    </row>
+    <row r="3" spans="1:10" ht="18" customHeight="1">
+      <c r="A3" s="63"/>
+      <c r="B3" s="64"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="70"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="70"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="53"/>
+    </row>
+    <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
+      <c r="A4" s="63"/>
+      <c r="B4" s="64"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="70"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="70"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="58"/>
+      <c r="J4" s="53"/>
+    </row>
+    <row r="5" spans="1:10" ht="28.5" customHeight="1">
+      <c r="A5" s="66" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="50"/>
-      <c r="D1" s="57" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" s="58"/>
-      <c r="F1" s="57" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="58"/>
-      <c r="H1" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="51"/>
-      <c r="B2" s="52"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="59" t="s">
+      <c r="B5" s="67"/>
+      <c r="C5" s="56"/>
+      <c r="D5" s="71" t="s">
+        <v>98</v>
+      </c>
+      <c r="E5" s="67"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="67"/>
+      <c r="H5" s="67"/>
+      <c r="I5" s="67"/>
+      <c r="J5" s="72"/>
+    </row>
+    <row r="6" spans="1:10" ht="21" customHeight="1">
+      <c r="A6" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="44"/>
+      <c r="C6" s="44"/>
+      <c r="D6" s="44"/>
+      <c r="E6" s="44"/>
+      <c r="F6" s="44"/>
+      <c r="G6" s="44"/>
+      <c r="H6" s="44"/>
+      <c r="I6" s="44"/>
+      <c r="J6" s="45"/>
+    </row>
+    <row r="7" spans="1:10" ht="36.75" customHeight="1">
+      <c r="A7" s="73"/>
+      <c r="B7" s="74"/>
+      <c r="C7" s="74"/>
+      <c r="D7" s="74"/>
+      <c r="E7" s="74"/>
+      <c r="F7" s="74"/>
+      <c r="G7" s="74"/>
+      <c r="H7" s="74"/>
+      <c r="I7" s="74"/>
+      <c r="J7" s="75"/>
+    </row>
+    <row r="8" spans="1:10" ht="36.75" customHeight="1">
+      <c r="A8" s="63"/>
+      <c r="B8" s="64"/>
+      <c r="C8" s="64"/>
+      <c r="D8" s="64"/>
+      <c r="E8" s="64"/>
+      <c r="F8" s="64"/>
+      <c r="G8" s="64"/>
+      <c r="H8" s="64"/>
+      <c r="I8" s="64"/>
+      <c r="J8" s="76"/>
+    </row>
+    <row r="9" spans="1:10" ht="36.75" customHeight="1">
+      <c r="A9" s="63"/>
+      <c r="B9" s="64"/>
+      <c r="C9" s="64"/>
+      <c r="D9" s="64"/>
+      <c r="E9" s="64"/>
+      <c r="F9" s="64"/>
+      <c r="G9" s="64"/>
+      <c r="H9" s="64"/>
+      <c r="I9" s="64"/>
+      <c r="J9" s="76"/>
+    </row>
+    <row r="10" spans="1:10" ht="36.75" customHeight="1">
+      <c r="A10" s="63"/>
+      <c r="B10" s="64"/>
+      <c r="C10" s="64"/>
+      <c r="D10" s="64"/>
+      <c r="E10" s="64"/>
+      <c r="F10" s="64"/>
+      <c r="G10" s="64"/>
+      <c r="H10" s="64"/>
+      <c r="I10" s="64"/>
+      <c r="J10" s="76"/>
+    </row>
+    <row r="11" spans="1:10" ht="36.75" customHeight="1">
+      <c r="A11" s="63"/>
+      <c r="B11" s="64"/>
+      <c r="C11" s="64"/>
+      <c r="D11" s="64"/>
+      <c r="E11" s="64"/>
+      <c r="F11" s="64"/>
+      <c r="G11" s="64"/>
+      <c r="H11" s="64"/>
+      <c r="I11" s="64"/>
+      <c r="J11" s="76"/>
+    </row>
+    <row r="12" spans="1:10" ht="36.75" customHeight="1">
+      <c r="A12" s="63"/>
+      <c r="B12" s="64"/>
+      <c r="C12" s="64"/>
+      <c r="D12" s="64"/>
+      <c r="E12" s="64"/>
+      <c r="F12" s="64"/>
+      <c r="G12" s="64"/>
+      <c r="H12" s="64"/>
+      <c r="I12" s="64"/>
+      <c r="J12" s="76"/>
+    </row>
+    <row r="13" spans="1:10" ht="36.75" customHeight="1">
+      <c r="A13" s="63"/>
+      <c r="B13" s="64"/>
+      <c r="C13" s="64"/>
+      <c r="D13" s="64"/>
+      <c r="E13" s="64"/>
+      <c r="F13" s="64"/>
+      <c r="G13" s="64"/>
+      <c r="H13" s="64"/>
+      <c r="I13" s="64"/>
+      <c r="J13" s="76"/>
+    </row>
+    <row r="14" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A14" s="51" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="44"/>
+      <c r="C14" s="44"/>
+      <c r="D14" s="44"/>
+      <c r="E14" s="44"/>
+      <c r="F14" s="44"/>
+      <c r="G14" s="44"/>
+      <c r="H14" s="44"/>
+      <c r="I14" s="44"/>
+      <c r="J14" s="45"/>
+    </row>
+    <row r="15" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A15" s="51" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" s="44"/>
+      <c r="C15" s="48"/>
+      <c r="D15" s="43" t="s">
+        <v>69</v>
+      </c>
+      <c r="E15" s="44"/>
+      <c r="F15" s="44"/>
+      <c r="G15" s="44"/>
+      <c r="H15" s="48"/>
+      <c r="I15" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="J15" s="15" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A16" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" s="44"/>
+      <c r="C16" s="48"/>
+      <c r="D16" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="E16" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="F16" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="G16" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="H16" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="I16" s="44"/>
+      <c r="J16" s="45"/>
+    </row>
+    <row r="17" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A17" s="47" t="s">
+        <v>71</v>
+      </c>
+      <c r="B17" s="44"/>
+      <c r="C17" s="48"/>
+      <c r="D17" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="E17" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="F17" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="G17" s="17"/>
+      <c r="H17" s="43" t="s">
+        <v>107</v>
+      </c>
+      <c r="I17" s="44"/>
+      <c r="J17" s="45"/>
+    </row>
+    <row r="18" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A18" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="B18" s="44"/>
+      <c r="C18" s="48"/>
+      <c r="D18" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="E18" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="F18" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="G18" s="17"/>
+      <c r="H18" s="43"/>
+      <c r="I18" s="44"/>
+      <c r="J18" s="45"/>
+    </row>
+    <row r="19" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A19" s="47" t="s">
+        <v>73</v>
+      </c>
+      <c r="B19" s="44"/>
+      <c r="C19" s="48"/>
+      <c r="D19" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="E19" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="F19" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="G19" s="141" t="s">
+        <v>108</v>
+      </c>
+      <c r="H19" s="143" t="s">
+        <v>109</v>
+      </c>
+      <c r="I19" s="44"/>
+      <c r="J19" s="45"/>
+    </row>
+    <row r="20" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A20" s="47" t="s">
+        <v>74</v>
+      </c>
+      <c r="B20" s="44"/>
+      <c r="C20" s="48"/>
+      <c r="D20" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="E20" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="F20" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="G20" s="17"/>
+      <c r="H20" s="43"/>
+      <c r="I20" s="44"/>
+      <c r="J20" s="45"/>
+    </row>
+    <row r="21" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A21" s="47" t="s">
+        <v>75</v>
+      </c>
+      <c r="B21" s="44"/>
+      <c r="C21" s="48"/>
+      <c r="D21" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="E21" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="F21" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="G21" s="17"/>
+      <c r="H21" s="43"/>
+      <c r="I21" s="44"/>
+      <c r="J21" s="45"/>
+    </row>
+    <row r="22" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A22" s="47" t="s">
+        <v>76</v>
+      </c>
+      <c r="B22" s="49"/>
+      <c r="C22" s="50"/>
+      <c r="D22" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="E2" s="60"/>
-      <c r="F2" s="59" t="s">
-        <v>95</v>
-      </c>
-      <c r="G2" s="60"/>
-      <c r="H2" s="41">
-        <v>46121</v>
-      </c>
-      <c r="I2" s="44" t="s">
-        <v>96</v>
-      </c>
-      <c r="J2" s="45"/>
-    </row>
-    <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="51"/>
-      <c r="B3" s="52"/>
-      <c r="C3" s="53"/>
-      <c r="D3" s="61"/>
-      <c r="E3" s="53"/>
-      <c r="F3" s="61"/>
-      <c r="G3" s="53"/>
-      <c r="H3" s="42"/>
-      <c r="I3" s="42"/>
-      <c r="J3" s="46"/>
-    </row>
-    <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="51"/>
-      <c r="B4" s="52"/>
-      <c r="C4" s="53"/>
-      <c r="D4" s="61"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="61"/>
-      <c r="G4" s="53"/>
-      <c r="H4" s="42"/>
-      <c r="I4" s="42"/>
-      <c r="J4" s="46"/>
-    </row>
-    <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="116" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5" s="117"/>
-      <c r="C5" s="58"/>
-      <c r="D5" s="119" t="s">
-        <v>109</v>
-      </c>
-      <c r="E5" s="117"/>
-      <c r="F5" s="117"/>
-      <c r="G5" s="117"/>
-      <c r="H5" s="117"/>
-      <c r="I5" s="117"/>
-      <c r="J5" s="120"/>
-    </row>
-    <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="118" t="s">
+      <c r="E22" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="F22" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="G22" s="141" t="s">
+        <v>108</v>
+      </c>
+      <c r="H22" s="43" t="s">
+        <v>110</v>
+      </c>
+      <c r="I22" s="144"/>
+      <c r="J22" s="145"/>
+    </row>
+    <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
+      <c r="A23" s="40" t="s">
+        <v>77</v>
+      </c>
+      <c r="B23" s="41"/>
+      <c r="C23" s="42"/>
+      <c r="D23" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="E23" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="F23" s="19"/>
+      <c r="G23" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="H23" s="46"/>
+      <c r="I23" s="134"/>
+      <c r="J23" s="142"/>
+    </row>
+    <row r="24" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A24" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="64"/>
-      <c r="C6" s="64"/>
-      <c r="D6" s="64"/>
-      <c r="E6" s="64"/>
-      <c r="F6" s="64"/>
-      <c r="G6" s="64"/>
-      <c r="H6" s="64"/>
-      <c r="I6" s="64"/>
-      <c r="J6" s="112"/>
-    </row>
-    <row r="7" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A7" s="121"/>
-      <c r="B7" s="122"/>
-      <c r="C7" s="122"/>
-      <c r="D7" s="122"/>
-      <c r="E7" s="122"/>
-      <c r="F7" s="122"/>
-      <c r="G7" s="122"/>
-      <c r="H7" s="122"/>
-      <c r="I7" s="122"/>
-      <c r="J7" s="123"/>
-    </row>
-    <row r="8" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A8" s="51"/>
-      <c r="B8" s="52"/>
-      <c r="C8" s="52"/>
-      <c r="D8" s="52"/>
-      <c r="E8" s="52"/>
-      <c r="F8" s="52"/>
-      <c r="G8" s="52"/>
-      <c r="H8" s="52"/>
-      <c r="I8" s="52"/>
-      <c r="J8" s="124"/>
-    </row>
-    <row r="9" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A9" s="51"/>
-      <c r="B9" s="52"/>
-      <c r="C9" s="52"/>
-      <c r="D9" s="52"/>
-      <c r="E9" s="52"/>
-      <c r="F9" s="52"/>
-      <c r="G9" s="52"/>
-      <c r="H9" s="52"/>
-      <c r="I9" s="52"/>
-      <c r="J9" s="124"/>
-    </row>
-    <row r="10" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A10" s="51"/>
-      <c r="B10" s="52"/>
-      <c r="C10" s="52"/>
-      <c r="D10" s="52"/>
-      <c r="E10" s="52"/>
-      <c r="F10" s="52"/>
-      <c r="G10" s="52"/>
-      <c r="H10" s="52"/>
-      <c r="I10" s="52"/>
-      <c r="J10" s="124"/>
-    </row>
-    <row r="11" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A11" s="51"/>
-      <c r="B11" s="52"/>
-      <c r="C11" s="52"/>
-      <c r="D11" s="52"/>
-      <c r="E11" s="52"/>
-      <c r="F11" s="52"/>
-      <c r="G11" s="52"/>
-      <c r="H11" s="52"/>
-      <c r="I11" s="52"/>
-      <c r="J11" s="124"/>
-    </row>
-    <row r="12" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A12" s="51"/>
-      <c r="B12" s="52"/>
-      <c r="C12" s="52"/>
-      <c r="D12" s="52"/>
-      <c r="E12" s="52"/>
-      <c r="F12" s="52"/>
-      <c r="G12" s="52"/>
-      <c r="H12" s="52"/>
-      <c r="I12" s="52"/>
-      <c r="J12" s="124"/>
-    </row>
-    <row r="13" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A13" s="51"/>
-      <c r="B13" s="52"/>
-      <c r="C13" s="52"/>
-      <c r="D13" s="52"/>
-      <c r="E13" s="52"/>
-      <c r="F13" s="52"/>
-      <c r="G13" s="52"/>
-      <c r="H13" s="52"/>
-      <c r="I13" s="52"/>
-      <c r="J13" s="124"/>
-    </row>
-    <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="118" t="s">
+      <c r="B24" s="44"/>
+      <c r="C24" s="44"/>
+      <c r="D24" s="44"/>
+      <c r="E24" s="44"/>
+      <c r="F24" s="44"/>
+      <c r="G24" s="44"/>
+      <c r="H24" s="44"/>
+      <c r="I24" s="44"/>
+      <c r="J24" s="45"/>
+    </row>
+    <row r="25" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A25" s="51" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="64"/>
-      <c r="C14" s="64"/>
-      <c r="D14" s="64"/>
-      <c r="E14" s="64"/>
-      <c r="F14" s="64"/>
-      <c r="G14" s="64"/>
-      <c r="H14" s="64"/>
-      <c r="I14" s="64"/>
-      <c r="J14" s="112"/>
-    </row>
-    <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="118" t="s">
+      <c r="B25" s="44"/>
+      <c r="C25" s="48"/>
+      <c r="D25" s="43" t="s">
+        <v>121</v>
+      </c>
+      <c r="E25" s="44"/>
+      <c r="F25" s="44"/>
+      <c r="G25" s="44"/>
+      <c r="H25" s="48"/>
+      <c r="I25" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="64"/>
-      <c r="C15" s="65"/>
-      <c r="D15" s="111" t="s">
-        <v>73</v>
-      </c>
-      <c r="E15" s="64"/>
-      <c r="F15" s="64"/>
-      <c r="G15" s="64"/>
-      <c r="H15" s="65"/>
-      <c r="I15" s="14" t="s">
+      <c r="J25" s="15" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A26" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="J15" s="15" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="118" t="s">
+      <c r="B26" s="44"/>
+      <c r="C26" s="48"/>
+      <c r="D26" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="B16" s="64"/>
-      <c r="C16" s="65"/>
-      <c r="D16" s="14" t="s">
+      <c r="E26" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="E16" s="14" t="s">
+      <c r="F26" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="F16" s="14" t="s">
+      <c r="G26" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="G16" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="H16" s="125" t="s">
-        <v>18</v>
-      </c>
-      <c r="I16" s="64"/>
-      <c r="J16" s="112"/>
-    </row>
-    <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="113" t="s">
-        <v>75</v>
-      </c>
-      <c r="B17" s="64"/>
-      <c r="C17" s="65"/>
-      <c r="D17" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="E17" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="F17" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="G17" s="17"/>
-      <c r="H17" s="111" t="s">
-        <v>90</v>
-      </c>
-      <c r="I17" s="64"/>
-      <c r="J17" s="112"/>
-    </row>
-    <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="113" t="s">
-        <v>76</v>
-      </c>
-      <c r="B18" s="64"/>
-      <c r="C18" s="65"/>
-      <c r="D18" s="16" t="s">
-        <v>98</v>
-      </c>
-      <c r="E18" s="16" t="s">
-        <v>105</v>
-      </c>
-      <c r="F18" s="17" t="s">
-        <v>104</v>
-      </c>
-      <c r="G18" s="17"/>
-      <c r="H18" s="111" t="s">
-        <v>106</v>
-      </c>
-      <c r="I18" s="64"/>
-      <c r="J18" s="112"/>
-    </row>
-    <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="113" t="s">
-        <v>77</v>
-      </c>
-      <c r="B19" s="64"/>
-      <c r="C19" s="65"/>
-      <c r="D19" s="16" t="s">
-        <v>99</v>
-      </c>
-      <c r="E19" s="16" t="s">
-        <v>86</v>
-      </c>
-      <c r="F19" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="G19" s="17"/>
-      <c r="H19" s="111" t="s">
-        <v>91</v>
-      </c>
-      <c r="I19" s="64"/>
-      <c r="J19" s="112"/>
-    </row>
-    <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="113" t="s">
+      <c r="H26" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="I26" s="44"/>
+      <c r="J26" s="45"/>
+    </row>
+    <row r="27" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
+      <c r="A27" s="40" t="s">
         <v>78</v>
       </c>
-      <c r="B20" s="64"/>
-      <c r="C20" s="65"/>
-      <c r="D20" s="16" t="s">
-        <v>100</v>
-      </c>
-      <c r="E20" s="16" t="s">
-        <v>105</v>
-      </c>
-      <c r="F20" s="17" t="s">
-        <v>119</v>
-      </c>
-      <c r="G20" s="17"/>
-      <c r="H20" s="111" t="s">
-        <v>107</v>
-      </c>
-      <c r="I20" s="64"/>
-      <c r="J20" s="112"/>
-    </row>
-    <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="113" t="s">
-        <v>79</v>
-      </c>
-      <c r="B21" s="64"/>
-      <c r="C21" s="65"/>
-      <c r="D21" s="16" t="s">
-        <v>101</v>
-      </c>
-      <c r="E21" s="16" t="s">
-        <v>105</v>
-      </c>
-      <c r="F21" s="17" t="s">
-        <v>103</v>
-      </c>
-      <c r="G21" s="17"/>
-      <c r="H21" s="111" t="s">
-        <v>108</v>
-      </c>
-      <c r="I21" s="64"/>
-      <c r="J21" s="112"/>
-    </row>
-    <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="113" t="s">
+      <c r="B27" s="41"/>
+      <c r="C27" s="42"/>
+      <c r="D27" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="E27" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="B22" s="114"/>
-      <c r="C22" s="115"/>
-      <c r="D22" s="16" t="s">
-        <v>102</v>
-      </c>
-      <c r="E22" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="F22" s="17" t="s">
-        <v>89</v>
-      </c>
-      <c r="G22" s="17"/>
-      <c r="H22" s="111" t="s">
-        <v>92</v>
-      </c>
-      <c r="I22" s="64"/>
-      <c r="J22" s="112"/>
-    </row>
-    <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="113" t="s">
-        <v>81</v>
-      </c>
-      <c r="B23" s="114"/>
-      <c r="C23" s="115"/>
-      <c r="D23" s="16" t="s">
-        <v>83</v>
-      </c>
-      <c r="E23" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="F23" s="17"/>
-      <c r="G23" s="17" t="s">
-        <v>83</v>
-      </c>
-      <c r="H23" s="111" t="s">
-        <v>93</v>
-      </c>
-      <c r="I23" s="64"/>
-      <c r="J23" s="112"/>
-    </row>
-    <row r="24" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A24" s="126" t="s">
-        <v>82</v>
-      </c>
-      <c r="B24" s="127"/>
-      <c r="C24" s="128"/>
-      <c r="D24" s="18" t="s">
-        <v>125</v>
-      </c>
-      <c r="E24" s="18" t="s">
-        <v>84</v>
-      </c>
-      <c r="F24" s="19"/>
-      <c r="G24" s="19" t="s">
-        <v>126</v>
-      </c>
-      <c r="H24" s="129" t="s">
-        <v>124</v>
-      </c>
-      <c r="I24" s="130"/>
-      <c r="J24" s="131"/>
-    </row>
-    <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
-    <row r="26" spans="1:10" ht="12.75" customHeight="1"/>
-    <row r="27" spans="1:10" ht="12.75" customHeight="1"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="H27" s="46"/>
+      <c r="I27" s="134"/>
+      <c r="J27" s="142"/>
+    </row>
     <row r="28" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="29" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="30" spans="1:10" ht="12.75" customHeight="1"/>
@@ -9092,20 +9130,18 @@
     <row r="998" ht="12.75" customHeight="1"/>
     <row r="999" ht="12.75" customHeight="1"/>
     <row r="1000" ht="12.75" customHeight="1"/>
-    <row r="1001" ht="12.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="33">
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="H24:J24"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:C20"/>
+  <mergeCells count="38">
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="H27:J27"/>
     <mergeCell ref="A23:C23"/>
     <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A24:J24"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="D25:H25"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="H26:J26"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="J2:J4"/>
     <mergeCell ref="H16:J16"/>
@@ -9114,20 +9150,26 @@
     <mergeCell ref="H2:H4"/>
     <mergeCell ref="D15:H15"/>
     <mergeCell ref="I2:I4"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
     <mergeCell ref="A1:C4"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="F2:G4"/>
-    <mergeCell ref="A21:C21"/>
     <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A17:C17"/>
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="A7:J13"/>
-    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A17:C17"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -9137,11 +9179,11 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C78CA393-23BF-41B0-813C-E687DA2E87EF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AA3E9D0-D005-485B-8D11-310BAE2ED20F}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J995"/>
+  <dimension ref="A1:J994"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="5.140625" customWidth="1"/>
@@ -9150,279 +9192,266 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="60" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="61"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="55" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="56"/>
+      <c r="F1" s="55" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="56"/>
+      <c r="H1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="18" customHeight="1">
+      <c r="A2" s="63"/>
+      <c r="B2" s="64"/>
+      <c r="C2" s="65"/>
+      <c r="D2" s="68" t="s">
+        <v>86</v>
+      </c>
+      <c r="E2" s="69"/>
+      <c r="F2" s="68" t="s">
+        <v>87</v>
+      </c>
+      <c r="G2" s="69"/>
+      <c r="H2" s="57">
+        <v>46121</v>
+      </c>
+      <c r="I2" s="59" t="s">
+        <v>88</v>
+      </c>
+      <c r="J2" s="52"/>
+    </row>
+    <row r="3" spans="1:10" ht="18" customHeight="1">
+      <c r="A3" s="63"/>
+      <c r="B3" s="64"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="70"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="70"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="53"/>
+    </row>
+    <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
+      <c r="A4" s="63"/>
+      <c r="B4" s="64"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="70"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="70"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="58"/>
+      <c r="J4" s="53"/>
+    </row>
+    <row r="5" spans="1:10" ht="28.5" customHeight="1">
+      <c r="A5" s="66" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="50"/>
-      <c r="D1" s="57" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" s="58"/>
-      <c r="F1" s="57" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="58"/>
-      <c r="H1" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="51"/>
-      <c r="B2" s="52"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="59" t="s">
-        <v>94</v>
-      </c>
-      <c r="E2" s="60"/>
-      <c r="F2" s="59" t="s">
-        <v>95</v>
-      </c>
-      <c r="G2" s="60"/>
-      <c r="H2" s="41">
-        <v>46121</v>
-      </c>
-      <c r="I2" s="44" t="s">
-        <v>96</v>
-      </c>
-      <c r="J2" s="45"/>
-    </row>
-    <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="51"/>
-      <c r="B3" s="52"/>
-      <c r="C3" s="53"/>
-      <c r="D3" s="61"/>
-      <c r="E3" s="53"/>
-      <c r="F3" s="61"/>
-      <c r="G3" s="53"/>
-      <c r="H3" s="42"/>
-      <c r="I3" s="42"/>
-      <c r="J3" s="46"/>
-    </row>
-    <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="51"/>
-      <c r="B4" s="52"/>
-      <c r="C4" s="53"/>
-      <c r="D4" s="61"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="61"/>
-      <c r="G4" s="53"/>
-      <c r="H4" s="42"/>
-      <c r="I4" s="42"/>
-      <c r="J4" s="46"/>
-    </row>
-    <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="116" t="s">
+      <c r="B5" s="67"/>
+      <c r="C5" s="56"/>
+      <c r="D5" s="71" t="s">
+        <v>117</v>
+      </c>
+      <c r="E5" s="67"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="67"/>
+      <c r="H5" s="67"/>
+      <c r="I5" s="67"/>
+      <c r="J5" s="72"/>
+    </row>
+    <row r="6" spans="1:10" ht="21" customHeight="1">
+      <c r="A6" s="51" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="117"/>
-      <c r="C5" s="58"/>
-      <c r="D5" s="119" t="s">
-        <v>110</v>
-      </c>
-      <c r="E5" s="117"/>
-      <c r="F5" s="117"/>
-      <c r="G5" s="117"/>
-      <c r="H5" s="117"/>
-      <c r="I5" s="117"/>
-      <c r="J5" s="120"/>
-    </row>
-    <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="118" t="s">
+      <c r="B6" s="44"/>
+      <c r="C6" s="44"/>
+      <c r="D6" s="44"/>
+      <c r="E6" s="44"/>
+      <c r="F6" s="44"/>
+      <c r="G6" s="44"/>
+      <c r="H6" s="44"/>
+      <c r="I6" s="44"/>
+      <c r="J6" s="45"/>
+    </row>
+    <row r="7" spans="1:10" ht="36.75" customHeight="1">
+      <c r="A7" s="73"/>
+      <c r="B7" s="74"/>
+      <c r="C7" s="74"/>
+      <c r="D7" s="74"/>
+      <c r="E7" s="74"/>
+      <c r="F7" s="74"/>
+      <c r="G7" s="74"/>
+      <c r="H7" s="74"/>
+      <c r="I7" s="74"/>
+      <c r="J7" s="75"/>
+    </row>
+    <row r="8" spans="1:10" ht="36.75" customHeight="1">
+      <c r="A8" s="63"/>
+      <c r="B8" s="64"/>
+      <c r="C8" s="64"/>
+      <c r="D8" s="64"/>
+      <c r="E8" s="64"/>
+      <c r="F8" s="64"/>
+      <c r="G8" s="64"/>
+      <c r="H8" s="64"/>
+      <c r="I8" s="64"/>
+      <c r="J8" s="76"/>
+    </row>
+    <row r="9" spans="1:10" ht="36.75" customHeight="1">
+      <c r="A9" s="63"/>
+      <c r="B9" s="64"/>
+      <c r="C9" s="64"/>
+      <c r="D9" s="64"/>
+      <c r="E9" s="64"/>
+      <c r="F9" s="64"/>
+      <c r="G9" s="64"/>
+      <c r="H9" s="64"/>
+      <c r="I9" s="64"/>
+      <c r="J9" s="76"/>
+    </row>
+    <row r="10" spans="1:10" ht="36.75" customHeight="1">
+      <c r="A10" s="63"/>
+      <c r="B10" s="64"/>
+      <c r="C10" s="64"/>
+      <c r="D10" s="64"/>
+      <c r="E10" s="64"/>
+      <c r="F10" s="64"/>
+      <c r="G10" s="64"/>
+      <c r="H10" s="64"/>
+      <c r="I10" s="64"/>
+      <c r="J10" s="76"/>
+    </row>
+    <row r="11" spans="1:10" ht="36.75" customHeight="1">
+      <c r="A11" s="63"/>
+      <c r="B11" s="64"/>
+      <c r="C11" s="64"/>
+      <c r="D11" s="64"/>
+      <c r="E11" s="64"/>
+      <c r="F11" s="64"/>
+      <c r="G11" s="64"/>
+      <c r="H11" s="64"/>
+      <c r="I11" s="64"/>
+      <c r="J11" s="76"/>
+    </row>
+    <row r="12" spans="1:10" ht="36.75" customHeight="1">
+      <c r="A12" s="63"/>
+      <c r="B12" s="64"/>
+      <c r="C12" s="64"/>
+      <c r="D12" s="64"/>
+      <c r="E12" s="64"/>
+      <c r="F12" s="64"/>
+      <c r="G12" s="64"/>
+      <c r="H12" s="64"/>
+      <c r="I12" s="64"/>
+      <c r="J12" s="76"/>
+    </row>
+    <row r="13" spans="1:10" ht="36.75" customHeight="1">
+      <c r="A13" s="63"/>
+      <c r="B13" s="64"/>
+      <c r="C13" s="64"/>
+      <c r="D13" s="64"/>
+      <c r="E13" s="64"/>
+      <c r="F13" s="64"/>
+      <c r="G13" s="64"/>
+      <c r="H13" s="64"/>
+      <c r="I13" s="64"/>
+      <c r="J13" s="76"/>
+    </row>
+    <row r="14" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A14" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="64"/>
-      <c r="C6" s="64"/>
-      <c r="D6" s="64"/>
-      <c r="E6" s="64"/>
-      <c r="F6" s="64"/>
-      <c r="G6" s="64"/>
-      <c r="H6" s="64"/>
-      <c r="I6" s="64"/>
-      <c r="J6" s="112"/>
-    </row>
-    <row r="7" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A7" s="121"/>
-      <c r="B7" s="122"/>
-      <c r="C7" s="122"/>
-      <c r="D7" s="122"/>
-      <c r="E7" s="122"/>
-      <c r="F7" s="122"/>
-      <c r="G7" s="122"/>
-      <c r="H7" s="122"/>
-      <c r="I7" s="122"/>
-      <c r="J7" s="123"/>
-    </row>
-    <row r="8" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A8" s="51"/>
-      <c r="B8" s="52"/>
-      <c r="C8" s="52"/>
-      <c r="D8" s="52"/>
-      <c r="E8" s="52"/>
-      <c r="F8" s="52"/>
-      <c r="G8" s="52"/>
-      <c r="H8" s="52"/>
-      <c r="I8" s="52"/>
-      <c r="J8" s="124"/>
-    </row>
-    <row r="9" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A9" s="51"/>
-      <c r="B9" s="52"/>
-      <c r="C9" s="52"/>
-      <c r="D9" s="52"/>
-      <c r="E9" s="52"/>
-      <c r="F9" s="52"/>
-      <c r="G9" s="52"/>
-      <c r="H9" s="52"/>
-      <c r="I9" s="52"/>
-      <c r="J9" s="124"/>
-    </row>
-    <row r="10" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A10" s="51"/>
-      <c r="B10" s="52"/>
-      <c r="C10" s="52"/>
-      <c r="D10" s="52"/>
-      <c r="E10" s="52"/>
-      <c r="F10" s="52"/>
-      <c r="G10" s="52"/>
-      <c r="H10" s="52"/>
-      <c r="I10" s="52"/>
-      <c r="J10" s="124"/>
-    </row>
-    <row r="11" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A11" s="51"/>
-      <c r="B11" s="52"/>
-      <c r="C11" s="52"/>
-      <c r="D11" s="52"/>
-      <c r="E11" s="52"/>
-      <c r="F11" s="52"/>
-      <c r="G11" s="52"/>
-      <c r="H11" s="52"/>
-      <c r="I11" s="52"/>
-      <c r="J11" s="124"/>
-    </row>
-    <row r="12" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A12" s="51"/>
-      <c r="B12" s="52"/>
-      <c r="C12" s="52"/>
-      <c r="D12" s="52"/>
-      <c r="E12" s="52"/>
-      <c r="F12" s="52"/>
-      <c r="G12" s="52"/>
-      <c r="H12" s="52"/>
-      <c r="I12" s="52"/>
-      <c r="J12" s="124"/>
-    </row>
-    <row r="13" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A13" s="51"/>
-      <c r="B13" s="52"/>
-      <c r="C13" s="52"/>
-      <c r="D13" s="52"/>
-      <c r="E13" s="52"/>
-      <c r="F13" s="52"/>
-      <c r="G13" s="52"/>
-      <c r="H13" s="52"/>
-      <c r="I13" s="52"/>
-      <c r="J13" s="124"/>
-    </row>
-    <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="118" t="s">
+      <c r="B14" s="44"/>
+      <c r="C14" s="44"/>
+      <c r="D14" s="44"/>
+      <c r="E14" s="44"/>
+      <c r="F14" s="44"/>
+      <c r="G14" s="44"/>
+      <c r="H14" s="44"/>
+      <c r="I14" s="44"/>
+      <c r="J14" s="45"/>
+    </row>
+    <row r="15" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A15" s="51" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="64"/>
-      <c r="C14" s="64"/>
-      <c r="D14" s="64"/>
-      <c r="E14" s="64"/>
-      <c r="F14" s="64"/>
-      <c r="G14" s="64"/>
-      <c r="H14" s="64"/>
-      <c r="I14" s="64"/>
-      <c r="J14" s="112"/>
-    </row>
-    <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="118" t="s">
+      <c r="B15" s="44"/>
+      <c r="C15" s="48"/>
+      <c r="D15" s="43" t="s">
+        <v>102</v>
+      </c>
+      <c r="E15" s="44"/>
+      <c r="F15" s="44"/>
+      <c r="G15" s="44"/>
+      <c r="H15" s="48"/>
+      <c r="I15" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="64"/>
-      <c r="C15" s="65"/>
-      <c r="D15" s="111" t="s">
-        <v>113</v>
-      </c>
-      <c r="E15" s="64"/>
-      <c r="F15" s="64"/>
-      <c r="G15" s="64"/>
-      <c r="H15" s="65"/>
-      <c r="I15" s="14" t="s">
+      <c r="J15" s="15" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A16" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="J15" s="15" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="118" t="s">
+      <c r="B16" s="44"/>
+      <c r="C16" s="48"/>
+      <c r="D16" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="B16" s="64"/>
-      <c r="C16" s="65"/>
-      <c r="D16" s="14" t="s">
+      <c r="E16" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="E16" s="14" t="s">
+      <c r="F16" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="F16" s="14" t="s">
+      <c r="G16" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="G16" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="H16" s="125" t="s">
-        <v>18</v>
-      </c>
-      <c r="I16" s="64"/>
-      <c r="J16" s="112"/>
-    </row>
-    <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="113" t="s">
-        <v>75</v>
-      </c>
-      <c r="B17" s="64"/>
-      <c r="C17" s="65"/>
-      <c r="D17" s="40" t="s">
-        <v>111</v>
-      </c>
-      <c r="E17" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="F17" s="17"/>
-      <c r="G17" s="17" t="s">
-        <v>111</v>
-      </c>
-      <c r="H17" s="111" t="s">
-        <v>118</v>
-      </c>
-      <c r="I17" s="64"/>
-      <c r="J17" s="112"/>
-    </row>
-    <row r="18" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A18" s="126"/>
-      <c r="B18" s="127"/>
-      <c r="C18" s="128"/>
-      <c r="D18" s="18"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="19"/>
-      <c r="G18" s="19"/>
-      <c r="H18" s="129"/>
-      <c r="I18" s="130"/>
-      <c r="J18" s="131"/>
-    </row>
+      <c r="H16" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="I16" s="44"/>
+      <c r="J16" s="45"/>
+    </row>
+    <row r="17" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
+      <c r="A17" s="40" t="s">
+        <v>71</v>
+      </c>
+      <c r="B17" s="134"/>
+      <c r="C17" s="130"/>
+      <c r="D17" s="147" t="s">
+        <v>101</v>
+      </c>
+      <c r="E17" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="F17" s="19"/>
+      <c r="G17" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="H17" s="46"/>
+      <c r="I17" s="134"/>
+      <c r="J17" s="142"/>
+    </row>
+    <row r="18" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="19" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="20" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="21" spans="1:10" ht="12.75" customHeight="1"/>
@@ -10399,9 +10428,12 @@
     <row r="992" ht="12.75" customHeight="1"/>
     <row r="993" ht="12.75" customHeight="1"/>
     <row r="994" ht="12.75" customHeight="1"/>
-    <row r="995" ht="12.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="21">
+  <mergeCells count="19">
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
     <mergeCell ref="A14:J14"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="A7:J13"/>
@@ -10417,12 +10449,6 @@
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -10432,11 +10458,11 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AA3E9D0-D005-485B-8D11-310BAE2ED20F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C78CA393-23BF-41B0-813C-E687DA2E87EF}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J995"/>
+  <dimension ref="A1:J994"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="5.140625" customWidth="1"/>
@@ -10445,279 +10471,266 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="60" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="61"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="55" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="56"/>
+      <c r="F1" s="55" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="56"/>
+      <c r="H1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="18" customHeight="1">
+      <c r="A2" s="63"/>
+      <c r="B2" s="64"/>
+      <c r="C2" s="65"/>
+      <c r="D2" s="68" t="s">
+        <v>86</v>
+      </c>
+      <c r="E2" s="69"/>
+      <c r="F2" s="68" t="s">
+        <v>87</v>
+      </c>
+      <c r="G2" s="69"/>
+      <c r="H2" s="57">
+        <v>46121</v>
+      </c>
+      <c r="I2" s="59" t="s">
+        <v>88</v>
+      </c>
+      <c r="J2" s="52"/>
+    </row>
+    <row r="3" spans="1:10" ht="18" customHeight="1">
+      <c r="A3" s="63"/>
+      <c r="B3" s="64"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="70"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="70"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="53"/>
+    </row>
+    <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
+      <c r="A4" s="63"/>
+      <c r="B4" s="64"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="70"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="70"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="58"/>
+      <c r="J4" s="53"/>
+    </row>
+    <row r="5" spans="1:10" ht="28.5" customHeight="1">
+      <c r="A5" s="66" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="50"/>
-      <c r="D1" s="57" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" s="58"/>
-      <c r="F1" s="57" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="58"/>
-      <c r="H1" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="51"/>
-      <c r="B2" s="52"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="59" t="s">
-        <v>94</v>
-      </c>
-      <c r="E2" s="60"/>
-      <c r="F2" s="59" t="s">
-        <v>95</v>
-      </c>
-      <c r="G2" s="60"/>
-      <c r="H2" s="41">
-        <v>46121</v>
-      </c>
-      <c r="I2" s="44" t="s">
-        <v>96</v>
-      </c>
-      <c r="J2" s="45"/>
-    </row>
-    <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="51"/>
-      <c r="B3" s="52"/>
-      <c r="C3" s="53"/>
-      <c r="D3" s="61"/>
-      <c r="E3" s="53"/>
-      <c r="F3" s="61"/>
-      <c r="G3" s="53"/>
-      <c r="H3" s="42"/>
-      <c r="I3" s="42"/>
-      <c r="J3" s="46"/>
-    </row>
-    <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="51"/>
-      <c r="B4" s="52"/>
-      <c r="C4" s="53"/>
-      <c r="D4" s="61"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="61"/>
-      <c r="G4" s="53"/>
-      <c r="H4" s="42"/>
-      <c r="I4" s="42"/>
-      <c r="J4" s="46"/>
-    </row>
-    <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="116" t="s">
+      <c r="B5" s="67"/>
+      <c r="C5" s="56"/>
+      <c r="D5" s="71" t="s">
+        <v>118</v>
+      </c>
+      <c r="E5" s="67"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="67"/>
+      <c r="H5" s="67"/>
+      <c r="I5" s="67"/>
+      <c r="J5" s="72"/>
+    </row>
+    <row r="6" spans="1:10" ht="21" customHeight="1">
+      <c r="A6" s="51" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="117"/>
-      <c r="C5" s="58"/>
-      <c r="D5" s="119" t="s">
-        <v>110</v>
-      </c>
-      <c r="E5" s="117"/>
-      <c r="F5" s="117"/>
-      <c r="G5" s="117"/>
-      <c r="H5" s="117"/>
-      <c r="I5" s="117"/>
-      <c r="J5" s="120"/>
-    </row>
-    <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="118" t="s">
+      <c r="B6" s="44"/>
+      <c r="C6" s="44"/>
+      <c r="D6" s="44"/>
+      <c r="E6" s="44"/>
+      <c r="F6" s="44"/>
+      <c r="G6" s="44"/>
+      <c r="H6" s="44"/>
+      <c r="I6" s="44"/>
+      <c r="J6" s="45"/>
+    </row>
+    <row r="7" spans="1:10" ht="36.75" customHeight="1">
+      <c r="A7" s="73"/>
+      <c r="B7" s="74"/>
+      <c r="C7" s="74"/>
+      <c r="D7" s="74"/>
+      <c r="E7" s="74"/>
+      <c r="F7" s="74"/>
+      <c r="G7" s="74"/>
+      <c r="H7" s="74"/>
+      <c r="I7" s="74"/>
+      <c r="J7" s="75"/>
+    </row>
+    <row r="8" spans="1:10" ht="36.75" customHeight="1">
+      <c r="A8" s="63"/>
+      <c r="B8" s="64"/>
+      <c r="C8" s="64"/>
+      <c r="D8" s="64"/>
+      <c r="E8" s="64"/>
+      <c r="F8" s="64"/>
+      <c r="G8" s="64"/>
+      <c r="H8" s="64"/>
+      <c r="I8" s="64"/>
+      <c r="J8" s="76"/>
+    </row>
+    <row r="9" spans="1:10" ht="36.75" customHeight="1">
+      <c r="A9" s="63"/>
+      <c r="B9" s="64"/>
+      <c r="C9" s="64"/>
+      <c r="D9" s="64"/>
+      <c r="E9" s="64"/>
+      <c r="F9" s="64"/>
+      <c r="G9" s="64"/>
+      <c r="H9" s="64"/>
+      <c r="I9" s="64"/>
+      <c r="J9" s="76"/>
+    </row>
+    <row r="10" spans="1:10" ht="36.75" customHeight="1">
+      <c r="A10" s="63"/>
+      <c r="B10" s="64"/>
+      <c r="C10" s="64"/>
+      <c r="D10" s="64"/>
+      <c r="E10" s="64"/>
+      <c r="F10" s="64"/>
+      <c r="G10" s="64"/>
+      <c r="H10" s="64"/>
+      <c r="I10" s="64"/>
+      <c r="J10" s="76"/>
+    </row>
+    <row r="11" spans="1:10" ht="36.75" customHeight="1">
+      <c r="A11" s="63"/>
+      <c r="B11" s="64"/>
+      <c r="C11" s="64"/>
+      <c r="D11" s="64"/>
+      <c r="E11" s="64"/>
+      <c r="F11" s="64"/>
+      <c r="G11" s="64"/>
+      <c r="H11" s="64"/>
+      <c r="I11" s="64"/>
+      <c r="J11" s="76"/>
+    </row>
+    <row r="12" spans="1:10" ht="36.75" customHeight="1">
+      <c r="A12" s="63"/>
+      <c r="B12" s="64"/>
+      <c r="C12" s="64"/>
+      <c r="D12" s="64"/>
+      <c r="E12" s="64"/>
+      <c r="F12" s="64"/>
+      <c r="G12" s="64"/>
+      <c r="H12" s="64"/>
+      <c r="I12" s="64"/>
+      <c r="J12" s="76"/>
+    </row>
+    <row r="13" spans="1:10" ht="36.75" customHeight="1">
+      <c r="A13" s="63"/>
+      <c r="B13" s="64"/>
+      <c r="C13" s="64"/>
+      <c r="D13" s="64"/>
+      <c r="E13" s="64"/>
+      <c r="F13" s="64"/>
+      <c r="G13" s="64"/>
+      <c r="H13" s="64"/>
+      <c r="I13" s="64"/>
+      <c r="J13" s="76"/>
+    </row>
+    <row r="14" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A14" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="64"/>
-      <c r="C6" s="64"/>
-      <c r="D6" s="64"/>
-      <c r="E6" s="64"/>
-      <c r="F6" s="64"/>
-      <c r="G6" s="64"/>
-      <c r="H6" s="64"/>
-      <c r="I6" s="64"/>
-      <c r="J6" s="112"/>
-    </row>
-    <row r="7" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A7" s="121"/>
-      <c r="B7" s="122"/>
-      <c r="C7" s="122"/>
-      <c r="D7" s="122"/>
-      <c r="E7" s="122"/>
-      <c r="F7" s="122"/>
-      <c r="G7" s="122"/>
-      <c r="H7" s="122"/>
-      <c r="I7" s="122"/>
-      <c r="J7" s="123"/>
-    </row>
-    <row r="8" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A8" s="51"/>
-      <c r="B8" s="52"/>
-      <c r="C8" s="52"/>
-      <c r="D8" s="52"/>
-      <c r="E8" s="52"/>
-      <c r="F8" s="52"/>
-      <c r="G8" s="52"/>
-      <c r="H8" s="52"/>
-      <c r="I8" s="52"/>
-      <c r="J8" s="124"/>
-    </row>
-    <row r="9" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A9" s="51"/>
-      <c r="B9" s="52"/>
-      <c r="C9" s="52"/>
-      <c r="D9" s="52"/>
-      <c r="E9" s="52"/>
-      <c r="F9" s="52"/>
-      <c r="G9" s="52"/>
-      <c r="H9" s="52"/>
-      <c r="I9" s="52"/>
-      <c r="J9" s="124"/>
-    </row>
-    <row r="10" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A10" s="51"/>
-      <c r="B10" s="52"/>
-      <c r="C10" s="52"/>
-      <c r="D10" s="52"/>
-      <c r="E10" s="52"/>
-      <c r="F10" s="52"/>
-      <c r="G10" s="52"/>
-      <c r="H10" s="52"/>
-      <c r="I10" s="52"/>
-      <c r="J10" s="124"/>
-    </row>
-    <row r="11" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A11" s="51"/>
-      <c r="B11" s="52"/>
-      <c r="C11" s="52"/>
-      <c r="D11" s="52"/>
-      <c r="E11" s="52"/>
-      <c r="F11" s="52"/>
-      <c r="G11" s="52"/>
-      <c r="H11" s="52"/>
-      <c r="I11" s="52"/>
-      <c r="J11" s="124"/>
-    </row>
-    <row r="12" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A12" s="51"/>
-      <c r="B12" s="52"/>
-      <c r="C12" s="52"/>
-      <c r="D12" s="52"/>
-      <c r="E12" s="52"/>
-      <c r="F12" s="52"/>
-      <c r="G12" s="52"/>
-      <c r="H12" s="52"/>
-      <c r="I12" s="52"/>
-      <c r="J12" s="124"/>
-    </row>
-    <row r="13" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A13" s="51"/>
-      <c r="B13" s="52"/>
-      <c r="C13" s="52"/>
-      <c r="D13" s="52"/>
-      <c r="E13" s="52"/>
-      <c r="F13" s="52"/>
-      <c r="G13" s="52"/>
-      <c r="H13" s="52"/>
-      <c r="I13" s="52"/>
-      <c r="J13" s="124"/>
-    </row>
-    <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="118" t="s">
+      <c r="B14" s="44"/>
+      <c r="C14" s="44"/>
+      <c r="D14" s="44"/>
+      <c r="E14" s="44"/>
+      <c r="F14" s="44"/>
+      <c r="G14" s="44"/>
+      <c r="H14" s="44"/>
+      <c r="I14" s="44"/>
+      <c r="J14" s="45"/>
+    </row>
+    <row r="15" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A15" s="51" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="64"/>
-      <c r="C14" s="64"/>
-      <c r="D14" s="64"/>
-      <c r="E14" s="64"/>
-      <c r="F14" s="64"/>
-      <c r="G14" s="64"/>
-      <c r="H14" s="64"/>
-      <c r="I14" s="64"/>
-      <c r="J14" s="112"/>
-    </row>
-    <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="118" t="s">
+      <c r="B15" s="44"/>
+      <c r="C15" s="48"/>
+      <c r="D15" s="43" t="s">
+        <v>100</v>
+      </c>
+      <c r="E15" s="44"/>
+      <c r="F15" s="44"/>
+      <c r="G15" s="44"/>
+      <c r="H15" s="48"/>
+      <c r="I15" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="64"/>
-      <c r="C15" s="65"/>
-      <c r="D15" s="111" t="s">
-        <v>116</v>
-      </c>
-      <c r="E15" s="64"/>
-      <c r="F15" s="64"/>
-      <c r="G15" s="64"/>
-      <c r="H15" s="65"/>
-      <c r="I15" s="14" t="s">
+      <c r="J15" s="15" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A16" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="J15" s="15" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="118" t="s">
+      <c r="B16" s="44"/>
+      <c r="C16" s="48"/>
+      <c r="D16" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="B16" s="64"/>
-      <c r="C16" s="65"/>
-      <c r="D16" s="14" t="s">
+      <c r="E16" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="E16" s="14" t="s">
+      <c r="F16" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="F16" s="14" t="s">
+      <c r="G16" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="G16" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="H16" s="125" t="s">
-        <v>18</v>
-      </c>
-      <c r="I16" s="64"/>
-      <c r="J16" s="112"/>
-    </row>
-    <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="113" t="s">
-        <v>75</v>
-      </c>
-      <c r="B17" s="64"/>
-      <c r="C17" s="65"/>
-      <c r="D17" s="40" t="s">
-        <v>114</v>
-      </c>
-      <c r="E17" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="F17" s="17"/>
-      <c r="G17" s="17" t="s">
-        <v>114</v>
-      </c>
-      <c r="H17" s="111" t="s">
-        <v>115</v>
-      </c>
-      <c r="I17" s="64"/>
-      <c r="J17" s="112"/>
-    </row>
-    <row r="18" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A18" s="126"/>
-      <c r="B18" s="127"/>
-      <c r="C18" s="128"/>
-      <c r="D18" s="18"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="19"/>
-      <c r="G18" s="19"/>
-      <c r="H18" s="129"/>
-      <c r="I18" s="130"/>
-      <c r="J18" s="131"/>
-    </row>
+      <c r="H16" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="I16" s="44"/>
+      <c r="J16" s="45"/>
+    </row>
+    <row r="17" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
+      <c r="A17" s="40" t="s">
+        <v>71</v>
+      </c>
+      <c r="B17" s="134"/>
+      <c r="C17" s="130"/>
+      <c r="D17" s="147" t="s">
+        <v>119</v>
+      </c>
+      <c r="E17" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="F17" s="19"/>
+      <c r="G17" s="19" t="s">
+        <v>120</v>
+      </c>
+      <c r="H17" s="46"/>
+      <c r="I17" s="134"/>
+      <c r="J17" s="142"/>
+    </row>
+    <row r="18" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="19" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="20" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="21" spans="1:10" ht="12.75" customHeight="1"/>
@@ -11694,9 +11707,12 @@
     <row r="992" ht="12.75" customHeight="1"/>
     <row r="993" ht="12.75" customHeight="1"/>
     <row r="994" ht="12.75" customHeight="1"/>
-    <row r="995" ht="12.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="21">
+  <mergeCells count="19">
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
     <mergeCell ref="A14:J14"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="A7:J13"/>
@@ -11712,12 +11728,6 @@
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -11738,181 +11748,181 @@
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
       <c r="A1" s="139" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" s="61"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
+      <c r="F1" s="62"/>
+      <c r="G1" s="55" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" s="67"/>
+      <c r="I1" s="67"/>
+      <c r="J1" s="56"/>
+      <c r="K1" s="55" t="s">
+        <v>4</v>
+      </c>
+      <c r="L1" s="67"/>
+      <c r="M1" s="67"/>
+      <c r="N1" s="56"/>
+      <c r="O1" s="55" t="s">
+        <v>5</v>
+      </c>
+      <c r="P1" s="56"/>
+      <c r="Q1" s="55" t="s">
+        <v>6</v>
+      </c>
+      <c r="R1" s="56"/>
+      <c r="S1" s="55" t="s">
+        <v>7</v>
+      </c>
+      <c r="T1" s="72"/>
+    </row>
+    <row r="2" spans="1:26" ht="18" customHeight="1">
+      <c r="A2" s="63"/>
+      <c r="B2" s="64"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="64"/>
+      <c r="F2" s="65"/>
+      <c r="G2" s="68"/>
+      <c r="H2" s="74"/>
+      <c r="I2" s="74"/>
+      <c r="J2" s="69"/>
+      <c r="K2" s="68"/>
+      <c r="L2" s="74"/>
+      <c r="M2" s="74"/>
+      <c r="N2" s="69"/>
+      <c r="O2" s="68"/>
+      <c r="P2" s="69"/>
+      <c r="Q2" s="68"/>
+      <c r="R2" s="69"/>
+      <c r="S2" s="68"/>
+      <c r="T2" s="75"/>
+    </row>
+    <row r="3" spans="1:26" ht="18" customHeight="1">
+      <c r="A3" s="63"/>
+      <c r="B3" s="64"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="64"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="70"/>
+      <c r="H3" s="64"/>
+      <c r="I3" s="64"/>
+      <c r="J3" s="65"/>
+      <c r="K3" s="70"/>
+      <c r="L3" s="64"/>
+      <c r="M3" s="64"/>
+      <c r="N3" s="65"/>
+      <c r="O3" s="70"/>
+      <c r="P3" s="65"/>
+      <c r="Q3" s="70"/>
+      <c r="R3" s="65"/>
+      <c r="S3" s="70"/>
+      <c r="T3" s="76"/>
+    </row>
+    <row r="4" spans="1:26" ht="18" customHeight="1">
+      <c r="A4" s="123"/>
+      <c r="B4" s="124"/>
+      <c r="C4" s="124"/>
+      <c r="D4" s="124"/>
+      <c r="E4" s="124"/>
+      <c r="F4" s="125"/>
+      <c r="G4" s="126"/>
+      <c r="H4" s="124"/>
+      <c r="I4" s="124"/>
+      <c r="J4" s="125"/>
+      <c r="K4" s="126"/>
+      <c r="L4" s="124"/>
+      <c r="M4" s="124"/>
+      <c r="N4" s="125"/>
+      <c r="O4" s="126"/>
+      <c r="P4" s="125"/>
+      <c r="Q4" s="126"/>
+      <c r="R4" s="125"/>
+      <c r="S4" s="126"/>
+      <c r="T4" s="138"/>
+    </row>
+    <row r="5" spans="1:26" ht="18" customHeight="1">
+      <c r="A5" s="66" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="50"/>
-      <c r="G1" s="57" t="s">
-        <v>4</v>
-      </c>
-      <c r="H1" s="117"/>
-      <c r="I1" s="117"/>
-      <c r="J1" s="58"/>
-      <c r="K1" s="57" t="s">
-        <v>5</v>
-      </c>
-      <c r="L1" s="117"/>
-      <c r="M1" s="117"/>
-      <c r="N1" s="58"/>
-      <c r="O1" s="57" t="s">
-        <v>6</v>
-      </c>
-      <c r="P1" s="58"/>
-      <c r="Q1" s="57" t="s">
-        <v>7</v>
-      </c>
-      <c r="R1" s="58"/>
-      <c r="S1" s="57" t="s">
-        <v>8</v>
-      </c>
-      <c r="T1" s="120"/>
-    </row>
-    <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="51"/>
-      <c r="B2" s="52"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="59"/>
-      <c r="H2" s="122"/>
-      <c r="I2" s="122"/>
-      <c r="J2" s="60"/>
-      <c r="K2" s="59"/>
-      <c r="L2" s="122"/>
-      <c r="M2" s="122"/>
-      <c r="N2" s="60"/>
-      <c r="O2" s="59"/>
-      <c r="P2" s="60"/>
-      <c r="Q2" s="59"/>
-      <c r="R2" s="60"/>
-      <c r="S2" s="59"/>
-      <c r="T2" s="123"/>
-    </row>
-    <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="51"/>
-      <c r="B3" s="52"/>
-      <c r="C3" s="52"/>
-      <c r="D3" s="52"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="53"/>
-      <c r="G3" s="61"/>
-      <c r="H3" s="52"/>
-      <c r="I3" s="52"/>
-      <c r="J3" s="53"/>
-      <c r="K3" s="61"/>
-      <c r="L3" s="52"/>
-      <c r="M3" s="52"/>
-      <c r="N3" s="53"/>
-      <c r="O3" s="61"/>
-      <c r="P3" s="53"/>
-      <c r="Q3" s="61"/>
-      <c r="R3" s="53"/>
-      <c r="S3" s="61"/>
-      <c r="T3" s="124"/>
-    </row>
-    <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="54"/>
-      <c r="B4" s="55"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="55"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="56"/>
-      <c r="G4" s="62"/>
-      <c r="H4" s="55"/>
-      <c r="I4" s="55"/>
-      <c r="J4" s="56"/>
-      <c r="K4" s="62"/>
-      <c r="L4" s="55"/>
-      <c r="M4" s="55"/>
-      <c r="N4" s="56"/>
-      <c r="O4" s="62"/>
-      <c r="P4" s="56"/>
-      <c r="Q4" s="62"/>
-      <c r="R4" s="56"/>
-      <c r="S4" s="62"/>
-      <c r="T4" s="138"/>
-    </row>
-    <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="116" t="s">
+      <c r="B5" s="67"/>
+      <c r="C5" s="67"/>
+      <c r="D5" s="67"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="56"/>
+      <c r="G5" s="135" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="117"/>
-      <c r="C5" s="117"/>
-      <c r="D5" s="117"/>
-      <c r="E5" s="117"/>
-      <c r="F5" s="58"/>
-      <c r="G5" s="140" t="s">
+      <c r="H5" s="67"/>
+      <c r="I5" s="67"/>
+      <c r="J5" s="67"/>
+      <c r="K5" s="67"/>
+      <c r="L5" s="67"/>
+      <c r="M5" s="67"/>
+      <c r="N5" s="67"/>
+      <c r="O5" s="67"/>
+      <c r="P5" s="67"/>
+      <c r="Q5" s="67"/>
+      <c r="R5" s="67"/>
+      <c r="S5" s="67"/>
+      <c r="T5" s="72"/>
+    </row>
+    <row r="6" spans="1:26" ht="18" customHeight="1">
+      <c r="A6" s="51" t="s">
         <v>34</v>
       </c>
-      <c r="H5" s="117"/>
-      <c r="I5" s="117"/>
-      <c r="J5" s="117"/>
-      <c r="K5" s="117"/>
-      <c r="L5" s="117"/>
-      <c r="M5" s="117"/>
-      <c r="N5" s="117"/>
-      <c r="O5" s="117"/>
-      <c r="P5" s="117"/>
-      <c r="Q5" s="117"/>
-      <c r="R5" s="117"/>
-      <c r="S5" s="117"/>
-      <c r="T5" s="120"/>
-    </row>
-    <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="118" t="s">
+      <c r="B6" s="44"/>
+      <c r="C6" s="44"/>
+      <c r="D6" s="44"/>
+      <c r="E6" s="44"/>
+      <c r="F6" s="48"/>
+      <c r="G6" s="43" t="s">
+        <v>18</v>
+      </c>
+      <c r="H6" s="44"/>
+      <c r="I6" s="44"/>
+      <c r="J6" s="44"/>
+      <c r="K6" s="44"/>
+      <c r="L6" s="44"/>
+      <c r="M6" s="44"/>
+      <c r="N6" s="44"/>
+      <c r="O6" s="44"/>
+      <c r="P6" s="44"/>
+      <c r="Q6" s="44"/>
+      <c r="R6" s="44"/>
+      <c r="S6" s="44"/>
+      <c r="T6" s="45"/>
+    </row>
+    <row r="7" spans="1:26" ht="18" customHeight="1">
+      <c r="A7" s="51" t="s">
         <v>35</v>
       </c>
-      <c r="B6" s="64"/>
-      <c r="C6" s="64"/>
-      <c r="D6" s="64"/>
-      <c r="E6" s="64"/>
-      <c r="F6" s="65"/>
-      <c r="G6" s="111" t="s">
-        <v>19</v>
-      </c>
-      <c r="H6" s="64"/>
-      <c r="I6" s="64"/>
-      <c r="J6" s="64"/>
-      <c r="K6" s="64"/>
-      <c r="L6" s="64"/>
-      <c r="M6" s="64"/>
-      <c r="N6" s="64"/>
-      <c r="O6" s="64"/>
-      <c r="P6" s="64"/>
-      <c r="Q6" s="64"/>
-      <c r="R6" s="64"/>
-      <c r="S6" s="64"/>
-      <c r="T6" s="112"/>
-    </row>
-    <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="118" t="s">
+      <c r="B7" s="44"/>
+      <c r="C7" s="44"/>
+      <c r="D7" s="44"/>
+      <c r="E7" s="44"/>
+      <c r="F7" s="48"/>
+      <c r="G7" s="43" t="s">
         <v>36</v>
       </c>
-      <c r="B7" s="64"/>
-      <c r="C7" s="64"/>
-      <c r="D7" s="64"/>
-      <c r="E7" s="64"/>
-      <c r="F7" s="65"/>
-      <c r="G7" s="111" t="s">
-        <v>37</v>
-      </c>
-      <c r="H7" s="64"/>
-      <c r="I7" s="64"/>
-      <c r="J7" s="64"/>
-      <c r="K7" s="64"/>
-      <c r="L7" s="64"/>
-      <c r="M7" s="64"/>
-      <c r="N7" s="64"/>
-      <c r="O7" s="64"/>
-      <c r="P7" s="64"/>
-      <c r="Q7" s="64"/>
-      <c r="R7" s="64"/>
-      <c r="S7" s="64"/>
-      <c r="T7" s="112"/>
+      <c r="H7" s="44"/>
+      <c r="I7" s="44"/>
+      <c r="J7" s="44"/>
+      <c r="K7" s="44"/>
+      <c r="L7" s="44"/>
+      <c r="M7" s="44"/>
+      <c r="N7" s="44"/>
+      <c r="O7" s="44"/>
+      <c r="P7" s="44"/>
+      <c r="Q7" s="44"/>
+      <c r="R7" s="44"/>
+      <c r="S7" s="44"/>
+      <c r="T7" s="45"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="7"/>
@@ -11940,11 +11950,11 @@
       <c r="A9" s="20"/>
       <c r="B9" s="21"/>
       <c r="C9" s="22" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D9" s="23"/>
       <c r="E9" s="23" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F9" s="23"/>
       <c r="G9" s="24"/>
@@ -11974,7 +11984,7 @@
       <c r="C10" s="26"/>
       <c r="D10" s="21"/>
       <c r="E10" s="21" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F10" s="21"/>
       <c r="G10" s="27"/>
@@ -12004,7 +12014,7 @@
       <c r="C11" s="26"/>
       <c r="D11" s="21"/>
       <c r="E11" s="21" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F11" s="21"/>
       <c r="G11" s="27"/>
@@ -12034,7 +12044,7 @@
       <c r="C12" s="26"/>
       <c r="D12" s="21"/>
       <c r="E12" s="21" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F12" s="21"/>
       <c r="G12" s="27"/>
@@ -12064,7 +12074,7 @@
       <c r="C13" s="28"/>
       <c r="D13" s="29"/>
       <c r="E13" s="29" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F13" s="29"/>
       <c r="G13" s="30"/>
@@ -12111,79 +12121,79 @@
       <c r="T14" s="9"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="118" t="s">
+      <c r="A15" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15" s="48"/>
+      <c r="C15" s="137" t="s">
+        <v>37</v>
+      </c>
+      <c r="D15" s="48"/>
+      <c r="E15" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="B15" s="65"/>
-      <c r="C15" s="143" t="s">
-        <v>38</v>
-      </c>
-      <c r="D15" s="65"/>
-      <c r="E15" s="125" t="s">
+      <c r="F15" s="48"/>
+      <c r="G15" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="F15" s="65"/>
-      <c r="G15" s="125" t="s">
+      <c r="H15" s="44"/>
+      <c r="I15" s="48"/>
+      <c r="J15" s="54" t="s">
         <v>46</v>
       </c>
-      <c r="H15" s="64"/>
-      <c r="I15" s="65"/>
-      <c r="J15" s="125" t="s">
+      <c r="K15" s="48"/>
+      <c r="L15" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="K15" s="65"/>
-      <c r="L15" s="125" t="s">
+      <c r="M15" s="44"/>
+      <c r="N15" s="48"/>
+      <c r="O15" s="54" t="s">
         <v>48</v>
       </c>
-      <c r="M15" s="64"/>
-      <c r="N15" s="65"/>
-      <c r="O15" s="125" t="s">
+      <c r="P15" s="44"/>
+      <c r="Q15" s="48"/>
+      <c r="R15" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="P15" s="64"/>
-      <c r="Q15" s="65"/>
-      <c r="R15" s="14" t="s">
+      <c r="S15" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="S15" s="14" t="s">
+      <c r="T15" s="31" t="s">
         <v>51</v>
       </c>
-      <c r="T15" s="31" t="s">
+    </row>
+    <row r="16" spans="1:26" ht="48" customHeight="1">
+      <c r="A16" s="127">
+        <v>1</v>
+      </c>
+      <c r="B16" s="48"/>
+      <c r="C16" s="128" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="141">
-        <v>1</v>
-      </c>
-      <c r="B16" s="65"/>
-      <c r="C16" s="142" t="s">
+      <c r="D16" s="48"/>
+      <c r="E16" s="128" t="s">
         <v>53</v>
       </c>
-      <c r="D16" s="65"/>
-      <c r="E16" s="142" t="s">
+      <c r="F16" s="48"/>
+      <c r="G16" s="136" t="s">
         <v>54</v>
       </c>
-      <c r="F16" s="65"/>
-      <c r="G16" s="132" t="s">
+      <c r="H16" s="44"/>
+      <c r="I16" s="48"/>
+      <c r="J16" s="136" t="s">
         <v>55</v>
       </c>
-      <c r="H16" s="64"/>
-      <c r="I16" s="65"/>
-      <c r="J16" s="132" t="s">
+      <c r="K16" s="48"/>
+      <c r="L16" s="132" t="s">
         <v>56</v>
       </c>
-      <c r="K16" s="65"/>
-      <c r="L16" s="136" t="s">
+      <c r="M16" s="44"/>
+      <c r="N16" s="48"/>
+      <c r="O16" s="132" t="s">
         <v>57</v>
       </c>
-      <c r="M16" s="64"/>
-      <c r="N16" s="65"/>
-      <c r="O16" s="136" t="s">
-        <v>58</v>
-      </c>
-      <c r="P16" s="64"/>
-      <c r="Q16" s="65"/>
+      <c r="P16" s="44"/>
+      <c r="Q16" s="48"/>
       <c r="R16" s="32"/>
       <c r="S16" s="32"/>
       <c r="T16" s="33"/>
@@ -12195,37 +12205,37 @@
       <c r="Z16" s="34"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="141">
+      <c r="A17" s="127">
         <v>2</v>
       </c>
-      <c r="B17" s="65"/>
-      <c r="C17" s="142" t="s">
+      <c r="B17" s="48"/>
+      <c r="C17" s="128" t="s">
+        <v>58</v>
+      </c>
+      <c r="D17" s="48"/>
+      <c r="E17" s="128" t="s">
         <v>59</v>
       </c>
-      <c r="D17" s="65"/>
-      <c r="E17" s="142" t="s">
+      <c r="F17" s="48"/>
+      <c r="G17" s="136" t="s">
         <v>60</v>
       </c>
-      <c r="F17" s="65"/>
-      <c r="G17" s="132" t="s">
+      <c r="H17" s="44"/>
+      <c r="I17" s="48"/>
+      <c r="J17" s="136" t="s">
         <v>61</v>
       </c>
-      <c r="H17" s="64"/>
-      <c r="I17" s="65"/>
-      <c r="J17" s="132" t="s">
+      <c r="K17" s="48"/>
+      <c r="L17" s="132" t="s">
         <v>62</v>
       </c>
-      <c r="K17" s="65"/>
-      <c r="L17" s="136" t="s">
+      <c r="M17" s="44"/>
+      <c r="N17" s="48"/>
+      <c r="O17" s="132" t="s">
         <v>63</v>
       </c>
-      <c r="M17" s="64"/>
-      <c r="N17" s="65"/>
-      <c r="O17" s="136" t="s">
-        <v>64</v>
-      </c>
-      <c r="P17" s="64"/>
-      <c r="Q17" s="65"/>
+      <c r="P17" s="44"/>
+      <c r="Q17" s="48"/>
       <c r="R17" s="32"/>
       <c r="S17" s="32"/>
       <c r="T17" s="33"/>
@@ -12237,23 +12247,23 @@
       <c r="Z17" s="34"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="141"/>
-      <c r="B18" s="65"/>
-      <c r="C18" s="142"/>
-      <c r="D18" s="65"/>
-      <c r="E18" s="142"/>
-      <c r="F18" s="65"/>
-      <c r="G18" s="132"/>
-      <c r="H18" s="64"/>
-      <c r="I18" s="65"/>
-      <c r="J18" s="132"/>
-      <c r="K18" s="65"/>
-      <c r="L18" s="136"/>
-      <c r="M18" s="64"/>
-      <c r="N18" s="65"/>
-      <c r="O18" s="136"/>
-      <c r="P18" s="64"/>
-      <c r="Q18" s="65"/>
+      <c r="A18" s="127"/>
+      <c r="B18" s="48"/>
+      <c r="C18" s="128"/>
+      <c r="D18" s="48"/>
+      <c r="E18" s="128"/>
+      <c r="F18" s="48"/>
+      <c r="G18" s="136"/>
+      <c r="H18" s="44"/>
+      <c r="I18" s="48"/>
+      <c r="J18" s="136"/>
+      <c r="K18" s="48"/>
+      <c r="L18" s="132"/>
+      <c r="M18" s="44"/>
+      <c r="N18" s="48"/>
+      <c r="O18" s="132"/>
+      <c r="P18" s="44"/>
+      <c r="Q18" s="48"/>
       <c r="R18" s="32"/>
       <c r="S18" s="32"/>
       <c r="T18" s="33"/>
@@ -12265,23 +12275,23 @@
       <c r="Z18" s="34"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="141"/>
-      <c r="B19" s="65"/>
-      <c r="C19" s="142"/>
-      <c r="D19" s="65"/>
-      <c r="E19" s="142"/>
-      <c r="F19" s="65"/>
-      <c r="G19" s="132"/>
-      <c r="H19" s="64"/>
-      <c r="I19" s="65"/>
-      <c r="J19" s="132"/>
-      <c r="K19" s="65"/>
-      <c r="L19" s="136"/>
-      <c r="M19" s="64"/>
-      <c r="N19" s="65"/>
-      <c r="O19" s="136"/>
-      <c r="P19" s="64"/>
-      <c r="Q19" s="65"/>
+      <c r="A19" s="127"/>
+      <c r="B19" s="48"/>
+      <c r="C19" s="128"/>
+      <c r="D19" s="48"/>
+      <c r="E19" s="128"/>
+      <c r="F19" s="48"/>
+      <c r="G19" s="136"/>
+      <c r="H19" s="44"/>
+      <c r="I19" s="48"/>
+      <c r="J19" s="136"/>
+      <c r="K19" s="48"/>
+      <c r="L19" s="132"/>
+      <c r="M19" s="44"/>
+      <c r="N19" s="48"/>
+      <c r="O19" s="132"/>
+      <c r="P19" s="44"/>
+      <c r="Q19" s="48"/>
       <c r="R19" s="32"/>
       <c r="S19" s="32"/>
       <c r="T19" s="33"/>
@@ -12293,23 +12303,23 @@
       <c r="Z19" s="34"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="141"/>
-      <c r="B20" s="65"/>
-      <c r="C20" s="142"/>
-      <c r="D20" s="65"/>
-      <c r="E20" s="142"/>
-      <c r="F20" s="65"/>
-      <c r="G20" s="132"/>
-      <c r="H20" s="64"/>
-      <c r="I20" s="65"/>
-      <c r="J20" s="132"/>
-      <c r="K20" s="65"/>
-      <c r="L20" s="136"/>
-      <c r="M20" s="64"/>
-      <c r="N20" s="65"/>
-      <c r="O20" s="136"/>
-      <c r="P20" s="64"/>
-      <c r="Q20" s="65"/>
+      <c r="A20" s="127"/>
+      <c r="B20" s="48"/>
+      <c r="C20" s="128"/>
+      <c r="D20" s="48"/>
+      <c r="E20" s="128"/>
+      <c r="F20" s="48"/>
+      <c r="G20" s="136"/>
+      <c r="H20" s="44"/>
+      <c r="I20" s="48"/>
+      <c r="J20" s="136"/>
+      <c r="K20" s="48"/>
+      <c r="L20" s="132"/>
+      <c r="M20" s="44"/>
+      <c r="N20" s="48"/>
+      <c r="O20" s="132"/>
+      <c r="P20" s="44"/>
+      <c r="Q20" s="48"/>
       <c r="R20" s="32"/>
       <c r="S20" s="32"/>
       <c r="T20" s="33"/>
@@ -12321,23 +12331,23 @@
       <c r="Z20" s="34"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="141"/>
-      <c r="B21" s="65"/>
-      <c r="C21" s="142"/>
-      <c r="D21" s="65"/>
-      <c r="E21" s="142"/>
-      <c r="F21" s="65"/>
-      <c r="G21" s="132"/>
-      <c r="H21" s="64"/>
-      <c r="I21" s="65"/>
-      <c r="J21" s="132"/>
-      <c r="K21" s="65"/>
-      <c r="L21" s="136"/>
-      <c r="M21" s="64"/>
-      <c r="N21" s="65"/>
-      <c r="O21" s="136"/>
-      <c r="P21" s="64"/>
-      <c r="Q21" s="65"/>
+      <c r="A21" s="127"/>
+      <c r="B21" s="48"/>
+      <c r="C21" s="128"/>
+      <c r="D21" s="48"/>
+      <c r="E21" s="128"/>
+      <c r="F21" s="48"/>
+      <c r="G21" s="136"/>
+      <c r="H21" s="44"/>
+      <c r="I21" s="48"/>
+      <c r="J21" s="136"/>
+      <c r="K21" s="48"/>
+      <c r="L21" s="132"/>
+      <c r="M21" s="44"/>
+      <c r="N21" s="48"/>
+      <c r="O21" s="132"/>
+      <c r="P21" s="44"/>
+      <c r="Q21" s="48"/>
       <c r="R21" s="32"/>
       <c r="S21" s="32"/>
       <c r="T21" s="33"/>
@@ -12349,23 +12359,23 @@
       <c r="Z21" s="34"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="141"/>
-      <c r="B22" s="65"/>
-      <c r="C22" s="142"/>
-      <c r="D22" s="65"/>
-      <c r="E22" s="142"/>
-      <c r="F22" s="65"/>
-      <c r="G22" s="132"/>
-      <c r="H22" s="64"/>
-      <c r="I22" s="65"/>
-      <c r="J22" s="132"/>
-      <c r="K22" s="65"/>
-      <c r="L22" s="136"/>
-      <c r="M22" s="64"/>
-      <c r="N22" s="65"/>
-      <c r="O22" s="136"/>
-      <c r="P22" s="64"/>
-      <c r="Q22" s="65"/>
+      <c r="A22" s="127"/>
+      <c r="B22" s="48"/>
+      <c r="C22" s="128"/>
+      <c r="D22" s="48"/>
+      <c r="E22" s="128"/>
+      <c r="F22" s="48"/>
+      <c r="G22" s="136"/>
+      <c r="H22" s="44"/>
+      <c r="I22" s="48"/>
+      <c r="J22" s="136"/>
+      <c r="K22" s="48"/>
+      <c r="L22" s="132"/>
+      <c r="M22" s="44"/>
+      <c r="N22" s="48"/>
+      <c r="O22" s="132"/>
+      <c r="P22" s="44"/>
+      <c r="Q22" s="48"/>
       <c r="R22" s="32"/>
       <c r="S22" s="32"/>
       <c r="T22" s="33"/>
@@ -12377,23 +12387,23 @@
       <c r="Z22" s="34"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="141"/>
-      <c r="B23" s="65"/>
-      <c r="C23" s="142"/>
-      <c r="D23" s="65"/>
-      <c r="E23" s="142"/>
-      <c r="F23" s="65"/>
-      <c r="G23" s="132"/>
-      <c r="H23" s="64"/>
-      <c r="I23" s="65"/>
-      <c r="J23" s="132"/>
-      <c r="K23" s="65"/>
-      <c r="L23" s="136"/>
-      <c r="M23" s="64"/>
-      <c r="N23" s="65"/>
-      <c r="O23" s="136"/>
-      <c r="P23" s="64"/>
-      <c r="Q23" s="65"/>
+      <c r="A23" s="127"/>
+      <c r="B23" s="48"/>
+      <c r="C23" s="128"/>
+      <c r="D23" s="48"/>
+      <c r="E23" s="128"/>
+      <c r="F23" s="48"/>
+      <c r="G23" s="136"/>
+      <c r="H23" s="44"/>
+      <c r="I23" s="48"/>
+      <c r="J23" s="136"/>
+      <c r="K23" s="48"/>
+      <c r="L23" s="132"/>
+      <c r="M23" s="44"/>
+      <c r="N23" s="48"/>
+      <c r="O23" s="132"/>
+      <c r="P23" s="44"/>
+      <c r="Q23" s="48"/>
       <c r="R23" s="32"/>
       <c r="S23" s="32"/>
       <c r="T23" s="33"/>
@@ -12405,23 +12415,23 @@
       <c r="Z23" s="34"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="141"/>
-      <c r="B24" s="65"/>
-      <c r="C24" s="142"/>
-      <c r="D24" s="65"/>
-      <c r="E24" s="142"/>
-      <c r="F24" s="65"/>
-      <c r="G24" s="132"/>
-      <c r="H24" s="64"/>
-      <c r="I24" s="65"/>
-      <c r="J24" s="132"/>
-      <c r="K24" s="65"/>
-      <c r="L24" s="136"/>
-      <c r="M24" s="64"/>
-      <c r="N24" s="65"/>
-      <c r="O24" s="136"/>
-      <c r="P24" s="64"/>
-      <c r="Q24" s="65"/>
+      <c r="A24" s="127"/>
+      <c r="B24" s="48"/>
+      <c r="C24" s="128"/>
+      <c r="D24" s="48"/>
+      <c r="E24" s="128"/>
+      <c r="F24" s="48"/>
+      <c r="G24" s="136"/>
+      <c r="H24" s="44"/>
+      <c r="I24" s="48"/>
+      <c r="J24" s="136"/>
+      <c r="K24" s="48"/>
+      <c r="L24" s="132"/>
+      <c r="M24" s="44"/>
+      <c r="N24" s="48"/>
+      <c r="O24" s="132"/>
+      <c r="P24" s="44"/>
+      <c r="Q24" s="48"/>
       <c r="R24" s="32"/>
       <c r="S24" s="32"/>
       <c r="T24" s="33"/>
@@ -12433,23 +12443,23 @@
       <c r="Z24" s="34"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="141"/>
-      <c r="B25" s="65"/>
-      <c r="C25" s="142"/>
-      <c r="D25" s="65"/>
-      <c r="E25" s="142"/>
-      <c r="F25" s="65"/>
-      <c r="G25" s="132"/>
-      <c r="H25" s="64"/>
-      <c r="I25" s="65"/>
-      <c r="J25" s="132"/>
-      <c r="K25" s="65"/>
-      <c r="L25" s="136"/>
-      <c r="M25" s="64"/>
-      <c r="N25" s="65"/>
-      <c r="O25" s="136"/>
-      <c r="P25" s="64"/>
-      <c r="Q25" s="65"/>
+      <c r="A25" s="127"/>
+      <c r="B25" s="48"/>
+      <c r="C25" s="128"/>
+      <c r="D25" s="48"/>
+      <c r="E25" s="128"/>
+      <c r="F25" s="48"/>
+      <c r="G25" s="136"/>
+      <c r="H25" s="44"/>
+      <c r="I25" s="48"/>
+      <c r="J25" s="136"/>
+      <c r="K25" s="48"/>
+      <c r="L25" s="132"/>
+      <c r="M25" s="44"/>
+      <c r="N25" s="48"/>
+      <c r="O25" s="132"/>
+      <c r="P25" s="44"/>
+      <c r="Q25" s="48"/>
       <c r="R25" s="32"/>
       <c r="S25" s="32"/>
       <c r="T25" s="33"/>
@@ -12461,23 +12471,23 @@
       <c r="Z25" s="34"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="141"/>
-      <c r="B26" s="65"/>
-      <c r="C26" s="142"/>
-      <c r="D26" s="65"/>
-      <c r="E26" s="142"/>
-      <c r="F26" s="65"/>
-      <c r="G26" s="132"/>
-      <c r="H26" s="64"/>
-      <c r="I26" s="65"/>
-      <c r="J26" s="132"/>
-      <c r="K26" s="65"/>
-      <c r="L26" s="136"/>
-      <c r="M26" s="64"/>
-      <c r="N26" s="65"/>
-      <c r="O26" s="136"/>
-      <c r="P26" s="64"/>
-      <c r="Q26" s="65"/>
+      <c r="A26" s="127"/>
+      <c r="B26" s="48"/>
+      <c r="C26" s="128"/>
+      <c r="D26" s="48"/>
+      <c r="E26" s="128"/>
+      <c r="F26" s="48"/>
+      <c r="G26" s="136"/>
+      <c r="H26" s="44"/>
+      <c r="I26" s="48"/>
+      <c r="J26" s="136"/>
+      <c r="K26" s="48"/>
+      <c r="L26" s="132"/>
+      <c r="M26" s="44"/>
+      <c r="N26" s="48"/>
+      <c r="O26" s="132"/>
+      <c r="P26" s="44"/>
+      <c r="Q26" s="48"/>
       <c r="R26" s="32"/>
       <c r="S26" s="32"/>
       <c r="T26" s="33"/>
@@ -12489,23 +12499,23 @@
       <c r="Z26" s="34"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="141"/>
-      <c r="B27" s="65"/>
-      <c r="C27" s="142"/>
-      <c r="D27" s="65"/>
-      <c r="E27" s="142"/>
-      <c r="F27" s="65"/>
-      <c r="G27" s="132"/>
-      <c r="H27" s="64"/>
-      <c r="I27" s="65"/>
-      <c r="J27" s="132"/>
-      <c r="K27" s="65"/>
-      <c r="L27" s="136"/>
-      <c r="M27" s="64"/>
-      <c r="N27" s="65"/>
-      <c r="O27" s="136"/>
-      <c r="P27" s="64"/>
-      <c r="Q27" s="65"/>
+      <c r="A27" s="127"/>
+      <c r="B27" s="48"/>
+      <c r="C27" s="128"/>
+      <c r="D27" s="48"/>
+      <c r="E27" s="128"/>
+      <c r="F27" s="48"/>
+      <c r="G27" s="136"/>
+      <c r="H27" s="44"/>
+      <c r="I27" s="48"/>
+      <c r="J27" s="136"/>
+      <c r="K27" s="48"/>
+      <c r="L27" s="132"/>
+      <c r="M27" s="44"/>
+      <c r="N27" s="48"/>
+      <c r="O27" s="132"/>
+      <c r="P27" s="44"/>
+      <c r="Q27" s="48"/>
       <c r="R27" s="32"/>
       <c r="S27" s="32"/>
       <c r="T27" s="33"/>
@@ -12517,23 +12527,23 @@
       <c r="Z27" s="34"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="141"/>
-      <c r="B28" s="65"/>
-      <c r="C28" s="142"/>
-      <c r="D28" s="65"/>
-      <c r="E28" s="142"/>
-      <c r="F28" s="65"/>
-      <c r="G28" s="132"/>
-      <c r="H28" s="64"/>
-      <c r="I28" s="65"/>
-      <c r="J28" s="132"/>
-      <c r="K28" s="65"/>
-      <c r="L28" s="136"/>
-      <c r="M28" s="64"/>
-      <c r="N28" s="65"/>
-      <c r="O28" s="136"/>
-      <c r="P28" s="64"/>
-      <c r="Q28" s="65"/>
+      <c r="A28" s="127"/>
+      <c r="B28" s="48"/>
+      <c r="C28" s="128"/>
+      <c r="D28" s="48"/>
+      <c r="E28" s="128"/>
+      <c r="F28" s="48"/>
+      <c r="G28" s="136"/>
+      <c r="H28" s="44"/>
+      <c r="I28" s="48"/>
+      <c r="J28" s="136"/>
+      <c r="K28" s="48"/>
+      <c r="L28" s="132"/>
+      <c r="M28" s="44"/>
+      <c r="N28" s="48"/>
+      <c r="O28" s="132"/>
+      <c r="P28" s="44"/>
+      <c r="Q28" s="48"/>
       <c r="R28" s="32"/>
       <c r="S28" s="32"/>
       <c r="T28" s="33"/>
@@ -12545,23 +12555,23 @@
       <c r="Z28" s="34"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="141"/>
-      <c r="B29" s="65"/>
-      <c r="C29" s="142"/>
-      <c r="D29" s="65"/>
-      <c r="E29" s="142"/>
-      <c r="F29" s="65"/>
-      <c r="G29" s="132"/>
-      <c r="H29" s="64"/>
-      <c r="I29" s="65"/>
-      <c r="J29" s="132"/>
-      <c r="K29" s="65"/>
-      <c r="L29" s="136"/>
-      <c r="M29" s="64"/>
-      <c r="N29" s="65"/>
-      <c r="O29" s="136"/>
-      <c r="P29" s="64"/>
-      <c r="Q29" s="65"/>
+      <c r="A29" s="127"/>
+      <c r="B29" s="48"/>
+      <c r="C29" s="128"/>
+      <c r="D29" s="48"/>
+      <c r="E29" s="128"/>
+      <c r="F29" s="48"/>
+      <c r="G29" s="136"/>
+      <c r="H29" s="44"/>
+      <c r="I29" s="48"/>
+      <c r="J29" s="136"/>
+      <c r="K29" s="48"/>
+      <c r="L29" s="132"/>
+      <c r="M29" s="44"/>
+      <c r="N29" s="48"/>
+      <c r="O29" s="132"/>
+      <c r="P29" s="44"/>
+      <c r="Q29" s="48"/>
       <c r="R29" s="32"/>
       <c r="S29" s="32"/>
       <c r="T29" s="33"/>
@@ -12573,23 +12583,23 @@
       <c r="Z29" s="34"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="141"/>
-      <c r="B30" s="65"/>
-      <c r="C30" s="142"/>
-      <c r="D30" s="65"/>
-      <c r="E30" s="142"/>
-      <c r="F30" s="65"/>
-      <c r="G30" s="132"/>
-      <c r="H30" s="64"/>
-      <c r="I30" s="65"/>
-      <c r="J30" s="132"/>
-      <c r="K30" s="65"/>
-      <c r="L30" s="136"/>
-      <c r="M30" s="64"/>
-      <c r="N30" s="65"/>
-      <c r="O30" s="136"/>
-      <c r="P30" s="64"/>
-      <c r="Q30" s="65"/>
+      <c r="A30" s="127"/>
+      <c r="B30" s="48"/>
+      <c r="C30" s="128"/>
+      <c r="D30" s="48"/>
+      <c r="E30" s="128"/>
+      <c r="F30" s="48"/>
+      <c r="G30" s="136"/>
+      <c r="H30" s="44"/>
+      <c r="I30" s="48"/>
+      <c r="J30" s="136"/>
+      <c r="K30" s="48"/>
+      <c r="L30" s="132"/>
+      <c r="M30" s="44"/>
+      <c r="N30" s="48"/>
+      <c r="O30" s="132"/>
+      <c r="P30" s="44"/>
+      <c r="Q30" s="48"/>
       <c r="R30" s="32"/>
       <c r="S30" s="32"/>
       <c r="T30" s="33"/>
@@ -12601,23 +12611,23 @@
       <c r="Z30" s="34"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="144"/>
-      <c r="B31" s="135"/>
-      <c r="C31" s="145"/>
-      <c r="D31" s="135"/>
-      <c r="E31" s="145"/>
-      <c r="F31" s="135"/>
-      <c r="G31" s="133"/>
+      <c r="A31" s="129"/>
+      <c r="B31" s="130"/>
+      <c r="C31" s="131"/>
+      <c r="D31" s="130"/>
+      <c r="E31" s="131"/>
+      <c r="F31" s="130"/>
+      <c r="G31" s="140"/>
       <c r="H31" s="134"/>
-      <c r="I31" s="135"/>
-      <c r="J31" s="133"/>
-      <c r="K31" s="135"/>
-      <c r="L31" s="137"/>
+      <c r="I31" s="130"/>
+      <c r="J31" s="140"/>
+      <c r="K31" s="130"/>
+      <c r="L31" s="133"/>
       <c r="M31" s="134"/>
-      <c r="N31" s="135"/>
-      <c r="O31" s="137"/>
+      <c r="N31" s="130"/>
+      <c r="O31" s="133"/>
       <c r="P31" s="134"/>
-      <c r="Q31" s="135"/>
+      <c r="Q31" s="130"/>
       <c r="R31" s="35"/>
       <c r="S31" s="35"/>
       <c r="T31" s="36"/>
@@ -13615,6 +13625,118 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:T5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:T6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G7:T7"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="C30:D30"/>
     <mergeCell ref="E30:F30"/>
@@ -13639,118 +13761,6 @@
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="E28:F28"/>
     <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:T5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="G6:T6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="G7:T7"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/document/成果物ドキュメント_タスク編集機能.xlsx
+++ b/document/成果物ドキュメント_タスク編集機能.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\TaskManager62\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD07DDC1-56AF-4A36-8E4A-50E592B8C28A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{502FDFD8-6C95-47E8-9221-7AD3341C4819}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -552,17 +552,6 @@
     <phoneticPr fontId="10"/>
   </si>
   <si>
-    <t>ユーザーがシステムにログインしていること
-対象のタスクがシステムに存在すること</t>
-    <rPh sb="21" eb="23">
-      <t>タイショウ</t>
-    </rPh>
-    <rPh sb="33" eb="35">
-      <t>ソンザイ</t>
-    </rPh>
-    <phoneticPr fontId="10"/>
-  </si>
-  <si>
     <t>1．ユーザーがタスク詳細画面で編集するタスクを選択する
 2．システムがタスク編集画面を表示する
 3．ユーザーがタスクの編集内容を入力する
@@ -677,6 +666,26 @@
       <t>ショウサイガメン</t>
     </rPh>
     <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>対象のタスクがシステムに存在すること
+対象のタスクの担当者と同一のユーザーがログインしていること</t>
+    <rPh sb="0" eb="2">
+      <t>タイショウ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ソンザイ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>タイショウ</t>
+    </rPh>
+    <rPh sb="26" eb="29">
+      <t>タントウシャ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>ドウイツ</t>
+    </rPh>
+    <phoneticPr fontId="10"/>
   </si>
 </sst>
 </file>
@@ -1564,6 +1573,219 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1573,257 +1795,92 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -1831,62 +1888,14 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2443,85 +2452,85 @@
   <sheetData>
     <row r="1" spans="3:16" ht="30" customHeight="1"/>
     <row r="2" spans="3:16" ht="30" customHeight="1">
-      <c r="C2" s="79" t="s">
+      <c r="C2" s="47" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="80"/>
-      <c r="E2" s="80"/>
-      <c r="F2" s="80"/>
-      <c r="G2" s="80"/>
-      <c r="H2" s="80"/>
-      <c r="I2" s="80"/>
-      <c r="J2" s="80"/>
-      <c r="K2" s="80"/>
-      <c r="L2" s="80"/>
-      <c r="M2" s="80"/>
-      <c r="N2" s="80"/>
-      <c r="O2" s="80"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="48"/>
+      <c r="L2" s="48"/>
+      <c r="M2" s="48"/>
+      <c r="N2" s="48"/>
+      <c r="O2" s="48"/>
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="64"/>
-      <c r="D3" s="64"/>
-      <c r="E3" s="64"/>
-      <c r="F3" s="64"/>
-      <c r="G3" s="64"/>
-      <c r="H3" s="64"/>
-      <c r="I3" s="64"/>
-      <c r="J3" s="64"/>
-      <c r="K3" s="64"/>
-      <c r="L3" s="64"/>
-      <c r="M3" s="64"/>
-      <c r="N3" s="64"/>
-      <c r="O3" s="64"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="46"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="46"/>
+      <c r="G3" s="46"/>
+      <c r="H3" s="46"/>
+      <c r="I3" s="46"/>
+      <c r="J3" s="46"/>
+      <c r="K3" s="46"/>
+      <c r="L3" s="46"/>
+      <c r="M3" s="46"/>
+      <c r="N3" s="46"/>
+      <c r="O3" s="46"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="64"/>
-      <c r="D4" s="64"/>
-      <c r="E4" s="64"/>
-      <c r="F4" s="64"/>
-      <c r="G4" s="64"/>
-      <c r="H4" s="64"/>
-      <c r="I4" s="64"/>
-      <c r="J4" s="64"/>
-      <c r="K4" s="64"/>
-      <c r="L4" s="64"/>
-      <c r="M4" s="64"/>
-      <c r="N4" s="64"/>
-      <c r="O4" s="64"/>
+      <c r="C4" s="46"/>
+      <c r="D4" s="46"/>
+      <c r="E4" s="46"/>
+      <c r="F4" s="46"/>
+      <c r="G4" s="46"/>
+      <c r="H4" s="46"/>
+      <c r="I4" s="46"/>
+      <c r="J4" s="46"/>
+      <c r="K4" s="46"/>
+      <c r="L4" s="46"/>
+      <c r="M4" s="46"/>
+      <c r="N4" s="46"/>
+      <c r="O4" s="46"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="64"/>
-      <c r="D5" s="64"/>
-      <c r="E5" s="64"/>
-      <c r="F5" s="64"/>
-      <c r="G5" s="64"/>
-      <c r="H5" s="64"/>
-      <c r="I5" s="64"/>
-      <c r="J5" s="64"/>
-      <c r="K5" s="64"/>
-      <c r="L5" s="64"/>
-      <c r="M5" s="64"/>
-      <c r="N5" s="64"/>
-      <c r="O5" s="64"/>
+      <c r="C5" s="46"/>
+      <c r="D5" s="46"/>
+      <c r="E5" s="46"/>
+      <c r="F5" s="46"/>
+      <c r="G5" s="46"/>
+      <c r="H5" s="46"/>
+      <c r="I5" s="46"/>
+      <c r="J5" s="46"/>
+      <c r="K5" s="46"/>
+      <c r="L5" s="46"/>
+      <c r="M5" s="46"/>
+      <c r="N5" s="46"/>
+      <c r="O5" s="46"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="64"/>
-      <c r="D6" s="64"/>
-      <c r="E6" s="64"/>
-      <c r="F6" s="64"/>
-      <c r="G6" s="64"/>
-      <c r="H6" s="64"/>
-      <c r="I6" s="64"/>
-      <c r="J6" s="64"/>
-      <c r="K6" s="64"/>
-      <c r="L6" s="64"/>
-      <c r="M6" s="64"/>
-      <c r="N6" s="64"/>
-      <c r="O6" s="64"/>
+      <c r="C6" s="46"/>
+      <c r="D6" s="46"/>
+      <c r="E6" s="46"/>
+      <c r="F6" s="46"/>
+      <c r="G6" s="46"/>
+      <c r="H6" s="46"/>
+      <c r="I6" s="46"/>
+      <c r="J6" s="46"/>
+      <c r="K6" s="46"/>
+      <c r="L6" s="46"/>
+      <c r="M6" s="46"/>
+      <c r="N6" s="46"/>
+      <c r="O6" s="46"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -2541,46 +2550,46 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="81" t="s">
+      <c r="E8" s="49" t="s">
         <v>105</v>
       </c>
-      <c r="F8" s="64"/>
-      <c r="G8" s="64"/>
-      <c r="H8" s="64"/>
-      <c r="I8" s="64"/>
-      <c r="J8" s="64"/>
-      <c r="K8" s="64"/>
-      <c r="L8" s="64"/>
-      <c r="M8" s="64"/>
+      <c r="F8" s="46"/>
+      <c r="G8" s="46"/>
+      <c r="H8" s="46"/>
+      <c r="I8" s="46"/>
+      <c r="J8" s="46"/>
+      <c r="K8" s="46"/>
+      <c r="L8" s="46"/>
+      <c r="M8" s="46"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="77" t="s">
+      <c r="G13" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="H13" s="48"/>
-      <c r="I13" s="146">
+      <c r="H13" s="44"/>
+      <c r="I13" s="50">
         <v>46129</v>
       </c>
-      <c r="J13" s="44"/>
-      <c r="K13" s="48"/>
+      <c r="J13" s="43"/>
+      <c r="K13" s="44"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="77"/>
-      <c r="H14" s="48"/>
-      <c r="I14" s="77"/>
-      <c r="J14" s="44"/>
-      <c r="K14" s="48"/>
+      <c r="G14" s="42"/>
+      <c r="H14" s="44"/>
+      <c r="I14" s="42"/>
+      <c r="J14" s="43"/>
+      <c r="K14" s="44"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="77"/>
-      <c r="H15" s="48"/>
-      <c r="I15" s="77"/>
-      <c r="J15" s="44"/>
-      <c r="K15" s="48"/>
+      <c r="G15" s="42"/>
+      <c r="H15" s="44"/>
+      <c r="I15" s="42"/>
+      <c r="J15" s="43"/>
+      <c r="K15" s="44"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -2589,13 +2598,13 @@
       <c r="J16" s="3"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="78" t="s">
+      <c r="G17" s="45" t="s">
         <v>106</v>
       </c>
-      <c r="H17" s="64"/>
-      <c r="I17" s="64"/>
-      <c r="J17" s="64"/>
-      <c r="K17" s="64"/>
+      <c r="H17" s="46"/>
+      <c r="I17" s="46"/>
+      <c r="J17" s="46"/>
+      <c r="K17" s="46"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -3610,19 +3619,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="101" t="s">
+      <c r="A1" s="66" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="102"/>
-      <c r="C1" s="103"/>
-      <c r="D1" s="112" t="s">
+      <c r="B1" s="67"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="111"/>
-      <c r="F1" s="112" t="s">
+      <c r="E1" s="52"/>
+      <c r="F1" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="111"/>
+      <c r="G1" s="52"/>
       <c r="H1" s="39" t="s">
         <v>5</v>
       </c>
@@ -3634,192 +3643,192 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="104"/>
-      <c r="B2" s="105"/>
-      <c r="C2" s="106"/>
-      <c r="D2" s="113" t="s">
+      <c r="A2" s="69"/>
+      <c r="B2" s="70"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="53" t="s">
         <v>68</v>
       </c>
-      <c r="E2" s="114"/>
-      <c r="F2" s="113" t="s">
+      <c r="E2" s="54"/>
+      <c r="F2" s="53" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="114"/>
-      <c r="H2" s="117">
+      <c r="G2" s="54"/>
+      <c r="H2" s="59">
         <v>46121</v>
       </c>
-      <c r="I2" s="120" t="s">
+      <c r="I2" s="62" t="s">
         <v>66</v>
       </c>
-      <c r="J2" s="90"/>
+      <c r="J2" s="78"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="104"/>
-      <c r="B3" s="105"/>
-      <c r="C3" s="106"/>
-      <c r="D3" s="115"/>
-      <c r="E3" s="106"/>
-      <c r="F3" s="115"/>
-      <c r="G3" s="106"/>
-      <c r="H3" s="118"/>
-      <c r="I3" s="118"/>
-      <c r="J3" s="91"/>
+      <c r="A3" s="69"/>
+      <c r="B3" s="70"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="60"/>
+      <c r="I3" s="60"/>
+      <c r="J3" s="79"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="107"/>
-      <c r="B4" s="108"/>
-      <c r="C4" s="109"/>
-      <c r="D4" s="116"/>
-      <c r="E4" s="109"/>
-      <c r="F4" s="116"/>
-      <c r="G4" s="109"/>
-      <c r="H4" s="119"/>
-      <c r="I4" s="119"/>
-      <c r="J4" s="92"/>
+      <c r="A4" s="71"/>
+      <c r="B4" s="72"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="61"/>
+      <c r="I4" s="61"/>
+      <c r="J4" s="80"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="110" t="s">
+      <c r="A5" s="73" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="85"/>
-      <c r="C5" s="111"/>
-      <c r="D5" s="86" t="s">
+      <c r="B5" s="74"/>
+      <c r="C5" s="52"/>
+      <c r="D5" s="82" t="s">
         <v>65</v>
       </c>
-      <c r="E5" s="87"/>
-      <c r="F5" s="87"/>
-      <c r="G5" s="87"/>
-      <c r="H5" s="87"/>
-      <c r="I5" s="87"/>
-      <c r="J5" s="88"/>
+      <c r="E5" s="76"/>
+      <c r="F5" s="76"/>
+      <c r="G5" s="76"/>
+      <c r="H5" s="76"/>
+      <c r="I5" s="76"/>
+      <c r="J5" s="83"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="95" t="s">
+      <c r="A6" s="75" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="87"/>
-      <c r="C6" s="94"/>
-      <c r="D6" s="86" t="s">
+      <c r="B6" s="76"/>
+      <c r="C6" s="77"/>
+      <c r="D6" s="82" t="s">
         <v>113</v>
       </c>
-      <c r="E6" s="87"/>
-      <c r="F6" s="87"/>
-      <c r="G6" s="87"/>
-      <c r="H6" s="87"/>
-      <c r="I6" s="87"/>
-      <c r="J6" s="88"/>
+      <c r="E6" s="76"/>
+      <c r="F6" s="76"/>
+      <c r="G6" s="76"/>
+      <c r="H6" s="76"/>
+      <c r="I6" s="76"/>
+      <c r="J6" s="83"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="95" t="s">
+      <c r="A7" s="75" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="87"/>
-      <c r="C7" s="94"/>
-      <c r="D7" s="86" t="s">
+      <c r="B7" s="76"/>
+      <c r="C7" s="77"/>
+      <c r="D7" s="82" t="s">
         <v>64</v>
       </c>
-      <c r="E7" s="87"/>
-      <c r="F7" s="87"/>
-      <c r="G7" s="87"/>
-      <c r="H7" s="87"/>
-      <c r="I7" s="87"/>
-      <c r="J7" s="88"/>
+      <c r="E7" s="76"/>
+      <c r="F7" s="76"/>
+      <c r="G7" s="76"/>
+      <c r="H7" s="76"/>
+      <c r="I7" s="76"/>
+      <c r="J7" s="83"/>
     </row>
     <row r="8" spans="1:10" ht="31.5" customHeight="1">
-      <c r="A8" s="95" t="s">
+      <c r="A8" s="75" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="87"/>
-      <c r="C8" s="94"/>
-      <c r="D8" s="89" t="s">
+      <c r="B8" s="76"/>
+      <c r="C8" s="77"/>
+      <c r="D8" s="84" t="s">
+        <v>122</v>
+      </c>
+      <c r="E8" s="76"/>
+      <c r="F8" s="76"/>
+      <c r="G8" s="76"/>
+      <c r="H8" s="76"/>
+      <c r="I8" s="76"/>
+      <c r="J8" s="83"/>
+    </row>
+    <row r="9" spans="1:10" ht="93.75" customHeight="1">
+      <c r="A9" s="85" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="81" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="77"/>
+      <c r="D9" s="84" t="s">
         <v>114</v>
       </c>
-      <c r="E8" s="87"/>
-      <c r="F8" s="87"/>
-      <c r="G8" s="87"/>
-      <c r="H8" s="87"/>
-      <c r="I8" s="87"/>
-      <c r="J8" s="88"/>
-    </row>
-    <row r="9" spans="1:10" ht="93.75" customHeight="1">
-      <c r="A9" s="96" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" s="93" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" s="94"/>
-      <c r="D9" s="89" t="s">
+      <c r="E9" s="76"/>
+      <c r="F9" s="76"/>
+      <c r="G9" s="76"/>
+      <c r="H9" s="76"/>
+      <c r="I9" s="76"/>
+      <c r="J9" s="83"/>
+    </row>
+    <row r="10" spans="1:10" ht="64.5" customHeight="1">
+      <c r="A10" s="86"/>
+      <c r="B10" s="81" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="77"/>
+      <c r="D10" s="84" t="s">
+        <v>112</v>
+      </c>
+      <c r="E10" s="76"/>
+      <c r="F10" s="76"/>
+      <c r="G10" s="76"/>
+      <c r="H10" s="76"/>
+      <c r="I10" s="76"/>
+      <c r="J10" s="83"/>
+    </row>
+    <row r="11" spans="1:10" ht="64.5" customHeight="1">
+      <c r="A11" s="87"/>
+      <c r="B11" s="81" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="77"/>
+      <c r="D11" s="84" t="s">
         <v>115</v>
       </c>
-      <c r="E9" s="87"/>
-      <c r="F9" s="87"/>
-      <c r="G9" s="87"/>
-      <c r="H9" s="87"/>
-      <c r="I9" s="87"/>
-      <c r="J9" s="88"/>
-    </row>
-    <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="97"/>
-      <c r="B10" s="93" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="94"/>
-      <c r="D10" s="89" t="s">
-        <v>112</v>
-      </c>
-      <c r="E10" s="87"/>
-      <c r="F10" s="87"/>
-      <c r="G10" s="87"/>
-      <c r="H10" s="87"/>
-      <c r="I10" s="87"/>
-      <c r="J10" s="88"/>
-    </row>
-    <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="98"/>
-      <c r="B11" s="93" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" s="94"/>
-      <c r="D11" s="89" t="s">
-        <v>116</v>
-      </c>
-      <c r="E11" s="87"/>
-      <c r="F11" s="87"/>
-      <c r="G11" s="87"/>
-      <c r="H11" s="87"/>
-      <c r="I11" s="87"/>
-      <c r="J11" s="88"/>
+      <c r="E11" s="76"/>
+      <c r="F11" s="76"/>
+      <c r="G11" s="76"/>
+      <c r="H11" s="76"/>
+      <c r="I11" s="76"/>
+      <c r="J11" s="83"/>
     </row>
     <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="95" t="s">
+      <c r="A12" s="75" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="87"/>
-      <c r="C12" s="94"/>
-      <c r="D12" s="86" t="s">
+      <c r="B12" s="76"/>
+      <c r="C12" s="77"/>
+      <c r="D12" s="82" t="s">
         <v>111</v>
       </c>
-      <c r="E12" s="87"/>
-      <c r="F12" s="87"/>
-      <c r="G12" s="87"/>
-      <c r="H12" s="87"/>
-      <c r="I12" s="87"/>
-      <c r="J12" s="88"/>
+      <c r="E12" s="76"/>
+      <c r="F12" s="76"/>
+      <c r="G12" s="76"/>
+      <c r="H12" s="76"/>
+      <c r="I12" s="76"/>
+      <c r="J12" s="83"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A13" s="99" t="s">
+      <c r="A13" s="63" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="83"/>
-      <c r="C13" s="100"/>
-      <c r="D13" s="82"/>
-      <c r="E13" s="83"/>
-      <c r="F13" s="83"/>
-      <c r="G13" s="83"/>
-      <c r="H13" s="83"/>
-      <c r="I13" s="83"/>
-      <c r="J13" s="84"/>
+      <c r="B13" s="64"/>
+      <c r="C13" s="65"/>
+      <c r="D13" s="88"/>
+      <c r="E13" s="64"/>
+      <c r="F13" s="64"/>
+      <c r="G13" s="64"/>
+      <c r="H13" s="64"/>
+      <c r="I13" s="64"/>
+      <c r="J13" s="89"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -4810,17 +4819,13 @@
     <row r="1000" s="37" customFormat="1" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="D13:J13"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="D7:J7"/>
+    <mergeCell ref="D8:J8"/>
+    <mergeCell ref="D9:J9"/>
+    <mergeCell ref="D10:J10"/>
     <mergeCell ref="J2:J4"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B11:C11"/>
@@ -4830,13 +4835,17 @@
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A9:A11"/>
     <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D13:J13"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="D7:J7"/>
-    <mergeCell ref="D8:J8"/>
-    <mergeCell ref="D9:J9"/>
-    <mergeCell ref="D10:J10"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="D1:E1"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -4855,19 +4864,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="60" t="s">
+      <c r="A1" s="97" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="61"/>
-      <c r="C1" s="62"/>
-      <c r="D1" s="55" t="s">
+      <c r="B1" s="98"/>
+      <c r="C1" s="99"/>
+      <c r="D1" s="105" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="56"/>
-      <c r="F1" s="55" t="s">
+      <c r="E1" s="106"/>
+      <c r="F1" s="105" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="56"/>
+      <c r="G1" s="106"/>
       <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
@@ -4879,48 +4888,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="63"/>
-      <c r="B2" s="64"/>
-      <c r="C2" s="65"/>
-      <c r="D2" s="68" t="s">
+      <c r="A2" s="100"/>
+      <c r="B2" s="46"/>
+      <c r="C2" s="101"/>
+      <c r="D2" s="107" t="s">
         <v>86</v>
       </c>
-      <c r="E2" s="69"/>
-      <c r="F2" s="68" t="s">
+      <c r="E2" s="108"/>
+      <c r="F2" s="107" t="s">
         <v>87</v>
       </c>
-      <c r="G2" s="69"/>
-      <c r="H2" s="57">
+      <c r="G2" s="108"/>
+      <c r="H2" s="90">
         <v>46125</v>
       </c>
-      <c r="I2" s="59" t="s">
+      <c r="I2" s="93" t="s">
         <v>88</v>
       </c>
-      <c r="J2" s="52"/>
+      <c r="J2" s="94"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="63"/>
-      <c r="B3" s="64"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="70"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="70"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="53"/>
+      <c r="A3" s="100"/>
+      <c r="B3" s="46"/>
+      <c r="C3" s="101"/>
+      <c r="D3" s="109"/>
+      <c r="E3" s="101"/>
+      <c r="F3" s="109"/>
+      <c r="G3" s="101"/>
+      <c r="H3" s="91"/>
+      <c r="I3" s="91"/>
+      <c r="J3" s="95"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="123"/>
-      <c r="B4" s="124"/>
-      <c r="C4" s="125"/>
-      <c r="D4" s="126"/>
-      <c r="E4" s="125"/>
-      <c r="F4" s="126"/>
-      <c r="G4" s="125"/>
-      <c r="H4" s="121"/>
-      <c r="I4" s="121"/>
-      <c r="J4" s="122"/>
+      <c r="A4" s="102"/>
+      <c r="B4" s="103"/>
+      <c r="C4" s="104"/>
+      <c r="D4" s="110"/>
+      <c r="E4" s="104"/>
+      <c r="F4" s="110"/>
+      <c r="G4" s="104"/>
+      <c r="H4" s="92"/>
+      <c r="I4" s="92"/>
+      <c r="J4" s="96"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="7"/>
@@ -6276,19 +6285,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="60" t="s">
+      <c r="A1" s="97" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="61"/>
-      <c r="C1" s="62"/>
-      <c r="D1" s="55" t="s">
+      <c r="B1" s="98"/>
+      <c r="C1" s="99"/>
+      <c r="D1" s="105" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="56"/>
-      <c r="F1" s="55" t="s">
+      <c r="E1" s="106"/>
+      <c r="F1" s="105" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="56"/>
+      <c r="G1" s="106"/>
       <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
@@ -6300,48 +6309,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="63"/>
-      <c r="B2" s="64"/>
-      <c r="C2" s="65"/>
-      <c r="D2" s="68" t="s">
+      <c r="A2" s="100"/>
+      <c r="B2" s="46"/>
+      <c r="C2" s="101"/>
+      <c r="D2" s="107" t="s">
         <v>86</v>
       </c>
-      <c r="E2" s="69"/>
-      <c r="F2" s="68" t="s">
+      <c r="E2" s="108"/>
+      <c r="F2" s="107" t="s">
         <v>87</v>
       </c>
-      <c r="G2" s="69"/>
-      <c r="H2" s="57">
+      <c r="G2" s="108"/>
+      <c r="H2" s="90">
         <v>46122</v>
       </c>
-      <c r="I2" s="59" t="s">
+      <c r="I2" s="93" t="s">
         <v>104</v>
       </c>
-      <c r="J2" s="52"/>
+      <c r="J2" s="94"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="63"/>
-      <c r="B3" s="64"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="70"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="70"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="53"/>
+      <c r="A3" s="100"/>
+      <c r="B3" s="46"/>
+      <c r="C3" s="101"/>
+      <c r="D3" s="109"/>
+      <c r="E3" s="101"/>
+      <c r="F3" s="109"/>
+      <c r="G3" s="101"/>
+      <c r="H3" s="91"/>
+      <c r="I3" s="91"/>
+      <c r="J3" s="95"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="123"/>
-      <c r="B4" s="124"/>
-      <c r="C4" s="125"/>
-      <c r="D4" s="126"/>
-      <c r="E4" s="125"/>
-      <c r="F4" s="126"/>
-      <c r="G4" s="125"/>
-      <c r="H4" s="121"/>
-      <c r="I4" s="121"/>
-      <c r="J4" s="122"/>
+      <c r="A4" s="102"/>
+      <c r="B4" s="103"/>
+      <c r="C4" s="104"/>
+      <c r="D4" s="110"/>
+      <c r="E4" s="104"/>
+      <c r="F4" s="110"/>
+      <c r="G4" s="104"/>
+      <c r="H4" s="92"/>
+      <c r="I4" s="92"/>
+      <c r="J4" s="96"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="7"/>
@@ -7690,19 +7699,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="60" t="s">
+      <c r="A1" s="97" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="61"/>
-      <c r="C1" s="62"/>
-      <c r="D1" s="55" t="s">
+      <c r="B1" s="98"/>
+      <c r="C1" s="99"/>
+      <c r="D1" s="105" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="56"/>
-      <c r="F1" s="55" t="s">
+      <c r="E1" s="106"/>
+      <c r="F1" s="105" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="56"/>
+      <c r="G1" s="106"/>
       <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
@@ -7714,190 +7723,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="63"/>
-      <c r="B2" s="64"/>
-      <c r="C2" s="65"/>
-      <c r="D2" s="68" t="s">
+      <c r="A2" s="100"/>
+      <c r="B2" s="46"/>
+      <c r="C2" s="101"/>
+      <c r="D2" s="107" t="s">
         <v>86</v>
       </c>
-      <c r="E2" s="69"/>
-      <c r="F2" s="68" t="s">
+      <c r="E2" s="108"/>
+      <c r="F2" s="107" t="s">
         <v>87</v>
       </c>
-      <c r="G2" s="69"/>
-      <c r="H2" s="57">
+      <c r="G2" s="108"/>
+      <c r="H2" s="90">
         <v>46121</v>
       </c>
-      <c r="I2" s="59" t="s">
+      <c r="I2" s="93" t="s">
         <v>88</v>
       </c>
-      <c r="J2" s="52"/>
+      <c r="J2" s="94"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="63"/>
-      <c r="B3" s="64"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="70"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="70"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="53"/>
+      <c r="A3" s="100"/>
+      <c r="B3" s="46"/>
+      <c r="C3" s="101"/>
+      <c r="D3" s="109"/>
+      <c r="E3" s="101"/>
+      <c r="F3" s="109"/>
+      <c r="G3" s="101"/>
+      <c r="H3" s="91"/>
+      <c r="I3" s="91"/>
+      <c r="J3" s="95"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="63"/>
-      <c r="B4" s="64"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="70"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="70"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="58"/>
-      <c r="I4" s="58"/>
-      <c r="J4" s="53"/>
+      <c r="A4" s="100"/>
+      <c r="B4" s="46"/>
+      <c r="C4" s="101"/>
+      <c r="D4" s="109"/>
+      <c r="E4" s="101"/>
+      <c r="F4" s="109"/>
+      <c r="G4" s="101"/>
+      <c r="H4" s="91"/>
+      <c r="I4" s="91"/>
+      <c r="J4" s="95"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="66" t="s">
+      <c r="A5" s="121" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="67"/>
-      <c r="C5" s="56"/>
-      <c r="D5" s="71" t="s">
+      <c r="B5" s="122"/>
+      <c r="C5" s="106"/>
+      <c r="D5" s="123" t="s">
         <v>98</v>
       </c>
-      <c r="E5" s="67"/>
-      <c r="F5" s="67"/>
-      <c r="G5" s="67"/>
-      <c r="H5" s="67"/>
-      <c r="I5" s="67"/>
-      <c r="J5" s="72"/>
+      <c r="E5" s="122"/>
+      <c r="F5" s="122"/>
+      <c r="G5" s="122"/>
+      <c r="H5" s="122"/>
+      <c r="I5" s="122"/>
+      <c r="J5" s="124"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="51" t="s">
+      <c r="A6" s="117" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="44"/>
-      <c r="C6" s="44"/>
-      <c r="D6" s="44"/>
-      <c r="E6" s="44"/>
-      <c r="F6" s="44"/>
-      <c r="G6" s="44"/>
-      <c r="H6" s="44"/>
-      <c r="I6" s="44"/>
-      <c r="J6" s="45"/>
+      <c r="B6" s="43"/>
+      <c r="C6" s="43"/>
+      <c r="D6" s="43"/>
+      <c r="E6" s="43"/>
+      <c r="F6" s="43"/>
+      <c r="G6" s="43"/>
+      <c r="H6" s="43"/>
+      <c r="I6" s="43"/>
+      <c r="J6" s="118"/>
     </row>
     <row r="7" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A7" s="73"/>
-      <c r="B7" s="74"/>
-      <c r="C7" s="74"/>
-      <c r="D7" s="74"/>
-      <c r="E7" s="74"/>
-      <c r="F7" s="74"/>
-      <c r="G7" s="74"/>
-      <c r="H7" s="74"/>
-      <c r="I7" s="74"/>
-      <c r="J7" s="75"/>
+      <c r="A7" s="125"/>
+      <c r="B7" s="126"/>
+      <c r="C7" s="126"/>
+      <c r="D7" s="126"/>
+      <c r="E7" s="126"/>
+      <c r="F7" s="126"/>
+      <c r="G7" s="126"/>
+      <c r="H7" s="126"/>
+      <c r="I7" s="126"/>
+      <c r="J7" s="127"/>
     </row>
     <row r="8" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A8" s="63"/>
-      <c r="B8" s="64"/>
-      <c r="C8" s="64"/>
-      <c r="D8" s="64"/>
-      <c r="E8" s="64"/>
-      <c r="F8" s="64"/>
-      <c r="G8" s="64"/>
-      <c r="H8" s="64"/>
-      <c r="I8" s="64"/>
-      <c r="J8" s="76"/>
+      <c r="A8" s="100"/>
+      <c r="B8" s="46"/>
+      <c r="C8" s="46"/>
+      <c r="D8" s="46"/>
+      <c r="E8" s="46"/>
+      <c r="F8" s="46"/>
+      <c r="G8" s="46"/>
+      <c r="H8" s="46"/>
+      <c r="I8" s="46"/>
+      <c r="J8" s="128"/>
     </row>
     <row r="9" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A9" s="63"/>
-      <c r="B9" s="64"/>
-      <c r="C9" s="64"/>
-      <c r="D9" s="64"/>
-      <c r="E9" s="64"/>
-      <c r="F9" s="64"/>
-      <c r="G9" s="64"/>
-      <c r="H9" s="64"/>
-      <c r="I9" s="64"/>
-      <c r="J9" s="76"/>
+      <c r="A9" s="100"/>
+      <c r="B9" s="46"/>
+      <c r="C9" s="46"/>
+      <c r="D9" s="46"/>
+      <c r="E9" s="46"/>
+      <c r="F9" s="46"/>
+      <c r="G9" s="46"/>
+      <c r="H9" s="46"/>
+      <c r="I9" s="46"/>
+      <c r="J9" s="128"/>
     </row>
     <row r="10" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A10" s="63"/>
-      <c r="B10" s="64"/>
-      <c r="C10" s="64"/>
-      <c r="D10" s="64"/>
-      <c r="E10" s="64"/>
-      <c r="F10" s="64"/>
-      <c r="G10" s="64"/>
-      <c r="H10" s="64"/>
-      <c r="I10" s="64"/>
-      <c r="J10" s="76"/>
+      <c r="A10" s="100"/>
+      <c r="B10" s="46"/>
+      <c r="C10" s="46"/>
+      <c r="D10" s="46"/>
+      <c r="E10" s="46"/>
+      <c r="F10" s="46"/>
+      <c r="G10" s="46"/>
+      <c r="H10" s="46"/>
+      <c r="I10" s="46"/>
+      <c r="J10" s="128"/>
     </row>
     <row r="11" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A11" s="63"/>
-      <c r="B11" s="64"/>
-      <c r="C11" s="64"/>
-      <c r="D11" s="64"/>
-      <c r="E11" s="64"/>
-      <c r="F11" s="64"/>
-      <c r="G11" s="64"/>
-      <c r="H11" s="64"/>
-      <c r="I11" s="64"/>
-      <c r="J11" s="76"/>
+      <c r="A11" s="100"/>
+      <c r="B11" s="46"/>
+      <c r="C11" s="46"/>
+      <c r="D11" s="46"/>
+      <c r="E11" s="46"/>
+      <c r="F11" s="46"/>
+      <c r="G11" s="46"/>
+      <c r="H11" s="46"/>
+      <c r="I11" s="46"/>
+      <c r="J11" s="128"/>
     </row>
     <row r="12" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A12" s="63"/>
-      <c r="B12" s="64"/>
-      <c r="C12" s="64"/>
-      <c r="D12" s="64"/>
-      <c r="E12" s="64"/>
-      <c r="F12" s="64"/>
-      <c r="G12" s="64"/>
-      <c r="H12" s="64"/>
-      <c r="I12" s="64"/>
-      <c r="J12" s="76"/>
+      <c r="A12" s="100"/>
+      <c r="B12" s="46"/>
+      <c r="C12" s="46"/>
+      <c r="D12" s="46"/>
+      <c r="E12" s="46"/>
+      <c r="F12" s="46"/>
+      <c r="G12" s="46"/>
+      <c r="H12" s="46"/>
+      <c r="I12" s="46"/>
+      <c r="J12" s="128"/>
     </row>
     <row r="13" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A13" s="63"/>
-      <c r="B13" s="64"/>
-      <c r="C13" s="64"/>
-      <c r="D13" s="64"/>
-      <c r="E13" s="64"/>
-      <c r="F13" s="64"/>
-      <c r="G13" s="64"/>
-      <c r="H13" s="64"/>
-      <c r="I13" s="64"/>
-      <c r="J13" s="76"/>
+      <c r="A13" s="100"/>
+      <c r="B13" s="46"/>
+      <c r="C13" s="46"/>
+      <c r="D13" s="46"/>
+      <c r="E13" s="46"/>
+      <c r="F13" s="46"/>
+      <c r="G13" s="46"/>
+      <c r="H13" s="46"/>
+      <c r="I13" s="46"/>
+      <c r="J13" s="128"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="51" t="s">
+      <c r="A14" s="117" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="44"/>
-      <c r="C14" s="44"/>
-      <c r="D14" s="44"/>
-      <c r="E14" s="44"/>
-      <c r="F14" s="44"/>
-      <c r="G14" s="44"/>
-      <c r="H14" s="44"/>
-      <c r="I14" s="44"/>
-      <c r="J14" s="45"/>
+      <c r="B14" s="43"/>
+      <c r="C14" s="43"/>
+      <c r="D14" s="43"/>
+      <c r="E14" s="43"/>
+      <c r="F14" s="43"/>
+      <c r="G14" s="43"/>
+      <c r="H14" s="43"/>
+      <c r="I14" s="43"/>
+      <c r="J14" s="118"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="51" t="s">
+      <c r="A15" s="117" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="44"/>
-      <c r="C15" s="48"/>
-      <c r="D15" s="43" t="s">
+      <c r="B15" s="43"/>
+      <c r="C15" s="44"/>
+      <c r="D15" s="119" t="s">
         <v>69</v>
       </c>
-      <c r="E15" s="44"/>
-      <c r="F15" s="44"/>
-      <c r="G15" s="44"/>
-      <c r="H15" s="48"/>
+      <c r="E15" s="43"/>
+      <c r="F15" s="43"/>
+      <c r="G15" s="43"/>
+      <c r="H15" s="44"/>
       <c r="I15" s="14" t="s">
         <v>25</v>
       </c>
@@ -7906,11 +7915,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="51" t="s">
+      <c r="A16" s="117" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="44"/>
-      <c r="C16" s="48"/>
+      <c r="B16" s="43"/>
+      <c r="C16" s="44"/>
       <c r="D16" s="14" t="s">
         <v>27</v>
       </c>
@@ -7923,18 +7932,18 @@
       <c r="G16" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="H16" s="54" t="s">
+      <c r="H16" s="120" t="s">
         <v>17</v>
       </c>
-      <c r="I16" s="44"/>
-      <c r="J16" s="45"/>
+      <c r="I16" s="43"/>
+      <c r="J16" s="118"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="47" t="s">
+      <c r="A17" s="130" t="s">
         <v>71</v>
       </c>
-      <c r="B17" s="44"/>
-      <c r="C17" s="48"/>
+      <c r="B17" s="43"/>
+      <c r="C17" s="44"/>
       <c r="D17" s="16" t="s">
         <v>89</v>
       </c>
@@ -7945,18 +7954,18 @@
         <v>83</v>
       </c>
       <c r="G17" s="17"/>
-      <c r="H17" s="43" t="s">
+      <c r="H17" s="119" t="s">
         <v>107</v>
       </c>
-      <c r="I17" s="44"/>
-      <c r="J17" s="45"/>
+      <c r="I17" s="43"/>
+      <c r="J17" s="118"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="47" t="s">
+      <c r="A18" s="130" t="s">
         <v>72</v>
       </c>
-      <c r="B18" s="44"/>
-      <c r="C18" s="48"/>
+      <c r="B18" s="43"/>
+      <c r="C18" s="44"/>
       <c r="D18" s="16" t="s">
         <v>90</v>
       </c>
@@ -7967,16 +7976,16 @@
         <v>96</v>
       </c>
       <c r="G18" s="17"/>
-      <c r="H18" s="43"/>
-      <c r="I18" s="44"/>
-      <c r="J18" s="45"/>
+      <c r="H18" s="119"/>
+      <c r="I18" s="43"/>
+      <c r="J18" s="118"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="47" t="s">
+      <c r="A19" s="130" t="s">
         <v>73</v>
       </c>
-      <c r="B19" s="44"/>
-      <c r="C19" s="48"/>
+      <c r="B19" s="43"/>
+      <c r="C19" s="44"/>
       <c r="D19" s="16" t="s">
         <v>91</v>
       </c>
@@ -7986,21 +7995,21 @@
       <c r="F19" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="G19" s="141" t="s">
+      <c r="G19" s="40" t="s">
         <v>108</v>
       </c>
-      <c r="H19" s="143" t="s">
+      <c r="H19" s="129" t="s">
         <v>109</v>
       </c>
-      <c r="I19" s="44"/>
-      <c r="J19" s="45"/>
+      <c r="I19" s="43"/>
+      <c r="J19" s="118"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="47" t="s">
+      <c r="A20" s="130" t="s">
         <v>74</v>
       </c>
-      <c r="B20" s="44"/>
-      <c r="C20" s="48"/>
+      <c r="B20" s="43"/>
+      <c r="C20" s="44"/>
       <c r="D20" s="16" t="s">
         <v>92</v>
       </c>
@@ -8011,16 +8020,16 @@
         <v>103</v>
       </c>
       <c r="G20" s="17"/>
-      <c r="H20" s="43"/>
-      <c r="I20" s="44"/>
-      <c r="J20" s="45"/>
+      <c r="H20" s="119"/>
+      <c r="I20" s="43"/>
+      <c r="J20" s="118"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="47" t="s">
+      <c r="A21" s="130" t="s">
         <v>75</v>
       </c>
-      <c r="B21" s="44"/>
-      <c r="C21" s="48"/>
+      <c r="B21" s="43"/>
+      <c r="C21" s="44"/>
       <c r="D21" s="16" t="s">
         <v>93</v>
       </c>
@@ -8031,16 +8040,16 @@
         <v>95</v>
       </c>
       <c r="G21" s="17"/>
-      <c r="H21" s="43"/>
-      <c r="I21" s="44"/>
-      <c r="J21" s="45"/>
+      <c r="H21" s="119"/>
+      <c r="I21" s="43"/>
+      <c r="J21" s="118"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="47" t="s">
+      <c r="A22" s="130" t="s">
         <v>76</v>
       </c>
-      <c r="B22" s="49"/>
-      <c r="C22" s="50"/>
+      <c r="B22" s="131"/>
+      <c r="C22" s="132"/>
       <c r="D22" s="16" t="s">
         <v>94</v>
       </c>
@@ -8050,21 +8059,21 @@
       <c r="F22" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="G22" s="141" t="s">
+      <c r="G22" s="40" t="s">
         <v>108</v>
       </c>
-      <c r="H22" s="43" t="s">
+      <c r="H22" s="119" t="s">
         <v>110</v>
       </c>
-      <c r="I22" s="144"/>
-      <c r="J22" s="145"/>
+      <c r="I22" s="133"/>
+      <c r="J22" s="134"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="40" t="s">
+      <c r="A23" s="111" t="s">
         <v>77</v>
       </c>
-      <c r="B23" s="41"/>
-      <c r="C23" s="42"/>
+      <c r="B23" s="112"/>
+      <c r="C23" s="113"/>
       <c r="D23" s="18" t="s">
         <v>79</v>
       </c>
@@ -8075,37 +8084,37 @@
       <c r="G23" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="H23" s="46"/>
-      <c r="I23" s="134"/>
-      <c r="J23" s="142"/>
+      <c r="H23" s="114"/>
+      <c r="I23" s="115"/>
+      <c r="J23" s="116"/>
     </row>
     <row r="24" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A24" s="51" t="s">
+      <c r="A24" s="117" t="s">
         <v>23</v>
       </c>
-      <c r="B24" s="44"/>
-      <c r="C24" s="44"/>
-      <c r="D24" s="44"/>
-      <c r="E24" s="44"/>
-      <c r="F24" s="44"/>
-      <c r="G24" s="44"/>
-      <c r="H24" s="44"/>
-      <c r="I24" s="44"/>
-      <c r="J24" s="45"/>
+      <c r="B24" s="43"/>
+      <c r="C24" s="43"/>
+      <c r="D24" s="43"/>
+      <c r="E24" s="43"/>
+      <c r="F24" s="43"/>
+      <c r="G24" s="43"/>
+      <c r="H24" s="43"/>
+      <c r="I24" s="43"/>
+      <c r="J24" s="118"/>
     </row>
     <row r="25" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A25" s="51" t="s">
+      <c r="A25" s="117" t="s">
         <v>24</v>
       </c>
-      <c r="B25" s="44"/>
-      <c r="C25" s="48"/>
-      <c r="D25" s="43" t="s">
-        <v>121</v>
-      </c>
-      <c r="E25" s="44"/>
-      <c r="F25" s="44"/>
-      <c r="G25" s="44"/>
-      <c r="H25" s="48"/>
+      <c r="B25" s="43"/>
+      <c r="C25" s="44"/>
+      <c r="D25" s="119" t="s">
+        <v>120</v>
+      </c>
+      <c r="E25" s="43"/>
+      <c r="F25" s="43"/>
+      <c r="G25" s="43"/>
+      <c r="H25" s="44"/>
       <c r="I25" s="14" t="s">
         <v>25</v>
       </c>
@@ -8114,11 +8123,11 @@
       </c>
     </row>
     <row r="26" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A26" s="51" t="s">
+      <c r="A26" s="117" t="s">
         <v>26</v>
       </c>
-      <c r="B26" s="44"/>
-      <c r="C26" s="48"/>
+      <c r="B26" s="43"/>
+      <c r="C26" s="44"/>
       <c r="D26" s="14" t="s">
         <v>27</v>
       </c>
@@ -8131,31 +8140,31 @@
       <c r="G26" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="H26" s="54" t="s">
+      <c r="H26" s="120" t="s">
         <v>17</v>
       </c>
-      <c r="I26" s="44"/>
-      <c r="J26" s="45"/>
+      <c r="I26" s="43"/>
+      <c r="J26" s="118"/>
     </row>
     <row r="27" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A27" s="40" t="s">
+      <c r="A27" s="111" t="s">
         <v>78</v>
       </c>
-      <c r="B27" s="41"/>
-      <c r="C27" s="42"/>
+      <c r="B27" s="112"/>
+      <c r="C27" s="113"/>
       <c r="D27" s="18" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E27" s="18" t="s">
         <v>80</v>
       </c>
       <c r="F27" s="19"/>
       <c r="G27" s="18" t="s">
-        <v>122</v>
-      </c>
-      <c r="H27" s="46"/>
-      <c r="I27" s="134"/>
-      <c r="J27" s="142"/>
+        <v>121</v>
+      </c>
+      <c r="H27" s="114"/>
+      <c r="I27" s="115"/>
+      <c r="J27" s="116"/>
     </row>
     <row r="28" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="29" spans="1:10" ht="12.75" customHeight="1"/>
@@ -9132,6 +9141,28 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="38">
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A7:J13"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="I2:I4"/>
     <mergeCell ref="A27:C27"/>
     <mergeCell ref="H27:J27"/>
     <mergeCell ref="A23:C23"/>
@@ -9143,33 +9174,11 @@
     <mergeCell ref="A26:C26"/>
     <mergeCell ref="H26:J26"/>
     <mergeCell ref="A15:C15"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A7:J13"/>
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="H18:J18"/>
     <mergeCell ref="H19:J19"/>
     <mergeCell ref="H20:J20"/>
     <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A17:C17"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -9192,19 +9201,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="60" t="s">
+      <c r="A1" s="97" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="61"/>
-      <c r="C1" s="62"/>
-      <c r="D1" s="55" t="s">
+      <c r="B1" s="98"/>
+      <c r="C1" s="99"/>
+      <c r="D1" s="105" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="56"/>
-      <c r="F1" s="55" t="s">
+      <c r="E1" s="106"/>
+      <c r="F1" s="105" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="56"/>
+      <c r="G1" s="106"/>
       <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
@@ -9216,190 +9225,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="63"/>
-      <c r="B2" s="64"/>
-      <c r="C2" s="65"/>
-      <c r="D2" s="68" t="s">
+      <c r="A2" s="100"/>
+      <c r="B2" s="46"/>
+      <c r="C2" s="101"/>
+      <c r="D2" s="107" t="s">
         <v>86</v>
       </c>
-      <c r="E2" s="69"/>
-      <c r="F2" s="68" t="s">
+      <c r="E2" s="108"/>
+      <c r="F2" s="107" t="s">
         <v>87</v>
       </c>
-      <c r="G2" s="69"/>
-      <c r="H2" s="57">
+      <c r="G2" s="108"/>
+      <c r="H2" s="90">
         <v>46121</v>
       </c>
-      <c r="I2" s="59" t="s">
+      <c r="I2" s="93" t="s">
         <v>88</v>
       </c>
-      <c r="J2" s="52"/>
+      <c r="J2" s="94"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="63"/>
-      <c r="B3" s="64"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="70"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="70"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="53"/>
+      <c r="A3" s="100"/>
+      <c r="B3" s="46"/>
+      <c r="C3" s="101"/>
+      <c r="D3" s="109"/>
+      <c r="E3" s="101"/>
+      <c r="F3" s="109"/>
+      <c r="G3" s="101"/>
+      <c r="H3" s="91"/>
+      <c r="I3" s="91"/>
+      <c r="J3" s="95"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="63"/>
-      <c r="B4" s="64"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="70"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="70"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="58"/>
-      <c r="I4" s="58"/>
-      <c r="J4" s="53"/>
+      <c r="A4" s="100"/>
+      <c r="B4" s="46"/>
+      <c r="C4" s="101"/>
+      <c r="D4" s="109"/>
+      <c r="E4" s="101"/>
+      <c r="F4" s="109"/>
+      <c r="G4" s="101"/>
+      <c r="H4" s="91"/>
+      <c r="I4" s="91"/>
+      <c r="J4" s="95"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="66" t="s">
+      <c r="A5" s="121" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="67"/>
-      <c r="C5" s="56"/>
-      <c r="D5" s="71" t="s">
-        <v>117</v>
-      </c>
-      <c r="E5" s="67"/>
-      <c r="F5" s="67"/>
-      <c r="G5" s="67"/>
-      <c r="H5" s="67"/>
-      <c r="I5" s="67"/>
-      <c r="J5" s="72"/>
+      <c r="B5" s="122"/>
+      <c r="C5" s="106"/>
+      <c r="D5" s="123" t="s">
+        <v>116</v>
+      </c>
+      <c r="E5" s="122"/>
+      <c r="F5" s="122"/>
+      <c r="G5" s="122"/>
+      <c r="H5" s="122"/>
+      <c r="I5" s="122"/>
+      <c r="J5" s="124"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="51" t="s">
+      <c r="A6" s="117" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="44"/>
-      <c r="C6" s="44"/>
-      <c r="D6" s="44"/>
-      <c r="E6" s="44"/>
-      <c r="F6" s="44"/>
-      <c r="G6" s="44"/>
-      <c r="H6" s="44"/>
-      <c r="I6" s="44"/>
-      <c r="J6" s="45"/>
+      <c r="B6" s="43"/>
+      <c r="C6" s="43"/>
+      <c r="D6" s="43"/>
+      <c r="E6" s="43"/>
+      <c r="F6" s="43"/>
+      <c r="G6" s="43"/>
+      <c r="H6" s="43"/>
+      <c r="I6" s="43"/>
+      <c r="J6" s="118"/>
     </row>
     <row r="7" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A7" s="73"/>
-      <c r="B7" s="74"/>
-      <c r="C7" s="74"/>
-      <c r="D7" s="74"/>
-      <c r="E7" s="74"/>
-      <c r="F7" s="74"/>
-      <c r="G7" s="74"/>
-      <c r="H7" s="74"/>
-      <c r="I7" s="74"/>
-      <c r="J7" s="75"/>
+      <c r="A7" s="125"/>
+      <c r="B7" s="126"/>
+      <c r="C7" s="126"/>
+      <c r="D7" s="126"/>
+      <c r="E7" s="126"/>
+      <c r="F7" s="126"/>
+      <c r="G7" s="126"/>
+      <c r="H7" s="126"/>
+      <c r="I7" s="126"/>
+      <c r="J7" s="127"/>
     </row>
     <row r="8" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A8" s="63"/>
-      <c r="B8" s="64"/>
-      <c r="C8" s="64"/>
-      <c r="D8" s="64"/>
-      <c r="E8" s="64"/>
-      <c r="F8" s="64"/>
-      <c r="G8" s="64"/>
-      <c r="H8" s="64"/>
-      <c r="I8" s="64"/>
-      <c r="J8" s="76"/>
+      <c r="A8" s="100"/>
+      <c r="B8" s="46"/>
+      <c r="C8" s="46"/>
+      <c r="D8" s="46"/>
+      <c r="E8" s="46"/>
+      <c r="F8" s="46"/>
+      <c r="G8" s="46"/>
+      <c r="H8" s="46"/>
+      <c r="I8" s="46"/>
+      <c r="J8" s="128"/>
     </row>
     <row r="9" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A9" s="63"/>
-      <c r="B9" s="64"/>
-      <c r="C9" s="64"/>
-      <c r="D9" s="64"/>
-      <c r="E9" s="64"/>
-      <c r="F9" s="64"/>
-      <c r="G9" s="64"/>
-      <c r="H9" s="64"/>
-      <c r="I9" s="64"/>
-      <c r="J9" s="76"/>
+      <c r="A9" s="100"/>
+      <c r="B9" s="46"/>
+      <c r="C9" s="46"/>
+      <c r="D9" s="46"/>
+      <c r="E9" s="46"/>
+      <c r="F9" s="46"/>
+      <c r="G9" s="46"/>
+      <c r="H9" s="46"/>
+      <c r="I9" s="46"/>
+      <c r="J9" s="128"/>
     </row>
     <row r="10" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A10" s="63"/>
-      <c r="B10" s="64"/>
-      <c r="C10" s="64"/>
-      <c r="D10" s="64"/>
-      <c r="E10" s="64"/>
-      <c r="F10" s="64"/>
-      <c r="G10" s="64"/>
-      <c r="H10" s="64"/>
-      <c r="I10" s="64"/>
-      <c r="J10" s="76"/>
+      <c r="A10" s="100"/>
+      <c r="B10" s="46"/>
+      <c r="C10" s="46"/>
+      <c r="D10" s="46"/>
+      <c r="E10" s="46"/>
+      <c r="F10" s="46"/>
+      <c r="G10" s="46"/>
+      <c r="H10" s="46"/>
+      <c r="I10" s="46"/>
+      <c r="J10" s="128"/>
     </row>
     <row r="11" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A11" s="63"/>
-      <c r="B11" s="64"/>
-      <c r="C11" s="64"/>
-      <c r="D11" s="64"/>
-      <c r="E11" s="64"/>
-      <c r="F11" s="64"/>
-      <c r="G11" s="64"/>
-      <c r="H11" s="64"/>
-      <c r="I11" s="64"/>
-      <c r="J11" s="76"/>
+      <c r="A11" s="100"/>
+      <c r="B11" s="46"/>
+      <c r="C11" s="46"/>
+      <c r="D11" s="46"/>
+      <c r="E11" s="46"/>
+      <c r="F11" s="46"/>
+      <c r="G11" s="46"/>
+      <c r="H11" s="46"/>
+      <c r="I11" s="46"/>
+      <c r="J11" s="128"/>
     </row>
     <row r="12" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A12" s="63"/>
-      <c r="B12" s="64"/>
-      <c r="C12" s="64"/>
-      <c r="D12" s="64"/>
-      <c r="E12" s="64"/>
-      <c r="F12" s="64"/>
-      <c r="G12" s="64"/>
-      <c r="H12" s="64"/>
-      <c r="I12" s="64"/>
-      <c r="J12" s="76"/>
+      <c r="A12" s="100"/>
+      <c r="B12" s="46"/>
+      <c r="C12" s="46"/>
+      <c r="D12" s="46"/>
+      <c r="E12" s="46"/>
+      <c r="F12" s="46"/>
+      <c r="G12" s="46"/>
+      <c r="H12" s="46"/>
+      <c r="I12" s="46"/>
+      <c r="J12" s="128"/>
     </row>
     <row r="13" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A13" s="63"/>
-      <c r="B13" s="64"/>
-      <c r="C13" s="64"/>
-      <c r="D13" s="64"/>
-      <c r="E13" s="64"/>
-      <c r="F13" s="64"/>
-      <c r="G13" s="64"/>
-      <c r="H13" s="64"/>
-      <c r="I13" s="64"/>
-      <c r="J13" s="76"/>
+      <c r="A13" s="100"/>
+      <c r="B13" s="46"/>
+      <c r="C13" s="46"/>
+      <c r="D13" s="46"/>
+      <c r="E13" s="46"/>
+      <c r="F13" s="46"/>
+      <c r="G13" s="46"/>
+      <c r="H13" s="46"/>
+      <c r="I13" s="46"/>
+      <c r="J13" s="128"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="51" t="s">
+      <c r="A14" s="117" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="44"/>
-      <c r="C14" s="44"/>
-      <c r="D14" s="44"/>
-      <c r="E14" s="44"/>
-      <c r="F14" s="44"/>
-      <c r="G14" s="44"/>
-      <c r="H14" s="44"/>
-      <c r="I14" s="44"/>
-      <c r="J14" s="45"/>
+      <c r="B14" s="43"/>
+      <c r="C14" s="43"/>
+      <c r="D14" s="43"/>
+      <c r="E14" s="43"/>
+      <c r="F14" s="43"/>
+      <c r="G14" s="43"/>
+      <c r="H14" s="43"/>
+      <c r="I14" s="43"/>
+      <c r="J14" s="118"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="51" t="s">
+      <c r="A15" s="117" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="44"/>
-      <c r="C15" s="48"/>
-      <c r="D15" s="43" t="s">
+      <c r="B15" s="43"/>
+      <c r="C15" s="44"/>
+      <c r="D15" s="119" t="s">
         <v>102</v>
       </c>
-      <c r="E15" s="44"/>
-      <c r="F15" s="44"/>
-      <c r="G15" s="44"/>
-      <c r="H15" s="48"/>
+      <c r="E15" s="43"/>
+      <c r="F15" s="43"/>
+      <c r="G15" s="43"/>
+      <c r="H15" s="44"/>
       <c r="I15" s="14" t="s">
         <v>25</v>
       </c>
@@ -9408,11 +9417,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="51" t="s">
+      <c r="A16" s="117" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="44"/>
-      <c r="C16" s="48"/>
+      <c r="B16" s="43"/>
+      <c r="C16" s="44"/>
       <c r="D16" s="14" t="s">
         <v>27</v>
       </c>
@@ -9425,19 +9434,19 @@
       <c r="G16" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="H16" s="54" t="s">
+      <c r="H16" s="120" t="s">
         <v>17</v>
       </c>
-      <c r="I16" s="44"/>
-      <c r="J16" s="45"/>
+      <c r="I16" s="43"/>
+      <c r="J16" s="118"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A17" s="40" t="s">
+      <c r="A17" s="111" t="s">
         <v>71</v>
       </c>
-      <c r="B17" s="134"/>
-      <c r="C17" s="130"/>
-      <c r="D17" s="147" t="s">
+      <c r="B17" s="115"/>
+      <c r="C17" s="135"/>
+      <c r="D17" s="41" t="s">
         <v>101</v>
       </c>
       <c r="E17" s="18" t="s">
@@ -9447,9 +9456,9 @@
       <c r="G17" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="H17" s="46"/>
-      <c r="I17" s="134"/>
-      <c r="J17" s="142"/>
+      <c r="H17" s="114"/>
+      <c r="I17" s="115"/>
+      <c r="J17" s="116"/>
     </row>
     <row r="18" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="19" spans="1:10" ht="12.75" customHeight="1"/>
@@ -10430,12 +10439,6 @@
     <row r="994" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="A14:J14"/>
-    <mergeCell ref="A15:C15"/>
     <mergeCell ref="A7:J13"/>
     <mergeCell ref="A1:C4"/>
     <mergeCell ref="D1:E1"/>
@@ -10448,6 +10451,12 @@
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A15:C15"/>
     <mergeCell ref="D15:H15"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
@@ -10471,19 +10480,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="60" t="s">
+      <c r="A1" s="97" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="61"/>
-      <c r="C1" s="62"/>
-      <c r="D1" s="55" t="s">
+      <c r="B1" s="98"/>
+      <c r="C1" s="99"/>
+      <c r="D1" s="105" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="56"/>
-      <c r="F1" s="55" t="s">
+      <c r="E1" s="106"/>
+      <c r="F1" s="105" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="56"/>
+      <c r="G1" s="106"/>
       <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
@@ -10495,190 +10504,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="63"/>
-      <c r="B2" s="64"/>
-      <c r="C2" s="65"/>
-      <c r="D2" s="68" t="s">
+      <c r="A2" s="100"/>
+      <c r="B2" s="46"/>
+      <c r="C2" s="101"/>
+      <c r="D2" s="107" t="s">
         <v>86</v>
       </c>
-      <c r="E2" s="69"/>
-      <c r="F2" s="68" t="s">
+      <c r="E2" s="108"/>
+      <c r="F2" s="107" t="s">
         <v>87</v>
       </c>
-      <c r="G2" s="69"/>
-      <c r="H2" s="57">
+      <c r="G2" s="108"/>
+      <c r="H2" s="90">
         <v>46121</v>
       </c>
-      <c r="I2" s="59" t="s">
+      <c r="I2" s="93" t="s">
         <v>88</v>
       </c>
-      <c r="J2" s="52"/>
+      <c r="J2" s="94"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="63"/>
-      <c r="B3" s="64"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="70"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="70"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="53"/>
+      <c r="A3" s="100"/>
+      <c r="B3" s="46"/>
+      <c r="C3" s="101"/>
+      <c r="D3" s="109"/>
+      <c r="E3" s="101"/>
+      <c r="F3" s="109"/>
+      <c r="G3" s="101"/>
+      <c r="H3" s="91"/>
+      <c r="I3" s="91"/>
+      <c r="J3" s="95"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="63"/>
-      <c r="B4" s="64"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="70"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="70"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="58"/>
-      <c r="I4" s="58"/>
-      <c r="J4" s="53"/>
+      <c r="A4" s="100"/>
+      <c r="B4" s="46"/>
+      <c r="C4" s="101"/>
+      <c r="D4" s="109"/>
+      <c r="E4" s="101"/>
+      <c r="F4" s="109"/>
+      <c r="G4" s="101"/>
+      <c r="H4" s="91"/>
+      <c r="I4" s="91"/>
+      <c r="J4" s="95"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="66" t="s">
+      <c r="A5" s="121" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="67"/>
-      <c r="C5" s="56"/>
-      <c r="D5" s="71" t="s">
-        <v>118</v>
-      </c>
-      <c r="E5" s="67"/>
-      <c r="F5" s="67"/>
-      <c r="G5" s="67"/>
-      <c r="H5" s="67"/>
-      <c r="I5" s="67"/>
-      <c r="J5" s="72"/>
+      <c r="B5" s="122"/>
+      <c r="C5" s="106"/>
+      <c r="D5" s="123" t="s">
+        <v>117</v>
+      </c>
+      <c r="E5" s="122"/>
+      <c r="F5" s="122"/>
+      <c r="G5" s="122"/>
+      <c r="H5" s="122"/>
+      <c r="I5" s="122"/>
+      <c r="J5" s="124"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="51" t="s">
+      <c r="A6" s="117" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="44"/>
-      <c r="C6" s="44"/>
-      <c r="D6" s="44"/>
-      <c r="E6" s="44"/>
-      <c r="F6" s="44"/>
-      <c r="G6" s="44"/>
-      <c r="H6" s="44"/>
-      <c r="I6" s="44"/>
-      <c r="J6" s="45"/>
+      <c r="B6" s="43"/>
+      <c r="C6" s="43"/>
+      <c r="D6" s="43"/>
+      <c r="E6" s="43"/>
+      <c r="F6" s="43"/>
+      <c r="G6" s="43"/>
+      <c r="H6" s="43"/>
+      <c r="I6" s="43"/>
+      <c r="J6" s="118"/>
     </row>
     <row r="7" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A7" s="73"/>
-      <c r="B7" s="74"/>
-      <c r="C7" s="74"/>
-      <c r="D7" s="74"/>
-      <c r="E7" s="74"/>
-      <c r="F7" s="74"/>
-      <c r="G7" s="74"/>
-      <c r="H7" s="74"/>
-      <c r="I7" s="74"/>
-      <c r="J7" s="75"/>
+      <c r="A7" s="125"/>
+      <c r="B7" s="126"/>
+      <c r="C7" s="126"/>
+      <c r="D7" s="126"/>
+      <c r="E7" s="126"/>
+      <c r="F7" s="126"/>
+      <c r="G7" s="126"/>
+      <c r="H7" s="126"/>
+      <c r="I7" s="126"/>
+      <c r="J7" s="127"/>
     </row>
     <row r="8" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A8" s="63"/>
-      <c r="B8" s="64"/>
-      <c r="C8" s="64"/>
-      <c r="D8" s="64"/>
-      <c r="E8" s="64"/>
-      <c r="F8" s="64"/>
-      <c r="G8" s="64"/>
-      <c r="H8" s="64"/>
-      <c r="I8" s="64"/>
-      <c r="J8" s="76"/>
+      <c r="A8" s="100"/>
+      <c r="B8" s="46"/>
+      <c r="C8" s="46"/>
+      <c r="D8" s="46"/>
+      <c r="E8" s="46"/>
+      <c r="F8" s="46"/>
+      <c r="G8" s="46"/>
+      <c r="H8" s="46"/>
+      <c r="I8" s="46"/>
+      <c r="J8" s="128"/>
     </row>
     <row r="9" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A9" s="63"/>
-      <c r="B9" s="64"/>
-      <c r="C9" s="64"/>
-      <c r="D9" s="64"/>
-      <c r="E9" s="64"/>
-      <c r="F9" s="64"/>
-      <c r="G9" s="64"/>
-      <c r="H9" s="64"/>
-      <c r="I9" s="64"/>
-      <c r="J9" s="76"/>
+      <c r="A9" s="100"/>
+      <c r="B9" s="46"/>
+      <c r="C9" s="46"/>
+      <c r="D9" s="46"/>
+      <c r="E9" s="46"/>
+      <c r="F9" s="46"/>
+      <c r="G9" s="46"/>
+      <c r="H9" s="46"/>
+      <c r="I9" s="46"/>
+      <c r="J9" s="128"/>
     </row>
     <row r="10" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A10" s="63"/>
-      <c r="B10" s="64"/>
-      <c r="C10" s="64"/>
-      <c r="D10" s="64"/>
-      <c r="E10" s="64"/>
-      <c r="F10" s="64"/>
-      <c r="G10" s="64"/>
-      <c r="H10" s="64"/>
-      <c r="I10" s="64"/>
-      <c r="J10" s="76"/>
+      <c r="A10" s="100"/>
+      <c r="B10" s="46"/>
+      <c r="C10" s="46"/>
+      <c r="D10" s="46"/>
+      <c r="E10" s="46"/>
+      <c r="F10" s="46"/>
+      <c r="G10" s="46"/>
+      <c r="H10" s="46"/>
+      <c r="I10" s="46"/>
+      <c r="J10" s="128"/>
     </row>
     <row r="11" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A11" s="63"/>
-      <c r="B11" s="64"/>
-      <c r="C11" s="64"/>
-      <c r="D11" s="64"/>
-      <c r="E11" s="64"/>
-      <c r="F11" s="64"/>
-      <c r="G11" s="64"/>
-      <c r="H11" s="64"/>
-      <c r="I11" s="64"/>
-      <c r="J11" s="76"/>
+      <c r="A11" s="100"/>
+      <c r="B11" s="46"/>
+      <c r="C11" s="46"/>
+      <c r="D11" s="46"/>
+      <c r="E11" s="46"/>
+      <c r="F11" s="46"/>
+      <c r="G11" s="46"/>
+      <c r="H11" s="46"/>
+      <c r="I11" s="46"/>
+      <c r="J11" s="128"/>
     </row>
     <row r="12" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A12" s="63"/>
-      <c r="B12" s="64"/>
-      <c r="C12" s="64"/>
-      <c r="D12" s="64"/>
-      <c r="E12" s="64"/>
-      <c r="F12" s="64"/>
-      <c r="G12" s="64"/>
-      <c r="H12" s="64"/>
-      <c r="I12" s="64"/>
-      <c r="J12" s="76"/>
+      <c r="A12" s="100"/>
+      <c r="B12" s="46"/>
+      <c r="C12" s="46"/>
+      <c r="D12" s="46"/>
+      <c r="E12" s="46"/>
+      <c r="F12" s="46"/>
+      <c r="G12" s="46"/>
+      <c r="H12" s="46"/>
+      <c r="I12" s="46"/>
+      <c r="J12" s="128"/>
     </row>
     <row r="13" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A13" s="63"/>
-      <c r="B13" s="64"/>
-      <c r="C13" s="64"/>
-      <c r="D13" s="64"/>
-      <c r="E13" s="64"/>
-      <c r="F13" s="64"/>
-      <c r="G13" s="64"/>
-      <c r="H13" s="64"/>
-      <c r="I13" s="64"/>
-      <c r="J13" s="76"/>
+      <c r="A13" s="100"/>
+      <c r="B13" s="46"/>
+      <c r="C13" s="46"/>
+      <c r="D13" s="46"/>
+      <c r="E13" s="46"/>
+      <c r="F13" s="46"/>
+      <c r="G13" s="46"/>
+      <c r="H13" s="46"/>
+      <c r="I13" s="46"/>
+      <c r="J13" s="128"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="51" t="s">
+      <c r="A14" s="117" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="44"/>
-      <c r="C14" s="44"/>
-      <c r="D14" s="44"/>
-      <c r="E14" s="44"/>
-      <c r="F14" s="44"/>
-      <c r="G14" s="44"/>
-      <c r="H14" s="44"/>
-      <c r="I14" s="44"/>
-      <c r="J14" s="45"/>
+      <c r="B14" s="43"/>
+      <c r="C14" s="43"/>
+      <c r="D14" s="43"/>
+      <c r="E14" s="43"/>
+      <c r="F14" s="43"/>
+      <c r="G14" s="43"/>
+      <c r="H14" s="43"/>
+      <c r="I14" s="43"/>
+      <c r="J14" s="118"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="51" t="s">
+      <c r="A15" s="117" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="44"/>
-      <c r="C15" s="48"/>
-      <c r="D15" s="43" t="s">
+      <c r="B15" s="43"/>
+      <c r="C15" s="44"/>
+      <c r="D15" s="119" t="s">
         <v>100</v>
       </c>
-      <c r="E15" s="44"/>
-      <c r="F15" s="44"/>
-      <c r="G15" s="44"/>
-      <c r="H15" s="48"/>
+      <c r="E15" s="43"/>
+      <c r="F15" s="43"/>
+      <c r="G15" s="43"/>
+      <c r="H15" s="44"/>
       <c r="I15" s="14" t="s">
         <v>25</v>
       </c>
@@ -10687,11 +10696,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="51" t="s">
+      <c r="A16" s="117" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="44"/>
-      <c r="C16" s="48"/>
+      <c r="B16" s="43"/>
+      <c r="C16" s="44"/>
       <c r="D16" s="14" t="s">
         <v>27</v>
       </c>
@@ -10704,31 +10713,31 @@
       <c r="G16" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="H16" s="54" t="s">
+      <c r="H16" s="120" t="s">
         <v>17</v>
       </c>
-      <c r="I16" s="44"/>
-      <c r="J16" s="45"/>
+      <c r="I16" s="43"/>
+      <c r="J16" s="118"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A17" s="40" t="s">
+      <c r="A17" s="111" t="s">
         <v>71</v>
       </c>
-      <c r="B17" s="134"/>
-      <c r="C17" s="130"/>
-      <c r="D17" s="147" t="s">
-        <v>119</v>
+      <c r="B17" s="115"/>
+      <c r="C17" s="135"/>
+      <c r="D17" s="41" t="s">
+        <v>118</v>
       </c>
       <c r="E17" s="18" t="s">
         <v>80</v>
       </c>
       <c r="F17" s="19"/>
       <c r="G17" s="19" t="s">
-        <v>120</v>
-      </c>
-      <c r="H17" s="46"/>
-      <c r="I17" s="134"/>
-      <c r="J17" s="142"/>
+        <v>119</v>
+      </c>
+      <c r="H17" s="114"/>
+      <c r="I17" s="115"/>
+      <c r="J17" s="116"/>
     </row>
     <row r="18" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="19" spans="1:10" ht="12.75" customHeight="1"/>
@@ -11709,12 +11718,6 @@
     <row r="994" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="A14:J14"/>
-    <mergeCell ref="A15:C15"/>
     <mergeCell ref="A7:J13"/>
     <mergeCell ref="A1:C4"/>
     <mergeCell ref="D1:E1"/>
@@ -11727,6 +11730,12 @@
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A15:C15"/>
     <mergeCell ref="D15:H15"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
@@ -11747,182 +11756,182 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="139" t="s">
+      <c r="A1" s="141" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="61"/>
-      <c r="C1" s="61"/>
-      <c r="D1" s="61"/>
-      <c r="E1" s="61"/>
-      <c r="F1" s="62"/>
-      <c r="G1" s="55" t="s">
+      <c r="B1" s="98"/>
+      <c r="C1" s="98"/>
+      <c r="D1" s="98"/>
+      <c r="E1" s="98"/>
+      <c r="F1" s="99"/>
+      <c r="G1" s="105" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="67"/>
-      <c r="I1" s="67"/>
-      <c r="J1" s="56"/>
-      <c r="K1" s="55" t="s">
+      <c r="H1" s="122"/>
+      <c r="I1" s="122"/>
+      <c r="J1" s="106"/>
+      <c r="K1" s="105" t="s">
         <v>4</v>
       </c>
-      <c r="L1" s="67"/>
-      <c r="M1" s="67"/>
-      <c r="N1" s="56"/>
-      <c r="O1" s="55" t="s">
+      <c r="L1" s="122"/>
+      <c r="M1" s="122"/>
+      <c r="N1" s="106"/>
+      <c r="O1" s="105" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="56"/>
-      <c r="Q1" s="55" t="s">
+      <c r="P1" s="106"/>
+      <c r="Q1" s="105" t="s">
         <v>6</v>
       </c>
-      <c r="R1" s="56"/>
-      <c r="S1" s="55" t="s">
+      <c r="R1" s="106"/>
+      <c r="S1" s="105" t="s">
         <v>7</v>
       </c>
-      <c r="T1" s="72"/>
+      <c r="T1" s="124"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="63"/>
-      <c r="B2" s="64"/>
-      <c r="C2" s="64"/>
-      <c r="D2" s="64"/>
-      <c r="E2" s="64"/>
-      <c r="F2" s="65"/>
-      <c r="G2" s="68"/>
-      <c r="H2" s="74"/>
-      <c r="I2" s="74"/>
-      <c r="J2" s="69"/>
-      <c r="K2" s="68"/>
-      <c r="L2" s="74"/>
-      <c r="M2" s="74"/>
-      <c r="N2" s="69"/>
-      <c r="O2" s="68"/>
-      <c r="P2" s="69"/>
-      <c r="Q2" s="68"/>
-      <c r="R2" s="69"/>
-      <c r="S2" s="68"/>
-      <c r="T2" s="75"/>
+      <c r="A2" s="100"/>
+      <c r="B2" s="46"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="46"/>
+      <c r="E2" s="46"/>
+      <c r="F2" s="101"/>
+      <c r="G2" s="107"/>
+      <c r="H2" s="126"/>
+      <c r="I2" s="126"/>
+      <c r="J2" s="108"/>
+      <c r="K2" s="107"/>
+      <c r="L2" s="126"/>
+      <c r="M2" s="126"/>
+      <c r="N2" s="108"/>
+      <c r="O2" s="107"/>
+      <c r="P2" s="108"/>
+      <c r="Q2" s="107"/>
+      <c r="R2" s="108"/>
+      <c r="S2" s="107"/>
+      <c r="T2" s="127"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="63"/>
-      <c r="B3" s="64"/>
-      <c r="C3" s="64"/>
-      <c r="D3" s="64"/>
-      <c r="E3" s="64"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="70"/>
-      <c r="H3" s="64"/>
-      <c r="I3" s="64"/>
-      <c r="J3" s="65"/>
-      <c r="K3" s="70"/>
-      <c r="L3" s="64"/>
-      <c r="M3" s="64"/>
-      <c r="N3" s="65"/>
-      <c r="O3" s="70"/>
-      <c r="P3" s="65"/>
-      <c r="Q3" s="70"/>
-      <c r="R3" s="65"/>
-      <c r="S3" s="70"/>
-      <c r="T3" s="76"/>
+      <c r="A3" s="100"/>
+      <c r="B3" s="46"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="46"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="101"/>
+      <c r="G3" s="109"/>
+      <c r="H3" s="46"/>
+      <c r="I3" s="46"/>
+      <c r="J3" s="101"/>
+      <c r="K3" s="109"/>
+      <c r="L3" s="46"/>
+      <c r="M3" s="46"/>
+      <c r="N3" s="101"/>
+      <c r="O3" s="109"/>
+      <c r="P3" s="101"/>
+      <c r="Q3" s="109"/>
+      <c r="R3" s="101"/>
+      <c r="S3" s="109"/>
+      <c r="T3" s="128"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="123"/>
-      <c r="B4" s="124"/>
-      <c r="C4" s="124"/>
-      <c r="D4" s="124"/>
-      <c r="E4" s="124"/>
-      <c r="F4" s="125"/>
-      <c r="G4" s="126"/>
-      <c r="H4" s="124"/>
-      <c r="I4" s="124"/>
-      <c r="J4" s="125"/>
-      <c r="K4" s="126"/>
-      <c r="L4" s="124"/>
-      <c r="M4" s="124"/>
-      <c r="N4" s="125"/>
-      <c r="O4" s="126"/>
-      <c r="P4" s="125"/>
-      <c r="Q4" s="126"/>
-      <c r="R4" s="125"/>
-      <c r="S4" s="126"/>
-      <c r="T4" s="138"/>
+      <c r="A4" s="102"/>
+      <c r="B4" s="103"/>
+      <c r="C4" s="103"/>
+      <c r="D4" s="103"/>
+      <c r="E4" s="103"/>
+      <c r="F4" s="104"/>
+      <c r="G4" s="110"/>
+      <c r="H4" s="103"/>
+      <c r="I4" s="103"/>
+      <c r="J4" s="104"/>
+      <c r="K4" s="110"/>
+      <c r="L4" s="103"/>
+      <c r="M4" s="103"/>
+      <c r="N4" s="104"/>
+      <c r="O4" s="110"/>
+      <c r="P4" s="104"/>
+      <c r="Q4" s="110"/>
+      <c r="R4" s="104"/>
+      <c r="S4" s="110"/>
+      <c r="T4" s="140"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="66" t="s">
+      <c r="A5" s="121" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="67"/>
-      <c r="C5" s="67"/>
-      <c r="D5" s="67"/>
-      <c r="E5" s="67"/>
-      <c r="F5" s="56"/>
-      <c r="G5" s="135" t="s">
+      <c r="B5" s="122"/>
+      <c r="C5" s="122"/>
+      <c r="D5" s="122"/>
+      <c r="E5" s="122"/>
+      <c r="F5" s="106"/>
+      <c r="G5" s="142" t="s">
         <v>33</v>
       </c>
-      <c r="H5" s="67"/>
-      <c r="I5" s="67"/>
-      <c r="J5" s="67"/>
-      <c r="K5" s="67"/>
-      <c r="L5" s="67"/>
-      <c r="M5" s="67"/>
-      <c r="N5" s="67"/>
-      <c r="O5" s="67"/>
-      <c r="P5" s="67"/>
-      <c r="Q5" s="67"/>
-      <c r="R5" s="67"/>
-      <c r="S5" s="67"/>
-      <c r="T5" s="72"/>
+      <c r="H5" s="122"/>
+      <c r="I5" s="122"/>
+      <c r="J5" s="122"/>
+      <c r="K5" s="122"/>
+      <c r="L5" s="122"/>
+      <c r="M5" s="122"/>
+      <c r="N5" s="122"/>
+      <c r="O5" s="122"/>
+      <c r="P5" s="122"/>
+      <c r="Q5" s="122"/>
+      <c r="R5" s="122"/>
+      <c r="S5" s="122"/>
+      <c r="T5" s="124"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="51" t="s">
+      <c r="A6" s="117" t="s">
         <v>34</v>
       </c>
-      <c r="B6" s="44"/>
-      <c r="C6" s="44"/>
-      <c r="D6" s="44"/>
-      <c r="E6" s="44"/>
-      <c r="F6" s="48"/>
-      <c r="G6" s="43" t="s">
+      <c r="B6" s="43"/>
+      <c r="C6" s="43"/>
+      <c r="D6" s="43"/>
+      <c r="E6" s="43"/>
+      <c r="F6" s="44"/>
+      <c r="G6" s="119" t="s">
         <v>18</v>
       </c>
-      <c r="H6" s="44"/>
-      <c r="I6" s="44"/>
-      <c r="J6" s="44"/>
-      <c r="K6" s="44"/>
-      <c r="L6" s="44"/>
-      <c r="M6" s="44"/>
-      <c r="N6" s="44"/>
-      <c r="O6" s="44"/>
-      <c r="P6" s="44"/>
-      <c r="Q6" s="44"/>
-      <c r="R6" s="44"/>
-      <c r="S6" s="44"/>
-      <c r="T6" s="45"/>
+      <c r="H6" s="43"/>
+      <c r="I6" s="43"/>
+      <c r="J6" s="43"/>
+      <c r="K6" s="43"/>
+      <c r="L6" s="43"/>
+      <c r="M6" s="43"/>
+      <c r="N6" s="43"/>
+      <c r="O6" s="43"/>
+      <c r="P6" s="43"/>
+      <c r="Q6" s="43"/>
+      <c r="R6" s="43"/>
+      <c r="S6" s="43"/>
+      <c r="T6" s="118"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="51" t="s">
+      <c r="A7" s="117" t="s">
         <v>35</v>
       </c>
-      <c r="B7" s="44"/>
-      <c r="C7" s="44"/>
-      <c r="D7" s="44"/>
-      <c r="E7" s="44"/>
-      <c r="F7" s="48"/>
-      <c r="G7" s="43" t="s">
+      <c r="B7" s="43"/>
+      <c r="C7" s="43"/>
+      <c r="D7" s="43"/>
+      <c r="E7" s="43"/>
+      <c r="F7" s="44"/>
+      <c r="G7" s="119" t="s">
         <v>36</v>
       </c>
-      <c r="H7" s="44"/>
-      <c r="I7" s="44"/>
-      <c r="J7" s="44"/>
-      <c r="K7" s="44"/>
-      <c r="L7" s="44"/>
-      <c r="M7" s="44"/>
-      <c r="N7" s="44"/>
-      <c r="O7" s="44"/>
-      <c r="P7" s="44"/>
-      <c r="Q7" s="44"/>
-      <c r="R7" s="44"/>
-      <c r="S7" s="44"/>
-      <c r="T7" s="45"/>
+      <c r="H7" s="43"/>
+      <c r="I7" s="43"/>
+      <c r="J7" s="43"/>
+      <c r="K7" s="43"/>
+      <c r="L7" s="43"/>
+      <c r="M7" s="43"/>
+      <c r="N7" s="43"/>
+      <c r="O7" s="43"/>
+      <c r="P7" s="43"/>
+      <c r="Q7" s="43"/>
+      <c r="R7" s="43"/>
+      <c r="S7" s="43"/>
+      <c r="T7" s="118"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="7"/>
@@ -12121,37 +12130,37 @@
       <c r="T14" s="9"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="51" t="s">
+      <c r="A15" s="117" t="s">
         <v>43</v>
       </c>
-      <c r="B15" s="48"/>
-      <c r="C15" s="137" t="s">
+      <c r="B15" s="44"/>
+      <c r="C15" s="145" t="s">
         <v>37</v>
       </c>
-      <c r="D15" s="48"/>
-      <c r="E15" s="54" t="s">
+      <c r="D15" s="44"/>
+      <c r="E15" s="120" t="s">
         <v>44</v>
       </c>
-      <c r="F15" s="48"/>
-      <c r="G15" s="54" t="s">
+      <c r="F15" s="44"/>
+      <c r="G15" s="120" t="s">
         <v>45</v>
       </c>
-      <c r="H15" s="44"/>
-      <c r="I15" s="48"/>
-      <c r="J15" s="54" t="s">
+      <c r="H15" s="43"/>
+      <c r="I15" s="44"/>
+      <c r="J15" s="120" t="s">
         <v>46</v>
       </c>
-      <c r="K15" s="48"/>
-      <c r="L15" s="54" t="s">
+      <c r="K15" s="44"/>
+      <c r="L15" s="120" t="s">
         <v>47</v>
       </c>
-      <c r="M15" s="44"/>
-      <c r="N15" s="48"/>
-      <c r="O15" s="54" t="s">
+      <c r="M15" s="43"/>
+      <c r="N15" s="44"/>
+      <c r="O15" s="120" t="s">
         <v>48</v>
       </c>
-      <c r="P15" s="44"/>
-      <c r="Q15" s="48"/>
+      <c r="P15" s="43"/>
+      <c r="Q15" s="44"/>
       <c r="R15" s="14" t="s">
         <v>49</v>
       </c>
@@ -12163,37 +12172,37 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="127">
+      <c r="A16" s="143">
         <v>1</v>
       </c>
-      <c r="B16" s="48"/>
-      <c r="C16" s="128" t="s">
+      <c r="B16" s="44"/>
+      <c r="C16" s="144" t="s">
         <v>52</v>
       </c>
-      <c r="D16" s="48"/>
-      <c r="E16" s="128" t="s">
+      <c r="D16" s="44"/>
+      <c r="E16" s="144" t="s">
         <v>53</v>
       </c>
-      <c r="F16" s="48"/>
+      <c r="F16" s="44"/>
       <c r="G16" s="136" t="s">
         <v>54</v>
       </c>
-      <c r="H16" s="44"/>
-      <c r="I16" s="48"/>
+      <c r="H16" s="43"/>
+      <c r="I16" s="44"/>
       <c r="J16" s="136" t="s">
         <v>55</v>
       </c>
-      <c r="K16" s="48"/>
-      <c r="L16" s="132" t="s">
+      <c r="K16" s="44"/>
+      <c r="L16" s="138" t="s">
         <v>56</v>
       </c>
-      <c r="M16" s="44"/>
-      <c r="N16" s="48"/>
-      <c r="O16" s="132" t="s">
+      <c r="M16" s="43"/>
+      <c r="N16" s="44"/>
+      <c r="O16" s="138" t="s">
         <v>57</v>
       </c>
-      <c r="P16" s="44"/>
-      <c r="Q16" s="48"/>
+      <c r="P16" s="43"/>
+      <c r="Q16" s="44"/>
       <c r="R16" s="32"/>
       <c r="S16" s="32"/>
       <c r="T16" s="33"/>
@@ -12205,37 +12214,37 @@
       <c r="Z16" s="34"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="127">
+      <c r="A17" s="143">
         <v>2</v>
       </c>
-      <c r="B17" s="48"/>
-      <c r="C17" s="128" t="s">
+      <c r="B17" s="44"/>
+      <c r="C17" s="144" t="s">
         <v>58</v>
       </c>
-      <c r="D17" s="48"/>
-      <c r="E17" s="128" t="s">
+      <c r="D17" s="44"/>
+      <c r="E17" s="144" t="s">
         <v>59</v>
       </c>
-      <c r="F17" s="48"/>
+      <c r="F17" s="44"/>
       <c r="G17" s="136" t="s">
         <v>60</v>
       </c>
-      <c r="H17" s="44"/>
-      <c r="I17" s="48"/>
+      <c r="H17" s="43"/>
+      <c r="I17" s="44"/>
       <c r="J17" s="136" t="s">
         <v>61</v>
       </c>
-      <c r="K17" s="48"/>
-      <c r="L17" s="132" t="s">
+      <c r="K17" s="44"/>
+      <c r="L17" s="138" t="s">
         <v>62</v>
       </c>
-      <c r="M17" s="44"/>
-      <c r="N17" s="48"/>
-      <c r="O17" s="132" t="s">
+      <c r="M17" s="43"/>
+      <c r="N17" s="44"/>
+      <c r="O17" s="138" t="s">
         <v>63</v>
       </c>
-      <c r="P17" s="44"/>
-      <c r="Q17" s="48"/>
+      <c r="P17" s="43"/>
+      <c r="Q17" s="44"/>
       <c r="R17" s="32"/>
       <c r="S17" s="32"/>
       <c r="T17" s="33"/>
@@ -12247,23 +12256,23 @@
       <c r="Z17" s="34"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="127"/>
-      <c r="B18" s="48"/>
-      <c r="C18" s="128"/>
-      <c r="D18" s="48"/>
-      <c r="E18" s="128"/>
-      <c r="F18" s="48"/>
+      <c r="A18" s="143"/>
+      <c r="B18" s="44"/>
+      <c r="C18" s="144"/>
+      <c r="D18" s="44"/>
+      <c r="E18" s="144"/>
+      <c r="F18" s="44"/>
       <c r="G18" s="136"/>
-      <c r="H18" s="44"/>
-      <c r="I18" s="48"/>
+      <c r="H18" s="43"/>
+      <c r="I18" s="44"/>
       <c r="J18" s="136"/>
-      <c r="K18" s="48"/>
-      <c r="L18" s="132"/>
-      <c r="M18" s="44"/>
-      <c r="N18" s="48"/>
-      <c r="O18" s="132"/>
-      <c r="P18" s="44"/>
-      <c r="Q18" s="48"/>
+      <c r="K18" s="44"/>
+      <c r="L18" s="138"/>
+      <c r="M18" s="43"/>
+      <c r="N18" s="44"/>
+      <c r="O18" s="138"/>
+      <c r="P18" s="43"/>
+      <c r="Q18" s="44"/>
       <c r="R18" s="32"/>
       <c r="S18" s="32"/>
       <c r="T18" s="33"/>
@@ -12275,23 +12284,23 @@
       <c r="Z18" s="34"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="127"/>
-      <c r="B19" s="48"/>
-      <c r="C19" s="128"/>
-      <c r="D19" s="48"/>
-      <c r="E19" s="128"/>
-      <c r="F19" s="48"/>
+      <c r="A19" s="143"/>
+      <c r="B19" s="44"/>
+      <c r="C19" s="144"/>
+      <c r="D19" s="44"/>
+      <c r="E19" s="144"/>
+      <c r="F19" s="44"/>
       <c r="G19" s="136"/>
-      <c r="H19" s="44"/>
-      <c r="I19" s="48"/>
+      <c r="H19" s="43"/>
+      <c r="I19" s="44"/>
       <c r="J19" s="136"/>
-      <c r="K19" s="48"/>
-      <c r="L19" s="132"/>
-      <c r="M19" s="44"/>
-      <c r="N19" s="48"/>
-      <c r="O19" s="132"/>
-      <c r="P19" s="44"/>
-      <c r="Q19" s="48"/>
+      <c r="K19" s="44"/>
+      <c r="L19" s="138"/>
+      <c r="M19" s="43"/>
+      <c r="N19" s="44"/>
+      <c r="O19" s="138"/>
+      <c r="P19" s="43"/>
+      <c r="Q19" s="44"/>
       <c r="R19" s="32"/>
       <c r="S19" s="32"/>
       <c r="T19" s="33"/>
@@ -12303,23 +12312,23 @@
       <c r="Z19" s="34"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="127"/>
-      <c r="B20" s="48"/>
-      <c r="C20" s="128"/>
-      <c r="D20" s="48"/>
-      <c r="E20" s="128"/>
-      <c r="F20" s="48"/>
+      <c r="A20" s="143"/>
+      <c r="B20" s="44"/>
+      <c r="C20" s="144"/>
+      <c r="D20" s="44"/>
+      <c r="E20" s="144"/>
+      <c r="F20" s="44"/>
       <c r="G20" s="136"/>
-      <c r="H20" s="44"/>
-      <c r="I20" s="48"/>
+      <c r="H20" s="43"/>
+      <c r="I20" s="44"/>
       <c r="J20" s="136"/>
-      <c r="K20" s="48"/>
-      <c r="L20" s="132"/>
-      <c r="M20" s="44"/>
-      <c r="N20" s="48"/>
-      <c r="O20" s="132"/>
-      <c r="P20" s="44"/>
-      <c r="Q20" s="48"/>
+      <c r="K20" s="44"/>
+      <c r="L20" s="138"/>
+      <c r="M20" s="43"/>
+      <c r="N20" s="44"/>
+      <c r="O20" s="138"/>
+      <c r="P20" s="43"/>
+      <c r="Q20" s="44"/>
       <c r="R20" s="32"/>
       <c r="S20" s="32"/>
       <c r="T20" s="33"/>
@@ -12331,23 +12340,23 @@
       <c r="Z20" s="34"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="127"/>
-      <c r="B21" s="48"/>
-      <c r="C21" s="128"/>
-      <c r="D21" s="48"/>
-      <c r="E21" s="128"/>
-      <c r="F21" s="48"/>
+      <c r="A21" s="143"/>
+      <c r="B21" s="44"/>
+      <c r="C21" s="144"/>
+      <c r="D21" s="44"/>
+      <c r="E21" s="144"/>
+      <c r="F21" s="44"/>
       <c r="G21" s="136"/>
-      <c r="H21" s="44"/>
-      <c r="I21" s="48"/>
+      <c r="H21" s="43"/>
+      <c r="I21" s="44"/>
       <c r="J21" s="136"/>
-      <c r="K21" s="48"/>
-      <c r="L21" s="132"/>
-      <c r="M21" s="44"/>
-      <c r="N21" s="48"/>
-      <c r="O21" s="132"/>
-      <c r="P21" s="44"/>
-      <c r="Q21" s="48"/>
+      <c r="K21" s="44"/>
+      <c r="L21" s="138"/>
+      <c r="M21" s="43"/>
+      <c r="N21" s="44"/>
+      <c r="O21" s="138"/>
+      <c r="P21" s="43"/>
+      <c r="Q21" s="44"/>
       <c r="R21" s="32"/>
       <c r="S21" s="32"/>
       <c r="T21" s="33"/>
@@ -12359,23 +12368,23 @@
       <c r="Z21" s="34"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="127"/>
-      <c r="B22" s="48"/>
-      <c r="C22" s="128"/>
-      <c r="D22" s="48"/>
-      <c r="E22" s="128"/>
-      <c r="F22" s="48"/>
+      <c r="A22" s="143"/>
+      <c r="B22" s="44"/>
+      <c r="C22" s="144"/>
+      <c r="D22" s="44"/>
+      <c r="E22" s="144"/>
+      <c r="F22" s="44"/>
       <c r="G22" s="136"/>
-      <c r="H22" s="44"/>
-      <c r="I22" s="48"/>
+      <c r="H22" s="43"/>
+      <c r="I22" s="44"/>
       <c r="J22" s="136"/>
-      <c r="K22" s="48"/>
-      <c r="L22" s="132"/>
-      <c r="M22" s="44"/>
-      <c r="N22" s="48"/>
-      <c r="O22" s="132"/>
-      <c r="P22" s="44"/>
-      <c r="Q22" s="48"/>
+      <c r="K22" s="44"/>
+      <c r="L22" s="138"/>
+      <c r="M22" s="43"/>
+      <c r="N22" s="44"/>
+      <c r="O22" s="138"/>
+      <c r="P22" s="43"/>
+      <c r="Q22" s="44"/>
       <c r="R22" s="32"/>
       <c r="S22" s="32"/>
       <c r="T22" s="33"/>
@@ -12387,23 +12396,23 @@
       <c r="Z22" s="34"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="127"/>
-      <c r="B23" s="48"/>
-      <c r="C23" s="128"/>
-      <c r="D23" s="48"/>
-      <c r="E23" s="128"/>
-      <c r="F23" s="48"/>
+      <c r="A23" s="143"/>
+      <c r="B23" s="44"/>
+      <c r="C23" s="144"/>
+      <c r="D23" s="44"/>
+      <c r="E23" s="144"/>
+      <c r="F23" s="44"/>
       <c r="G23" s="136"/>
-      <c r="H23" s="44"/>
-      <c r="I23" s="48"/>
+      <c r="H23" s="43"/>
+      <c r="I23" s="44"/>
       <c r="J23" s="136"/>
-      <c r="K23" s="48"/>
-      <c r="L23" s="132"/>
-      <c r="M23" s="44"/>
-      <c r="N23" s="48"/>
-      <c r="O23" s="132"/>
-      <c r="P23" s="44"/>
-      <c r="Q23" s="48"/>
+      <c r="K23" s="44"/>
+      <c r="L23" s="138"/>
+      <c r="M23" s="43"/>
+      <c r="N23" s="44"/>
+      <c r="O23" s="138"/>
+      <c r="P23" s="43"/>
+      <c r="Q23" s="44"/>
       <c r="R23" s="32"/>
       <c r="S23" s="32"/>
       <c r="T23" s="33"/>
@@ -12415,23 +12424,23 @@
       <c r="Z23" s="34"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="127"/>
-      <c r="B24" s="48"/>
-      <c r="C24" s="128"/>
-      <c r="D24" s="48"/>
-      <c r="E24" s="128"/>
-      <c r="F24" s="48"/>
+      <c r="A24" s="143"/>
+      <c r="B24" s="44"/>
+      <c r="C24" s="144"/>
+      <c r="D24" s="44"/>
+      <c r="E24" s="144"/>
+      <c r="F24" s="44"/>
       <c r="G24" s="136"/>
-      <c r="H24" s="44"/>
-      <c r="I24" s="48"/>
+      <c r="H24" s="43"/>
+      <c r="I24" s="44"/>
       <c r="J24" s="136"/>
-      <c r="K24" s="48"/>
-      <c r="L24" s="132"/>
-      <c r="M24" s="44"/>
-      <c r="N24" s="48"/>
-      <c r="O24" s="132"/>
-      <c r="P24" s="44"/>
-      <c r="Q24" s="48"/>
+      <c r="K24" s="44"/>
+      <c r="L24" s="138"/>
+      <c r="M24" s="43"/>
+      <c r="N24" s="44"/>
+      <c r="O24" s="138"/>
+      <c r="P24" s="43"/>
+      <c r="Q24" s="44"/>
       <c r="R24" s="32"/>
       <c r="S24" s="32"/>
       <c r="T24" s="33"/>
@@ -12443,23 +12452,23 @@
       <c r="Z24" s="34"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="127"/>
-      <c r="B25" s="48"/>
-      <c r="C25" s="128"/>
-      <c r="D25" s="48"/>
-      <c r="E25" s="128"/>
-      <c r="F25" s="48"/>
+      <c r="A25" s="143"/>
+      <c r="B25" s="44"/>
+      <c r="C25" s="144"/>
+      <c r="D25" s="44"/>
+      <c r="E25" s="144"/>
+      <c r="F25" s="44"/>
       <c r="G25" s="136"/>
-      <c r="H25" s="44"/>
-      <c r="I25" s="48"/>
+      <c r="H25" s="43"/>
+      <c r="I25" s="44"/>
       <c r="J25" s="136"/>
-      <c r="K25" s="48"/>
-      <c r="L25" s="132"/>
-      <c r="M25" s="44"/>
-      <c r="N25" s="48"/>
-      <c r="O25" s="132"/>
-      <c r="P25" s="44"/>
-      <c r="Q25" s="48"/>
+      <c r="K25" s="44"/>
+      <c r="L25" s="138"/>
+      <c r="M25" s="43"/>
+      <c r="N25" s="44"/>
+      <c r="O25" s="138"/>
+      <c r="P25" s="43"/>
+      <c r="Q25" s="44"/>
       <c r="R25" s="32"/>
       <c r="S25" s="32"/>
       <c r="T25" s="33"/>
@@ -12471,23 +12480,23 @@
       <c r="Z25" s="34"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="127"/>
-      <c r="B26" s="48"/>
-      <c r="C26" s="128"/>
-      <c r="D26" s="48"/>
-      <c r="E26" s="128"/>
-      <c r="F26" s="48"/>
+      <c r="A26" s="143"/>
+      <c r="B26" s="44"/>
+      <c r="C26" s="144"/>
+      <c r="D26" s="44"/>
+      <c r="E26" s="144"/>
+      <c r="F26" s="44"/>
       <c r="G26" s="136"/>
-      <c r="H26" s="44"/>
-      <c r="I26" s="48"/>
+      <c r="H26" s="43"/>
+      <c r="I26" s="44"/>
       <c r="J26" s="136"/>
-      <c r="K26" s="48"/>
-      <c r="L26" s="132"/>
-      <c r="M26" s="44"/>
-      <c r="N26" s="48"/>
-      <c r="O26" s="132"/>
-      <c r="P26" s="44"/>
-      <c r="Q26" s="48"/>
+      <c r="K26" s="44"/>
+      <c r="L26" s="138"/>
+      <c r="M26" s="43"/>
+      <c r="N26" s="44"/>
+      <c r="O26" s="138"/>
+      <c r="P26" s="43"/>
+      <c r="Q26" s="44"/>
       <c r="R26" s="32"/>
       <c r="S26" s="32"/>
       <c r="T26" s="33"/>
@@ -12499,23 +12508,23 @@
       <c r="Z26" s="34"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="127"/>
-      <c r="B27" s="48"/>
-      <c r="C27" s="128"/>
-      <c r="D27" s="48"/>
-      <c r="E27" s="128"/>
-      <c r="F27" s="48"/>
+      <c r="A27" s="143"/>
+      <c r="B27" s="44"/>
+      <c r="C27" s="144"/>
+      <c r="D27" s="44"/>
+      <c r="E27" s="144"/>
+      <c r="F27" s="44"/>
       <c r="G27" s="136"/>
-      <c r="H27" s="44"/>
-      <c r="I27" s="48"/>
+      <c r="H27" s="43"/>
+      <c r="I27" s="44"/>
       <c r="J27" s="136"/>
-      <c r="K27" s="48"/>
-      <c r="L27" s="132"/>
-      <c r="M27" s="44"/>
-      <c r="N27" s="48"/>
-      <c r="O27" s="132"/>
-      <c r="P27" s="44"/>
-      <c r="Q27" s="48"/>
+      <c r="K27" s="44"/>
+      <c r="L27" s="138"/>
+      <c r="M27" s="43"/>
+      <c r="N27" s="44"/>
+      <c r="O27" s="138"/>
+      <c r="P27" s="43"/>
+      <c r="Q27" s="44"/>
       <c r="R27" s="32"/>
       <c r="S27" s="32"/>
       <c r="T27" s="33"/>
@@ -12527,23 +12536,23 @@
       <c r="Z27" s="34"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="127"/>
-      <c r="B28" s="48"/>
-      <c r="C28" s="128"/>
-      <c r="D28" s="48"/>
-      <c r="E28" s="128"/>
-      <c r="F28" s="48"/>
+      <c r="A28" s="143"/>
+      <c r="B28" s="44"/>
+      <c r="C28" s="144"/>
+      <c r="D28" s="44"/>
+      <c r="E28" s="144"/>
+      <c r="F28" s="44"/>
       <c r="G28" s="136"/>
-      <c r="H28" s="44"/>
-      <c r="I28" s="48"/>
+      <c r="H28" s="43"/>
+      <c r="I28" s="44"/>
       <c r="J28" s="136"/>
-      <c r="K28" s="48"/>
-      <c r="L28" s="132"/>
-      <c r="M28" s="44"/>
-      <c r="N28" s="48"/>
-      <c r="O28" s="132"/>
-      <c r="P28" s="44"/>
-      <c r="Q28" s="48"/>
+      <c r="K28" s="44"/>
+      <c r="L28" s="138"/>
+      <c r="M28" s="43"/>
+      <c r="N28" s="44"/>
+      <c r="O28" s="138"/>
+      <c r="P28" s="43"/>
+      <c r="Q28" s="44"/>
       <c r="R28" s="32"/>
       <c r="S28" s="32"/>
       <c r="T28" s="33"/>
@@ -12555,23 +12564,23 @@
       <c r="Z28" s="34"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="127"/>
-      <c r="B29" s="48"/>
-      <c r="C29" s="128"/>
-      <c r="D29" s="48"/>
-      <c r="E29" s="128"/>
-      <c r="F29" s="48"/>
+      <c r="A29" s="143"/>
+      <c r="B29" s="44"/>
+      <c r="C29" s="144"/>
+      <c r="D29" s="44"/>
+      <c r="E29" s="144"/>
+      <c r="F29" s="44"/>
       <c r="G29" s="136"/>
-      <c r="H29" s="44"/>
-      <c r="I29" s="48"/>
+      <c r="H29" s="43"/>
+      <c r="I29" s="44"/>
       <c r="J29" s="136"/>
-      <c r="K29" s="48"/>
-      <c r="L29" s="132"/>
-      <c r="M29" s="44"/>
-      <c r="N29" s="48"/>
-      <c r="O29" s="132"/>
-      <c r="P29" s="44"/>
-      <c r="Q29" s="48"/>
+      <c r="K29" s="44"/>
+      <c r="L29" s="138"/>
+      <c r="M29" s="43"/>
+      <c r="N29" s="44"/>
+      <c r="O29" s="138"/>
+      <c r="P29" s="43"/>
+      <c r="Q29" s="44"/>
       <c r="R29" s="32"/>
       <c r="S29" s="32"/>
       <c r="T29" s="33"/>
@@ -12583,23 +12592,23 @@
       <c r="Z29" s="34"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="127"/>
-      <c r="B30" s="48"/>
-      <c r="C30" s="128"/>
-      <c r="D30" s="48"/>
-      <c r="E30" s="128"/>
-      <c r="F30" s="48"/>
+      <c r="A30" s="143"/>
+      <c r="B30" s="44"/>
+      <c r="C30" s="144"/>
+      <c r="D30" s="44"/>
+      <c r="E30" s="144"/>
+      <c r="F30" s="44"/>
       <c r="G30" s="136"/>
-      <c r="H30" s="44"/>
-      <c r="I30" s="48"/>
+      <c r="H30" s="43"/>
+      <c r="I30" s="44"/>
       <c r="J30" s="136"/>
-      <c r="K30" s="48"/>
-      <c r="L30" s="132"/>
-      <c r="M30" s="44"/>
-      <c r="N30" s="48"/>
-      <c r="O30" s="132"/>
-      <c r="P30" s="44"/>
-      <c r="Q30" s="48"/>
+      <c r="K30" s="44"/>
+      <c r="L30" s="138"/>
+      <c r="M30" s="43"/>
+      <c r="N30" s="44"/>
+      <c r="O30" s="138"/>
+      <c r="P30" s="43"/>
+      <c r="Q30" s="44"/>
       <c r="R30" s="32"/>
       <c r="S30" s="32"/>
       <c r="T30" s="33"/>
@@ -12611,23 +12620,23 @@
       <c r="Z30" s="34"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="129"/>
-      <c r="B31" s="130"/>
-      <c r="C31" s="131"/>
-      <c r="D31" s="130"/>
-      <c r="E31" s="131"/>
-      <c r="F31" s="130"/>
-      <c r="G31" s="140"/>
-      <c r="H31" s="134"/>
-      <c r="I31" s="130"/>
-      <c r="J31" s="140"/>
-      <c r="K31" s="130"/>
-      <c r="L31" s="133"/>
-      <c r="M31" s="134"/>
-      <c r="N31" s="130"/>
-      <c r="O31" s="133"/>
-      <c r="P31" s="134"/>
-      <c r="Q31" s="130"/>
+      <c r="A31" s="146"/>
+      <c r="B31" s="135"/>
+      <c r="C31" s="147"/>
+      <c r="D31" s="135"/>
+      <c r="E31" s="147"/>
+      <c r="F31" s="135"/>
+      <c r="G31" s="137"/>
+      <c r="H31" s="115"/>
+      <c r="I31" s="135"/>
+      <c r="J31" s="137"/>
+      <c r="K31" s="135"/>
+      <c r="L31" s="139"/>
+      <c r="M31" s="115"/>
+      <c r="N31" s="135"/>
+      <c r="O31" s="139"/>
+      <c r="P31" s="115"/>
+      <c r="Q31" s="135"/>
       <c r="R31" s="35"/>
       <c r="S31" s="35"/>
       <c r="T31" s="36"/>
@@ -13625,62 +13634,62 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="G5:T5"/>
     <mergeCell ref="A6:F6"/>
@@ -13705,62 +13714,62 @@
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
